--- a/Data/FlightPlan/FPL_23OCT26.xlsx
+++ b/Data/FlightPlan/FPL_23OCT26.xlsx
@@ -533,6 +533,9 @@
     <t>12:00</t>
   </si>
   <si>
+    <t>12:11</t>
+  </si>
+  <si>
     <t>13:55</t>
   </si>
   <si>
@@ -776,7 +779,7 @@
     <t>10:20</t>
   </si>
   <si>
-    <t>13:02</t>
+    <t>12:51</t>
   </si>
   <si>
     <t>17:40</t>
@@ -791,6 +794,9 @@
     <t>10:07</t>
   </si>
   <si>
+    <t>12:08</t>
+  </si>
+  <si>
     <t>NOZ</t>
   </si>
   <si>
@@ -812,132 +818,135 @@
     <t>16:50</t>
   </si>
   <si>
+    <t>VN-A629</t>
+  </si>
+  <si>
+    <t>13:24</t>
+  </si>
+  <si>
+    <t>VTE</t>
+  </si>
+  <si>
+    <t>18:25</t>
+  </si>
+  <si>
+    <t>19:10</t>
+  </si>
+  <si>
+    <t>MNL</t>
+  </si>
+  <si>
+    <t>22:25</t>
+  </si>
+  <si>
+    <t>02:10</t>
+  </si>
+  <si>
+    <t>03:00</t>
+  </si>
+  <si>
+    <t>04:35</t>
+  </si>
+  <si>
+    <t>VN-A630</t>
+  </si>
+  <si>
+    <t>07:00</t>
+  </si>
+  <si>
+    <t>10:03</t>
+  </si>
+  <si>
+    <t>VN-A632</t>
+  </si>
+  <si>
+    <t>07:40</t>
+  </si>
+  <si>
+    <t>07:48</t>
+  </si>
+  <si>
+    <t>10:32</t>
+  </si>
+  <si>
+    <t>BKK</t>
+  </si>
+  <si>
+    <t>18:15</t>
+  </si>
+  <si>
+    <t>20:15</t>
+  </si>
+  <si>
+    <t>20:45</t>
+  </si>
+  <si>
+    <t>VN-A633</t>
+  </si>
+  <si>
+    <t>13:04</t>
+  </si>
+  <si>
+    <t>VN-A634</t>
+  </si>
+  <si>
+    <t>HKT</t>
+  </si>
+  <si>
+    <t>10:55</t>
+  </si>
+  <si>
+    <t>11:16</t>
+  </si>
+  <si>
+    <t>19:40</t>
+  </si>
+  <si>
+    <t>VN-A636</t>
+  </si>
+  <si>
+    <t>07:15</t>
+  </si>
+  <si>
+    <t>09:55</t>
+  </si>
+  <si>
+    <t>09:34</t>
+  </si>
+  <si>
+    <t>16:10</t>
+  </si>
+  <si>
+    <t>20:10</t>
+  </si>
+  <si>
+    <t>VN-A637</t>
+  </si>
+  <si>
+    <t>05:00</t>
+  </si>
+  <si>
+    <t>06:50</t>
+  </si>
+  <si>
+    <t>06:48</t>
+  </si>
+  <si>
+    <t>07:20</t>
+  </si>
+  <si>
+    <t>09:15</t>
+  </si>
+  <si>
+    <t>13:40</t>
+  </si>
+  <si>
+    <t>20:00</t>
+  </si>
+  <si>
     <t>19:00</t>
   </si>
   <si>
-    <t>VN-A629</t>
-  </si>
-  <si>
-    <t>13:24</t>
-  </si>
-  <si>
-    <t>VTE</t>
-  </si>
-  <si>
-    <t>18:25</t>
-  </si>
-  <si>
-    <t>19:10</t>
-  </si>
-  <si>
-    <t>MNL</t>
-  </si>
-  <si>
-    <t>22:25</t>
-  </si>
-  <si>
-    <t>02:10</t>
-  </si>
-  <si>
-    <t>03:00</t>
-  </si>
-  <si>
-    <t>04:35</t>
-  </si>
-  <si>
-    <t>VN-A630</t>
-  </si>
-  <si>
-    <t>07:00</t>
-  </si>
-  <si>
-    <t>10:03</t>
-  </si>
-  <si>
-    <t>VN-A632</t>
-  </si>
-  <si>
-    <t>07:40</t>
-  </si>
-  <si>
-    <t>07:48</t>
-  </si>
-  <si>
-    <t>10:32</t>
-  </si>
-  <si>
-    <t>BKK</t>
-  </si>
-  <si>
-    <t>18:15</t>
-  </si>
-  <si>
-    <t>20:15</t>
-  </si>
-  <si>
-    <t>20:45</t>
-  </si>
-  <si>
-    <t>VN-A633</t>
-  </si>
-  <si>
-    <t>13:04</t>
-  </si>
-  <si>
-    <t>VN-A634</t>
-  </si>
-  <si>
-    <t>HKT</t>
-  </si>
-  <si>
-    <t>10:55</t>
-  </si>
-  <si>
-    <t>11:16</t>
-  </si>
-  <si>
-    <t>19:40</t>
-  </si>
-  <si>
-    <t>VN-A636</t>
-  </si>
-  <si>
-    <t>07:15</t>
-  </si>
-  <si>
-    <t>09:55</t>
-  </si>
-  <si>
-    <t>09:34</t>
-  </si>
-  <si>
-    <t>16:10</t>
-  </si>
-  <si>
-    <t>20:10</t>
-  </si>
-  <si>
-    <t>VN-A637</t>
-  </si>
-  <si>
-    <t>05:00</t>
-  </si>
-  <si>
-    <t>06:50</t>
-  </si>
-  <si>
-    <t>06:48</t>
-  </si>
-  <si>
-    <t>07:20</t>
-  </si>
-  <si>
-    <t>09:15</t>
-  </si>
-  <si>
-    <t>13:40</t>
-  </si>
-  <si>
     <t>VN-A639</t>
   </si>
   <si>
@@ -986,6 +995,9 @@
     <t>12:25</t>
   </si>
   <si>
+    <t>12:29</t>
+  </si>
+  <si>
     <t>VN-A645</t>
   </si>
   <si>
@@ -1067,6 +1079,9 @@
     <t>09:56</t>
   </si>
   <si>
+    <t>11:52</t>
+  </si>
+  <si>
     <t>21:15</t>
   </si>
   <si>
@@ -1331,7 +1346,7 @@
     <t>Total Record(s): 316</t>
   </si>
   <si>
-    <t xml:space="preserve">Generated on  Oct 23, 2026 10:48</t>
+    <t xml:space="preserve">Generated on  Oct 23, 2026 11:05</t>
   </si>
   <si>
     <t>Page 1 of 1</t>
@@ -4418,7 +4433,9 @@
       </c>
       <c r="K89" s="7"/>
       <c r="L89" s="7"/>
-      <c r="M89" s="7"/>
+      <c t="s" r="M89" s="7">
+        <v>174</v>
+      </c>
     </row>
     <row r="90" ht="15" customHeight="1">
       <c t="s" r="A90" s="6">
@@ -4447,7 +4464,7 @@
         <v>110</v>
       </c>
       <c t="s" r="J90" s="7">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="K90" s="7"/>
       <c r="L90" s="7"/>
@@ -4477,7 +4494,7 @@
         <v>98</v>
       </c>
       <c t="s" r="I91" s="7">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c t="s" r="J91" s="7">
         <v>132</v>
@@ -4510,10 +4527,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I92" s="7">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c t="s" r="J92" s="7">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="K92" s="7"/>
       <c r="L92" s="7"/>
@@ -4546,7 +4563,7 @@
         <v>106</v>
       </c>
       <c t="s" r="J93" s="7">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="K93" s="7"/>
       <c r="L93" s="7"/>
@@ -4579,7 +4596,7 @@
       </c>
       <c r="D95" s="7"/>
       <c t="s" r="E95" s="7">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="F95" s="7">
         <v>321</v>
@@ -4588,10 +4605,10 @@
         <v>17</v>
       </c>
       <c t="s" r="H95" s="8">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c t="s" r="I95" s="7">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c t="s" r="J95" s="7">
         <v>66</v>
@@ -4599,7 +4616,7 @@
       <c r="K95" s="7"/>
       <c r="L95" s="7"/>
       <c t="s" r="M95" s="7">
-        <v>182</v>
+        <v>183</v>
       </c>
     </row>
     <row r="96" ht="14.25" customHeight="1">
@@ -4614,19 +4631,19 @@
       </c>
       <c r="D96" s="7"/>
       <c t="s" r="E96" s="7">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="F96" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G96" s="8">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c t="s" r="H96" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I96" s="7">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c t="s" r="J96" s="7">
         <v>100</v>
@@ -4634,7 +4651,7 @@
       <c r="K96" s="7"/>
       <c r="L96" s="7"/>
       <c t="s" r="M96" s="7">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="97" ht="14.25" customHeight="1">
@@ -4649,7 +4666,7 @@
       </c>
       <c r="D97" s="7"/>
       <c t="s" r="E97" s="7">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="F97" s="7">
         <v>321</v>
@@ -4667,11 +4684,11 @@
         <v>141</v>
       </c>
       <c t="s" r="K97" s="7">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="L97" s="7"/>
       <c t="s" r="M97" s="7">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="98" ht="14.25" customHeight="1">
@@ -4686,7 +4703,7 @@
       </c>
       <c r="D98" s="7"/>
       <c t="s" r="E98" s="7">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="F98" s="7">
         <v>321</v>
@@ -4701,7 +4718,7 @@
         <v>54</v>
       </c>
       <c t="s" r="J98" s="7">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c t="s" r="K98" s="7">
         <v>102</v>
@@ -4723,7 +4740,7 @@
       </c>
       <c r="D99" s="7"/>
       <c t="s" r="E99" s="7">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="F99" s="7">
         <v>321</v>
@@ -4760,7 +4777,7 @@
       </c>
       <c r="D100" s="7"/>
       <c t="s" r="E100" s="7">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="F100" s="7">
         <v>321</v>
@@ -4772,7 +4789,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I100" s="7">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c t="s" r="J100" s="7">
         <v>106</v>
@@ -4782,7 +4799,7 @@
       </c>
       <c r="L100" s="7"/>
       <c t="s" r="M100" s="7">
-        <v>189</v>
+        <v>190</v>
       </c>
     </row>
     <row r="101" ht="14.25" customHeight="1">
@@ -4797,7 +4814,7 @@
       </c>
       <c r="D101" s="7"/>
       <c t="s" r="E101" s="7">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="F101" s="7">
         <v>321</v>
@@ -4812,14 +4829,14 @@
         <v>127</v>
       </c>
       <c t="s" r="J101" s="7">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c t="s" r="K101" s="7">
         <v>128</v>
       </c>
       <c r="L101" s="7"/>
       <c t="s" r="M101" s="7">
-        <v>191</v>
+        <v>192</v>
       </c>
     </row>
     <row r="102" ht="14.25" customHeight="1">
@@ -4834,7 +4851,7 @@
       </c>
       <c r="D102" s="7"/>
       <c t="s" r="E102" s="7">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="F102" s="7">
         <v>321</v>
@@ -4843,7 +4860,7 @@
         <v>43</v>
       </c>
       <c t="s" r="H102" s="8">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c t="s" r="I102" s="7">
         <v>83</v>
@@ -4882,7 +4899,7 @@
       </c>
       <c r="D104" s="7"/>
       <c t="s" r="E104" s="7">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F104" s="7">
         <v>321</v>
@@ -4894,14 +4911,16 @@
         <v>98</v>
       </c>
       <c t="s" r="I104" s="7">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c t="s" r="J104" s="7">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="K104" s="7"/>
       <c r="L104" s="7"/>
-      <c r="M104" s="7"/>
+      <c t="s" r="M104" s="7">
+        <v>196</v>
+      </c>
     </row>
     <row r="105" ht="15" customHeight="1">
       <c t="s" r="A105" s="6">
@@ -4915,7 +4934,7 @@
       </c>
       <c r="D105" s="7"/>
       <c t="s" r="E105" s="7">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F105" s="7">
         <v>321</v>
@@ -4927,7 +4946,7 @@
         <v>43</v>
       </c>
       <c t="s" r="I105" s="7">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c t="s" r="J105" s="7">
         <v>103</v>
@@ -4948,7 +4967,7 @@
       </c>
       <c r="D106" s="7"/>
       <c t="s" r="E106" s="7">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F106" s="7">
         <v>321</v>
@@ -4981,7 +5000,7 @@
       </c>
       <c r="D107" s="7"/>
       <c t="s" r="E107" s="7">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F107" s="7">
         <v>321</v>
@@ -5014,7 +5033,7 @@
       </c>
       <c r="D108" s="7"/>
       <c t="s" r="E108" s="7">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F108" s="7">
         <v>321</v>
@@ -5023,10 +5042,10 @@
         <v>17</v>
       </c>
       <c t="s" r="H108" s="8">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c t="s" r="I108" s="7">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c t="s" r="J108" s="7">
         <v>81</v>
@@ -5047,22 +5066,22 @@
       </c>
       <c r="D109" s="7"/>
       <c t="s" r="E109" s="7">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F109" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G109" s="8">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c t="s" r="H109" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I109" s="7">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c t="s" r="J109" s="7">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="K109" s="7"/>
       <c r="L109" s="7"/>
@@ -5080,7 +5099,7 @@
       </c>
       <c r="D110" s="7"/>
       <c t="s" r="E110" s="7">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F110" s="7">
         <v>321</v>
@@ -5095,10 +5114,10 @@
         <v>82</v>
       </c>
       <c t="s" r="J110" s="7">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c t="s" r="K110" s="7">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="L110" s="7"/>
       <c t="s" r="M110" s="7">
@@ -5132,7 +5151,7 @@
       </c>
       <c r="D112" s="7"/>
       <c t="s" r="E112" s="7">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="F112" s="7">
         <v>321</v>
@@ -5147,12 +5166,12 @@
         <v>159</v>
       </c>
       <c t="s" r="J112" s="7">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="K112" s="7"/>
       <c r="L112" s="7"/>
       <c t="s" r="M112" s="7">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
     <row r="113" ht="14.25" customHeight="1">
@@ -5167,7 +5186,7 @@
       </c>
       <c r="D113" s="7"/>
       <c t="s" r="E113" s="7">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="F113" s="7">
         <v>321</v>
@@ -5179,10 +5198,10 @@
         <v>43</v>
       </c>
       <c t="s" r="I113" s="7">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c t="s" r="J113" s="7">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="K113" s="7"/>
       <c r="L113" s="7"/>
@@ -5200,7 +5219,7 @@
       </c>
       <c r="D114" s="7"/>
       <c t="s" r="E114" s="7">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="F114" s="7">
         <v>321</v>
@@ -5212,10 +5231,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I114" s="7">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c t="s" r="J114" s="7">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="K114" s="7"/>
       <c r="L114" s="7"/>
@@ -5233,7 +5252,7 @@
       </c>
       <c r="D115" s="7"/>
       <c t="s" r="E115" s="7">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="F115" s="7">
         <v>321</v>
@@ -5245,10 +5264,10 @@
         <v>134</v>
       </c>
       <c t="s" r="I115" s="7">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c t="s" r="J115" s="7">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="K115" s="7"/>
       <c r="L115" s="7"/>
@@ -5266,7 +5285,7 @@
       </c>
       <c r="D116" s="7"/>
       <c t="s" r="E116" s="7">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="F116" s="7">
         <v>321</v>
@@ -5278,10 +5297,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I116" s="7">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c t="s" r="J116" s="7">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="K116" s="7"/>
       <c r="L116" s="7"/>
@@ -5299,7 +5318,7 @@
       </c>
       <c r="D117" s="7"/>
       <c t="s" r="E117" s="7">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="F117" s="7">
         <v>321</v>
@@ -5311,10 +5330,10 @@
         <v>98</v>
       </c>
       <c t="s" r="I117" s="7">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c t="s" r="J117" s="7">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="K117" s="7"/>
       <c r="L117" s="7"/>
@@ -5332,7 +5351,7 @@
       </c>
       <c r="D118" s="7"/>
       <c t="s" r="E118" s="7">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="F118" s="7">
         <v>321</v>
@@ -5344,10 +5363,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I118" s="7">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c t="s" r="J118" s="7">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="K118" s="7"/>
       <c r="L118" s="7"/>
@@ -5380,7 +5399,7 @@
       </c>
       <c r="D120" s="7"/>
       <c t="s" r="E120" s="7">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="F120" s="7">
         <v>321</v>
@@ -5389,18 +5408,18 @@
         <v>17</v>
       </c>
       <c t="s" r="H120" s="8">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c t="s" r="I120" s="7">
         <v>44</v>
       </c>
       <c t="s" r="J120" s="7">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="K120" s="7"/>
       <c r="L120" s="7"/>
       <c t="s" r="M120" s="7">
-        <v>221</v>
+        <v>222</v>
       </c>
     </row>
     <row r="121" ht="14.25" customHeight="1">
@@ -5415,13 +5434,13 @@
       </c>
       <c r="D121" s="7"/>
       <c t="s" r="E121" s="7">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="F121" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G121" s="8">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c t="s" r="H121" s="8">
         <v>17</v>
@@ -5430,7 +5449,7 @@
         <v>35</v>
       </c>
       <c t="s" r="J121" s="7">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="K121" s="7"/>
       <c r="L121" s="7"/>
@@ -5448,7 +5467,7 @@
       </c>
       <c r="D122" s="7"/>
       <c t="s" r="E122" s="7">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="F122" s="7">
         <v>321</v>
@@ -5457,7 +5476,7 @@
         <v>17</v>
       </c>
       <c t="s" r="H122" s="8">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c t="s" r="I122" s="7">
         <v>153</v>
@@ -5481,13 +5500,13 @@
       </c>
       <c r="D123" s="7"/>
       <c t="s" r="E123" s="7">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="F123" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G123" s="8">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c t="s" r="H123" s="8">
         <v>17</v>
@@ -5496,7 +5515,7 @@
         <v>48</v>
       </c>
       <c t="s" r="J123" s="7">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="K123" s="7"/>
       <c r="L123" s="7"/>
@@ -5529,19 +5548,19 @@
       </c>
       <c r="D125" s="7"/>
       <c t="s" r="E125" s="7">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="F125" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G125" s="8">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c t="s" r="H125" s="8">
         <v>43</v>
       </c>
       <c t="s" r="I125" s="7">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c t="s" r="J125" s="7">
         <v>86</v>
@@ -5549,7 +5568,7 @@
       <c r="K125" s="7"/>
       <c r="L125" s="7"/>
       <c t="s" r="M125" s="7">
-        <v>227</v>
+        <v>228</v>
       </c>
     </row>
     <row r="126" ht="14.25" customHeight="1">
@@ -5564,7 +5583,7 @@
       </c>
       <c r="D126" s="7"/>
       <c t="s" r="E126" s="7">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="F126" s="7">
         <v>321</v>
@@ -5584,7 +5603,7 @@
       <c r="K126" s="7"/>
       <c r="L126" s="7"/>
       <c t="s" r="M126" s="7">
-        <v>228</v>
+        <v>229</v>
       </c>
     </row>
     <row r="127" ht="14.25" customHeight="1">
@@ -5599,7 +5618,7 @@
       </c>
       <c r="D127" s="7"/>
       <c t="s" r="E127" s="7">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="F127" s="7">
         <v>321</v>
@@ -5632,7 +5651,7 @@
       </c>
       <c r="D128" s="7"/>
       <c t="s" r="E128" s="7">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="F128" s="7">
         <v>321</v>
@@ -5641,10 +5660,10 @@
         <v>17</v>
       </c>
       <c t="s" r="H128" s="8">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c t="s" r="I128" s="7">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c t="s" r="J128" s="7">
         <v>132</v>
@@ -5665,13 +5684,13 @@
       </c>
       <c r="D129" s="7"/>
       <c t="s" r="E129" s="7">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="F129" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G129" s="8">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c t="s" r="H129" s="8">
         <v>17</v>
@@ -5698,7 +5717,7 @@
       </c>
       <c r="D130" s="7"/>
       <c t="s" r="E130" s="7">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="F130" s="7">
         <v>321</v>
@@ -5713,7 +5732,7 @@
         <v>80</v>
       </c>
       <c t="s" r="J130" s="7">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="K130" s="7"/>
       <c r="L130" s="7"/>
@@ -5731,7 +5750,7 @@
       </c>
       <c r="D131" s="7"/>
       <c t="s" r="E131" s="7">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="F131" s="7">
         <v>321</v>
@@ -5743,10 +5762,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I131" s="7">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c t="s" r="J131" s="7">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="K131" s="7"/>
       <c r="L131" s="7"/>
@@ -5779,7 +5798,7 @@
       </c>
       <c r="D133" s="7"/>
       <c t="s" r="E133" s="7">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="F133" s="7">
         <v>321</v>
@@ -5788,10 +5807,10 @@
         <v>17</v>
       </c>
       <c t="s" r="H133" s="8">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c t="s" r="I133" s="7">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c t="s" r="J133" s="7">
         <v>95</v>
@@ -5799,7 +5818,7 @@
       <c r="K133" s="7"/>
       <c r="L133" s="7"/>
       <c t="s" r="M133" s="7">
-        <v>235</v>
+        <v>236</v>
       </c>
     </row>
     <row r="134" ht="14.25" customHeight="1">
@@ -5814,19 +5833,19 @@
       </c>
       <c r="D134" s="7"/>
       <c t="s" r="E134" s="7">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="F134" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G134" s="8">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c t="s" r="H134" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I134" s="7">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c t="s" r="J134" s="7">
         <v>44</v>
@@ -5834,7 +5853,7 @@
       <c r="K134" s="7"/>
       <c r="L134" s="7"/>
       <c t="s" r="M134" s="7">
-        <v>182</v>
+        <v>183</v>
       </c>
     </row>
     <row r="135" ht="15" customHeight="1">
@@ -5849,7 +5868,7 @@
       </c>
       <c r="D135" s="7"/>
       <c t="s" r="E135" s="7">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="F135" s="7">
         <v>321</v>
@@ -5861,15 +5880,15 @@
         <v>77</v>
       </c>
       <c t="s" r="I135" s="7">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c t="s" r="J135" s="7">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="K135" s="7"/>
       <c r="L135" s="7"/>
       <c t="s" r="M135" s="7">
-        <v>237</v>
+        <v>238</v>
       </c>
     </row>
     <row r="136" ht="14.25" customHeight="1">
@@ -5884,7 +5903,7 @@
       </c>
       <c r="D136" s="7"/>
       <c t="s" r="E136" s="7">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="F136" s="7">
         <v>321</v>
@@ -5896,7 +5915,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I136" s="7">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c t="s" r="J136" s="7">
         <v>37</v>
@@ -5917,7 +5936,7 @@
       </c>
       <c r="D137" s="7"/>
       <c t="s" r="E137" s="7">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="F137" s="7">
         <v>321</v>
@@ -5926,13 +5945,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H137" s="8">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c t="s" r="I137" s="7">
         <v>125</v>
       </c>
       <c t="s" r="J137" s="7">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="K137" s="7"/>
       <c r="L137" s="7"/>
@@ -5950,13 +5969,13 @@
       </c>
       <c r="D138" s="7"/>
       <c t="s" r="E138" s="7">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="F138" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G138" s="8">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c t="s" r="H138" s="8">
         <v>17</v>
@@ -5965,7 +5984,7 @@
         <v>105</v>
       </c>
       <c t="s" r="J138" s="7">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="K138" s="7"/>
       <c r="L138" s="7"/>
@@ -5994,31 +6013,31 @@
         <v>7615</v>
       </c>
       <c t="s" r="C140" s="7">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="D140" s="7"/>
       <c t="s" r="E140" s="7">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="F140" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G140" s="8">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c t="s" r="H140" s="8">
         <v>43</v>
       </c>
       <c t="s" r="I140" s="7">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c t="s" r="J140" s="7">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="K140" s="7"/>
       <c r="L140" s="7"/>
       <c t="s" r="M140" s="7">
-        <v>244</v>
+        <v>245</v>
       </c>
     </row>
     <row r="141" ht="14.25" customHeight="1">
@@ -6029,11 +6048,11 @@
         <v>7615</v>
       </c>
       <c t="s" r="C141" s="7">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="D141" s="7"/>
       <c t="s" r="E141" s="7">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="F141" s="7">
         <v>321</v>
@@ -6045,10 +6064,10 @@
         <v>124</v>
       </c>
       <c t="s" r="I141" s="7">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c t="s" r="J141" s="7">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="K141" s="7"/>
       <c r="L141" s="7"/>
@@ -6062,11 +6081,11 @@
         <v>7706</v>
       </c>
       <c t="s" r="C142" s="7">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="D142" s="7"/>
       <c t="s" r="E142" s="7">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="F142" s="7">
         <v>321</v>
@@ -6078,7 +6097,7 @@
         <v>43</v>
       </c>
       <c t="s" r="I142" s="7">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c t="s" r="J142" s="7">
         <v>165</v>
@@ -6095,11 +6114,11 @@
         <v>7706</v>
       </c>
       <c t="s" r="C143" s="7">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="D143" s="7"/>
       <c t="s" r="E143" s="7">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="F143" s="7">
         <v>321</v>
@@ -6108,13 +6127,13 @@
         <v>43</v>
       </c>
       <c t="s" r="H143" s="8">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c t="s" r="I143" s="7">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c t="s" r="J143" s="7">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="K143" s="7"/>
       <c r="L143" s="7"/>
@@ -6140,14 +6159,14 @@
         <v>13</v>
       </c>
       <c t="s" r="B145" s="7">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c t="s" r="C145" s="7">
         <v>14</v>
       </c>
       <c r="D145" s="7"/>
       <c t="s" r="E145" s="7">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="F145" s="7">
         <v>321</v>
@@ -6162,12 +6181,12 @@
         <v>31</v>
       </c>
       <c t="s" r="J145" s="7">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="K145" s="7"/>
       <c r="L145" s="7"/>
       <c t="s" r="M145" s="7">
-        <v>253</v>
+        <v>254</v>
       </c>
     </row>
     <row r="146" ht="14.25" customHeight="1">
@@ -6182,7 +6201,7 @@
       </c>
       <c r="D146" s="7"/>
       <c t="s" r="E146" s="7">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="F146" s="7">
         <v>321</v>
@@ -6194,7 +6213,7 @@
         <v>118</v>
       </c>
       <c t="s" r="I146" s="7">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c t="s" r="J146" s="7">
         <v>110</v>
@@ -6202,7 +6221,7 @@
       <c r="K146" s="7"/>
       <c r="L146" s="7"/>
       <c t="s" r="M146" s="7">
-        <v>255</v>
+        <v>256</v>
       </c>
     </row>
     <row r="147" ht="14.25" customHeight="1">
@@ -6217,7 +6236,7 @@
       </c>
       <c r="D147" s="7"/>
       <c t="s" r="E147" s="7">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="F147" s="7">
         <v>321</v>
@@ -6232,7 +6251,7 @@
         <v>54</v>
       </c>
       <c t="s" r="J147" s="7">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="K147" s="7"/>
       <c r="L147" s="7"/>
@@ -6250,7 +6269,7 @@
       </c>
       <c r="D148" s="7"/>
       <c t="s" r="E148" s="7">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="F148" s="7">
         <v>321</v>
@@ -6265,7 +6284,7 @@
         <v>22</v>
       </c>
       <c t="s" r="J148" s="7">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="K148" s="7"/>
       <c r="L148" s="7"/>
@@ -6283,7 +6302,7 @@
       </c>
       <c r="D149" s="7"/>
       <c t="s" r="E149" s="7">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="F149" s="7">
         <v>321</v>
@@ -6295,10 +6314,10 @@
         <v>43</v>
       </c>
       <c t="s" r="I149" s="7">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c t="s" r="J149" s="7">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="K149" s="7"/>
       <c r="L149" s="7"/>
@@ -6331,7 +6350,7 @@
       </c>
       <c r="D151" s="7"/>
       <c t="s" r="E151" s="7">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="F151" s="7">
         <v>321</v>
@@ -6346,12 +6365,12 @@
         <v>148</v>
       </c>
       <c t="s" r="J151" s="7">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="K151" s="7"/>
       <c r="L151" s="7"/>
       <c t="s" r="M151" s="7">
-        <v>259</v>
+        <v>260</v>
       </c>
     </row>
     <row r="152" ht="14.25" customHeight="1">
@@ -6366,7 +6385,7 @@
       </c>
       <c r="D152" s="7"/>
       <c t="s" r="E152" s="7">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="F152" s="7">
         <v>321</v>
@@ -6381,11 +6400,13 @@
         <v>74</v>
       </c>
       <c t="s" r="J152" s="7">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="K152" s="7"/>
       <c r="L152" s="7"/>
-      <c r="M152" s="7"/>
+      <c t="s" r="M152" s="7">
+        <v>261</v>
+      </c>
     </row>
     <row r="153" ht="14.25" customHeight="1">
       <c t="s" r="A153" s="6">
@@ -6399,7 +6420,7 @@
       </c>
       <c r="D153" s="7"/>
       <c t="s" r="E153" s="7">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="F153" s="7">
         <v>321</v>
@@ -6428,11 +6449,11 @@
         <v>5068</v>
       </c>
       <c t="s" r="C154" s="7">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="D154" s="7"/>
       <c t="s" r="E154" s="7">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="F154" s="7">
         <v>321</v>
@@ -6461,11 +6482,11 @@
         <v>5068</v>
       </c>
       <c t="s" r="C155" s="7">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="D155" s="7"/>
       <c t="s" r="E155" s="7">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="F155" s="7">
         <v>321</v>
@@ -6474,13 +6495,13 @@
         <v>43</v>
       </c>
       <c t="s" r="H155" s="8">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c t="s" r="I155" s="7">
         <v>70</v>
       </c>
       <c t="s" r="J155" s="7">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="K155" s="7"/>
       <c r="L155" s="7"/>
@@ -6494,17 +6515,17 @@
         <v>5069</v>
       </c>
       <c t="s" r="C156" s="7">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="D156" s="7"/>
       <c t="s" r="E156" s="7">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="F156" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G156" s="8">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c t="s" r="H156" s="8">
         <v>43</v>
@@ -6513,7 +6534,7 @@
         <v>30</v>
       </c>
       <c t="s" r="J156" s="7">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="K156" s="7"/>
       <c r="L156" s="7"/>
@@ -6546,7 +6567,7 @@
       </c>
       <c r="D158" s="7"/>
       <c t="s" r="E158" s="7">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="F158" s="7">
         <v>321</v>
@@ -6561,12 +6582,12 @@
         <v>84</v>
       </c>
       <c t="s" r="J158" s="7">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="K158" s="7"/>
       <c r="L158" s="7"/>
       <c t="s" r="M158" s="7">
-        <v>265</v>
+        <v>267</v>
       </c>
     </row>
     <row r="159" ht="14.25" customHeight="1">
@@ -6581,7 +6602,7 @@
       </c>
       <c r="D159" s="7"/>
       <c t="s" r="E159" s="7">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="F159" s="7">
         <v>321</v>
@@ -6596,7 +6617,7 @@
         <v>103</v>
       </c>
       <c t="s" r="J159" s="7">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="K159" s="7"/>
       <c r="L159" s="7"/>
@@ -6607,14 +6628,14 @@
         <v>13</v>
       </c>
       <c r="B160" s="7">
-        <v>384</v>
+        <v>822</v>
       </c>
       <c t="s" r="C160" s="7">
         <v>14</v>
       </c>
       <c r="D160" s="7"/>
       <c t="s" r="E160" s="7">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="F160" s="7">
         <v>321</v>
@@ -6623,47 +6644,29 @@
         <v>17</v>
       </c>
       <c t="s" r="H160" s="8">
-        <v>180</v>
+        <v>42</v>
       </c>
       <c t="s" r="I160" s="7">
-        <v>144</v>
+        <v>115</v>
       </c>
       <c t="s" r="J160" s="7">
-        <v>177</v>
+        <v>84</v>
       </c>
       <c r="K160" s="7"/>
       <c r="L160" s="7"/>
       <c r="M160" s="7"/>
     </row>
     <row r="161" ht="14.25" customHeight="1">
-      <c t="s" r="A161" s="6">
-        <v>13</v>
-      </c>
-      <c r="B161" s="7">
-        <v>385</v>
-      </c>
-      <c t="s" r="C161" s="7">
-        <v>14</v>
-      </c>
+      <c r="A161" s="6"/>
+      <c r="B161" s="7"/>
+      <c r="C161" s="7"/>
       <c r="D161" s="7"/>
-      <c t="s" r="E161" s="7">
-        <v>263</v>
-      </c>
-      <c r="F161" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G161" s="8">
-        <v>180</v>
-      </c>
-      <c t="s" r="H161" s="8">
-        <v>17</v>
-      </c>
-      <c t="s" r="I161" s="7">
-        <v>267</v>
-      </c>
-      <c t="s" r="J161" s="7">
-        <v>48</v>
-      </c>
+      <c r="E161" s="7"/>
+      <c r="F161" s="7"/>
+      <c r="G161" s="8"/>
+      <c r="H161" s="8"/>
+      <c r="I161" s="7"/>
+      <c r="J161" s="7"/>
       <c r="K161" s="7"/>
       <c r="L161" s="7"/>
       <c r="M161" s="7"/>
@@ -6673,14 +6676,14 @@
         <v>13</v>
       </c>
       <c r="B162" s="7">
-        <v>822</v>
+        <v>1813</v>
       </c>
       <c t="s" r="C162" s="7">
         <v>14</v>
       </c>
       <c r="D162" s="7"/>
       <c t="s" r="E162" s="7">
-        <v>263</v>
+        <v>269</v>
       </c>
       <c r="F162" s="7">
         <v>321</v>
@@ -6689,29 +6692,49 @@
         <v>17</v>
       </c>
       <c t="s" r="H162" s="8">
-        <v>42</v>
+        <v>220</v>
       </c>
       <c t="s" r="I162" s="7">
-        <v>115</v>
+        <v>159</v>
       </c>
       <c t="s" r="J162" s="7">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="K162" s="7"/>
       <c r="L162" s="7"/>
-      <c r="M162" s="7"/>
+      <c t="s" r="M162" s="7">
+        <v>270</v>
+      </c>
     </row>
     <row r="163" ht="14.25" customHeight="1">
-      <c r="A163" s="6"/>
-      <c r="B163" s="7"/>
-      <c r="C163" s="7"/>
+      <c t="s" r="A163" s="6">
+        <v>13</v>
+      </c>
+      <c r="B163" s="7">
+        <v>1814</v>
+      </c>
+      <c t="s" r="C163" s="7">
+        <v>14</v>
+      </c>
       <c r="D163" s="7"/>
-      <c r="E163" s="7"/>
-      <c r="F163" s="7"/>
-      <c r="G163" s="8"/>
-      <c r="H163" s="8"/>
-      <c r="I163" s="7"/>
-      <c r="J163" s="7"/>
+      <c t="s" r="E163" s="7">
+        <v>269</v>
+      </c>
+      <c r="F163" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G163" s="8">
+        <v>220</v>
+      </c>
+      <c t="s" r="H163" s="8">
+        <v>17</v>
+      </c>
+      <c t="s" r="I163" s="7">
+        <v>142</v>
+      </c>
+      <c t="s" r="J163" s="7">
+        <v>78</v>
+      </c>
       <c r="K163" s="7"/>
       <c r="L163" s="7"/>
       <c r="M163" s="7"/>
@@ -6721,14 +6744,14 @@
         <v>13</v>
       </c>
       <c r="B164" s="7">
-        <v>1813</v>
+        <v>1831</v>
       </c>
       <c t="s" r="C164" s="7">
         <v>14</v>
       </c>
       <c r="D164" s="7"/>
       <c t="s" r="E164" s="7">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="F164" s="7">
         <v>321</v>
@@ -6737,48 +6760,46 @@
         <v>17</v>
       </c>
       <c t="s" r="H164" s="8">
-        <v>219</v>
+        <v>271</v>
       </c>
       <c t="s" r="I164" s="7">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c t="s" r="J164" s="7">
-        <v>90</v>
+        <v>272</v>
       </c>
       <c r="K164" s="7"/>
       <c r="L164" s="7"/>
-      <c t="s" r="M164" s="7">
-        <v>269</v>
-      </c>
+      <c r="M164" s="7"/>
     </row>
     <row r="165" ht="15" customHeight="1">
       <c t="s" r="A165" s="6">
         <v>13</v>
       </c>
       <c r="B165" s="7">
-        <v>1814</v>
+        <v>1832</v>
       </c>
       <c t="s" r="C165" s="7">
         <v>14</v>
       </c>
       <c r="D165" s="7"/>
       <c t="s" r="E165" s="7">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="F165" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G165" s="8">
-        <v>219</v>
+        <v>271</v>
       </c>
       <c t="s" r="H165" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I165" s="7">
-        <v>142</v>
+        <v>273</v>
       </c>
       <c t="s" r="J165" s="7">
-        <v>78</v>
+        <v>215</v>
       </c>
       <c r="K165" s="7"/>
       <c r="L165" s="7"/>
@@ -6789,14 +6810,14 @@
         <v>13</v>
       </c>
       <c r="B166" s="7">
-        <v>1831</v>
+        <v>858</v>
       </c>
       <c t="s" r="C166" s="7">
         <v>14</v>
       </c>
       <c r="D166" s="7"/>
       <c t="s" r="E166" s="7">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="F166" s="7">
         <v>321</v>
@@ -6805,13 +6826,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H166" s="8">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c t="s" r="I166" s="7">
-        <v>160</v>
+        <v>275</v>
       </c>
       <c t="s" r="J166" s="7">
-        <v>271</v>
+        <v>276</v>
       </c>
       <c r="K166" s="7"/>
       <c r="L166" s="7"/>
@@ -6819,102 +6840,86 @@
     </row>
     <row r="167" ht="14.25" customHeight="1">
       <c t="s" r="A167" s="6">
-        <v>13</v>
+        <v>29</v>
       </c>
       <c r="B167" s="7">
-        <v>1832</v>
+        <v>859</v>
       </c>
       <c t="s" r="C167" s="7">
         <v>14</v>
       </c>
       <c r="D167" s="7"/>
       <c t="s" r="E167" s="7">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="F167" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G167" s="8">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c t="s" r="H167" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I167" s="7">
-        <v>272</v>
+        <v>277</v>
       </c>
       <c t="s" r="J167" s="7">
-        <v>214</v>
+        <v>278</v>
       </c>
       <c r="K167" s="7"/>
       <c r="L167" s="7"/>
       <c r="M167" s="7"/>
     </row>
     <row r="168" ht="14.25" customHeight="1">
-      <c t="s" r="A168" s="6">
-        <v>13</v>
-      </c>
-      <c r="B168" s="7">
-        <v>858</v>
-      </c>
-      <c t="s" r="C168" s="7">
-        <v>14</v>
-      </c>
+      <c r="A168" s="6"/>
+      <c r="B168" s="7"/>
+      <c r="C168" s="7"/>
       <c r="D168" s="7"/>
-      <c t="s" r="E168" s="7">
-        <v>268</v>
-      </c>
-      <c r="F168" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G168" s="8">
-        <v>17</v>
-      </c>
-      <c t="s" r="H168" s="8">
-        <v>273</v>
-      </c>
-      <c t="s" r="I168" s="7">
-        <v>274</v>
-      </c>
-      <c t="s" r="J168" s="7">
-        <v>275</v>
-      </c>
+      <c r="E168" s="7"/>
+      <c r="F168" s="7"/>
+      <c r="G168" s="8"/>
+      <c r="H168" s="8"/>
+      <c r="I168" s="7"/>
+      <c r="J168" s="7"/>
       <c r="K168" s="7"/>
       <c r="L168" s="7"/>
       <c r="M168" s="7"/>
     </row>
     <row r="169" ht="14.25" customHeight="1">
       <c t="s" r="A169" s="6">
-        <v>29</v>
+        <v>13</v>
       </c>
       <c r="B169" s="7">
-        <v>859</v>
+        <v>125</v>
       </c>
       <c t="s" r="C169" s="7">
         <v>14</v>
       </c>
       <c r="D169" s="7"/>
       <c t="s" r="E169" s="7">
-        <v>268</v>
+        <v>279</v>
       </c>
       <c r="F169" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G169" s="8">
-        <v>273</v>
+        <v>43</v>
       </c>
       <c t="s" r="H169" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I169" s="7">
-        <v>276</v>
+        <v>280</v>
       </c>
       <c t="s" r="J169" s="7">
-        <v>277</v>
+        <v>148</v>
       </c>
       <c r="K169" s="7"/>
       <c r="L169" s="7"/>
-      <c r="M169" s="7"/>
+      <c t="s" r="M169" s="7">
+        <v>281</v>
+      </c>
     </row>
     <row r="170" ht="15" customHeight="1">
       <c r="A170" s="6"/>
@@ -6936,14 +6941,14 @@
         <v>13</v>
       </c>
       <c r="B171" s="7">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c t="s" r="C171" s="7">
         <v>14</v>
       </c>
       <c r="D171" s="7"/>
       <c t="s" r="E171" s="7">
-        <v>278</v>
+        <v>282</v>
       </c>
       <c r="F171" s="7">
         <v>321</v>
@@ -6955,80 +6960,98 @@
         <v>17</v>
       </c>
       <c t="s" r="I171" s="7">
-        <v>279</v>
+        <v>167</v>
       </c>
       <c t="s" r="J171" s="7">
-        <v>148</v>
+        <v>283</v>
       </c>
       <c r="K171" s="7"/>
       <c r="L171" s="7"/>
       <c t="s" r="M171" s="7">
-        <v>280</v>
+        <v>284</v>
       </c>
     </row>
     <row r="172" ht="14.25" customHeight="1">
-      <c r="A172" s="6"/>
-      <c r="B172" s="7"/>
-      <c r="C172" s="7"/>
+      <c t="s" r="A172" s="6">
+        <v>13</v>
+      </c>
+      <c r="B172" s="7">
+        <v>630</v>
+      </c>
+      <c t="s" r="C172" s="7">
+        <v>14</v>
+      </c>
       <c r="D172" s="7"/>
-      <c r="E172" s="7"/>
-      <c r="F172" s="7"/>
-      <c r="G172" s="8"/>
-      <c r="H172" s="8"/>
-      <c r="I172" s="7"/>
-      <c r="J172" s="7"/>
+      <c t="s" r="E172" s="7">
+        <v>282</v>
+      </c>
+      <c r="F172" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G172" s="8">
+        <v>17</v>
+      </c>
+      <c t="s" r="H172" s="8">
+        <v>98</v>
+      </c>
+      <c t="s" r="I172" s="7">
+        <v>86</v>
+      </c>
+      <c t="s" r="J172" s="7">
+        <v>255</v>
+      </c>
       <c r="K172" s="7"/>
       <c r="L172" s="7"/>
-      <c r="M172" s="7"/>
+      <c t="s" r="M172" s="7">
+        <v>285</v>
+      </c>
     </row>
     <row r="173" ht="14.25" customHeight="1">
       <c t="s" r="A173" s="6">
         <v>13</v>
       </c>
       <c r="B173" s="7">
-        <v>123</v>
+        <v>629</v>
       </c>
       <c t="s" r="C173" s="7">
         <v>14</v>
       </c>
       <c r="D173" s="7"/>
       <c t="s" r="E173" s="7">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="F173" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G173" s="8">
-        <v>43</v>
+        <v>98</v>
       </c>
       <c t="s" r="H173" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I173" s="7">
-        <v>167</v>
+        <v>74</v>
       </c>
       <c t="s" r="J173" s="7">
-        <v>282</v>
+        <v>205</v>
       </c>
       <c r="K173" s="7"/>
       <c r="L173" s="7"/>
-      <c t="s" r="M173" s="7">
-        <v>283</v>
-      </c>
+      <c r="M173" s="7"/>
     </row>
     <row r="174" ht="14.25" customHeight="1">
       <c t="s" r="A174" s="6">
         <v>13</v>
       </c>
       <c r="B174" s="7">
-        <v>630</v>
+        <v>807</v>
       </c>
       <c t="s" r="C174" s="7">
         <v>14</v>
       </c>
       <c r="D174" s="7"/>
       <c t="s" r="E174" s="7">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="F174" s="7">
         <v>321</v>
@@ -7037,48 +7060,46 @@
         <v>17</v>
       </c>
       <c t="s" r="H174" s="8">
-        <v>98</v>
+        <v>286</v>
       </c>
       <c t="s" r="I174" s="7">
-        <v>86</v>
+        <v>151</v>
       </c>
       <c t="s" r="J174" s="7">
-        <v>254</v>
+        <v>69</v>
       </c>
       <c r="K174" s="7"/>
       <c r="L174" s="7"/>
-      <c t="s" r="M174" s="7">
-        <v>284</v>
-      </c>
+      <c r="M174" s="7"/>
     </row>
     <row r="175" ht="15" customHeight="1">
       <c t="s" r="A175" s="6">
         <v>13</v>
       </c>
       <c r="B175" s="7">
-        <v>629</v>
+        <v>800</v>
       </c>
       <c t="s" r="C175" s="7">
         <v>14</v>
       </c>
       <c r="D175" s="7"/>
       <c t="s" r="E175" s="7">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="F175" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G175" s="8">
-        <v>98</v>
+        <v>286</v>
       </c>
       <c t="s" r="H175" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I175" s="7">
-        <v>74</v>
+        <v>123</v>
       </c>
       <c t="s" r="J175" s="7">
-        <v>204</v>
+        <v>79</v>
       </c>
       <c r="K175" s="7"/>
       <c r="L175" s="7"/>
@@ -7089,14 +7110,14 @@
         <v>13</v>
       </c>
       <c r="B176" s="7">
-        <v>807</v>
+        <v>282</v>
       </c>
       <c t="s" r="C176" s="7">
         <v>14</v>
       </c>
       <c r="D176" s="7"/>
       <c t="s" r="E176" s="7">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="F176" s="7">
         <v>321</v>
@@ -7105,13 +7126,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H176" s="8">
-        <v>285</v>
+        <v>77</v>
       </c>
       <c t="s" r="I176" s="7">
-        <v>151</v>
+        <v>287</v>
       </c>
       <c t="s" r="J176" s="7">
-        <v>69</v>
+        <v>288</v>
       </c>
       <c r="K176" s="7"/>
       <c r="L176" s="7"/>
@@ -7122,63 +7143,45 @@
         <v>13</v>
       </c>
       <c r="B177" s="7">
-        <v>800</v>
+        <v>283</v>
       </c>
       <c t="s" r="C177" s="7">
         <v>14</v>
       </c>
       <c r="D177" s="7"/>
       <c t="s" r="E177" s="7">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="F177" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G177" s="8">
-        <v>285</v>
+        <v>77</v>
       </c>
       <c t="s" r="H177" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I177" s="7">
-        <v>123</v>
+        <v>289</v>
       </c>
       <c t="s" r="J177" s="7">
-        <v>79</v>
+        <v>192</v>
       </c>
       <c r="K177" s="7"/>
       <c r="L177" s="7"/>
       <c r="M177" s="7"/>
     </row>
     <row r="178" ht="14.25" customHeight="1">
-      <c t="s" r="A178" s="6">
-        <v>13</v>
-      </c>
-      <c r="B178" s="7">
-        <v>282</v>
-      </c>
-      <c t="s" r="C178" s="7">
-        <v>14</v>
-      </c>
+      <c r="A178" s="6"/>
+      <c r="B178" s="7"/>
+      <c r="C178" s="7"/>
       <c r="D178" s="7"/>
-      <c t="s" r="E178" s="7">
-        <v>281</v>
-      </c>
-      <c r="F178" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G178" s="8">
-        <v>17</v>
-      </c>
-      <c t="s" r="H178" s="8">
-        <v>77</v>
-      </c>
-      <c t="s" r="I178" s="7">
-        <v>286</v>
-      </c>
-      <c t="s" r="J178" s="7">
-        <v>287</v>
-      </c>
+      <c r="E178" s="7"/>
+      <c r="F178" s="7"/>
+      <c r="G178" s="8"/>
+      <c r="H178" s="8"/>
+      <c r="I178" s="7"/>
+      <c r="J178" s="7"/>
       <c r="K178" s="7"/>
       <c r="L178" s="7"/>
       <c r="M178" s="7"/>
@@ -7188,45 +7191,65 @@
         <v>13</v>
       </c>
       <c r="B179" s="7">
-        <v>283</v>
+        <v>929</v>
       </c>
       <c t="s" r="C179" s="7">
         <v>14</v>
       </c>
       <c r="D179" s="7"/>
       <c t="s" r="E179" s="7">
-        <v>281</v>
+        <v>290</v>
       </c>
       <c r="F179" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G179" s="8">
-        <v>77</v>
+        <v>43</v>
       </c>
       <c t="s" r="H179" s="8">
-        <v>17</v>
+        <v>109</v>
       </c>
       <c t="s" r="I179" s="7">
-        <v>288</v>
+        <v>73</v>
       </c>
       <c t="s" r="J179" s="7">
-        <v>191</v>
+        <v>54</v>
       </c>
       <c r="K179" s="7"/>
       <c r="L179" s="7"/>
-      <c r="M179" s="7"/>
+      <c t="s" r="M179" s="7">
+        <v>291</v>
+      </c>
     </row>
     <row r="180" ht="15" customHeight="1">
-      <c r="A180" s="6"/>
-      <c r="B180" s="7"/>
-      <c r="C180" s="7"/>
+      <c t="s" r="A180" s="6">
+        <v>13</v>
+      </c>
+      <c r="B180" s="7">
+        <v>928</v>
+      </c>
+      <c t="s" r="C180" s="7">
+        <v>14</v>
+      </c>
       <c r="D180" s="7"/>
-      <c r="E180" s="7"/>
-      <c r="F180" s="7"/>
-      <c r="G180" s="8"/>
-      <c r="H180" s="8"/>
-      <c r="I180" s="7"/>
-      <c r="J180" s="7"/>
+      <c t="s" r="E180" s="7">
+        <v>290</v>
+      </c>
+      <c r="F180" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G180" s="8">
+        <v>109</v>
+      </c>
+      <c t="s" r="H180" s="8">
+        <v>43</v>
+      </c>
+      <c t="s" r="I180" s="7">
+        <v>103</v>
+      </c>
+      <c t="s" r="J180" s="7">
+        <v>287</v>
+      </c>
       <c r="K180" s="7"/>
       <c r="L180" s="7"/>
       <c r="M180" s="7"/>
@@ -7236,14 +7259,14 @@
         <v>13</v>
       </c>
       <c r="B181" s="7">
-        <v>929</v>
+        <v>962</v>
       </c>
       <c t="s" r="C181" s="7">
         <v>14</v>
       </c>
       <c r="D181" s="7"/>
       <c t="s" r="E181" s="7">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="F181" s="7">
         <v>321</v>
@@ -7252,49 +7275,29 @@
         <v>43</v>
       </c>
       <c t="s" r="H181" s="8">
-        <v>109</v>
+        <v>16</v>
       </c>
       <c t="s" r="I181" s="7">
-        <v>73</v>
+        <v>28</v>
       </c>
       <c t="s" r="J181" s="7">
-        <v>54</v>
+        <v>167</v>
       </c>
       <c r="K181" s="7"/>
       <c r="L181" s="7"/>
-      <c t="s" r="M181" s="7">
-        <v>290</v>
-      </c>
+      <c r="M181" s="7"/>
     </row>
     <row r="182" ht="14.25" customHeight="1">
-      <c t="s" r="A182" s="6">
-        <v>13</v>
-      </c>
-      <c r="B182" s="7">
-        <v>928</v>
-      </c>
-      <c t="s" r="C182" s="7">
-        <v>14</v>
-      </c>
+      <c r="A182" s="6"/>
+      <c r="B182" s="7"/>
+      <c r="C182" s="7"/>
       <c r="D182" s="7"/>
-      <c t="s" r="E182" s="7">
-        <v>289</v>
-      </c>
-      <c r="F182" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G182" s="8">
-        <v>109</v>
-      </c>
-      <c t="s" r="H182" s="8">
-        <v>43</v>
-      </c>
-      <c t="s" r="I182" s="7">
-        <v>103</v>
-      </c>
-      <c t="s" r="J182" s="7">
-        <v>286</v>
-      </c>
+      <c r="E182" s="7"/>
+      <c r="F182" s="7"/>
+      <c r="G182" s="8"/>
+      <c r="H182" s="8"/>
+      <c r="I182" s="7"/>
+      <c r="J182" s="7"/>
       <c r="K182" s="7"/>
       <c r="L182" s="7"/>
       <c r="M182" s="7"/>
@@ -7304,45 +7307,65 @@
         <v>13</v>
       </c>
       <c r="B183" s="7">
-        <v>962</v>
+        <v>809</v>
       </c>
       <c t="s" r="C183" s="7">
         <v>14</v>
       </c>
       <c r="D183" s="7"/>
       <c t="s" r="E183" s="7">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="F183" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G183" s="8">
-        <v>43</v>
+        <v>17</v>
       </c>
       <c t="s" r="H183" s="8">
-        <v>16</v>
+        <v>293</v>
       </c>
       <c t="s" r="I183" s="7">
-        <v>28</v>
+        <v>96</v>
       </c>
       <c t="s" r="J183" s="7">
-        <v>167</v>
+        <v>294</v>
       </c>
       <c r="K183" s="7"/>
       <c r="L183" s="7"/>
-      <c r="M183" s="7"/>
+      <c t="s" r="M183" s="7">
+        <v>295</v>
+      </c>
     </row>
     <row r="184" ht="14.25" customHeight="1">
-      <c r="A184" s="6"/>
-      <c r="B184" s="7"/>
-      <c r="C184" s="7"/>
+      <c t="s" r="A184" s="6">
+        <v>13</v>
+      </c>
+      <c r="B184" s="7">
+        <v>808</v>
+      </c>
+      <c t="s" r="C184" s="7">
+        <v>14</v>
+      </c>
       <c r="D184" s="7"/>
-      <c r="E184" s="7"/>
-      <c r="F184" s="7"/>
-      <c r="G184" s="8"/>
-      <c r="H184" s="8"/>
-      <c r="I184" s="7"/>
-      <c r="J184" s="7"/>
+      <c t="s" r="E184" s="7">
+        <v>292</v>
+      </c>
+      <c r="F184" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G184" s="8">
+        <v>293</v>
+      </c>
+      <c t="s" r="H184" s="8">
+        <v>17</v>
+      </c>
+      <c t="s" r="I184" s="7">
+        <v>238</v>
+      </c>
+      <c t="s" r="J184" s="7">
+        <v>122</v>
+      </c>
       <c r="K184" s="7"/>
       <c r="L184" s="7"/>
       <c r="M184" s="7"/>
@@ -7352,14 +7375,14 @@
         <v>13</v>
       </c>
       <c r="B185" s="7">
-        <v>809</v>
+        <v>134</v>
       </c>
       <c t="s" r="C185" s="7">
         <v>14</v>
       </c>
       <c r="D185" s="7"/>
       <c t="s" r="E185" s="7">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="F185" s="7">
         <v>321</v>
@@ -7368,18 +7391,20 @@
         <v>17</v>
       </c>
       <c t="s" r="H185" s="8">
-        <v>292</v>
+        <v>43</v>
       </c>
       <c t="s" r="I185" s="7">
-        <v>96</v>
+        <v>229</v>
       </c>
       <c t="s" r="J185" s="7">
-        <v>293</v>
-      </c>
-      <c r="K185" s="7"/>
+        <v>175</v>
+      </c>
+      <c t="s" r="K185" s="7">
+        <v>143</v>
+      </c>
       <c r="L185" s="7"/>
       <c t="s" r="M185" s="7">
-        <v>294</v>
+        <v>70</v>
       </c>
     </row>
     <row r="186" ht="14.25" customHeight="1">
@@ -7387,29 +7412,29 @@
         <v>13</v>
       </c>
       <c r="B186" s="7">
-        <v>808</v>
+        <v>151</v>
       </c>
       <c t="s" r="C186" s="7">
         <v>14</v>
       </c>
       <c r="D186" s="7"/>
       <c t="s" r="E186" s="7">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="F186" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G186" s="8">
-        <v>292</v>
+        <v>43</v>
       </c>
       <c t="s" r="H186" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I186" s="7">
-        <v>237</v>
+        <v>24</v>
       </c>
       <c t="s" r="J186" s="7">
-        <v>122</v>
+        <v>296</v>
       </c>
       <c r="K186" s="7"/>
       <c r="L186" s="7"/>
@@ -7420,14 +7445,14 @@
         <v>13</v>
       </c>
       <c r="B187" s="7">
-        <v>134</v>
+        <v>152</v>
       </c>
       <c t="s" r="C187" s="7">
         <v>14</v>
       </c>
       <c r="D187" s="7"/>
       <c t="s" r="E187" s="7">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="F187" s="7">
         <v>321</v>
@@ -7439,48 +7464,30 @@
         <v>43</v>
       </c>
       <c t="s" r="I187" s="7">
-        <v>228</v>
+        <v>210</v>
       </c>
       <c t="s" r="J187" s="7">
-        <v>174</v>
+        <v>106</v>
       </c>
       <c t="s" r="K187" s="7">
-        <v>143</v>
+        <v>179</v>
       </c>
       <c r="L187" s="7"/>
       <c t="s" r="M187" s="7">
-        <v>70</v>
+        <v>201</v>
       </c>
     </row>
     <row r="188" ht="14.25" customHeight="1">
-      <c t="s" r="A188" s="6">
-        <v>13</v>
-      </c>
-      <c r="B188" s="7">
-        <v>151</v>
-      </c>
-      <c t="s" r="C188" s="7">
-        <v>14</v>
-      </c>
+      <c r="A188" s="6"/>
+      <c r="B188" s="7"/>
+      <c r="C188" s="7"/>
       <c r="D188" s="7"/>
-      <c t="s" r="E188" s="7">
-        <v>291</v>
-      </c>
-      <c r="F188" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G188" s="8">
-        <v>43</v>
-      </c>
-      <c t="s" r="H188" s="8">
-        <v>17</v>
-      </c>
-      <c t="s" r="I188" s="7">
-        <v>24</v>
-      </c>
-      <c t="s" r="J188" s="7">
-        <v>295</v>
-      </c>
+      <c r="E188" s="7"/>
+      <c r="F188" s="7"/>
+      <c r="G188" s="8"/>
+      <c r="H188" s="8"/>
+      <c r="I188" s="7"/>
+      <c r="J188" s="7"/>
       <c r="K188" s="7"/>
       <c r="L188" s="7"/>
       <c r="M188" s="7"/>
@@ -7490,49 +7497,65 @@
         <v>13</v>
       </c>
       <c r="B189" s="7">
-        <v>152</v>
+        <v>925</v>
       </c>
       <c t="s" r="C189" s="7">
         <v>14</v>
       </c>
       <c r="D189" s="7"/>
       <c t="s" r="E189" s="7">
-        <v>291</v>
+        <v>297</v>
       </c>
       <c r="F189" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G189" s="8">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c t="s" r="H189" s="8">
-        <v>43</v>
+        <v>77</v>
       </c>
       <c t="s" r="I189" s="7">
-        <v>209</v>
+        <v>298</v>
       </c>
       <c t="s" r="J189" s="7">
-        <v>106</v>
-      </c>
-      <c t="s" r="K189" s="7">
-        <v>178</v>
-      </c>
+        <v>299</v>
+      </c>
+      <c r="K189" s="7"/>
       <c r="L189" s="7"/>
       <c t="s" r="M189" s="7">
-        <v>200</v>
+        <v>300</v>
       </c>
     </row>
     <row r="190" ht="15" customHeight="1">
-      <c r="A190" s="6"/>
-      <c r="B190" s="7"/>
-      <c r="C190" s="7"/>
+      <c t="s" r="A190" s="6">
+        <v>13</v>
+      </c>
+      <c r="B190" s="7">
+        <v>693</v>
+      </c>
+      <c t="s" r="C190" s="7">
+        <v>14</v>
+      </c>
       <c r="D190" s="7"/>
-      <c r="E190" s="7"/>
-      <c r="F190" s="7"/>
-      <c r="G190" s="8"/>
-      <c r="H190" s="8"/>
-      <c r="I190" s="7"/>
-      <c r="J190" s="7"/>
+      <c t="s" r="E190" s="7">
+        <v>297</v>
+      </c>
+      <c r="F190" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G190" s="8">
+        <v>77</v>
+      </c>
+      <c t="s" r="H190" s="8">
+        <v>152</v>
+      </c>
+      <c t="s" r="I190" s="7">
+        <v>301</v>
+      </c>
+      <c t="s" r="J190" s="7">
+        <v>211</v>
+      </c>
       <c r="K190" s="7"/>
       <c r="L190" s="7"/>
       <c r="M190" s="7"/>
@@ -7542,65 +7565,45 @@
         <v>13</v>
       </c>
       <c r="B191" s="7">
-        <v>925</v>
+        <v>692</v>
       </c>
       <c t="s" r="C191" s="7">
         <v>14</v>
       </c>
       <c r="D191" s="7"/>
       <c t="s" r="E191" s="7">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="F191" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G191" s="8">
-        <v>16</v>
+        <v>152</v>
       </c>
       <c t="s" r="H191" s="8">
         <v>77</v>
       </c>
       <c t="s" r="I191" s="7">
-        <v>297</v>
+        <v>272</v>
       </c>
       <c t="s" r="J191" s="7">
-        <v>298</v>
+        <v>302</v>
       </c>
       <c r="K191" s="7"/>
       <c r="L191" s="7"/>
-      <c t="s" r="M191" s="7">
-        <v>299</v>
-      </c>
+      <c r="M191" s="7"/>
     </row>
     <row r="192" ht="14.25" customHeight="1">
-      <c t="s" r="A192" s="6">
-        <v>13</v>
-      </c>
-      <c r="B192" s="7">
-        <v>693</v>
-      </c>
-      <c t="s" r="C192" s="7">
-        <v>14</v>
-      </c>
+      <c r="A192" s="6"/>
+      <c r="B192" s="7"/>
+      <c r="C192" s="7"/>
       <c r="D192" s="7"/>
-      <c t="s" r="E192" s="7">
-        <v>296</v>
-      </c>
-      <c r="F192" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G192" s="8">
-        <v>77</v>
-      </c>
-      <c t="s" r="H192" s="8">
-        <v>152</v>
-      </c>
-      <c t="s" r="I192" s="7">
-        <v>300</v>
-      </c>
-      <c t="s" r="J192" s="7">
-        <v>210</v>
-      </c>
+      <c r="E192" s="7"/>
+      <c r="F192" s="7"/>
+      <c r="G192" s="8"/>
+      <c r="H192" s="8"/>
+      <c r="I192" s="7"/>
+      <c r="J192" s="7"/>
       <c r="K192" s="7"/>
       <c r="L192" s="7"/>
       <c r="M192" s="7"/>
@@ -7610,82 +7613,104 @@
         <v>13</v>
       </c>
       <c r="B193" s="7">
-        <v>692</v>
+        <v>224</v>
       </c>
       <c t="s" r="C193" s="7">
         <v>14</v>
       </c>
       <c r="D193" s="7"/>
       <c t="s" r="E193" s="7">
-        <v>296</v>
+        <v>303</v>
       </c>
       <c r="F193" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G193" s="8">
-        <v>152</v>
+        <v>17</v>
       </c>
       <c t="s" r="H193" s="8">
-        <v>77</v>
+        <v>198</v>
       </c>
       <c t="s" r="I193" s="7">
-        <v>271</v>
+        <v>304</v>
       </c>
       <c t="s" r="J193" s="7">
-        <v>301</v>
+        <v>305</v>
       </c>
       <c r="K193" s="7"/>
       <c r="L193" s="7"/>
-      <c r="M193" s="7"/>
+      <c t="s" r="M193" s="7">
+        <v>306</v>
+      </c>
     </row>
     <row r="194" ht="14.25" customHeight="1">
-      <c r="A194" s="6"/>
-      <c r="B194" s="7"/>
-      <c r="C194" s="7"/>
+      <c t="s" r="A194" s="6">
+        <v>13</v>
+      </c>
+      <c r="B194" s="7">
+        <v>741</v>
+      </c>
+      <c t="s" r="C194" s="7">
+        <v>14</v>
+      </c>
       <c r="D194" s="7"/>
-      <c r="E194" s="7"/>
-      <c r="F194" s="7"/>
-      <c r="G194" s="8"/>
-      <c r="H194" s="8"/>
-      <c r="I194" s="7"/>
-      <c r="J194" s="7"/>
+      <c t="s" r="E194" s="7">
+        <v>303</v>
+      </c>
+      <c r="F194" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G194" s="8">
+        <v>198</v>
+      </c>
+      <c t="s" r="H194" s="8">
+        <v>134</v>
+      </c>
+      <c t="s" r="I194" s="7">
+        <v>307</v>
+      </c>
+      <c t="s" r="J194" s="7">
+        <v>34</v>
+      </c>
       <c r="K194" s="7"/>
       <c r="L194" s="7"/>
-      <c r="M194" s="7"/>
+      <c t="s" r="M194" s="7">
+        <v>120</v>
+      </c>
     </row>
     <row r="195" ht="15" customHeight="1">
       <c t="s" r="A195" s="6">
         <v>13</v>
       </c>
       <c r="B195" s="7">
-        <v>224</v>
+        <v>740</v>
       </c>
       <c t="s" r="C195" s="7">
         <v>14</v>
       </c>
       <c r="D195" s="7"/>
       <c t="s" r="E195" s="7">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="F195" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G195" s="8">
-        <v>17</v>
+        <v>134</v>
       </c>
       <c t="s" r="H195" s="8">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c t="s" r="I195" s="7">
-        <v>303</v>
+        <v>308</v>
       </c>
       <c t="s" r="J195" s="7">
-        <v>304</v>
+        <v>149</v>
       </c>
       <c r="K195" s="7"/>
       <c r="L195" s="7"/>
       <c t="s" r="M195" s="7">
-        <v>305</v>
+        <v>150</v>
       </c>
     </row>
     <row r="196" ht="14.25" customHeight="1">
@@ -7693,99 +7718,95 @@
         <v>13</v>
       </c>
       <c r="B196" s="7">
-        <v>741</v>
+        <v>227</v>
       </c>
       <c t="s" r="C196" s="7">
         <v>14</v>
       </c>
       <c r="D196" s="7"/>
       <c t="s" r="E196" s="7">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="F196" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G196" s="8">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c t="s" r="H196" s="8">
-        <v>134</v>
+        <v>17</v>
       </c>
       <c t="s" r="I196" s="7">
-        <v>306</v>
+        <v>100</v>
       </c>
       <c t="s" r="J196" s="7">
-        <v>34</v>
+        <v>54</v>
       </c>
       <c r="K196" s="7"/>
       <c r="L196" s="7"/>
-      <c t="s" r="M196" s="7">
-        <v>120</v>
-      </c>
+      <c r="M196" s="7"/>
     </row>
     <row r="197" ht="14.25" customHeight="1">
       <c t="s" r="A197" s="6">
         <v>13</v>
       </c>
       <c r="B197" s="7">
-        <v>740</v>
+        <v>252</v>
       </c>
       <c t="s" r="C197" s="7">
         <v>14</v>
       </c>
       <c r="D197" s="7"/>
       <c t="s" r="E197" s="7">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="F197" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G197" s="8">
-        <v>134</v>
+        <v>17</v>
       </c>
       <c t="s" r="H197" s="8">
-        <v>197</v>
+        <v>239</v>
       </c>
       <c t="s" r="I197" s="7">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c t="s" r="J197" s="7">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="K197" s="7"/>
       <c r="L197" s="7"/>
-      <c t="s" r="M197" s="7">
-        <v>150</v>
-      </c>
+      <c r="M197" s="7"/>
     </row>
     <row r="198" ht="14.25" customHeight="1">
       <c t="s" r="A198" s="6">
         <v>13</v>
       </c>
       <c r="B198" s="7">
-        <v>227</v>
+        <v>253</v>
       </c>
       <c t="s" r="C198" s="7">
         <v>14</v>
       </c>
       <c r="D198" s="7"/>
       <c t="s" r="E198" s="7">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="F198" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G198" s="8">
-        <v>197</v>
+        <v>239</v>
       </c>
       <c t="s" r="H198" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I198" s="7">
-        <v>100</v>
+        <v>301</v>
       </c>
       <c t="s" r="J198" s="7">
-        <v>54</v>
+        <v>126</v>
       </c>
       <c r="K198" s="7"/>
       <c r="L198" s="7"/>
@@ -7796,14 +7817,14 @@
         <v>13</v>
       </c>
       <c r="B199" s="7">
-        <v>252</v>
+        <v>384</v>
       </c>
       <c t="s" r="C199" s="7">
         <v>14</v>
       </c>
       <c r="D199" s="7"/>
       <c t="s" r="E199" s="7">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="F199" s="7">
         <v>321</v>
@@ -7812,50 +7833,58 @@
         <v>17</v>
       </c>
       <c t="s" r="H199" s="8">
-        <v>238</v>
+        <v>181</v>
       </c>
       <c t="s" r="I199" s="7">
-        <v>308</v>
+        <v>144</v>
       </c>
       <c t="s" r="J199" s="7">
-        <v>153</v>
-      </c>
-      <c r="K199" s="7"/>
+        <v>178</v>
+      </c>
+      <c t="s" r="K199" s="7">
+        <v>105</v>
+      </c>
       <c r="L199" s="7"/>
-      <c r="M199" s="7"/>
+      <c t="s" r="M199" s="7">
+        <v>310</v>
+      </c>
     </row>
     <row r="200" ht="15" customHeight="1">
       <c t="s" r="A200" s="6">
         <v>13</v>
       </c>
       <c r="B200" s="7">
-        <v>253</v>
+        <v>385</v>
       </c>
       <c t="s" r="C200" s="7">
         <v>14</v>
       </c>
       <c r="D200" s="7"/>
       <c t="s" r="E200" s="7">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="F200" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G200" s="8">
-        <v>238</v>
+        <v>181</v>
       </c>
       <c t="s" r="H200" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I200" s="7">
-        <v>300</v>
+        <v>311</v>
       </c>
       <c t="s" r="J200" s="7">
-        <v>126</v>
-      </c>
-      <c r="K200" s="7"/>
+        <v>48</v>
+      </c>
+      <c t="s" r="K200" s="7">
+        <v>128</v>
+      </c>
       <c r="L200" s="7"/>
-      <c r="M200" s="7"/>
+      <c t="s" r="M200" s="7">
+        <v>224</v>
+      </c>
     </row>
     <row r="201" ht="14.25" customHeight="1">
       <c r="A201" s="6"/>
@@ -7884,7 +7913,7 @@
       </c>
       <c r="D202" s="7"/>
       <c t="s" r="E202" s="7">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="F202" s="7">
         <v>321</v>
@@ -7896,15 +7925,15 @@
         <v>43</v>
       </c>
       <c t="s" r="I202" s="7">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c t="s" r="J202" s="7">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="K202" s="7"/>
       <c r="L202" s="7"/>
       <c t="s" r="M202" s="7">
-        <v>310</v>
+        <v>313</v>
       </c>
     </row>
     <row r="203" ht="14.25" customHeight="1">
@@ -7919,7 +7948,7 @@
       </c>
       <c r="D203" s="7"/>
       <c t="s" r="E203" s="7">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="F203" s="7">
         <v>321</v>
@@ -7931,7 +7960,7 @@
         <v>134</v>
       </c>
       <c t="s" r="I203" s="7">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c t="s" r="J203" s="7">
         <v>110</v>
@@ -7952,7 +7981,7 @@
       </c>
       <c r="D204" s="7"/>
       <c t="s" r="E204" s="7">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="F204" s="7">
         <v>321</v>
@@ -7985,7 +8014,7 @@
       </c>
       <c r="D205" s="7"/>
       <c t="s" r="E205" s="7">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="F205" s="7">
         <v>321</v>
@@ -7994,7 +8023,7 @@
         <v>43</v>
       </c>
       <c t="s" r="H205" s="8">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c t="s" r="I205" s="7">
         <v>153</v>
@@ -8018,13 +8047,13 @@
       </c>
       <c r="D206" s="7"/>
       <c t="s" r="E206" s="7">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="F206" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G206" s="8">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c t="s" r="H206" s="8">
         <v>43</v>
@@ -8033,7 +8062,7 @@
         <v>59</v>
       </c>
       <c t="s" r="J206" s="7">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="K206" s="7"/>
       <c r="L206" s="7"/>
@@ -8051,7 +8080,7 @@
       </c>
       <c r="D207" s="7"/>
       <c t="s" r="E207" s="7">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="F207" s="7">
         <v>321</v>
@@ -8063,10 +8092,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I207" s="7">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c t="s" r="J207" s="7">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="K207" s="7"/>
       <c r="L207" s="7"/>
@@ -8084,7 +8113,7 @@
       </c>
       <c r="D208" s="7"/>
       <c t="s" r="E208" s="7">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="F208" s="7">
         <v>321</v>
@@ -8096,7 +8125,7 @@
         <v>43</v>
       </c>
       <c t="s" r="I208" s="7">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c t="s" r="J208" s="7">
         <v>60</v>
@@ -8132,7 +8161,7 @@
       </c>
       <c r="D210" s="7"/>
       <c t="s" r="E210" s="7">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="F210" s="7">
         <v>321</v>
@@ -8141,18 +8170,18 @@
         <v>17</v>
       </c>
       <c t="s" r="H210" s="8">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c t="s" r="I210" s="7">
         <v>138</v>
       </c>
       <c t="s" r="J210" s="7">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="K210" s="7"/>
       <c r="L210" s="7"/>
       <c t="s" r="M210" s="7">
-        <v>313</v>
+        <v>316</v>
       </c>
     </row>
     <row r="211" ht="14.25" customHeight="1">
@@ -8167,27 +8196,27 @@
       </c>
       <c r="D211" s="7"/>
       <c t="s" r="E211" s="7">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="F211" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G211" s="8">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c t="s" r="H211" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I211" s="7">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c t="s" r="J211" s="7">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="K211" s="7"/>
       <c r="L211" s="7"/>
       <c t="s" r="M211" s="7">
-        <v>315</v>
+        <v>318</v>
       </c>
     </row>
     <row r="212" ht="14.25" customHeight="1">
@@ -8202,7 +8231,7 @@
       </c>
       <c r="D212" s="7"/>
       <c t="s" r="E212" s="7">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="F212" s="7">
         <v>321</v>
@@ -8235,7 +8264,7 @@
       </c>
       <c r="D213" s="7"/>
       <c t="s" r="E213" s="7">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="F213" s="7">
         <v>321</v>
@@ -8247,7 +8276,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I213" s="7">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c t="s" r="J213" s="7">
         <v>154</v>
@@ -8268,7 +8297,7 @@
       </c>
       <c r="D214" s="7"/>
       <c t="s" r="E214" s="7">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="F214" s="7">
         <v>321</v>
@@ -8283,7 +8312,7 @@
         <v>25</v>
       </c>
       <c t="s" r="J214" s="7">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="K214" s="7"/>
       <c r="L214" s="7"/>
@@ -8301,7 +8330,7 @@
       </c>
       <c r="D215" s="7"/>
       <c t="s" r="E215" s="7">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="F215" s="7">
         <v>321</v>
@@ -8316,7 +8345,7 @@
         <v>128</v>
       </c>
       <c t="s" r="J215" s="7">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="K215" s="7"/>
       <c r="L215" s="7"/>
@@ -8349,7 +8378,7 @@
       </c>
       <c r="D217" s="7"/>
       <c t="s" r="E217" s="7">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="F217" s="7">
         <v>321</v>
@@ -8361,15 +8390,15 @@
         <v>17</v>
       </c>
       <c t="s" r="I217" s="7">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c t="s" r="J217" s="7">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="K217" s="7"/>
       <c r="L217" s="7"/>
       <c t="s" r="M217" s="7">
-        <v>320</v>
+        <v>323</v>
       </c>
     </row>
     <row r="218" ht="14.25" customHeight="1">
@@ -8384,7 +8413,7 @@
       </c>
       <c r="D218" s="7"/>
       <c t="s" r="E218" s="7">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="F218" s="7">
         <v>321</v>
@@ -8393,13 +8422,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H218" s="8">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c t="s" r="I218" s="7">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c t="s" r="J218" s="7">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="K218" s="7"/>
       <c r="L218" s="7"/>
@@ -8417,13 +8446,13 @@
       </c>
       <c r="D219" s="7"/>
       <c t="s" r="E219" s="7">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="F219" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G219" s="8">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c t="s" r="H219" s="8">
         <v>17</v>
@@ -8450,7 +8479,7 @@
       </c>
       <c r="D220" s="7"/>
       <c t="s" r="E220" s="7">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="F220" s="7">
         <v>321</v>
@@ -8459,13 +8488,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H220" s="8">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c t="s" r="I220" s="7">
         <v>112</v>
       </c>
       <c t="s" r="J220" s="7">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="K220" s="7"/>
       <c r="L220" s="7"/>
@@ -8483,19 +8512,19 @@
       </c>
       <c r="D221" s="7"/>
       <c t="s" r="E221" s="7">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="F221" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G221" s="8">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c t="s" r="H221" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I221" s="7">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c t="s" r="J221" s="7">
         <v>145</v>
@@ -8531,7 +8560,7 @@
       </c>
       <c r="D223" s="7"/>
       <c t="s" r="E223" s="7">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="F223" s="7">
         <v>321</v>
@@ -8551,7 +8580,7 @@
       <c r="K223" s="7"/>
       <c r="L223" s="7"/>
       <c t="s" r="M223" s="7">
-        <v>323</v>
+        <v>326</v>
       </c>
     </row>
     <row r="224" ht="14.25" customHeight="1">
@@ -8566,7 +8595,7 @@
       </c>
       <c r="D224" s="7"/>
       <c t="s" r="E224" s="7">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="F224" s="7">
         <v>321</v>
@@ -8581,11 +8610,13 @@
         <v>172</v>
       </c>
       <c t="s" r="J224" s="7">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="K224" s="7"/>
       <c r="L224" s="7"/>
-      <c r="M224" s="7"/>
+      <c t="s" r="M224" s="7">
+        <v>328</v>
+      </c>
     </row>
     <row r="225" ht="15" customHeight="1">
       <c t="s" r="A225" s="6">
@@ -8599,7 +8630,7 @@
       </c>
       <c r="D225" s="7"/>
       <c t="s" r="E225" s="7">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="F225" s="7">
         <v>321</v>
@@ -8611,7 +8642,7 @@
         <v>124</v>
       </c>
       <c t="s" r="I225" s="7">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c t="s" r="J225" s="7">
         <v>69</v>
@@ -8632,7 +8663,7 @@
       </c>
       <c r="D226" s="7"/>
       <c t="s" r="E226" s="7">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="F226" s="7">
         <v>321</v>
@@ -8647,7 +8678,7 @@
         <v>24</v>
       </c>
       <c t="s" r="J226" s="7">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="K226" s="7"/>
       <c r="L226" s="7"/>
@@ -8680,7 +8711,7 @@
       </c>
       <c r="D228" s="7"/>
       <c t="s" r="E228" s="7">
-        <v>325</v>
+        <v>329</v>
       </c>
       <c r="F228" s="7">
         <v>321</v>
@@ -8692,7 +8723,7 @@
         <v>43</v>
       </c>
       <c t="s" r="I228" s="7">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c t="s" r="J228" s="7">
         <v>35</v>
@@ -8700,7 +8731,7 @@
       <c r="K228" s="7"/>
       <c r="L228" s="7"/>
       <c t="s" r="M228" s="7">
-        <v>327</v>
+        <v>331</v>
       </c>
     </row>
     <row r="229" ht="14.25" customHeight="1">
@@ -8715,7 +8746,7 @@
       </c>
       <c r="D229" s="7"/>
       <c t="s" r="E229" s="7">
-        <v>325</v>
+        <v>329</v>
       </c>
       <c r="F229" s="7">
         <v>321</v>
@@ -8730,7 +8761,7 @@
         <v>37</v>
       </c>
       <c t="s" r="J229" s="7">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="K229" s="7"/>
       <c r="L229" s="7"/>
@@ -8748,7 +8779,7 @@
       </c>
       <c r="D230" s="7"/>
       <c t="s" r="E230" s="7">
-        <v>325</v>
+        <v>329</v>
       </c>
       <c r="F230" s="7">
         <v>321</v>
@@ -8763,7 +8794,7 @@
         <v>91</v>
       </c>
       <c t="s" r="J230" s="7">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="K230" s="7"/>
       <c r="L230" s="7"/>
@@ -8781,7 +8812,7 @@
       </c>
       <c r="D231" s="7"/>
       <c t="s" r="E231" s="7">
-        <v>325</v>
+        <v>329</v>
       </c>
       <c r="F231" s="7">
         <v>321</v>
@@ -8793,7 +8824,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I231" s="7">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c t="s" r="J231" s="7">
         <v>128</v>
@@ -8829,13 +8860,13 @@
       </c>
       <c r="D233" s="7"/>
       <c t="s" r="E233" s="7">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="F233" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G233" s="8">
-        <v>329</v>
+        <v>333</v>
       </c>
       <c t="s" r="H233" s="8">
         <v>17</v>
@@ -8844,12 +8875,12 @@
         <v>172</v>
       </c>
       <c t="s" r="J233" s="7">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="K233" s="7"/>
       <c r="L233" s="7"/>
       <c t="s" r="M233" s="7">
-        <v>330</v>
+        <v>334</v>
       </c>
     </row>
     <row r="234" ht="14.25" customHeight="1">
@@ -8864,7 +8895,7 @@
       </c>
       <c r="D234" s="7"/>
       <c t="s" r="E234" s="7">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="F234" s="7">
         <v>321</v>
@@ -8873,7 +8904,7 @@
         <v>17</v>
       </c>
       <c t="s" r="H234" s="8">
-        <v>329</v>
+        <v>333</v>
       </c>
       <c t="s" r="I234" s="7">
         <v>71</v>
@@ -8912,7 +8943,7 @@
       </c>
       <c r="D236" s="7"/>
       <c t="s" r="E236" s="7">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="F236" s="7">
         <v>321</v>
@@ -8924,7 +8955,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I236" s="7">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c t="s" r="J236" s="7">
         <v>44</v>
@@ -8947,7 +8978,7 @@
       </c>
       <c r="D237" s="7"/>
       <c t="s" r="E237" s="7">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="F237" s="7">
         <v>321</v>
@@ -8959,14 +8990,16 @@
         <v>43</v>
       </c>
       <c t="s" r="I237" s="7">
-        <v>332</v>
+        <v>336</v>
       </c>
       <c t="s" r="J237" s="7">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="K237" s="7"/>
       <c r="L237" s="7"/>
-      <c r="M237" s="7"/>
+      <c t="s" r="M237" s="7">
+        <v>266</v>
+      </c>
     </row>
     <row r="238" ht="14.25" customHeight="1">
       <c t="s" r="A238" s="6">
@@ -8980,7 +9013,7 @@
       </c>
       <c r="D238" s="7"/>
       <c t="s" r="E238" s="7">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="F238" s="7">
         <v>321</v>
@@ -8995,14 +9028,14 @@
         <v>54</v>
       </c>
       <c t="s" r="J238" s="7">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c t="s" r="K238" s="7">
-        <v>333</v>
+        <v>337</v>
       </c>
       <c r="L238" s="7"/>
       <c t="s" r="M238" s="7">
-        <v>334</v>
+        <v>338</v>
       </c>
     </row>
     <row r="239" ht="14.25" customHeight="1">
@@ -9017,7 +9050,7 @@
       </c>
       <c r="D239" s="7"/>
       <c t="s" r="E239" s="7">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="F239" s="7">
         <v>321</v>
@@ -9035,7 +9068,7 @@
         <v>59</v>
       </c>
       <c t="s" r="K239" s="7">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="L239" s="7"/>
       <c t="s" r="M239" s="7">
@@ -9054,7 +9087,7 @@
       </c>
       <c r="D240" s="7"/>
       <c t="s" r="E240" s="7">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="F240" s="7">
         <v>321</v>
@@ -9087,7 +9120,7 @@
       </c>
       <c r="D241" s="7"/>
       <c t="s" r="E241" s="7">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="F241" s="7">
         <v>321</v>
@@ -9099,10 +9132,10 @@
         <v>43</v>
       </c>
       <c t="s" r="I241" s="7">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c t="s" r="J241" s="7">
-        <v>335</v>
+        <v>339</v>
       </c>
       <c r="K241" s="7"/>
       <c r="L241" s="7"/>
@@ -9120,7 +9153,7 @@
       </c>
       <c r="D242" s="7"/>
       <c t="s" r="E242" s="7">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="F242" s="7">
         <v>321</v>
@@ -9129,10 +9162,10 @@
         <v>43</v>
       </c>
       <c t="s" r="H242" s="8">
-        <v>336</v>
+        <v>340</v>
       </c>
       <c t="s" r="I242" s="7">
-        <v>337</v>
+        <v>341</v>
       </c>
       <c t="s" r="J242" s="7">
         <v>84</v>
@@ -9168,19 +9201,19 @@
       </c>
       <c r="D244" s="7"/>
       <c t="s" r="E244" s="7">
-        <v>338</v>
+        <v>342</v>
       </c>
       <c r="F244" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G244" s="8">
-        <v>339</v>
+        <v>343</v>
       </c>
       <c t="s" r="H244" s="8">
         <v>43</v>
       </c>
       <c t="s" r="I244" s="7">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c t="s" r="J244" s="7">
         <v>149</v>
@@ -9188,7 +9221,7 @@
       <c r="K244" s="7"/>
       <c r="L244" s="7"/>
       <c t="s" r="M244" s="7">
-        <v>340</v>
+        <v>344</v>
       </c>
     </row>
     <row r="245" ht="15" customHeight="1">
@@ -9203,7 +9236,7 @@
       </c>
       <c r="D245" s="7"/>
       <c t="s" r="E245" s="7">
-        <v>338</v>
+        <v>342</v>
       </c>
       <c r="F245" s="7">
         <v>321</v>
@@ -9212,7 +9245,7 @@
         <v>43</v>
       </c>
       <c t="s" r="H245" s="8">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c t="s" r="I245" s="7">
         <v>18</v>
@@ -9236,19 +9269,19 @@
       </c>
       <c r="D246" s="7"/>
       <c t="s" r="E246" s="7">
-        <v>338</v>
+        <v>342</v>
       </c>
       <c r="F246" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G246" s="8">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c t="s" r="H246" s="8">
         <v>43</v>
       </c>
       <c t="s" r="I246" s="7">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c t="s" r="J246" s="7">
         <v>58</v>
@@ -9269,7 +9302,7 @@
       </c>
       <c r="D247" s="7"/>
       <c t="s" r="E247" s="7">
-        <v>338</v>
+        <v>342</v>
       </c>
       <c r="F247" s="7">
         <v>321</v>
@@ -9278,10 +9311,10 @@
         <v>43</v>
       </c>
       <c t="s" r="H247" s="8">
-        <v>341</v>
+        <v>345</v>
       </c>
       <c t="s" r="I247" s="7">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c t="s" r="J247" s="7">
         <v>105</v>
@@ -9302,13 +9335,13 @@
       </c>
       <c r="D248" s="7"/>
       <c t="s" r="E248" s="7">
-        <v>338</v>
+        <v>342</v>
       </c>
       <c r="F248" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G248" s="8">
-        <v>341</v>
+        <v>345</v>
       </c>
       <c t="s" r="H248" s="8">
         <v>43</v>
@@ -9317,7 +9350,7 @@
         <v>27</v>
       </c>
       <c t="s" r="J248" s="7">
-        <v>342</v>
+        <v>346</v>
       </c>
       <c r="K248" s="7"/>
       <c r="L248" s="7"/>
@@ -9335,7 +9368,7 @@
       </c>
       <c r="D249" s="7"/>
       <c t="s" r="E249" s="7">
-        <v>338</v>
+        <v>342</v>
       </c>
       <c r="F249" s="7">
         <v>321</v>
@@ -9344,10 +9377,10 @@
         <v>43</v>
       </c>
       <c t="s" r="H249" s="8">
-        <v>339</v>
+        <v>343</v>
       </c>
       <c t="s" r="I249" s="7">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c t="s" r="J249" s="7">
         <v>51</v>
@@ -9383,7 +9416,7 @@
       </c>
       <c r="D251" s="7"/>
       <c t="s" r="E251" s="7">
-        <v>343</v>
+        <v>347</v>
       </c>
       <c r="F251" s="7">
         <v>321</v>
@@ -9395,7 +9428,7 @@
         <v>124</v>
       </c>
       <c t="s" r="I251" s="7">
-        <v>344</v>
+        <v>348</v>
       </c>
       <c t="s" r="J251" s="7">
         <v>63</v>
@@ -9403,7 +9436,7 @@
       <c r="K251" s="7"/>
       <c r="L251" s="7"/>
       <c t="s" r="M251" s="7">
-        <v>345</v>
+        <v>349</v>
       </c>
     </row>
     <row r="252" ht="14.25" customHeight="1">
@@ -9418,7 +9451,7 @@
       </c>
       <c r="D252" s="7"/>
       <c t="s" r="E252" s="7">
-        <v>343</v>
+        <v>347</v>
       </c>
       <c r="F252" s="7">
         <v>321</v>
@@ -9427,13 +9460,13 @@
         <v>124</v>
       </c>
       <c t="s" r="H252" s="8">
-        <v>346</v>
+        <v>350</v>
       </c>
       <c t="s" r="I252" s="7">
         <v>37</v>
       </c>
       <c t="s" r="J252" s="7">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="K252" s="7"/>
       <c r="L252" s="7"/>
@@ -9451,22 +9484,22 @@
       </c>
       <c r="D253" s="7"/>
       <c t="s" r="E253" s="7">
-        <v>343</v>
+        <v>347</v>
       </c>
       <c r="F253" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G253" s="8">
-        <v>346</v>
+        <v>350</v>
       </c>
       <c t="s" r="H253" s="8">
         <v>124</v>
       </c>
       <c t="s" r="I253" s="7">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c t="s" r="J253" s="7">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="K253" s="7"/>
       <c r="L253" s="7"/>
@@ -9484,7 +9517,7 @@
       </c>
       <c r="D254" s="7"/>
       <c t="s" r="E254" s="7">
-        <v>343</v>
+        <v>347</v>
       </c>
       <c r="F254" s="7">
         <v>321</v>
@@ -9496,10 +9529,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I254" s="7">
-        <v>347</v>
+        <v>351</v>
       </c>
       <c t="s" r="J254" s="7">
-        <v>348</v>
+        <v>352</v>
       </c>
       <c r="K254" s="7"/>
       <c r="L254" s="7"/>
@@ -9532,7 +9565,7 @@
       </c>
       <c r="D256" s="7"/>
       <c t="s" r="E256" s="7">
-        <v>349</v>
+        <v>353</v>
       </c>
       <c r="F256" s="7">
         <v>321</v>
@@ -9547,12 +9580,12 @@
         <v>116</v>
       </c>
       <c t="s" r="J256" s="7">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="K256" s="7"/>
       <c r="L256" s="7"/>
       <c t="s" r="M256" s="7">
-        <v>350</v>
+        <v>354</v>
       </c>
     </row>
     <row r="257" ht="14.25" customHeight="1">
@@ -9567,7 +9600,7 @@
       </c>
       <c r="D257" s="7"/>
       <c t="s" r="E257" s="7">
-        <v>349</v>
+        <v>353</v>
       </c>
       <c r="F257" s="7">
         <v>321</v>
@@ -9582,12 +9615,12 @@
         <v>96</v>
       </c>
       <c t="s" r="J257" s="7">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="K257" s="7"/>
       <c r="L257" s="7"/>
       <c t="s" r="M257" s="7">
-        <v>351</v>
+        <v>355</v>
       </c>
     </row>
     <row r="258" ht="14.25" customHeight="1">
@@ -9602,7 +9635,7 @@
       </c>
       <c r="D258" s="7"/>
       <c t="s" r="E258" s="7">
-        <v>349</v>
+        <v>353</v>
       </c>
       <c r="F258" s="7">
         <v>321</v>
@@ -9614,14 +9647,16 @@
         <v>17</v>
       </c>
       <c t="s" r="I258" s="7">
-        <v>340</v>
+        <v>344</v>
       </c>
       <c t="s" r="J258" s="7">
         <v>89</v>
       </c>
       <c r="K258" s="7"/>
       <c r="L258" s="7"/>
-      <c r="M258" s="7"/>
+      <c t="s" r="M258" s="7">
+        <v>356</v>
+      </c>
     </row>
     <row r="259" ht="14.25" customHeight="1">
       <c t="s" r="A259" s="6">
@@ -9635,7 +9670,7 @@
       </c>
       <c r="D259" s="7"/>
       <c t="s" r="E259" s="7">
-        <v>349</v>
+        <v>353</v>
       </c>
       <c r="F259" s="7">
         <v>321</v>
@@ -9647,10 +9682,10 @@
         <v>43</v>
       </c>
       <c t="s" r="I259" s="7">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c t="s" r="J259" s="7">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="K259" s="7"/>
       <c r="L259" s="7"/>
@@ -9668,7 +9703,7 @@
       </c>
       <c r="D260" s="7"/>
       <c t="s" r="E260" s="7">
-        <v>349</v>
+        <v>353</v>
       </c>
       <c r="F260" s="7">
         <v>321</v>
@@ -9677,10 +9712,10 @@
         <v>43</v>
       </c>
       <c t="s" r="H260" s="8">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c t="s" r="I260" s="7">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c t="s" r="J260" s="7">
         <v>112</v>
@@ -9701,19 +9736,19 @@
       </c>
       <c r="D261" s="7"/>
       <c t="s" r="E261" s="7">
-        <v>349</v>
+        <v>353</v>
       </c>
       <c r="F261" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G261" s="8">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c t="s" r="H261" s="8">
         <v>43</v>
       </c>
       <c t="s" r="I261" s="7">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c t="s" r="J261" s="7">
         <v>127</v>
@@ -9734,7 +9769,7 @@
       </c>
       <c r="D262" s="7"/>
       <c t="s" r="E262" s="7">
-        <v>349</v>
+        <v>353</v>
       </c>
       <c r="F262" s="7">
         <v>321</v>
@@ -9746,10 +9781,10 @@
         <v>98</v>
       </c>
       <c t="s" r="I262" s="7">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c t="s" r="J262" s="7">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="K262" s="7"/>
       <c r="L262" s="7"/>
@@ -9767,7 +9802,7 @@
       </c>
       <c r="D263" s="7"/>
       <c t="s" r="E263" s="7">
-        <v>349</v>
+        <v>353</v>
       </c>
       <c r="F263" s="7">
         <v>321</v>
@@ -9779,7 +9814,7 @@
         <v>43</v>
       </c>
       <c t="s" r="I263" s="7">
-        <v>352</v>
+        <v>357</v>
       </c>
       <c t="s" r="J263" s="7">
         <v>114</v>
@@ -9815,7 +9850,7 @@
       </c>
       <c r="D265" s="7"/>
       <c t="s" r="E265" s="7">
-        <v>353</v>
+        <v>358</v>
       </c>
       <c r="F265" s="7">
         <v>321</v>
@@ -9830,12 +9865,12 @@
         <v>120</v>
       </c>
       <c t="s" r="J265" s="7">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="K265" s="7"/>
       <c r="L265" s="7"/>
       <c t="s" r="M265" s="7">
-        <v>354</v>
+        <v>359</v>
       </c>
     </row>
     <row r="266" ht="14.25" customHeight="1">
@@ -9850,7 +9885,7 @@
       </c>
       <c r="D266" s="7"/>
       <c t="s" r="E266" s="7">
-        <v>353</v>
+        <v>358</v>
       </c>
       <c r="F266" s="7">
         <v>321</v>
@@ -9859,7 +9894,7 @@
         <v>17</v>
       </c>
       <c t="s" r="H266" s="8">
-        <v>355</v>
+        <v>360</v>
       </c>
       <c t="s" r="I266" s="7">
         <v>132</v>
@@ -9883,22 +9918,22 @@
       </c>
       <c r="D267" s="7"/>
       <c t="s" r="E267" s="7">
-        <v>353</v>
+        <v>358</v>
       </c>
       <c r="F267" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G267" s="8">
-        <v>355</v>
+        <v>360</v>
       </c>
       <c t="s" r="H267" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I267" s="7">
-        <v>356</v>
+        <v>361</v>
       </c>
       <c t="s" r="J267" s="7">
-        <v>357</v>
+        <v>362</v>
       </c>
       <c r="K267" s="7"/>
       <c r="L267" s="7"/>
@@ -9931,7 +9966,7 @@
       </c>
       <c r="D269" s="7"/>
       <c t="s" r="E269" s="7">
-        <v>358</v>
+        <v>363</v>
       </c>
       <c r="F269" s="7">
         <v>321</v>
@@ -9940,7 +9975,7 @@
         <v>43</v>
       </c>
       <c t="s" r="H269" s="8">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c t="s" r="I269" s="7">
         <v>51</v>
@@ -9966,19 +10001,19 @@
       </c>
       <c r="D270" s="7"/>
       <c t="s" r="E270" s="7">
-        <v>358</v>
+        <v>363</v>
       </c>
       <c r="F270" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G270" s="8">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c t="s" r="H270" s="8">
         <v>43</v>
       </c>
       <c t="s" r="I270" s="7">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c t="s" r="J270" s="7">
         <v>74</v>
@@ -9986,7 +10021,7 @@
       <c r="K270" s="7"/>
       <c r="L270" s="7"/>
       <c t="s" r="M270" s="7">
-        <v>359</v>
+        <v>364</v>
       </c>
     </row>
     <row r="271" ht="14.25" customHeight="1">
@@ -10001,7 +10036,7 @@
       </c>
       <c r="D271" s="7"/>
       <c t="s" r="E271" s="7">
-        <v>358</v>
+        <v>363</v>
       </c>
       <c r="F271" s="7">
         <v>321</v>
@@ -10013,10 +10048,10 @@
         <v>21</v>
       </c>
       <c t="s" r="I271" s="7">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c t="s" r="J271" s="7">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="K271" s="7"/>
       <c r="L271" s="7"/>
@@ -10034,7 +10069,7 @@
       </c>
       <c r="D272" s="7"/>
       <c t="s" r="E272" s="7">
-        <v>358</v>
+        <v>363</v>
       </c>
       <c r="F272" s="7">
         <v>321</v>
@@ -10067,7 +10102,7 @@
       </c>
       <c r="D273" s="7"/>
       <c t="s" r="E273" s="7">
-        <v>358</v>
+        <v>363</v>
       </c>
       <c r="F273" s="7">
         <v>321</v>
@@ -10082,7 +10117,7 @@
         <v>24</v>
       </c>
       <c t="s" r="J273" s="7">
-        <v>360</v>
+        <v>365</v>
       </c>
       <c r="K273" s="7"/>
       <c r="L273" s="7"/>
@@ -10100,7 +10135,7 @@
       </c>
       <c r="D274" s="7"/>
       <c t="s" r="E274" s="7">
-        <v>358</v>
+        <v>363</v>
       </c>
       <c r="F274" s="7">
         <v>321</v>
@@ -10115,7 +10150,7 @@
         <v>80</v>
       </c>
       <c t="s" r="J274" s="7">
-        <v>361</v>
+        <v>366</v>
       </c>
       <c r="K274" s="7"/>
       <c r="L274" s="7"/>
@@ -10133,7 +10168,7 @@
       </c>
       <c r="D275" s="7"/>
       <c t="s" r="E275" s="7">
-        <v>358</v>
+        <v>363</v>
       </c>
       <c r="F275" s="7">
         <v>321</v>
@@ -10142,10 +10177,10 @@
         <v>43</v>
       </c>
       <c t="s" r="H275" s="8">
-        <v>362</v>
+        <v>367</v>
       </c>
       <c t="s" r="I275" s="7">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c t="s" r="J275" s="7">
         <v>60</v>
@@ -10166,22 +10201,22 @@
       </c>
       <c r="D276" s="7"/>
       <c t="s" r="E276" s="7">
-        <v>358</v>
+        <v>363</v>
       </c>
       <c r="F276" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G276" s="8">
-        <v>362</v>
+        <v>367</v>
       </c>
       <c t="s" r="H276" s="8">
         <v>43</v>
       </c>
       <c t="s" r="I276" s="7">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c t="s" r="J276" s="7">
-        <v>363</v>
+        <v>368</v>
       </c>
       <c r="K276" s="7"/>
       <c r="L276" s="7"/>
@@ -10214,7 +10249,7 @@
       </c>
       <c r="D278" s="7"/>
       <c t="s" r="E278" s="7">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="F278" s="7">
         <v>320</v>
@@ -10226,7 +10261,7 @@
         <v>118</v>
       </c>
       <c t="s" r="I278" s="7">
-        <v>333</v>
+        <v>337</v>
       </c>
       <c t="s" r="J278" s="7">
         <v>143</v>
@@ -10247,7 +10282,7 @@
       </c>
       <c r="D279" s="7"/>
       <c t="s" r="E279" s="7">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="F279" s="7">
         <v>320</v>
@@ -10259,10 +10294,10 @@
         <v>98</v>
       </c>
       <c t="s" r="I279" s="7">
-        <v>354</v>
+        <v>359</v>
       </c>
       <c t="s" r="J279" s="7">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="K279" s="7"/>
       <c r="L279" s="7"/>
@@ -10295,19 +10330,19 @@
       </c>
       <c r="D281" s="7"/>
       <c t="s" r="E281" s="7">
-        <v>365</v>
+        <v>370</v>
       </c>
       <c r="F281" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G281" s="8">
-        <v>339</v>
+        <v>343</v>
       </c>
       <c t="s" r="H281" s="8">
         <v>124</v>
       </c>
       <c t="s" r="I281" s="7">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c t="s" r="J281" s="7">
         <v>35</v>
@@ -10345,7 +10380,7 @@
       </c>
       <c r="D283" s="7"/>
       <c t="s" r="E283" s="7">
-        <v>366</v>
+        <v>371</v>
       </c>
       <c r="F283" s="7">
         <v>320</v>
@@ -10357,7 +10392,7 @@
         <v>43</v>
       </c>
       <c t="s" r="I283" s="7">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c t="s" r="J283" s="7">
         <v>51</v>
@@ -10365,7 +10400,7 @@
       <c r="K283" s="7"/>
       <c r="L283" s="7"/>
       <c t="s" r="M283" s="7">
-        <v>367</v>
+        <v>372</v>
       </c>
     </row>
     <row r="284" ht="14.25" customHeight="1">
@@ -10380,7 +10415,7 @@
       </c>
       <c r="D284" s="7"/>
       <c t="s" r="E284" s="7">
-        <v>366</v>
+        <v>371</v>
       </c>
       <c r="F284" s="7">
         <v>320</v>
@@ -10389,13 +10424,13 @@
         <v>43</v>
       </c>
       <c t="s" r="H284" s="8">
-        <v>368</v>
+        <v>373</v>
       </c>
       <c t="s" r="I284" s="7">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c t="s" r="J284" s="7">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="K284" s="7"/>
       <c r="L284" s="7"/>
@@ -10413,13 +10448,13 @@
       </c>
       <c r="D285" s="7"/>
       <c t="s" r="E285" s="7">
-        <v>366</v>
+        <v>371</v>
       </c>
       <c r="F285" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G285" s="8">
-        <v>368</v>
+        <v>373</v>
       </c>
       <c t="s" r="H285" s="8">
         <v>43</v>
@@ -10428,7 +10463,7 @@
         <v>70</v>
       </c>
       <c t="s" r="J285" s="7">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="K285" s="7"/>
       <c r="L285" s="7"/>
@@ -10446,7 +10481,7 @@
       </c>
       <c r="D286" s="7"/>
       <c t="s" r="E286" s="7">
-        <v>366</v>
+        <v>371</v>
       </c>
       <c r="F286" s="7">
         <v>320</v>
@@ -10455,13 +10490,13 @@
         <v>43</v>
       </c>
       <c t="s" r="H286" s="8">
-        <v>369</v>
+        <v>374</v>
       </c>
       <c t="s" r="I286" s="7">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c t="s" r="J286" s="7">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="K286" s="7"/>
       <c r="L286" s="7"/>
@@ -10479,13 +10514,13 @@
       </c>
       <c r="D287" s="7"/>
       <c t="s" r="E287" s="7">
-        <v>366</v>
+        <v>371</v>
       </c>
       <c r="F287" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G287" s="8">
-        <v>369</v>
+        <v>374</v>
       </c>
       <c t="s" r="H287" s="8">
         <v>43</v>
@@ -10494,7 +10529,7 @@
         <v>146</v>
       </c>
       <c t="s" r="J287" s="7">
-        <v>370</v>
+        <v>375</v>
       </c>
       <c r="K287" s="7"/>
       <c r="L287" s="7"/>
@@ -10527,7 +10562,7 @@
       </c>
       <c r="D289" s="7"/>
       <c t="s" r="E289" s="7">
-        <v>371</v>
+        <v>376</v>
       </c>
       <c r="F289" s="7">
         <v>321</v>
@@ -10536,10 +10571,10 @@
         <v>43</v>
       </c>
       <c t="s" r="H289" s="8">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c t="s" r="I289" s="7">
-        <v>372</v>
+        <v>377</v>
       </c>
       <c t="s" r="J289" s="7">
         <v>89</v>
@@ -10547,7 +10582,7 @@
       <c r="K289" s="7"/>
       <c r="L289" s="7"/>
       <c t="s" r="M289" s="7">
-        <v>373</v>
+        <v>378</v>
       </c>
     </row>
     <row r="290" ht="15" customHeight="1">
@@ -10562,13 +10597,13 @@
       </c>
       <c r="D290" s="7"/>
       <c t="s" r="E290" s="7">
-        <v>371</v>
+        <v>376</v>
       </c>
       <c r="F290" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G290" s="8">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c t="s" r="H290" s="8">
         <v>43</v>
@@ -10577,12 +10612,12 @@
         <v>110</v>
       </c>
       <c t="s" r="J290" s="7">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="K290" s="7"/>
       <c r="L290" s="7"/>
       <c t="s" r="M290" s="7">
-        <v>374</v>
+        <v>379</v>
       </c>
     </row>
     <row r="291" ht="14.25" customHeight="1">
@@ -10597,7 +10632,7 @@
       </c>
       <c r="D291" s="7"/>
       <c t="s" r="E291" s="7">
-        <v>371</v>
+        <v>376</v>
       </c>
       <c r="F291" s="7">
         <v>321</v>
@@ -10606,13 +10641,13 @@
         <v>43</v>
       </c>
       <c t="s" r="H291" s="8">
-        <v>375</v>
+        <v>380</v>
       </c>
       <c t="s" r="I291" s="7">
         <v>153</v>
       </c>
       <c t="s" r="J291" s="7">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="K291" s="7"/>
       <c r="L291" s="7"/>
@@ -10630,19 +10665,19 @@
       </c>
       <c r="D292" s="7"/>
       <c t="s" r="E292" s="7">
-        <v>371</v>
+        <v>376</v>
       </c>
       <c r="F292" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G292" s="8">
-        <v>375</v>
+        <v>380</v>
       </c>
       <c t="s" r="H292" s="8">
         <v>43</v>
       </c>
       <c t="s" r="I292" s="7">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c t="s" r="J292" s="7">
         <v>107</v>
@@ -10678,7 +10713,7 @@
       </c>
       <c r="D294" s="7"/>
       <c t="s" r="E294" s="7">
-        <v>376</v>
+        <v>381</v>
       </c>
       <c r="F294" s="7">
         <v>320</v>
@@ -10690,10 +10725,10 @@
         <v>152</v>
       </c>
       <c t="s" r="I294" s="7">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c t="s" r="J294" s="7">
-        <v>354</v>
+        <v>359</v>
       </c>
       <c r="K294" s="7"/>
       <c r="L294" s="7"/>
@@ -10711,7 +10746,7 @@
       </c>
       <c r="D295" s="7"/>
       <c t="s" r="E295" s="7">
-        <v>376</v>
+        <v>381</v>
       </c>
       <c r="F295" s="7">
         <v>320</v>
@@ -10723,7 +10758,7 @@
         <v>98</v>
       </c>
       <c t="s" r="I295" s="7">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c t="s" r="J295" s="7">
         <v>23</v>
@@ -10759,7 +10794,7 @@
       </c>
       <c r="D297" s="7"/>
       <c t="s" r="E297" s="7">
-        <v>377</v>
+        <v>382</v>
       </c>
       <c r="F297" s="7">
         <v>320</v>
@@ -10768,18 +10803,18 @@
         <v>17</v>
       </c>
       <c t="s" r="H297" s="8">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c t="s" r="I297" s="7">
         <v>97</v>
       </c>
       <c t="s" r="J297" s="7">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="K297" s="7"/>
       <c r="L297" s="7"/>
       <c t="s" r="M297" s="7">
-        <v>183</v>
+        <v>184</v>
       </c>
     </row>
     <row r="298" ht="14.25" customHeight="1">
@@ -10794,13 +10829,13 @@
       </c>
       <c r="D298" s="7"/>
       <c t="s" r="E298" s="7">
-        <v>377</v>
+        <v>382</v>
       </c>
       <c r="F298" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G298" s="8">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c t="s" r="H298" s="8">
         <v>17</v>
@@ -10827,7 +10862,7 @@
       </c>
       <c r="D299" s="7"/>
       <c t="s" r="E299" s="7">
-        <v>377</v>
+        <v>382</v>
       </c>
       <c r="F299" s="7">
         <v>320</v>
@@ -10860,7 +10895,7 @@
       </c>
       <c r="D300" s="7"/>
       <c t="s" r="E300" s="7">
-        <v>377</v>
+        <v>382</v>
       </c>
       <c r="F300" s="7">
         <v>320</v>
@@ -10872,7 +10907,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I300" s="7">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c t="s" r="J300" s="7">
         <v>23</v>
@@ -10893,7 +10928,7 @@
       </c>
       <c r="D301" s="7"/>
       <c t="s" r="E301" s="7">
-        <v>377</v>
+        <v>382</v>
       </c>
       <c r="F301" s="7">
         <v>320</v>
@@ -10902,13 +10937,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H301" s="8">
-        <v>378</v>
+        <v>383</v>
       </c>
       <c t="s" r="I301" s="7">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c t="s" r="J301" s="7">
-        <v>360</v>
+        <v>365</v>
       </c>
       <c r="K301" s="7"/>
       <c r="L301" s="7"/>
@@ -10926,13 +10961,13 @@
       </c>
       <c r="D302" s="7"/>
       <c t="s" r="E302" s="7">
-        <v>377</v>
+        <v>382</v>
       </c>
       <c r="F302" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G302" s="8">
-        <v>378</v>
+        <v>383</v>
       </c>
       <c t="s" r="H302" s="8">
         <v>17</v>
@@ -10941,7 +10976,7 @@
         <v>80</v>
       </c>
       <c t="s" r="J302" s="7">
-        <v>342</v>
+        <v>346</v>
       </c>
       <c r="K302" s="7"/>
       <c r="L302" s="7"/>
@@ -10974,27 +11009,27 @@
       </c>
       <c r="D304" s="7"/>
       <c t="s" r="E304" s="7">
-        <v>379</v>
+        <v>384</v>
       </c>
       <c r="F304" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G304" s="8">
-        <v>339</v>
+        <v>343</v>
       </c>
       <c t="s" r="H304" s="8">
         <v>98</v>
       </c>
       <c t="s" r="I304" s="7">
-        <v>380</v>
+        <v>385</v>
       </c>
       <c t="s" r="J304" s="7">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="K304" s="7"/>
       <c r="L304" s="7"/>
       <c t="s" r="M304" s="7">
-        <v>381</v>
+        <v>386</v>
       </c>
     </row>
     <row r="305" ht="15" customHeight="1">
@@ -11009,7 +11044,7 @@
       </c>
       <c r="D305" s="7"/>
       <c t="s" r="E305" s="7">
-        <v>379</v>
+        <v>384</v>
       </c>
       <c r="F305" s="7">
         <v>321</v>
@@ -11024,7 +11059,7 @@
         <v>107</v>
       </c>
       <c t="s" r="J305" s="7">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="K305" s="7"/>
       <c r="L305" s="7"/>
@@ -11042,7 +11077,7 @@
       </c>
       <c r="D306" s="7"/>
       <c t="s" r="E306" s="7">
-        <v>379</v>
+        <v>384</v>
       </c>
       <c r="F306" s="7">
         <v>321</v>
@@ -11051,10 +11086,10 @@
         <v>17</v>
       </c>
       <c t="s" r="H306" s="8">
-        <v>339</v>
+        <v>343</v>
       </c>
       <c t="s" r="I306" s="7">
-        <v>382</v>
+        <v>387</v>
       </c>
       <c t="s" r="J306" s="7">
         <v>31</v>
@@ -11090,7 +11125,7 @@
       </c>
       <c r="D308" s="7"/>
       <c t="s" r="E308" s="7">
-        <v>383</v>
+        <v>388</v>
       </c>
       <c r="F308" s="7">
         <v>320</v>
@@ -11110,7 +11145,7 @@
       <c r="K308" s="7"/>
       <c r="L308" s="7"/>
       <c t="s" r="M308" s="7">
-        <v>384</v>
+        <v>389</v>
       </c>
     </row>
     <row r="309" ht="14.25" customHeight="1">
@@ -11125,7 +11160,7 @@
       </c>
       <c r="D309" s="7"/>
       <c t="s" r="E309" s="7">
-        <v>383</v>
+        <v>388</v>
       </c>
       <c r="F309" s="7">
         <v>320</v>
@@ -11158,7 +11193,7 @@
       </c>
       <c r="D310" s="7"/>
       <c t="s" r="E310" s="7">
-        <v>383</v>
+        <v>388</v>
       </c>
       <c r="F310" s="7">
         <v>320</v>
@@ -11173,7 +11208,7 @@
         <v>103</v>
       </c>
       <c t="s" r="J310" s="7">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="K310" s="7"/>
       <c r="L310" s="7"/>
@@ -11191,7 +11226,7 @@
       </c>
       <c r="D311" s="7"/>
       <c t="s" r="E311" s="7">
-        <v>383</v>
+        <v>388</v>
       </c>
       <c r="F311" s="7">
         <v>320</v>
@@ -11224,7 +11259,7 @@
       </c>
       <c r="D312" s="7"/>
       <c t="s" r="E312" s="7">
-        <v>383</v>
+        <v>388</v>
       </c>
       <c r="F312" s="7">
         <v>320</v>
@@ -11239,7 +11274,7 @@
         <v>106</v>
       </c>
       <c t="s" r="J312" s="7">
-        <v>361</v>
+        <v>366</v>
       </c>
       <c r="K312" s="7"/>
       <c r="L312" s="7"/>
@@ -11257,7 +11292,7 @@
       </c>
       <c r="D313" s="7"/>
       <c t="s" r="E313" s="7">
-        <v>383</v>
+        <v>388</v>
       </c>
       <c r="F313" s="7">
         <v>320</v>
@@ -11269,7 +11304,7 @@
         <v>43</v>
       </c>
       <c t="s" r="I313" s="7">
-        <v>385</v>
+        <v>390</v>
       </c>
       <c t="s" r="J313" s="7">
         <v>93</v>
@@ -11305,7 +11340,7 @@
       </c>
       <c r="D315" s="7"/>
       <c t="s" r="E315" s="7">
-        <v>386</v>
+        <v>391</v>
       </c>
       <c r="F315" s="7">
         <v>321</v>
@@ -11340,7 +11375,7 @@
       </c>
       <c r="D316" s="7"/>
       <c t="s" r="E316" s="7">
-        <v>386</v>
+        <v>391</v>
       </c>
       <c r="F316" s="7">
         <v>321</v>
@@ -11352,7 +11387,7 @@
         <v>43</v>
       </c>
       <c t="s" r="I316" s="7">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c t="s" r="J316" s="7">
         <v>141</v>
@@ -11373,7 +11408,7 @@
       </c>
       <c r="D317" s="7"/>
       <c t="s" r="E317" s="7">
-        <v>386</v>
+        <v>391</v>
       </c>
       <c r="F317" s="7">
         <v>321</v>
@@ -11385,7 +11420,7 @@
         <v>124</v>
       </c>
       <c t="s" r="I317" s="7">
-        <v>387</v>
+        <v>392</v>
       </c>
       <c t="s" r="J317" s="7">
         <v>19</v>
@@ -11406,7 +11441,7 @@
       </c>
       <c r="D318" s="7"/>
       <c t="s" r="E318" s="7">
-        <v>386</v>
+        <v>391</v>
       </c>
       <c r="F318" s="7">
         <v>321</v>
@@ -11418,7 +11453,7 @@
         <v>43</v>
       </c>
       <c t="s" r="I318" s="7">
-        <v>334</v>
+        <v>338</v>
       </c>
       <c t="s" r="J318" s="7">
         <v>79</v>
@@ -11439,7 +11474,7 @@
       </c>
       <c r="D319" s="7"/>
       <c t="s" r="E319" s="7">
-        <v>386</v>
+        <v>391</v>
       </c>
       <c r="F319" s="7">
         <v>321</v>
@@ -11472,7 +11507,7 @@
       </c>
       <c r="D320" s="7"/>
       <c t="s" r="E320" s="7">
-        <v>386</v>
+        <v>391</v>
       </c>
       <c r="F320" s="7">
         <v>321</v>
@@ -11481,13 +11516,13 @@
         <v>21</v>
       </c>
       <c t="s" r="H320" s="8">
-        <v>339</v>
+        <v>343</v>
       </c>
       <c t="s" r="I320" s="7">
-        <v>388</v>
+        <v>393</v>
       </c>
       <c t="s" r="J320" s="7">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="K320" s="7"/>
       <c r="L320" s="7"/>
@@ -11520,7 +11555,7 @@
       </c>
       <c r="D322" s="7"/>
       <c t="s" r="E322" s="7">
-        <v>389</v>
+        <v>394</v>
       </c>
       <c r="F322" s="7">
         <v>320</v>
@@ -11532,7 +11567,7 @@
         <v>43</v>
       </c>
       <c t="s" r="I322" s="7">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c t="s" r="J322" s="7">
         <v>86</v>
@@ -11540,7 +11575,7 @@
       <c r="K322" s="7"/>
       <c r="L322" s="7"/>
       <c t="s" r="M322" s="7">
-        <v>390</v>
+        <v>395</v>
       </c>
     </row>
     <row r="323" ht="14.25" customHeight="1">
@@ -11555,7 +11590,7 @@
       </c>
       <c r="D323" s="7"/>
       <c t="s" r="E323" s="7">
-        <v>389</v>
+        <v>394</v>
       </c>
       <c r="F323" s="7">
         <v>320</v>
@@ -11567,7 +11602,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I323" s="7">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c t="s" r="J323" s="7">
         <v>141</v>
@@ -11575,7 +11610,7 @@
       <c r="K323" s="7"/>
       <c r="L323" s="7"/>
       <c t="s" r="M323" s="7">
-        <v>391</v>
+        <v>396</v>
       </c>
     </row>
     <row r="324" ht="14.25" customHeight="1">
@@ -11590,7 +11625,7 @@
       </c>
       <c r="D324" s="7"/>
       <c t="s" r="E324" s="7">
-        <v>389</v>
+        <v>394</v>
       </c>
       <c r="F324" s="7">
         <v>320</v>
@@ -11602,7 +11637,7 @@
         <v>171</v>
       </c>
       <c t="s" r="I324" s="7">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c t="s" r="J324" s="7">
         <v>123</v>
@@ -11623,7 +11658,7 @@
       </c>
       <c r="D325" s="7"/>
       <c t="s" r="E325" s="7">
-        <v>389</v>
+        <v>394</v>
       </c>
       <c r="F325" s="7">
         <v>320</v>
@@ -11635,10 +11670,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I325" s="7">
-        <v>392</v>
+        <v>397</v>
       </c>
       <c t="s" r="J325" s="7">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="K325" s="7"/>
       <c r="L325" s="7"/>
@@ -11656,7 +11691,7 @@
       </c>
       <c r="D326" s="7"/>
       <c t="s" r="E326" s="7">
-        <v>389</v>
+        <v>394</v>
       </c>
       <c r="F326" s="7">
         <v>320</v>
@@ -11665,10 +11700,10 @@
         <v>17</v>
       </c>
       <c t="s" r="H326" s="8">
-        <v>393</v>
+        <v>398</v>
       </c>
       <c t="s" r="I326" s="7">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c t="s" r="J326" s="7">
         <v>80</v>
@@ -11689,19 +11724,19 @@
       </c>
       <c r="D327" s="7"/>
       <c t="s" r="E327" s="7">
-        <v>389</v>
+        <v>394</v>
       </c>
       <c r="F327" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G327" s="8">
-        <v>393</v>
+        <v>398</v>
       </c>
       <c t="s" r="H327" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I327" s="7">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c t="s" r="J327" s="7">
         <v>162</v>
@@ -11737,7 +11772,7 @@
       </c>
       <c r="D329" s="7"/>
       <c t="s" r="E329" s="7">
-        <v>394</v>
+        <v>399</v>
       </c>
       <c r="F329" s="7">
         <v>320</v>
@@ -11757,7 +11792,7 @@
       <c r="K329" s="7"/>
       <c r="L329" s="7"/>
       <c t="s" r="M329" s="7">
-        <v>395</v>
+        <v>400</v>
       </c>
     </row>
     <row r="330" ht="15" customHeight="1">
@@ -11772,7 +11807,7 @@
       </c>
       <c r="D330" s="7"/>
       <c t="s" r="E330" s="7">
-        <v>394</v>
+        <v>399</v>
       </c>
       <c r="F330" s="7">
         <v>320</v>
@@ -11787,12 +11822,12 @@
         <v>148</v>
       </c>
       <c t="s" r="J330" s="7">
-        <v>396</v>
+        <v>401</v>
       </c>
       <c r="K330" s="7"/>
       <c r="L330" s="7"/>
       <c t="s" r="M330" s="7">
-        <v>397</v>
+        <v>402</v>
       </c>
     </row>
     <row r="331" ht="14.25" customHeight="1">
@@ -11807,7 +11842,7 @@
       </c>
       <c r="D331" s="7"/>
       <c t="s" r="E331" s="7">
-        <v>394</v>
+        <v>399</v>
       </c>
       <c r="F331" s="7">
         <v>320</v>
@@ -11819,7 +11854,7 @@
         <v>124</v>
       </c>
       <c t="s" r="I331" s="7">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c t="s" r="J331" s="7">
         <v>35</v>
@@ -11840,7 +11875,7 @@
       </c>
       <c r="D332" s="7"/>
       <c t="s" r="E332" s="7">
-        <v>394</v>
+        <v>399</v>
       </c>
       <c r="F332" s="7">
         <v>320</v>
@@ -11873,7 +11908,7 @@
       </c>
       <c r="D333" s="7"/>
       <c t="s" r="E333" s="7">
-        <v>394</v>
+        <v>399</v>
       </c>
       <c r="F333" s="7">
         <v>320</v>
@@ -11888,7 +11923,7 @@
         <v>91</v>
       </c>
       <c t="s" r="J333" s="7">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="K333" s="7"/>
       <c r="L333" s="7"/>
@@ -11906,7 +11941,7 @@
       </c>
       <c r="D334" s="7"/>
       <c t="s" r="E334" s="7">
-        <v>394</v>
+        <v>399</v>
       </c>
       <c r="F334" s="7">
         <v>320</v>
@@ -11918,7 +11953,7 @@
         <v>43</v>
       </c>
       <c t="s" r="I334" s="7">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c t="s" r="J334" s="7">
         <v>80</v>
@@ -11939,7 +11974,7 @@
       </c>
       <c r="D335" s="7"/>
       <c t="s" r="E335" s="7">
-        <v>394</v>
+        <v>399</v>
       </c>
       <c r="F335" s="7">
         <v>320</v>
@@ -11948,13 +11983,13 @@
         <v>43</v>
       </c>
       <c t="s" r="H335" s="8">
-        <v>398</v>
+        <v>403</v>
       </c>
       <c t="s" r="I335" s="7">
-        <v>352</v>
+        <v>357</v>
       </c>
       <c t="s" r="J335" s="7">
-        <v>399</v>
+        <v>404</v>
       </c>
       <c r="K335" s="7"/>
       <c r="L335" s="7"/>
@@ -11972,22 +12007,22 @@
       </c>
       <c r="D336" s="7"/>
       <c t="s" r="E336" s="7">
-        <v>394</v>
+        <v>399</v>
       </c>
       <c r="F336" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G336" s="8">
-        <v>398</v>
+        <v>403</v>
       </c>
       <c t="s" r="H336" s="8">
         <v>43</v>
       </c>
       <c t="s" r="I336" s="7">
-        <v>400</v>
+        <v>405</v>
       </c>
       <c t="s" r="J336" s="7">
-        <v>401</v>
+        <v>406</v>
       </c>
       <c r="K336" s="7"/>
       <c r="L336" s="7"/>
@@ -12020,7 +12055,7 @@
       </c>
       <c r="D338" s="7"/>
       <c t="s" r="E338" s="7">
-        <v>402</v>
+        <v>407</v>
       </c>
       <c r="F338" s="7">
         <v>321</v>
@@ -12032,7 +12067,7 @@
         <v>98</v>
       </c>
       <c t="s" r="I338" s="7">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c t="s" r="J338" s="7">
         <v>40</v>
@@ -12040,7 +12075,7 @@
       <c r="K338" s="7"/>
       <c r="L338" s="7"/>
       <c t="s" r="M338" s="7">
-        <v>332</v>
+        <v>336</v>
       </c>
     </row>
     <row r="339" ht="14.25" customHeight="1">
@@ -12055,7 +12090,7 @@
       </c>
       <c r="D339" s="7"/>
       <c t="s" r="E339" s="7">
-        <v>402</v>
+        <v>407</v>
       </c>
       <c r="F339" s="7">
         <v>321</v>
@@ -12067,7 +12102,7 @@
         <v>68</v>
       </c>
       <c t="s" r="I339" s="7">
-        <v>387</v>
+        <v>392</v>
       </c>
       <c t="s" r="J339" s="7">
         <v>23</v>
@@ -12088,7 +12123,7 @@
       </c>
       <c r="D340" s="7"/>
       <c t="s" r="E340" s="7">
-        <v>402</v>
+        <v>407</v>
       </c>
       <c r="F340" s="7">
         <v>321</v>
@@ -12100,10 +12135,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I340" s="7">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c t="s" r="J340" s="7">
-        <v>267</v>
+        <v>311</v>
       </c>
       <c r="K340" s="7"/>
       <c r="L340" s="7"/>
@@ -12121,7 +12156,7 @@
       </c>
       <c r="D341" s="7"/>
       <c t="s" r="E341" s="7">
-        <v>402</v>
+        <v>407</v>
       </c>
       <c r="F341" s="7">
         <v>321</v>
@@ -12130,13 +12165,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H341" s="8">
-        <v>362</v>
+        <v>367</v>
       </c>
       <c t="s" r="I341" s="7">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c t="s" r="J341" s="7">
-        <v>403</v>
+        <v>408</v>
       </c>
       <c r="K341" s="7"/>
       <c r="L341" s="7"/>
@@ -12154,22 +12189,22 @@
       </c>
       <c r="D342" s="7"/>
       <c t="s" r="E342" s="7">
-        <v>402</v>
+        <v>407</v>
       </c>
       <c r="F342" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G342" s="8">
-        <v>362</v>
+        <v>367</v>
       </c>
       <c t="s" r="H342" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I342" s="7">
-        <v>404</v>
+        <v>409</v>
       </c>
       <c t="s" r="J342" s="7">
-        <v>405</v>
+        <v>410</v>
       </c>
       <c r="K342" s="7"/>
       <c r="L342" s="7"/>
@@ -12202,13 +12237,13 @@
       </c>
       <c r="D344" s="7"/>
       <c t="s" r="E344" s="7">
-        <v>406</v>
+        <v>411</v>
       </c>
       <c r="F344" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G344" s="8">
-        <v>336</v>
+        <v>340</v>
       </c>
       <c t="s" r="H344" s="8">
         <v>43</v>
@@ -12222,7 +12257,7 @@
       <c r="K344" s="7"/>
       <c r="L344" s="7"/>
       <c t="s" r="M344" s="7">
-        <v>326</v>
+        <v>330</v>
       </c>
     </row>
     <row r="345" ht="15" customHeight="1">
@@ -12237,7 +12272,7 @@
       </c>
       <c r="D345" s="7"/>
       <c t="s" r="E345" s="7">
-        <v>406</v>
+        <v>411</v>
       </c>
       <c r="F345" s="7">
         <v>321</v>
@@ -12270,7 +12305,7 @@
       </c>
       <c r="D346" s="7"/>
       <c t="s" r="E346" s="7">
-        <v>406</v>
+        <v>411</v>
       </c>
       <c r="F346" s="7">
         <v>321</v>
@@ -12282,10 +12317,10 @@
         <v>43</v>
       </c>
       <c t="s" r="I346" s="7">
-        <v>392</v>
+        <v>397</v>
       </c>
       <c t="s" r="J346" s="7">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="K346" s="7"/>
       <c r="L346" s="7"/>
@@ -12303,7 +12338,7 @@
       </c>
       <c r="D347" s="7"/>
       <c t="s" r="E347" s="7">
-        <v>406</v>
+        <v>411</v>
       </c>
       <c r="F347" s="7">
         <v>321</v>
@@ -12315,10 +12350,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I347" s="7">
-        <v>407</v>
+        <v>412</v>
       </c>
       <c t="s" r="J347" s="7">
-        <v>352</v>
+        <v>357</v>
       </c>
       <c r="K347" s="7"/>
       <c r="L347" s="7"/>
@@ -12351,7 +12386,7 @@
       </c>
       <c r="D349" s="7"/>
       <c t="s" r="E349" s="7">
-        <v>408</v>
+        <v>413</v>
       </c>
       <c r="F349" s="7">
         <v>321</v>
@@ -12363,7 +12398,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I349" s="7">
-        <v>409</v>
+        <v>414</v>
       </c>
       <c t="s" r="J349" s="7">
         <v>136</v>
@@ -12371,7 +12406,7 @@
       <c r="K349" s="7"/>
       <c r="L349" s="7"/>
       <c t="s" r="M349" s="7">
-        <v>410</v>
+        <v>415</v>
       </c>
     </row>
     <row r="350" ht="15" customHeight="1">
@@ -12386,7 +12421,7 @@
       </c>
       <c r="D350" s="7"/>
       <c t="s" r="E350" s="7">
-        <v>408</v>
+        <v>413</v>
       </c>
       <c r="F350" s="7">
         <v>321</v>
@@ -12398,7 +12433,7 @@
         <v>98</v>
       </c>
       <c t="s" r="I350" s="7">
-        <v>411</v>
+        <v>416</v>
       </c>
       <c t="s" r="J350" s="7">
         <v>99</v>
@@ -12421,7 +12456,7 @@
       </c>
       <c r="D351" s="7"/>
       <c t="s" r="E351" s="7">
-        <v>408</v>
+        <v>413</v>
       </c>
       <c r="F351" s="7">
         <v>321</v>
@@ -12430,10 +12465,10 @@
         <v>98</v>
       </c>
       <c t="s" r="H351" s="8">
-        <v>346</v>
+        <v>350</v>
       </c>
       <c t="s" r="I351" s="7">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c t="s" r="J351" s="7">
         <v>143</v>
@@ -12454,19 +12489,19 @@
       </c>
       <c r="D352" s="7"/>
       <c t="s" r="E352" s="7">
-        <v>408</v>
+        <v>413</v>
       </c>
       <c r="F352" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G352" s="8">
-        <v>346</v>
+        <v>350</v>
       </c>
       <c t="s" r="H352" s="8">
         <v>98</v>
       </c>
       <c t="s" r="I352" s="7">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c t="s" r="J352" s="7">
         <v>91</v>
@@ -12487,7 +12522,7 @@
       </c>
       <c r="D353" s="7"/>
       <c t="s" r="E353" s="7">
-        <v>408</v>
+        <v>413</v>
       </c>
       <c r="F353" s="7">
         <v>321</v>
@@ -12496,13 +12531,13 @@
         <v>98</v>
       </c>
       <c t="s" r="H353" s="8">
-        <v>346</v>
+        <v>350</v>
       </c>
       <c t="s" r="I353" s="7">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c t="s" r="J353" s="7">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="K353" s="7"/>
       <c r="L353" s="7"/>
@@ -12520,19 +12555,19 @@
       </c>
       <c r="D354" s="7"/>
       <c t="s" r="E354" s="7">
-        <v>408</v>
+        <v>413</v>
       </c>
       <c r="F354" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G354" s="8">
-        <v>346</v>
+        <v>350</v>
       </c>
       <c t="s" r="H354" s="8">
         <v>98</v>
       </c>
       <c t="s" r="I354" s="7">
-        <v>412</v>
+        <v>417</v>
       </c>
       <c t="s" r="J354" s="7">
         <v>82</v>
@@ -12553,7 +12588,7 @@
       </c>
       <c r="D355" s="7"/>
       <c t="s" r="E355" s="7">
-        <v>408</v>
+        <v>413</v>
       </c>
       <c r="F355" s="7">
         <v>321</v>
@@ -12565,7 +12600,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I355" s="7">
-        <v>413</v>
+        <v>418</v>
       </c>
       <c t="s" r="J355" s="7">
         <v>116</v>
@@ -12601,7 +12636,7 @@
       </c>
       <c r="D357" s="7"/>
       <c t="s" r="E357" s="7">
-        <v>414</v>
+        <v>419</v>
       </c>
       <c r="F357" s="7">
         <v>321</v>
@@ -12616,12 +12651,12 @@
         <v>51</v>
       </c>
       <c t="s" r="J357" s="7">
-        <v>415</v>
+        <v>420</v>
       </c>
       <c r="K357" s="7"/>
       <c r="L357" s="7"/>
       <c t="s" r="M357" s="7">
-        <v>416</v>
+        <v>421</v>
       </c>
     </row>
     <row r="358" ht="14.25" customHeight="1">
@@ -12636,7 +12671,7 @@
       </c>
       <c r="D358" s="7"/>
       <c t="s" r="E358" s="7">
-        <v>414</v>
+        <v>419</v>
       </c>
       <c r="F358" s="7">
         <v>321</v>
@@ -12648,15 +12683,15 @@
         <v>98</v>
       </c>
       <c t="s" r="I358" s="7">
-        <v>396</v>
+        <v>401</v>
       </c>
       <c t="s" r="J358" s="7">
-        <v>387</v>
+        <v>392</v>
       </c>
       <c r="K358" s="7"/>
       <c r="L358" s="7"/>
       <c t="s" r="M358" s="7">
-        <v>417</v>
+        <v>422</v>
       </c>
     </row>
     <row r="359" ht="14.25" customHeight="1">
@@ -12671,7 +12706,7 @@
       </c>
       <c r="D359" s="7"/>
       <c t="s" r="E359" s="7">
-        <v>414</v>
+        <v>419</v>
       </c>
       <c r="F359" s="7">
         <v>321</v>
@@ -12683,7 +12718,7 @@
         <v>21</v>
       </c>
       <c t="s" r="I359" s="7">
-        <v>418</v>
+        <v>423</v>
       </c>
       <c t="s" r="J359" s="7">
         <v>22</v>
@@ -12704,7 +12739,7 @@
       </c>
       <c r="D360" s="7"/>
       <c t="s" r="E360" s="7">
-        <v>414</v>
+        <v>419</v>
       </c>
       <c r="F360" s="7">
         <v>321</v>
@@ -12719,7 +12754,7 @@
         <v>132</v>
       </c>
       <c t="s" r="J360" s="7">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="K360" s="7"/>
       <c r="L360" s="7"/>
@@ -12752,7 +12787,7 @@
       </c>
       <c r="D362" s="7"/>
       <c t="s" r="E362" s="7">
-        <v>419</v>
+        <v>424</v>
       </c>
       <c r="F362" s="7">
         <v>320</v>
@@ -12761,10 +12796,10 @@
         <v>17</v>
       </c>
       <c t="s" r="H362" s="8">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c t="s" r="I362" s="7">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c t="s" r="J362" s="7">
         <v>96</v>
@@ -12772,7 +12807,7 @@
       <c r="K362" s="7"/>
       <c r="L362" s="7"/>
       <c t="s" r="M362" s="7">
-        <v>420</v>
+        <v>425</v>
       </c>
     </row>
     <row r="363" ht="14.25" customHeight="1">
@@ -12787,13 +12822,13 @@
       </c>
       <c r="D363" s="7"/>
       <c t="s" r="E363" s="7">
-        <v>419</v>
+        <v>424</v>
       </c>
       <c r="F363" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G363" s="8">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c t="s" r="H363" s="8">
         <v>17</v>
@@ -12809,7 +12844,7 @@
       </c>
       <c r="L363" s="7"/>
       <c t="s" r="M363" s="7">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="364" ht="14.25" customHeight="1">
@@ -12824,7 +12859,7 @@
       </c>
       <c r="D364" s="7"/>
       <c t="s" r="E364" s="7">
-        <v>419</v>
+        <v>424</v>
       </c>
       <c r="F364" s="7">
         <v>320</v>
@@ -12833,13 +12868,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H364" s="8">
-        <v>393</v>
+        <v>398</v>
       </c>
       <c t="s" r="I364" s="7">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c t="s" r="J364" s="7">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="K364" s="7"/>
       <c r="L364" s="7"/>
@@ -12857,13 +12892,13 @@
       </c>
       <c r="D365" s="7"/>
       <c t="s" r="E365" s="7">
-        <v>419</v>
+        <v>424</v>
       </c>
       <c r="F365" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G365" s="8">
-        <v>393</v>
+        <v>398</v>
       </c>
       <c t="s" r="H365" s="8">
         <v>17</v>
@@ -12890,7 +12925,7 @@
       </c>
       <c r="D366" s="7"/>
       <c t="s" r="E366" s="7">
-        <v>419</v>
+        <v>424</v>
       </c>
       <c r="F366" s="7">
         <v>320</v>
@@ -12923,7 +12958,7 @@
       </c>
       <c r="D367" s="7"/>
       <c t="s" r="E367" s="7">
-        <v>419</v>
+        <v>424</v>
       </c>
       <c r="F367" s="7">
         <v>320</v>
@@ -12935,10 +12970,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I367" s="7">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c t="s" r="J367" s="7">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="K367" s="7"/>
       <c r="L367" s="7"/>
@@ -12971,7 +13006,7 @@
       </c>
       <c r="D369" s="7"/>
       <c t="s" r="E369" s="7">
-        <v>421</v>
+        <v>426</v>
       </c>
       <c r="F369" s="7">
         <v>321</v>
@@ -12986,7 +13021,7 @@
         <v>55</v>
       </c>
       <c t="s" r="J369" s="7">
-        <v>392</v>
+        <v>397</v>
       </c>
       <c r="K369" s="7"/>
       <c r="L369" s="7"/>
@@ -13004,7 +13039,7 @@
       </c>
       <c r="D370" s="7"/>
       <c t="s" r="E370" s="7">
-        <v>421</v>
+        <v>426</v>
       </c>
       <c r="F370" s="7">
         <v>321</v>
@@ -13016,10 +13051,10 @@
         <v>43</v>
       </c>
       <c t="s" r="I370" s="7">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c t="s" r="J370" s="7">
-        <v>267</v>
+        <v>311</v>
       </c>
       <c r="K370" s="7"/>
       <c r="L370" s="7"/>
@@ -13052,7 +13087,7 @@
       </c>
       <c r="D372" s="7"/>
       <c t="s" r="E372" s="7">
-        <v>422</v>
+        <v>427</v>
       </c>
       <c r="F372" s="7">
         <v>330</v>
@@ -13061,13 +13096,13 @@
         <v>124</v>
       </c>
       <c t="s" r="H372" s="8">
-        <v>423</v>
+        <v>428</v>
       </c>
       <c t="s" r="I372" s="7">
         <v>163</v>
       </c>
       <c t="s" r="J372" s="7">
-        <v>424</v>
+        <v>429</v>
       </c>
       <c r="K372" s="7"/>
       <c r="L372" s="7"/>
@@ -13085,22 +13120,22 @@
       </c>
       <c r="D373" s="7"/>
       <c t="s" r="E373" s="7">
-        <v>422</v>
+        <v>427</v>
       </c>
       <c r="F373" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G373" s="8">
-        <v>423</v>
+        <v>428</v>
       </c>
       <c t="s" r="H373" s="8">
         <v>124</v>
       </c>
       <c t="s" r="I373" s="7">
-        <v>370</v>
+        <v>375</v>
       </c>
       <c t="s" r="J373" s="7">
-        <v>425</v>
+        <v>430</v>
       </c>
       <c r="K373" s="7"/>
       <c r="L373" s="7"/>
@@ -13133,7 +13168,7 @@
       </c>
       <c r="D375" s="7"/>
       <c t="s" r="E375" s="7">
-        <v>426</v>
+        <v>431</v>
       </c>
       <c r="F375" s="7">
         <v>330</v>
@@ -13142,13 +13177,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H375" s="8">
-        <v>427</v>
+        <v>432</v>
       </c>
       <c t="s" r="I375" s="7">
-        <v>415</v>
+        <v>420</v>
       </c>
       <c t="s" r="J375" s="7">
-        <v>361</v>
+        <v>366</v>
       </c>
       <c r="K375" s="7"/>
       <c r="L375" s="7"/>
@@ -13168,22 +13203,22 @@
       </c>
       <c r="D376" s="7"/>
       <c t="s" r="E376" s="7">
-        <v>426</v>
+        <v>431</v>
       </c>
       <c r="F376" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G376" s="8">
-        <v>427</v>
+        <v>432</v>
       </c>
       <c t="s" r="H376" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I376" s="7">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c t="s" r="J376" s="7">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="K376" s="7"/>
       <c r="L376" s="7"/>
@@ -13216,7 +13251,7 @@
       </c>
       <c r="D378" s="7"/>
       <c t="s" r="E378" s="7">
-        <v>428</v>
+        <v>433</v>
       </c>
       <c r="F378" s="7">
         <v>330</v>
@@ -13225,7 +13260,7 @@
         <v>17</v>
       </c>
       <c t="s" r="H378" s="8">
-        <v>429</v>
+        <v>434</v>
       </c>
       <c t="s" r="I378" s="7">
         <v>100</v>
@@ -13249,22 +13284,22 @@
       </c>
       <c r="D379" s="7"/>
       <c t="s" r="E379" s="7">
-        <v>428</v>
+        <v>433</v>
       </c>
       <c r="F379" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G379" s="8">
-        <v>429</v>
+        <v>434</v>
       </c>
       <c t="s" r="H379" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I379" s="7">
-        <v>403</v>
+        <v>408</v>
       </c>
       <c t="s" r="J379" s="7">
-        <v>409</v>
+        <v>414</v>
       </c>
       <c r="K379" s="7"/>
       <c r="L379" s="7"/>
@@ -13293,11 +13328,11 @@
         <v>5805</v>
       </c>
       <c t="s" r="C381" s="7">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="D381" s="7"/>
       <c t="s" r="E381" s="7">
-        <v>430</v>
+        <v>435</v>
       </c>
       <c r="F381" s="7">
         <v>330</v>
@@ -13306,7 +13341,7 @@
         <v>124</v>
       </c>
       <c t="s" r="H381" s="8">
-        <v>431</v>
+        <v>436</v>
       </c>
       <c t="s" r="I381" s="7">
         <v>169</v>
@@ -13317,7 +13352,7 @@
       <c r="K381" s="7"/>
       <c r="L381" s="7"/>
       <c t="s" r="M381" s="7">
-        <v>432</v>
+        <v>437</v>
       </c>
     </row>
     <row r="382" ht="14.25" customHeight="1">
@@ -13328,23 +13363,23 @@
         <v>5806</v>
       </c>
       <c t="s" r="C382" s="7">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="D382" s="7"/>
       <c t="s" r="E382" s="7">
-        <v>430</v>
+        <v>435</v>
       </c>
       <c r="F382" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G382" s="8">
-        <v>431</v>
+        <v>436</v>
       </c>
       <c t="s" r="H382" s="8">
         <v>124</v>
       </c>
       <c t="s" r="I382" s="7">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c t="s" r="J382" s="7">
         <v>51</v>
@@ -13380,7 +13415,7 @@
       </c>
       <c r="D384" s="7"/>
       <c t="s" r="E384" s="7">
-        <v>433</v>
+        <v>438</v>
       </c>
       <c r="F384" s="7">
         <v>330</v>
@@ -13389,7 +13424,7 @@
         <v>124</v>
       </c>
       <c t="s" r="H384" s="8">
-        <v>434</v>
+        <v>439</v>
       </c>
       <c t="s" r="I384" s="7">
         <v>119</v>
@@ -13400,7 +13435,7 @@
       <c r="K384" s="7"/>
       <c r="L384" s="7"/>
       <c t="s" r="M384" s="7">
-        <v>435</v>
+        <v>440</v>
       </c>
     </row>
     <row r="385" ht="15" customHeight="1">
@@ -13415,13 +13450,13 @@
       </c>
       <c r="D385" s="7"/>
       <c t="s" r="E385" s="7">
-        <v>433</v>
+        <v>438</v>
       </c>
       <c r="F385" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G385" s="8">
-        <v>434</v>
+        <v>439</v>
       </c>
       <c t="s" r="H385" s="8">
         <v>124</v>
@@ -13463,19 +13498,19 @@
       </c>
       <c r="D387" s="7"/>
       <c t="s" r="E387" s="7">
-        <v>436</v>
+        <v>441</v>
       </c>
       <c r="F387" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G387" s="8">
-        <v>437</v>
+        <v>442</v>
       </c>
       <c t="s" r="H387" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I387" s="7">
-        <v>396</v>
+        <v>401</v>
       </c>
       <c t="s" r="J387" s="7">
         <v>58</v>
@@ -13483,7 +13518,7 @@
       <c r="K387" s="7"/>
       <c r="L387" s="7"/>
       <c t="s" r="M387" s="7">
-        <v>438</v>
+        <v>443</v>
       </c>
     </row>
     <row r="388" ht="14.25" customHeight="1">
@@ -13498,7 +13533,7 @@
       </c>
       <c r="D388" s="7"/>
       <c t="s" r="E388" s="7">
-        <v>436</v>
+        <v>441</v>
       </c>
       <c r="F388" s="7">
         <v>330</v>
@@ -13513,7 +13548,7 @@
         <v>127</v>
       </c>
       <c t="s" r="J388" s="7">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="K388" s="7"/>
       <c r="L388" s="7"/>
@@ -13531,7 +13566,7 @@
       </c>
       <c r="D389" s="7"/>
       <c t="s" r="E389" s="7">
-        <v>436</v>
+        <v>441</v>
       </c>
       <c r="F389" s="7">
         <v>330</v>
@@ -13543,10 +13578,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I389" s="7">
-        <v>412</v>
+        <v>417</v>
       </c>
       <c t="s" r="J389" s="7">
-        <v>382</v>
+        <v>387</v>
       </c>
       <c r="K389" s="7"/>
       <c r="L389" s="7"/>
@@ -13554,7 +13589,7 @@
     </row>
     <row r="390" ht="16.5" customHeight="1">
       <c t="s" r="A390" s="9">
-        <v>439</v>
+        <v>444</v>
       </c>
       <c r="B390" s="9"/>
       <c r="C390" s="9"/>
@@ -13574,7 +13609,7 @@
     <row r="391" ht="65.25" customHeight="1"/>
     <row r="392" ht="16.5" customHeight="1">
       <c t="s" r="A392" s="10">
-        <v>440</v>
+        <v>445</v>
       </c>
       <c r="B392" s="10"/>
       <c r="C392" s="10"/>
@@ -13587,7 +13622,7 @@
       <c r="J392" s="10"/>
       <c r="K392" s="10"/>
       <c t="s" r="L392" s="11">
-        <v>441</v>
+        <v>446</v>
       </c>
       <c r="M392" s="11"/>
       <c r="N392" s="11"/>

--- a/Data/FlightPlan/FPL_23OCT26.xlsx
+++ b/Data/FlightPlan/FPL_23OCT26.xlsx
@@ -242,6 +242,9 @@
     <t>11:25</t>
   </si>
   <si>
+    <t>13:30</t>
+  </si>
+  <si>
     <t>HPH</t>
   </si>
   <si>
@@ -281,9 +284,6 @@
     <t>11:30</t>
   </si>
   <si>
-    <t>13:30</t>
-  </si>
-  <si>
     <t>16:35</t>
   </si>
   <si>
@@ -320,6 +320,9 @@
     <t>13:25</t>
   </si>
   <si>
+    <t>12:52</t>
+  </si>
+  <si>
     <t>14:00</t>
   </si>
   <si>
@@ -533,75 +536,78 @@
     <t>12:00</t>
   </si>
   <si>
+    <t>12:17</t>
+  </si>
+  <si>
+    <t>13:55</t>
+  </si>
+  <si>
+    <t>15:10</t>
+  </si>
+  <si>
+    <t>17:05</t>
+  </si>
+  <si>
+    <t>18:30</t>
+  </si>
+  <si>
+    <t>20:40</t>
+  </si>
+  <si>
+    <t>VN-A544</t>
+  </si>
+  <si>
+    <t>UIH</t>
+  </si>
+  <si>
+    <t>08:25</t>
+  </si>
+  <si>
+    <t>09:24</t>
+  </si>
+  <si>
+    <t>10:05</t>
+  </si>
+  <si>
+    <t>11:07</t>
+  </si>
+  <si>
+    <t>11:50</t>
+  </si>
+  <si>
+    <t>12:50</t>
+  </si>
+  <si>
+    <t>15:05</t>
+  </si>
+  <si>
+    <t>18:20</t>
+  </si>
+  <si>
+    <t>19:55</t>
+  </si>
+  <si>
+    <t>20:55</t>
+  </si>
+  <si>
+    <t>22:45</t>
+  </si>
+  <si>
+    <t>NGO</t>
+  </si>
+  <si>
+    <t>VN-A549</t>
+  </si>
+  <si>
+    <t>10:45</t>
+  </si>
+  <si>
+    <t>12:05</t>
+  </si>
+  <si>
     <t>12:11</t>
   </si>
   <si>
-    <t>13:55</t>
-  </si>
-  <si>
-    <t>15:10</t>
-  </si>
-  <si>
-    <t>17:05</t>
-  </si>
-  <si>
-    <t>18:30</t>
-  </si>
-  <si>
-    <t>20:40</t>
-  </si>
-  <si>
-    <t>VN-A544</t>
-  </si>
-  <si>
-    <t>UIH</t>
-  </si>
-  <si>
-    <t>08:25</t>
-  </si>
-  <si>
-    <t>09:24</t>
-  </si>
-  <si>
-    <t>10:05</t>
-  </si>
-  <si>
-    <t>11:07</t>
-  </si>
-  <si>
-    <t>11:50</t>
-  </si>
-  <si>
-    <t>12:50</t>
-  </si>
-  <si>
-    <t>15:05</t>
-  </si>
-  <si>
-    <t>18:20</t>
-  </si>
-  <si>
-    <t>19:55</t>
-  </si>
-  <si>
-    <t>20:55</t>
-  </si>
-  <si>
-    <t>22:45</t>
-  </si>
-  <si>
-    <t>NGO</t>
-  </si>
-  <si>
-    <t>VN-A549</t>
-  </si>
-  <si>
-    <t>10:45</t>
-  </si>
-  <si>
-    <t>12:05</t>
-  </si>
-  <si>
     <t>12:40</t>
   </si>
   <si>
@@ -794,7 +800,7 @@
     <t>10:07</t>
   </si>
   <si>
-    <t>12:08</t>
+    <t>11:47</t>
   </si>
   <si>
     <t>NOZ</t>
@@ -938,6 +944,9 @@
     <t>09:15</t>
   </si>
   <si>
+    <t>13:09</t>
+  </si>
+  <si>
     <t>13:40</t>
   </si>
   <si>
@@ -983,6 +992,9 @@
     <t>10:29</t>
   </si>
   <si>
+    <t>13:39</t>
+  </si>
+  <si>
     <t>17:50</t>
   </si>
   <si>
@@ -1022,6 +1034,9 @@
     <t>09:45</t>
   </si>
   <si>
+    <t>13:16</t>
+  </si>
+  <si>
     <t>13:20</t>
   </si>
   <si>
@@ -1031,6 +1046,12 @@
     <t>22:05</t>
   </si>
   <si>
+    <t>21:30</t>
+  </si>
+  <si>
+    <t>22:55</t>
+  </si>
+  <si>
     <t>FUK</t>
   </si>
   <si>
@@ -1064,9 +1085,6 @@
     <t>MFM</t>
   </si>
   <si>
-    <t>22:55</t>
-  </si>
-  <si>
     <t>05:35</t>
   </si>
   <si>
@@ -1109,9 +1127,6 @@
     <t>19:15</t>
   </si>
   <si>
-    <t>21:30</t>
-  </si>
-  <si>
     <t>CAN</t>
   </si>
   <si>
@@ -1145,10 +1160,7 @@
     <t>07:25</t>
   </si>
   <si>
-    <t>11:47</t>
-  </si>
-  <si>
-    <t>13:57</t>
+    <t>14:44</t>
   </si>
   <si>
     <t>KHH</t>
@@ -1187,6 +1199,9 @@
     <t>VN-A674</t>
   </si>
   <si>
+    <t>12:32</t>
+  </si>
+  <si>
     <t>13:10</t>
   </si>
   <si>
@@ -1316,6 +1331,9 @@
     <t>MEL</t>
   </si>
   <si>
+    <t>00:01</t>
+  </si>
+  <si>
     <t>VN-A815</t>
   </si>
   <si>
@@ -1346,7 +1364,7 @@
     <t>Total Record(s): 316</t>
   </si>
   <si>
-    <t xml:space="preserve">Generated on  Oct 23, 2026 11:05</t>
+    <t xml:space="preserve">Generated on  Oct 23, 2026 11:39</t>
   </si>
   <si>
     <t>Page 1 of 1</t>
@@ -2692,7 +2710,9 @@
       </c>
       <c r="K32" s="7"/>
       <c r="L32" s="7"/>
-      <c r="M32" s="7"/>
+      <c t="s" r="M32" s="7">
+        <v>77</v>
+      </c>
     </row>
     <row r="33" ht="14.25" customHeight="1">
       <c t="s" r="A33" s="6">
@@ -2715,13 +2735,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H33" s="8">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c t="s" r="I33" s="7">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c t="s" r="J33" s="7">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="K33" s="7"/>
       <c r="L33" s="7"/>
@@ -2745,7 +2765,7 @@
         <v>321</v>
       </c>
       <c t="s" r="G34" s="8">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c t="s" r="H34" s="8">
         <v>17</v>
@@ -2754,7 +2774,7 @@
         <v>59</v>
       </c>
       <c t="s" r="J34" s="7">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="K34" s="7"/>
       <c r="L34" s="7"/>
@@ -2784,10 +2804,10 @@
         <v>43</v>
       </c>
       <c t="s" r="I35" s="7">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c t="s" r="J35" s="7">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="K35" s="7"/>
       <c r="L35" s="7"/>
@@ -2817,10 +2837,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I36" s="7">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c t="s" r="J36" s="7">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="K36" s="7"/>
       <c r="L36" s="7"/>
@@ -2853,7 +2873,7 @@
       </c>
       <c r="D38" s="7"/>
       <c t="s" r="E38" s="7">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="F38" s="7">
         <v>321</v>
@@ -2862,18 +2882,18 @@
         <v>17</v>
       </c>
       <c t="s" r="H38" s="8">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c t="s" r="I38" s="7">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c t="s" r="J38" s="7">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="K38" s="7"/>
       <c r="L38" s="7"/>
       <c t="s" r="M38" s="7">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="39" ht="14.25" customHeight="1">
@@ -2888,22 +2908,22 @@
       </c>
       <c r="D39" s="7"/>
       <c t="s" r="E39" s="7">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="F39" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G39" s="8">
+        <v>78</v>
+      </c>
+      <c t="s" r="H39" s="8">
+        <v>17</v>
+      </c>
+      <c t="s" r="I39" s="7">
+        <v>90</v>
+      </c>
+      <c t="s" r="J39" s="7">
         <v>77</v>
-      </c>
-      <c t="s" r="H39" s="8">
-        <v>17</v>
-      </c>
-      <c t="s" r="I39" s="7">
-        <v>89</v>
-      </c>
-      <c t="s" r="J39" s="7">
-        <v>90</v>
       </c>
       <c r="K39" s="7"/>
       <c r="L39" s="7"/>
@@ -2921,7 +2941,7 @@
       </c>
       <c r="D40" s="7"/>
       <c t="s" r="E40" s="7">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="F40" s="7">
         <v>321</v>
@@ -2930,7 +2950,7 @@
         <v>17</v>
       </c>
       <c t="s" r="H40" s="8">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c t="s" r="I40" s="7">
         <v>55</v>
@@ -2954,13 +2974,13 @@
       </c>
       <c r="D41" s="7"/>
       <c t="s" r="E41" s="7">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="F41" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G41" s="8">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c t="s" r="H41" s="8">
         <v>17</v>
@@ -2987,7 +3007,7 @@
       </c>
       <c r="D42" s="7"/>
       <c t="s" r="E42" s="7">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="F42" s="7">
         <v>321</v>
@@ -2999,7 +3019,7 @@
         <v>92</v>
       </c>
       <c t="s" r="I42" s="7">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c t="s" r="J42" s="7">
         <v>28</v>
@@ -3020,7 +3040,7 @@
       </c>
       <c r="D43" s="7"/>
       <c t="s" r="E43" s="7">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="F43" s="7">
         <v>321</v>
@@ -3157,7 +3177,9 @@
       </c>
       <c r="K47" s="7"/>
       <c r="L47" s="7"/>
-      <c r="M47" s="7"/>
+      <c t="s" r="M47" s="7">
+        <v>103</v>
+      </c>
     </row>
     <row r="48" ht="14.25" customHeight="1">
       <c t="s" r="A48" s="6">
@@ -3183,7 +3205,7 @@
         <v>43</v>
       </c>
       <c t="s" r="I48" s="7">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c t="s" r="J48" s="7">
         <v>58</v>
@@ -3216,10 +3238,10 @@
         <v>21</v>
       </c>
       <c t="s" r="I49" s="7">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c t="s" r="J49" s="7">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="K49" s="7"/>
       <c r="L49" s="7"/>
@@ -3249,10 +3271,10 @@
         <v>43</v>
       </c>
       <c t="s" r="I50" s="7">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c t="s" r="J50" s="7">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="K50" s="7"/>
       <c r="L50" s="7"/>
@@ -3285,7 +3307,7 @@
       </c>
       <c r="D52" s="7"/>
       <c t="s" r="E52" s="7">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="F52" s="7">
         <v>321</v>
@@ -3294,18 +3316,18 @@
         <v>17</v>
       </c>
       <c t="s" r="H52" s="8">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c t="s" r="I52" s="7">
         <v>66</v>
       </c>
       <c t="s" r="J52" s="7">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="K52" s="7"/>
       <c r="L52" s="7"/>
       <c t="s" r="M52" s="7">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="53" ht="14.25" customHeight="1">
@@ -3320,22 +3342,22 @@
       </c>
       <c r="D53" s="7"/>
       <c t="s" r="E53" s="7">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="F53" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G53" s="8">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c t="s" r="H53" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I53" s="7">
-        <v>90</v>
+        <v>77</v>
       </c>
       <c t="s" r="J53" s="7">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="K53" s="7"/>
       <c r="L53" s="7"/>
@@ -3353,7 +3375,7 @@
       </c>
       <c r="D54" s="7"/>
       <c t="s" r="E54" s="7">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="F54" s="7">
         <v>321</v>
@@ -3362,13 +3384,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H54" s="8">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c t="s" r="I54" s="7">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c t="s" r="J54" s="7">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="K54" s="7"/>
       <c r="L54" s="7"/>
@@ -3386,22 +3408,22 @@
       </c>
       <c r="D55" s="7"/>
       <c t="s" r="E55" s="7">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="F55" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G55" s="8">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c t="s" r="H55" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I55" s="7">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c t="s" r="J55" s="7">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="K55" s="7"/>
       <c r="L55" s="7"/>
@@ -3434,7 +3456,7 @@
       </c>
       <c r="D57" s="7"/>
       <c t="s" r="E57" s="7">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="F57" s="7">
         <v>321</v>
@@ -3443,13 +3465,13 @@
         <v>43</v>
       </c>
       <c t="s" r="H57" s="8">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c t="s" r="I57" s="7">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c t="s" r="J57" s="7">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="K57" s="7"/>
       <c r="L57" s="7"/>
@@ -3469,13 +3491,13 @@
       </c>
       <c r="D58" s="7"/>
       <c t="s" r="E58" s="7">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="F58" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G58" s="8">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c t="s" r="H58" s="8">
         <v>43</v>
@@ -3489,7 +3511,7 @@
       <c r="K58" s="7"/>
       <c r="L58" s="7"/>
       <c t="s" r="M58" s="7">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="59" ht="14.25" customHeight="1">
@@ -3504,7 +3526,7 @@
       </c>
       <c r="D59" s="7"/>
       <c t="s" r="E59" s="7">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="F59" s="7">
         <v>321</v>
@@ -3516,10 +3538,10 @@
         <v>98</v>
       </c>
       <c t="s" r="I59" s="7">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c t="s" r="J59" s="7">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="K59" s="7"/>
       <c r="L59" s="7"/>
@@ -3537,7 +3559,7 @@
       </c>
       <c r="D60" s="7"/>
       <c t="s" r="E60" s="7">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="F60" s="7">
         <v>321</v>
@@ -3552,7 +3574,7 @@
         <v>56</v>
       </c>
       <c t="s" r="J60" s="7">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="K60" s="7"/>
       <c r="L60" s="7"/>
@@ -3570,7 +3592,7 @@
       </c>
       <c r="D61" s="7"/>
       <c t="s" r="E61" s="7">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="F61" s="7">
         <v>321</v>
@@ -3579,13 +3601,13 @@
         <v>43</v>
       </c>
       <c t="s" r="H61" s="8">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c t="s" r="I61" s="7">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c t="s" r="J61" s="7">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="K61" s="7"/>
       <c r="L61" s="7"/>
@@ -3603,22 +3625,22 @@
       </c>
       <c r="D62" s="7"/>
       <c t="s" r="E62" s="7">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="F62" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G62" s="8">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c t="s" r="H62" s="8">
         <v>43</v>
       </c>
       <c t="s" r="I62" s="7">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c t="s" r="J62" s="7">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="K62" s="7"/>
       <c r="L62" s="7"/>
@@ -3651,7 +3673,7 @@
       </c>
       <c r="D64" s="7"/>
       <c t="s" r="E64" s="7">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="F64" s="7">
         <v>321</v>
@@ -3663,15 +3685,15 @@
         <v>42</v>
       </c>
       <c t="s" r="I64" s="7">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c t="s" r="J64" s="7">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="K64" s="7"/>
       <c r="L64" s="7"/>
       <c t="s" r="M64" s="7">
-        <v>131</v>
+        <v>132</v>
       </c>
     </row>
     <row r="65" ht="15" customHeight="1">
@@ -3686,7 +3708,7 @@
       </c>
       <c r="D65" s="7"/>
       <c t="s" r="E65" s="7">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="F65" s="7">
         <v>321</v>
@@ -3698,7 +3720,7 @@
         <v>43</v>
       </c>
       <c t="s" r="I65" s="7">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c t="s" r="J65" s="7">
         <v>48</v>
@@ -3734,7 +3756,7 @@
       </c>
       <c r="D67" s="7"/>
       <c t="s" r="E67" s="7">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="F67" s="7">
         <v>321</v>
@@ -3743,18 +3765,18 @@
         <v>17</v>
       </c>
       <c t="s" r="H67" s="8">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c t="s" r="I67" s="7">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c t="s" r="J67" s="7">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="K67" s="7"/>
       <c r="L67" s="7"/>
       <c t="s" r="M67" s="7">
-        <v>137</v>
+        <v>138</v>
       </c>
     </row>
     <row r="68" ht="14.25" customHeight="1">
@@ -3769,27 +3791,27 @@
       </c>
       <c r="D68" s="7"/>
       <c t="s" r="E68" s="7">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="F68" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G68" s="8">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c t="s" r="H68" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I68" s="7">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c t="s" r="J68" s="7">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="K68" s="7"/>
       <c r="L68" s="7"/>
       <c t="s" r="M68" s="7">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="69" ht="14.25" customHeight="1">
@@ -3819,7 +3841,7 @@
       </c>
       <c r="D70" s="7"/>
       <c t="s" r="E70" s="7">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="F70" s="7">
         <v>321</v>
@@ -3831,15 +3853,15 @@
         <v>43</v>
       </c>
       <c t="s" r="I70" s="7">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c t="s" r="J70" s="7">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="K70" s="7"/>
       <c r="L70" s="7"/>
       <c t="s" r="M70" s="7">
-        <v>110</v>
+        <v>111</v>
       </c>
     </row>
     <row r="71" ht="14.25" customHeight="1">
@@ -3854,7 +3876,7 @@
       </c>
       <c r="D71" s="7"/>
       <c t="s" r="E71" s="7">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="F71" s="7">
         <v>321</v>
@@ -3866,10 +3888,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I71" s="7">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c t="s" r="J71" s="7">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="K71" s="7"/>
       <c r="L71" s="7"/>
@@ -3887,7 +3909,7 @@
       </c>
       <c r="D72" s="7"/>
       <c t="s" r="E72" s="7">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="F72" s="7">
         <v>321</v>
@@ -3899,17 +3921,17 @@
         <v>43</v>
       </c>
       <c t="s" r="I72" s="7">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c t="s" r="J72" s="7">
         <v>70</v>
       </c>
       <c t="s" r="K72" s="7">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="L72" s="7"/>
       <c t="s" r="M72" s="7">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="73" ht="14.25" customHeight="1">
@@ -3924,7 +3946,7 @@
       </c>
       <c r="D73" s="7"/>
       <c t="s" r="E73" s="7">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="F73" s="7">
         <v>321</v>
@@ -3936,7 +3958,7 @@
         <v>53</v>
       </c>
       <c t="s" r="I73" s="7">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c t="s" r="J73" s="7">
         <v>95</v>
@@ -3972,7 +3994,7 @@
       </c>
       <c r="D75" s="7"/>
       <c t="s" r="E75" s="7">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="F75" s="7">
         <v>321</v>
@@ -3984,7 +4006,7 @@
         <v>98</v>
       </c>
       <c t="s" r="I75" s="7">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c t="s" r="J75" s="7">
         <v>96</v>
@@ -3992,7 +4014,7 @@
       <c r="K75" s="7"/>
       <c r="L75" s="7"/>
       <c t="s" r="M75" s="7">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="76" ht="14.25" customHeight="1">
@@ -4007,7 +4029,7 @@
       </c>
       <c r="D76" s="7"/>
       <c t="s" r="E76" s="7">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="F76" s="7">
         <v>321</v>
@@ -4019,15 +4041,15 @@
         <v>43</v>
       </c>
       <c t="s" r="I76" s="7">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c t="s" r="J76" s="7">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="K76" s="7"/>
       <c r="L76" s="7"/>
       <c t="s" r="M76" s="7">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="77" ht="14.25" customHeight="1">
@@ -4042,7 +4064,7 @@
       </c>
       <c r="D77" s="7"/>
       <c t="s" r="E77" s="7">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="F77" s="7">
         <v>321</v>
@@ -4057,7 +4079,7 @@
         <v>100</v>
       </c>
       <c t="s" r="J77" s="7">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="K77" s="7"/>
       <c r="L77" s="7"/>
@@ -4075,7 +4097,7 @@
       </c>
       <c r="D78" s="7"/>
       <c t="s" r="E78" s="7">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="F78" s="7">
         <v>321</v>
@@ -4087,7 +4109,7 @@
         <v>43</v>
       </c>
       <c t="s" r="I78" s="7">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c t="s" r="J78" s="7">
         <v>37</v>
@@ -4108,7 +4130,7 @@
       </c>
       <c r="D79" s="7"/>
       <c t="s" r="E79" s="7">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="F79" s="7">
         <v>321</v>
@@ -4117,10 +4139,10 @@
         <v>43</v>
       </c>
       <c t="s" r="H79" s="8">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c t="s" r="I79" s="7">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c t="s" r="J79" s="7">
         <v>24</v>
@@ -4141,22 +4163,22 @@
       </c>
       <c r="D80" s="7"/>
       <c t="s" r="E80" s="7">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="F80" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G80" s="8">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c t="s" r="H80" s="8">
         <v>43</v>
       </c>
       <c t="s" r="I80" s="7">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c t="s" r="J80" s="7">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="K80" s="7"/>
       <c r="L80" s="7"/>
@@ -4174,7 +4196,7 @@
       </c>
       <c r="D81" s="7"/>
       <c t="s" r="E81" s="7">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="F81" s="7">
         <v>321</v>
@@ -4186,10 +4208,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I81" s="7">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c t="s" r="J81" s="7">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="K81" s="7"/>
       <c r="L81" s="7"/>
@@ -4222,7 +4244,7 @@
       </c>
       <c r="D83" s="7"/>
       <c t="s" r="E83" s="7">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="F83" s="7">
         <v>321</v>
@@ -4234,17 +4256,17 @@
         <v>33</v>
       </c>
       <c t="s" r="I83" s="7">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c t="s" r="J83" s="7">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c t="s" r="K83" s="7">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="L83" s="7"/>
       <c t="s" r="M83" s="7">
-        <v>144</v>
+        <v>145</v>
       </c>
     </row>
     <row r="84" ht="14.25" customHeight="1">
@@ -4259,7 +4281,7 @@
       </c>
       <c r="D84" s="7"/>
       <c t="s" r="E84" s="7">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="F84" s="7">
         <v>321</v>
@@ -4274,14 +4296,14 @@
         <v>24</v>
       </c>
       <c t="s" r="J84" s="7">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c t="s" r="K84" s="7">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="L84" s="7"/>
       <c t="s" r="M84" s="7">
-        <v>164</v>
+        <v>165</v>
       </c>
     </row>
     <row r="85" ht="15" customHeight="1">
@@ -4296,7 +4318,7 @@
       </c>
       <c r="D85" s="7"/>
       <c t="s" r="E85" s="7">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="F85" s="7">
         <v>321</v>
@@ -4308,10 +4330,10 @@
         <v>42</v>
       </c>
       <c t="s" r="I85" s="7">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c t="s" r="J85" s="7">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="K85" s="7"/>
       <c r="L85" s="7"/>
@@ -4344,7 +4366,7 @@
       </c>
       <c r="D87" s="7"/>
       <c t="s" r="E87" s="7">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="F87" s="7">
         <v>321</v>
@@ -4353,18 +4375,18 @@
         <v>17</v>
       </c>
       <c t="s" r="H87" s="8">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c t="s" r="I87" s="7">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c t="s" r="J87" s="7">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="K87" s="7"/>
       <c r="L87" s="7"/>
       <c t="s" r="M87" s="7">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="88" ht="14.25" customHeight="1">
@@ -4379,27 +4401,27 @@
       </c>
       <c r="D88" s="7"/>
       <c t="s" r="E88" s="7">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="F88" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G88" s="8">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c t="s" r="H88" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I88" s="7">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c t="s" r="J88" s="7">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="K88" s="7"/>
       <c r="L88" s="7"/>
       <c t="s" r="M88" s="7">
-        <v>170</v>
+        <v>171</v>
       </c>
     </row>
     <row r="89" ht="14.25" customHeight="1">
@@ -4414,7 +4436,7 @@
       </c>
       <c r="D89" s="7"/>
       <c t="s" r="E89" s="7">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="F89" s="7">
         <v>321</v>
@@ -4423,18 +4445,18 @@
         <v>17</v>
       </c>
       <c t="s" r="H89" s="8">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c t="s" r="I89" s="7">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c t="s" r="J89" s="7">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="K89" s="7"/>
       <c r="L89" s="7"/>
       <c t="s" r="M89" s="7">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="90" ht="15" customHeight="1">
@@ -4449,22 +4471,22 @@
       </c>
       <c r="D90" s="7"/>
       <c t="s" r="E90" s="7">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="F90" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G90" s="8">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c t="s" r="H90" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I90" s="7">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c t="s" r="J90" s="7">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="K90" s="7"/>
       <c r="L90" s="7"/>
@@ -4482,7 +4504,7 @@
       </c>
       <c r="D91" s="7"/>
       <c t="s" r="E91" s="7">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="F91" s="7">
         <v>321</v>
@@ -4494,10 +4516,10 @@
         <v>98</v>
       </c>
       <c t="s" r="I91" s="7">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c t="s" r="J91" s="7">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="K91" s="7"/>
       <c r="L91" s="7"/>
@@ -4515,7 +4537,7 @@
       </c>
       <c r="D92" s="7"/>
       <c t="s" r="E92" s="7">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="F92" s="7">
         <v>321</v>
@@ -4527,10 +4549,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I92" s="7">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c t="s" r="J92" s="7">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="K92" s="7"/>
       <c r="L92" s="7"/>
@@ -4548,7 +4570,7 @@
       </c>
       <c r="D93" s="7"/>
       <c t="s" r="E93" s="7">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="F93" s="7">
         <v>321</v>
@@ -4560,10 +4582,10 @@
         <v>98</v>
       </c>
       <c t="s" r="I93" s="7">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c t="s" r="J93" s="7">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="K93" s="7"/>
       <c r="L93" s="7"/>
@@ -4596,7 +4618,7 @@
       </c>
       <c r="D95" s="7"/>
       <c t="s" r="E95" s="7">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="F95" s="7">
         <v>321</v>
@@ -4605,10 +4627,10 @@
         <v>17</v>
       </c>
       <c t="s" r="H95" s="8">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c t="s" r="I95" s="7">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c t="s" r="J95" s="7">
         <v>66</v>
@@ -4616,7 +4638,7 @@
       <c r="K95" s="7"/>
       <c r="L95" s="7"/>
       <c t="s" r="M95" s="7">
-        <v>183</v>
+        <v>184</v>
       </c>
     </row>
     <row r="96" ht="14.25" customHeight="1">
@@ -4631,19 +4653,19 @@
       </c>
       <c r="D96" s="7"/>
       <c t="s" r="E96" s="7">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="F96" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G96" s="8">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c t="s" r="H96" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I96" s="7">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c t="s" r="J96" s="7">
         <v>100</v>
@@ -4651,7 +4673,7 @@
       <c r="K96" s="7"/>
       <c r="L96" s="7"/>
       <c t="s" r="M96" s="7">
-        <v>185</v>
+        <v>186</v>
       </c>
     </row>
     <row r="97" ht="14.25" customHeight="1">
@@ -4666,7 +4688,7 @@
       </c>
       <c r="D97" s="7"/>
       <c t="s" r="E97" s="7">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="F97" s="7">
         <v>321</v>
@@ -4678,17 +4700,17 @@
         <v>21</v>
       </c>
       <c t="s" r="I97" s="7">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c t="s" r="J97" s="7">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c t="s" r="K97" s="7">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="L97" s="7"/>
       <c t="s" r="M97" s="7">
-        <v>187</v>
+        <v>188</v>
       </c>
     </row>
     <row r="98" ht="14.25" customHeight="1">
@@ -4703,7 +4725,7 @@
       </c>
       <c r="D98" s="7"/>
       <c t="s" r="E98" s="7">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="F98" s="7">
         <v>321</v>
@@ -4712,20 +4734,20 @@
         <v>21</v>
       </c>
       <c t="s" r="H98" s="8">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c t="s" r="I98" s="7">
         <v>54</v>
       </c>
       <c t="s" r="J98" s="7">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c t="s" r="K98" s="7">
         <v>102</v>
       </c>
       <c r="L98" s="7"/>
       <c t="s" r="M98" s="7">
-        <v>130</v>
+        <v>131</v>
       </c>
     </row>
     <row r="99" ht="14.25" customHeight="1">
@@ -4740,19 +4762,19 @@
       </c>
       <c r="D99" s="7"/>
       <c t="s" r="E99" s="7">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="F99" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G99" s="8">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c t="s" r="H99" s="8">
         <v>21</v>
       </c>
       <c t="s" r="I99" s="7">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c t="s" r="J99" s="7">
         <v>59</v>
@@ -4762,7 +4784,7 @@
       </c>
       <c r="L99" s="7"/>
       <c t="s" r="M99" s="7">
-        <v>126</v>
+        <v>127</v>
       </c>
     </row>
     <row r="100" ht="15" customHeight="1">
@@ -4777,7 +4799,7 @@
       </c>
       <c r="D100" s="7"/>
       <c t="s" r="E100" s="7">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="F100" s="7">
         <v>321</v>
@@ -4789,17 +4811,17 @@
         <v>17</v>
       </c>
       <c t="s" r="I100" s="7">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c t="s" r="J100" s="7">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c t="s" r="K100" s="7">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="L100" s="7"/>
       <c t="s" r="M100" s="7">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="101" ht="14.25" customHeight="1">
@@ -4814,7 +4836,7 @@
       </c>
       <c r="D101" s="7"/>
       <c t="s" r="E101" s="7">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="F101" s="7">
         <v>321</v>
@@ -4826,17 +4848,17 @@
         <v>43</v>
       </c>
       <c t="s" r="I101" s="7">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c t="s" r="J101" s="7">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c t="s" r="K101" s="7">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="L101" s="7"/>
       <c t="s" r="M101" s="7">
-        <v>192</v>
+        <v>193</v>
       </c>
     </row>
     <row r="102" ht="14.25" customHeight="1">
@@ -4851,7 +4873,7 @@
       </c>
       <c r="D102" s="7"/>
       <c t="s" r="E102" s="7">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="F102" s="7">
         <v>321</v>
@@ -4860,13 +4882,13 @@
         <v>43</v>
       </c>
       <c t="s" r="H102" s="8">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c t="s" r="I102" s="7">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c t="s" r="J102" s="7">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="K102" s="7"/>
       <c r="L102" s="7"/>
@@ -4899,7 +4921,7 @@
       </c>
       <c r="D104" s="7"/>
       <c t="s" r="E104" s="7">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F104" s="7">
         <v>321</v>
@@ -4911,15 +4933,15 @@
         <v>98</v>
       </c>
       <c t="s" r="I104" s="7">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c t="s" r="J104" s="7">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="K104" s="7"/>
       <c r="L104" s="7"/>
       <c t="s" r="M104" s="7">
-        <v>196</v>
+        <v>198</v>
       </c>
     </row>
     <row r="105" ht="15" customHeight="1">
@@ -4934,7 +4956,7 @@
       </c>
       <c r="D105" s="7"/>
       <c t="s" r="E105" s="7">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F105" s="7">
         <v>321</v>
@@ -4946,10 +4968,10 @@
         <v>43</v>
       </c>
       <c t="s" r="I105" s="7">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c t="s" r="J105" s="7">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="K105" s="7"/>
       <c r="L105" s="7"/>
@@ -4967,7 +4989,7 @@
       </c>
       <c r="D106" s="7"/>
       <c t="s" r="E106" s="7">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F106" s="7">
         <v>321</v>
@@ -5000,7 +5022,7 @@
       </c>
       <c r="D107" s="7"/>
       <c t="s" r="E107" s="7">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F107" s="7">
         <v>321</v>
@@ -5012,10 +5034,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I107" s="7">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c t="s" r="J107" s="7">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="K107" s="7"/>
       <c r="L107" s="7"/>
@@ -5033,7 +5055,7 @@
       </c>
       <c r="D108" s="7"/>
       <c t="s" r="E108" s="7">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F108" s="7">
         <v>321</v>
@@ -5042,13 +5064,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H108" s="8">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c t="s" r="I108" s="7">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c t="s" r="J108" s="7">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="K108" s="7"/>
       <c r="L108" s="7"/>
@@ -5066,22 +5088,22 @@
       </c>
       <c r="D109" s="7"/>
       <c t="s" r="E109" s="7">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F109" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G109" s="8">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c t="s" r="H109" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I109" s="7">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c t="s" r="J109" s="7">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="K109" s="7"/>
       <c r="L109" s="7"/>
@@ -5099,7 +5121,7 @@
       </c>
       <c r="D110" s="7"/>
       <c t="s" r="E110" s="7">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F110" s="7">
         <v>321</v>
@@ -5111,17 +5133,17 @@
         <v>43</v>
       </c>
       <c t="s" r="I110" s="7">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c t="s" r="J110" s="7">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c t="s" r="K110" s="7">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="L110" s="7"/>
       <c t="s" r="M110" s="7">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="111" ht="14.25" customHeight="1">
@@ -5151,7 +5173,7 @@
       </c>
       <c r="D112" s="7"/>
       <c t="s" r="E112" s="7">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="F112" s="7">
         <v>321</v>
@@ -5160,18 +5182,18 @@
         <v>43</v>
       </c>
       <c t="s" r="H112" s="8">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c t="s" r="I112" s="7">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c t="s" r="J112" s="7">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="K112" s="7"/>
       <c r="L112" s="7"/>
       <c t="s" r="M112" s="7">
-        <v>206</v>
+        <v>208</v>
       </c>
     </row>
     <row r="113" ht="14.25" customHeight="1">
@@ -5186,22 +5208,22 @@
       </c>
       <c r="D113" s="7"/>
       <c t="s" r="E113" s="7">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="F113" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G113" s="8">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c t="s" r="H113" s="8">
         <v>43</v>
       </c>
       <c t="s" r="I113" s="7">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c t="s" r="J113" s="7">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="K113" s="7"/>
       <c r="L113" s="7"/>
@@ -5219,7 +5241,7 @@
       </c>
       <c r="D114" s="7"/>
       <c t="s" r="E114" s="7">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="F114" s="7">
         <v>321</v>
@@ -5231,10 +5253,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I114" s="7">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c t="s" r="J114" s="7">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="K114" s="7"/>
       <c r="L114" s="7"/>
@@ -5252,7 +5274,7 @@
       </c>
       <c r="D115" s="7"/>
       <c t="s" r="E115" s="7">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="F115" s="7">
         <v>321</v>
@@ -5261,13 +5283,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H115" s="8">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c t="s" r="I115" s="7">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c t="s" r="J115" s="7">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="K115" s="7"/>
       <c r="L115" s="7"/>
@@ -5285,22 +5307,22 @@
       </c>
       <c r="D116" s="7"/>
       <c t="s" r="E116" s="7">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="F116" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G116" s="8">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c t="s" r="H116" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I116" s="7">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c t="s" r="J116" s="7">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="K116" s="7"/>
       <c r="L116" s="7"/>
@@ -5318,7 +5340,7 @@
       </c>
       <c r="D117" s="7"/>
       <c t="s" r="E117" s="7">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="F117" s="7">
         <v>321</v>
@@ -5330,10 +5352,10 @@
         <v>98</v>
       </c>
       <c t="s" r="I117" s="7">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c t="s" r="J117" s="7">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="K117" s="7"/>
       <c r="L117" s="7"/>
@@ -5351,7 +5373,7 @@
       </c>
       <c r="D118" s="7"/>
       <c t="s" r="E118" s="7">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="F118" s="7">
         <v>321</v>
@@ -5363,10 +5385,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I118" s="7">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c t="s" r="J118" s="7">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="K118" s="7"/>
       <c r="L118" s="7"/>
@@ -5399,7 +5421,7 @@
       </c>
       <c r="D120" s="7"/>
       <c t="s" r="E120" s="7">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="F120" s="7">
         <v>321</v>
@@ -5408,18 +5430,18 @@
         <v>17</v>
       </c>
       <c t="s" r="H120" s="8">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c t="s" r="I120" s="7">
         <v>44</v>
       </c>
       <c t="s" r="J120" s="7">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="K120" s="7"/>
       <c r="L120" s="7"/>
       <c t="s" r="M120" s="7">
-        <v>222</v>
+        <v>224</v>
       </c>
     </row>
     <row r="121" ht="14.25" customHeight="1">
@@ -5434,13 +5456,13 @@
       </c>
       <c r="D121" s="7"/>
       <c t="s" r="E121" s="7">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="F121" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G121" s="8">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c t="s" r="H121" s="8">
         <v>17</v>
@@ -5449,7 +5471,7 @@
         <v>35</v>
       </c>
       <c t="s" r="J121" s="7">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="K121" s="7"/>
       <c r="L121" s="7"/>
@@ -5467,7 +5489,7 @@
       </c>
       <c r="D122" s="7"/>
       <c t="s" r="E122" s="7">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="F122" s="7">
         <v>321</v>
@@ -5476,13 +5498,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H122" s="8">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c t="s" r="I122" s="7">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c t="s" r="J122" s="7">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="K122" s="7"/>
       <c r="L122" s="7"/>
@@ -5500,13 +5522,13 @@
       </c>
       <c r="D123" s="7"/>
       <c t="s" r="E123" s="7">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="F123" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G123" s="8">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c t="s" r="H123" s="8">
         <v>17</v>
@@ -5515,7 +5537,7 @@
         <v>48</v>
       </c>
       <c t="s" r="J123" s="7">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="K123" s="7"/>
       <c r="L123" s="7"/>
@@ -5548,27 +5570,27 @@
       </c>
       <c r="D125" s="7"/>
       <c t="s" r="E125" s="7">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="F125" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G125" s="8">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c t="s" r="H125" s="8">
         <v>43</v>
       </c>
       <c t="s" r="I125" s="7">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c t="s" r="J125" s="7">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="K125" s="7"/>
       <c r="L125" s="7"/>
       <c t="s" r="M125" s="7">
-        <v>228</v>
+        <v>230</v>
       </c>
     </row>
     <row r="126" ht="14.25" customHeight="1">
@@ -5583,7 +5605,7 @@
       </c>
       <c r="D126" s="7"/>
       <c t="s" r="E126" s="7">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="F126" s="7">
         <v>321</v>
@@ -5598,12 +5620,12 @@
         <v>44</v>
       </c>
       <c t="s" r="J126" s="7">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="K126" s="7"/>
       <c r="L126" s="7"/>
       <c t="s" r="M126" s="7">
-        <v>229</v>
+        <v>231</v>
       </c>
     </row>
     <row r="127" ht="14.25" customHeight="1">
@@ -5618,7 +5640,7 @@
       </c>
       <c r="D127" s="7"/>
       <c t="s" r="E127" s="7">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="F127" s="7">
         <v>321</v>
@@ -5651,7 +5673,7 @@
       </c>
       <c r="D128" s="7"/>
       <c t="s" r="E128" s="7">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="F128" s="7">
         <v>321</v>
@@ -5660,13 +5682,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H128" s="8">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c t="s" r="I128" s="7">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c t="s" r="J128" s="7">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="K128" s="7"/>
       <c r="L128" s="7"/>
@@ -5684,13 +5706,13 @@
       </c>
       <c r="D129" s="7"/>
       <c t="s" r="E129" s="7">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="F129" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G129" s="8">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c t="s" r="H129" s="8">
         <v>17</v>
@@ -5699,7 +5721,7 @@
         <v>70</v>
       </c>
       <c t="s" r="J129" s="7">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="K129" s="7"/>
       <c r="L129" s="7"/>
@@ -5717,7 +5739,7 @@
       </c>
       <c r="D130" s="7"/>
       <c t="s" r="E130" s="7">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="F130" s="7">
         <v>321</v>
@@ -5729,10 +5751,10 @@
         <v>43</v>
       </c>
       <c t="s" r="I130" s="7">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c t="s" r="J130" s="7">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="K130" s="7"/>
       <c r="L130" s="7"/>
@@ -5750,7 +5772,7 @@
       </c>
       <c r="D131" s="7"/>
       <c t="s" r="E131" s="7">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="F131" s="7">
         <v>321</v>
@@ -5762,10 +5784,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I131" s="7">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c t="s" r="J131" s="7">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="K131" s="7"/>
       <c r="L131" s="7"/>
@@ -5798,7 +5820,7 @@
       </c>
       <c r="D133" s="7"/>
       <c t="s" r="E133" s="7">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="F133" s="7">
         <v>321</v>
@@ -5807,10 +5829,10 @@
         <v>17</v>
       </c>
       <c t="s" r="H133" s="8">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c t="s" r="I133" s="7">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c t="s" r="J133" s="7">
         <v>95</v>
@@ -5818,7 +5840,7 @@
       <c r="K133" s="7"/>
       <c r="L133" s="7"/>
       <c t="s" r="M133" s="7">
-        <v>236</v>
+        <v>238</v>
       </c>
     </row>
     <row r="134" ht="14.25" customHeight="1">
@@ -5833,19 +5855,19 @@
       </c>
       <c r="D134" s="7"/>
       <c t="s" r="E134" s="7">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="F134" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G134" s="8">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c t="s" r="H134" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I134" s="7">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c t="s" r="J134" s="7">
         <v>44</v>
@@ -5853,7 +5875,7 @@
       <c r="K134" s="7"/>
       <c r="L134" s="7"/>
       <c t="s" r="M134" s="7">
-        <v>183</v>
+        <v>184</v>
       </c>
     </row>
     <row r="135" ht="15" customHeight="1">
@@ -5868,7 +5890,7 @@
       </c>
       <c r="D135" s="7"/>
       <c t="s" r="E135" s="7">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="F135" s="7">
         <v>321</v>
@@ -5877,18 +5899,18 @@
         <v>17</v>
       </c>
       <c t="s" r="H135" s="8">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c t="s" r="I135" s="7">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c t="s" r="J135" s="7">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="K135" s="7"/>
       <c r="L135" s="7"/>
       <c t="s" r="M135" s="7">
-        <v>238</v>
+        <v>240</v>
       </c>
     </row>
     <row r="136" ht="14.25" customHeight="1">
@@ -5903,19 +5925,19 @@
       </c>
       <c r="D136" s="7"/>
       <c t="s" r="E136" s="7">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="F136" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G136" s="8">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c t="s" r="H136" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I136" s="7">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c t="s" r="J136" s="7">
         <v>37</v>
@@ -5936,7 +5958,7 @@
       </c>
       <c r="D137" s="7"/>
       <c t="s" r="E137" s="7">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="F137" s="7">
         <v>321</v>
@@ -5945,13 +5967,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H137" s="8">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c t="s" r="I137" s="7">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c t="s" r="J137" s="7">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="K137" s="7"/>
       <c r="L137" s="7"/>
@@ -5969,22 +5991,22 @@
       </c>
       <c r="D138" s="7"/>
       <c t="s" r="E138" s="7">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="F138" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G138" s="8">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c t="s" r="H138" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I138" s="7">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c t="s" r="J138" s="7">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="K138" s="7"/>
       <c r="L138" s="7"/>
@@ -6013,31 +6035,31 @@
         <v>7615</v>
       </c>
       <c t="s" r="C140" s="7">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="D140" s="7"/>
       <c t="s" r="E140" s="7">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="F140" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G140" s="8">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c t="s" r="H140" s="8">
         <v>43</v>
       </c>
       <c t="s" r="I140" s="7">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c t="s" r="J140" s="7">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="K140" s="7"/>
       <c r="L140" s="7"/>
       <c t="s" r="M140" s="7">
-        <v>245</v>
+        <v>247</v>
       </c>
     </row>
     <row r="141" ht="14.25" customHeight="1">
@@ -6048,11 +6070,11 @@
         <v>7615</v>
       </c>
       <c t="s" r="C141" s="7">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="D141" s="7"/>
       <c t="s" r="E141" s="7">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="F141" s="7">
         <v>321</v>
@@ -6061,13 +6083,13 @@
         <v>43</v>
       </c>
       <c t="s" r="H141" s="8">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c t="s" r="I141" s="7">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c t="s" r="J141" s="7">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="K141" s="7"/>
       <c r="L141" s="7"/>
@@ -6081,26 +6103,26 @@
         <v>7706</v>
       </c>
       <c t="s" r="C142" s="7">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="D142" s="7"/>
       <c t="s" r="E142" s="7">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="F142" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G142" s="8">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c t="s" r="H142" s="8">
         <v>43</v>
       </c>
       <c t="s" r="I142" s="7">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c t="s" r="J142" s="7">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="K142" s="7"/>
       <c r="L142" s="7"/>
@@ -6114,11 +6136,11 @@
         <v>7706</v>
       </c>
       <c t="s" r="C143" s="7">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="D143" s="7"/>
       <c t="s" r="E143" s="7">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="F143" s="7">
         <v>321</v>
@@ -6127,13 +6149,13 @@
         <v>43</v>
       </c>
       <c t="s" r="H143" s="8">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c t="s" r="I143" s="7">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c t="s" r="J143" s="7">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="K143" s="7"/>
       <c r="L143" s="7"/>
@@ -6159,14 +6181,14 @@
         <v>13</v>
       </c>
       <c t="s" r="B145" s="7">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c t="s" r="C145" s="7">
         <v>14</v>
       </c>
       <c r="D145" s="7"/>
       <c t="s" r="E145" s="7">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="F145" s="7">
         <v>321</v>
@@ -6181,12 +6203,12 @@
         <v>31</v>
       </c>
       <c t="s" r="J145" s="7">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="K145" s="7"/>
       <c r="L145" s="7"/>
       <c t="s" r="M145" s="7">
-        <v>254</v>
+        <v>256</v>
       </c>
     </row>
     <row r="146" ht="14.25" customHeight="1">
@@ -6201,7 +6223,7 @@
       </c>
       <c r="D146" s="7"/>
       <c t="s" r="E146" s="7">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="F146" s="7">
         <v>321</v>
@@ -6210,18 +6232,18 @@
         <v>43</v>
       </c>
       <c t="s" r="H146" s="8">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c t="s" r="I146" s="7">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c t="s" r="J146" s="7">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="K146" s="7"/>
       <c r="L146" s="7"/>
       <c t="s" r="M146" s="7">
-        <v>256</v>
+        <v>258</v>
       </c>
     </row>
     <row r="147" ht="14.25" customHeight="1">
@@ -6236,13 +6258,13 @@
       </c>
       <c r="D147" s="7"/>
       <c t="s" r="E147" s="7">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="F147" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G147" s="8">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c t="s" r="H147" s="8">
         <v>43</v>
@@ -6251,7 +6273,7 @@
         <v>54</v>
       </c>
       <c t="s" r="J147" s="7">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="K147" s="7"/>
       <c r="L147" s="7"/>
@@ -6269,7 +6291,7 @@
       </c>
       <c r="D148" s="7"/>
       <c t="s" r="E148" s="7">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="F148" s="7">
         <v>321</v>
@@ -6278,13 +6300,13 @@
         <v>43</v>
       </c>
       <c t="s" r="H148" s="8">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c t="s" r="I148" s="7">
         <v>22</v>
       </c>
       <c t="s" r="J148" s="7">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="K148" s="7"/>
       <c r="L148" s="7"/>
@@ -6302,22 +6324,22 @@
       </c>
       <c r="D149" s="7"/>
       <c t="s" r="E149" s="7">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="F149" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G149" s="8">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c t="s" r="H149" s="8">
         <v>43</v>
       </c>
       <c t="s" r="I149" s="7">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c t="s" r="J149" s="7">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="K149" s="7"/>
       <c r="L149" s="7"/>
@@ -6350,7 +6372,7 @@
       </c>
       <c r="D151" s="7"/>
       <c t="s" r="E151" s="7">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="F151" s="7">
         <v>321</v>
@@ -6362,15 +6384,15 @@
         <v>21</v>
       </c>
       <c t="s" r="I151" s="7">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c t="s" r="J151" s="7">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="K151" s="7"/>
       <c r="L151" s="7"/>
       <c t="s" r="M151" s="7">
-        <v>260</v>
+        <v>262</v>
       </c>
     </row>
     <row r="152" ht="14.25" customHeight="1">
@@ -6385,7 +6407,7 @@
       </c>
       <c r="D152" s="7"/>
       <c t="s" r="E152" s="7">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="F152" s="7">
         <v>321</v>
@@ -6400,12 +6422,12 @@
         <v>74</v>
       </c>
       <c t="s" r="J152" s="7">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="K152" s="7"/>
       <c r="L152" s="7"/>
       <c t="s" r="M152" s="7">
-        <v>261</v>
+        <v>263</v>
       </c>
     </row>
     <row r="153" ht="14.25" customHeight="1">
@@ -6420,7 +6442,7 @@
       </c>
       <c r="D153" s="7"/>
       <c t="s" r="E153" s="7">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="F153" s="7">
         <v>321</v>
@@ -6429,13 +6451,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H153" s="8">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c t="s" r="I153" s="7">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c t="s" r="J153" s="7">
-        <v>90</v>
+        <v>77</v>
       </c>
       <c r="K153" s="7"/>
       <c r="L153" s="7"/>
@@ -6449,17 +6471,17 @@
         <v>5068</v>
       </c>
       <c t="s" r="C154" s="7">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="D154" s="7"/>
       <c t="s" r="E154" s="7">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="F154" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G154" s="8">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c t="s" r="H154" s="8">
         <v>43</v>
@@ -6468,7 +6490,7 @@
         <v>37</v>
       </c>
       <c t="s" r="J154" s="7">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="K154" s="7"/>
       <c r="L154" s="7"/>
@@ -6482,11 +6504,11 @@
         <v>5068</v>
       </c>
       <c t="s" r="C155" s="7">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="D155" s="7"/>
       <c t="s" r="E155" s="7">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="F155" s="7">
         <v>321</v>
@@ -6495,13 +6517,13 @@
         <v>43</v>
       </c>
       <c t="s" r="H155" s="8">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c t="s" r="I155" s="7">
         <v>70</v>
       </c>
       <c t="s" r="J155" s="7">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="K155" s="7"/>
       <c r="L155" s="7"/>
@@ -6515,17 +6537,17 @@
         <v>5069</v>
       </c>
       <c t="s" r="C156" s="7">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="D156" s="7"/>
       <c t="s" r="E156" s="7">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="F156" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G156" s="8">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c t="s" r="H156" s="8">
         <v>43</v>
@@ -6534,7 +6556,7 @@
         <v>30</v>
       </c>
       <c t="s" r="J156" s="7">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="K156" s="7"/>
       <c r="L156" s="7"/>
@@ -6567,7 +6589,7 @@
       </c>
       <c r="D158" s="7"/>
       <c t="s" r="E158" s="7">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="F158" s="7">
         <v>321</v>
@@ -6579,15 +6601,15 @@
         <v>33</v>
       </c>
       <c t="s" r="I158" s="7">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c t="s" r="J158" s="7">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="K158" s="7"/>
       <c r="L158" s="7"/>
       <c t="s" r="M158" s="7">
-        <v>267</v>
+        <v>269</v>
       </c>
     </row>
     <row r="159" ht="14.25" customHeight="1">
@@ -6602,7 +6624,7 @@
       </c>
       <c r="D159" s="7"/>
       <c t="s" r="E159" s="7">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="F159" s="7">
         <v>321</v>
@@ -6614,10 +6636,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I159" s="7">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c t="s" r="J159" s="7">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="K159" s="7"/>
       <c r="L159" s="7"/>
@@ -6635,7 +6657,7 @@
       </c>
       <c r="D160" s="7"/>
       <c t="s" r="E160" s="7">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="F160" s="7">
         <v>321</v>
@@ -6647,10 +6669,10 @@
         <v>42</v>
       </c>
       <c t="s" r="I160" s="7">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c t="s" r="J160" s="7">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="K160" s="7"/>
       <c r="L160" s="7"/>
@@ -6683,7 +6705,7 @@
       </c>
       <c r="D162" s="7"/>
       <c t="s" r="E162" s="7">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="F162" s="7">
         <v>321</v>
@@ -6692,18 +6714,18 @@
         <v>17</v>
       </c>
       <c t="s" r="H162" s="8">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c t="s" r="I162" s="7">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c t="s" r="J162" s="7">
-        <v>90</v>
+        <v>77</v>
       </c>
       <c r="K162" s="7"/>
       <c r="L162" s="7"/>
       <c t="s" r="M162" s="7">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="163" ht="14.25" customHeight="1">
@@ -6718,22 +6740,22 @@
       </c>
       <c r="D163" s="7"/>
       <c t="s" r="E163" s="7">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="F163" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G163" s="8">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c t="s" r="H163" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I163" s="7">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c t="s" r="J163" s="7">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="K163" s="7"/>
       <c r="L163" s="7"/>
@@ -6751,7 +6773,7 @@
       </c>
       <c r="D164" s="7"/>
       <c t="s" r="E164" s="7">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="F164" s="7">
         <v>321</v>
@@ -6760,13 +6782,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H164" s="8">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c t="s" r="I164" s="7">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c t="s" r="J164" s="7">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="K164" s="7"/>
       <c r="L164" s="7"/>
@@ -6784,22 +6806,22 @@
       </c>
       <c r="D165" s="7"/>
       <c t="s" r="E165" s="7">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="F165" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G165" s="8">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c t="s" r="H165" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I165" s="7">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c t="s" r="J165" s="7">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="K165" s="7"/>
       <c r="L165" s="7"/>
@@ -6817,7 +6839,7 @@
       </c>
       <c r="D166" s="7"/>
       <c t="s" r="E166" s="7">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="F166" s="7">
         <v>321</v>
@@ -6826,13 +6848,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H166" s="8">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c t="s" r="I166" s="7">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c t="s" r="J166" s="7">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="K166" s="7"/>
       <c r="L166" s="7"/>
@@ -6850,22 +6872,22 @@
       </c>
       <c r="D167" s="7"/>
       <c t="s" r="E167" s="7">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="F167" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G167" s="8">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c t="s" r="H167" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I167" s="7">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c t="s" r="J167" s="7">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="K167" s="7"/>
       <c r="L167" s="7"/>
@@ -6898,7 +6920,7 @@
       </c>
       <c r="D169" s="7"/>
       <c t="s" r="E169" s="7">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="F169" s="7">
         <v>321</v>
@@ -6910,15 +6932,15 @@
         <v>17</v>
       </c>
       <c t="s" r="I169" s="7">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c t="s" r="J169" s="7">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="K169" s="7"/>
       <c r="L169" s="7"/>
       <c t="s" r="M169" s="7">
-        <v>281</v>
+        <v>283</v>
       </c>
     </row>
     <row r="170" ht="15" customHeight="1">
@@ -6948,7 +6970,7 @@
       </c>
       <c r="D171" s="7"/>
       <c t="s" r="E171" s="7">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="F171" s="7">
         <v>321</v>
@@ -6960,15 +6982,15 @@
         <v>17</v>
       </c>
       <c t="s" r="I171" s="7">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c t="s" r="J171" s="7">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="K171" s="7"/>
       <c r="L171" s="7"/>
       <c t="s" r="M171" s="7">
-        <v>284</v>
+        <v>286</v>
       </c>
     </row>
     <row r="172" ht="14.25" customHeight="1">
@@ -6983,7 +7005,7 @@
       </c>
       <c r="D172" s="7"/>
       <c t="s" r="E172" s="7">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="F172" s="7">
         <v>321</v>
@@ -6995,15 +7017,15 @@
         <v>98</v>
       </c>
       <c t="s" r="I172" s="7">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c t="s" r="J172" s="7">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="K172" s="7"/>
       <c r="L172" s="7"/>
       <c t="s" r="M172" s="7">
-        <v>285</v>
+        <v>287</v>
       </c>
     </row>
     <row r="173" ht="14.25" customHeight="1">
@@ -7018,7 +7040,7 @@
       </c>
       <c r="D173" s="7"/>
       <c t="s" r="E173" s="7">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="F173" s="7">
         <v>321</v>
@@ -7033,11 +7055,13 @@
         <v>74</v>
       </c>
       <c t="s" r="J173" s="7">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="K173" s="7"/>
       <c r="L173" s="7"/>
-      <c r="M173" s="7"/>
+      <c t="s" r="M173" s="7">
+        <v>223</v>
+      </c>
     </row>
     <row r="174" ht="14.25" customHeight="1">
       <c t="s" r="A174" s="6">
@@ -7051,7 +7075,7 @@
       </c>
       <c r="D174" s="7"/>
       <c t="s" r="E174" s="7">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="F174" s="7">
         <v>321</v>
@@ -7060,10 +7084,10 @@
         <v>17</v>
       </c>
       <c t="s" r="H174" s="8">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c t="s" r="I174" s="7">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c t="s" r="J174" s="7">
         <v>69</v>
@@ -7084,22 +7108,22 @@
       </c>
       <c r="D175" s="7"/>
       <c t="s" r="E175" s="7">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="F175" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G175" s="8">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c t="s" r="H175" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I175" s="7">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c t="s" r="J175" s="7">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="K175" s="7"/>
       <c r="L175" s="7"/>
@@ -7117,7 +7141,7 @@
       </c>
       <c r="D176" s="7"/>
       <c t="s" r="E176" s="7">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="F176" s="7">
         <v>321</v>
@@ -7126,13 +7150,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H176" s="8">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c t="s" r="I176" s="7">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c t="s" r="J176" s="7">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="K176" s="7"/>
       <c r="L176" s="7"/>
@@ -7150,22 +7174,22 @@
       </c>
       <c r="D177" s="7"/>
       <c t="s" r="E177" s="7">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="F177" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G177" s="8">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c t="s" r="H177" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I177" s="7">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c t="s" r="J177" s="7">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="K177" s="7"/>
       <c r="L177" s="7"/>
@@ -7198,7 +7222,7 @@
       </c>
       <c r="D179" s="7"/>
       <c t="s" r="E179" s="7">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="F179" s="7">
         <v>321</v>
@@ -7207,7 +7231,7 @@
         <v>43</v>
       </c>
       <c t="s" r="H179" s="8">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c t="s" r="I179" s="7">
         <v>73</v>
@@ -7218,7 +7242,7 @@
       <c r="K179" s="7"/>
       <c r="L179" s="7"/>
       <c t="s" r="M179" s="7">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="180" ht="15" customHeight="1">
@@ -7233,22 +7257,22 @@
       </c>
       <c r="D180" s="7"/>
       <c t="s" r="E180" s="7">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="F180" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G180" s="8">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c t="s" r="H180" s="8">
         <v>43</v>
       </c>
       <c t="s" r="I180" s="7">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c t="s" r="J180" s="7">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="K180" s="7"/>
       <c r="L180" s="7"/>
@@ -7266,7 +7290,7 @@
       </c>
       <c r="D181" s="7"/>
       <c t="s" r="E181" s="7">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="F181" s="7">
         <v>321</v>
@@ -7281,7 +7305,7 @@
         <v>28</v>
       </c>
       <c t="s" r="J181" s="7">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="K181" s="7"/>
       <c r="L181" s="7"/>
@@ -7314,7 +7338,7 @@
       </c>
       <c r="D183" s="7"/>
       <c t="s" r="E183" s="7">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="F183" s="7">
         <v>321</v>
@@ -7323,18 +7347,18 @@
         <v>17</v>
       </c>
       <c t="s" r="H183" s="8">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c t="s" r="I183" s="7">
         <v>96</v>
       </c>
       <c t="s" r="J183" s="7">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="K183" s="7"/>
       <c r="L183" s="7"/>
       <c t="s" r="M183" s="7">
-        <v>295</v>
+        <v>297</v>
       </c>
     </row>
     <row r="184" ht="14.25" customHeight="1">
@@ -7349,22 +7373,22 @@
       </c>
       <c r="D184" s="7"/>
       <c t="s" r="E184" s="7">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="F184" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G184" s="8">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c t="s" r="H184" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I184" s="7">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c t="s" r="J184" s="7">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="K184" s="7"/>
       <c r="L184" s="7"/>
@@ -7382,7 +7406,7 @@
       </c>
       <c r="D185" s="7"/>
       <c t="s" r="E185" s="7">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="F185" s="7">
         <v>321</v>
@@ -7394,13 +7418,13 @@
         <v>43</v>
       </c>
       <c t="s" r="I185" s="7">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c t="s" r="J185" s="7">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c t="s" r="K185" s="7">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="L185" s="7"/>
       <c t="s" r="M185" s="7">
@@ -7419,7 +7443,7 @@
       </c>
       <c r="D186" s="7"/>
       <c t="s" r="E186" s="7">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="F186" s="7">
         <v>321</v>
@@ -7434,7 +7458,7 @@
         <v>24</v>
       </c>
       <c t="s" r="J186" s="7">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="K186" s="7"/>
       <c r="L186" s="7"/>
@@ -7452,7 +7476,7 @@
       </c>
       <c r="D187" s="7"/>
       <c t="s" r="E187" s="7">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="F187" s="7">
         <v>321</v>
@@ -7464,17 +7488,17 @@
         <v>43</v>
       </c>
       <c t="s" r="I187" s="7">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c t="s" r="J187" s="7">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c t="s" r="K187" s="7">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="L187" s="7"/>
       <c t="s" r="M187" s="7">
-        <v>201</v>
+        <v>203</v>
       </c>
     </row>
     <row r="188" ht="14.25" customHeight="1">
@@ -7504,7 +7528,7 @@
       </c>
       <c r="D189" s="7"/>
       <c t="s" r="E189" s="7">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="F189" s="7">
         <v>321</v>
@@ -7513,18 +7537,18 @@
         <v>16</v>
       </c>
       <c t="s" r="H189" s="8">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c t="s" r="I189" s="7">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c t="s" r="J189" s="7">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="K189" s="7"/>
       <c r="L189" s="7"/>
       <c t="s" r="M189" s="7">
-        <v>300</v>
+        <v>302</v>
       </c>
     </row>
     <row r="190" ht="15" customHeight="1">
@@ -7539,22 +7563,22 @@
       </c>
       <c r="D190" s="7"/>
       <c t="s" r="E190" s="7">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="F190" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G190" s="8">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c t="s" r="H190" s="8">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c t="s" r="I190" s="7">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c t="s" r="J190" s="7">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="K190" s="7"/>
       <c r="L190" s="7"/>
@@ -7572,22 +7596,22 @@
       </c>
       <c r="D191" s="7"/>
       <c t="s" r="E191" s="7">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="F191" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G191" s="8">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c t="s" r="H191" s="8">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c t="s" r="I191" s="7">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c t="s" r="J191" s="7">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="K191" s="7"/>
       <c r="L191" s="7"/>
@@ -7620,7 +7644,7 @@
       </c>
       <c r="D193" s="7"/>
       <c t="s" r="E193" s="7">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="F193" s="7">
         <v>321</v>
@@ -7629,18 +7653,18 @@
         <v>17</v>
       </c>
       <c t="s" r="H193" s="8">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c t="s" r="I193" s="7">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c t="s" r="J193" s="7">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="K193" s="7"/>
       <c r="L193" s="7"/>
       <c t="s" r="M193" s="7">
-        <v>306</v>
+        <v>308</v>
       </c>
     </row>
     <row r="194" ht="14.25" customHeight="1">
@@ -7655,19 +7679,19 @@
       </c>
       <c r="D194" s="7"/>
       <c t="s" r="E194" s="7">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="F194" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G194" s="8">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c t="s" r="H194" s="8">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c t="s" r="I194" s="7">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c t="s" r="J194" s="7">
         <v>34</v>
@@ -7675,7 +7699,7 @@
       <c r="K194" s="7"/>
       <c r="L194" s="7"/>
       <c t="s" r="M194" s="7">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="195" ht="15" customHeight="1">
@@ -7690,27 +7714,27 @@
       </c>
       <c r="D195" s="7"/>
       <c t="s" r="E195" s="7">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="F195" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G195" s="8">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c t="s" r="H195" s="8">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c t="s" r="I195" s="7">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c t="s" r="J195" s="7">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="K195" s="7"/>
       <c r="L195" s="7"/>
       <c t="s" r="M195" s="7">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="196" ht="14.25" customHeight="1">
@@ -7725,13 +7749,13 @@
       </c>
       <c r="D196" s="7"/>
       <c t="s" r="E196" s="7">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="F196" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G196" s="8">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c t="s" r="H196" s="8">
         <v>17</v>
@@ -7744,7 +7768,9 @@
       </c>
       <c r="K196" s="7"/>
       <c r="L196" s="7"/>
-      <c r="M196" s="7"/>
+      <c t="s" r="M196" s="7">
+        <v>311</v>
+      </c>
     </row>
     <row r="197" ht="14.25" customHeight="1">
       <c t="s" r="A197" s="6">
@@ -7758,7 +7784,7 @@
       </c>
       <c r="D197" s="7"/>
       <c t="s" r="E197" s="7">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="F197" s="7">
         <v>321</v>
@@ -7767,13 +7793,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H197" s="8">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c t="s" r="I197" s="7">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c t="s" r="J197" s="7">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="K197" s="7"/>
       <c r="L197" s="7"/>
@@ -7791,22 +7817,22 @@
       </c>
       <c r="D198" s="7"/>
       <c t="s" r="E198" s="7">
+        <v>305</v>
+      </c>
+      <c r="F198" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G198" s="8">
+        <v>241</v>
+      </c>
+      <c t="s" r="H198" s="8">
+        <v>17</v>
+      </c>
+      <c t="s" r="I198" s="7">
         <v>303</v>
       </c>
-      <c r="F198" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G198" s="8">
-        <v>239</v>
-      </c>
-      <c t="s" r="H198" s="8">
-        <v>17</v>
-      </c>
-      <c t="s" r="I198" s="7">
-        <v>301</v>
-      </c>
       <c t="s" r="J198" s="7">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="K198" s="7"/>
       <c r="L198" s="7"/>
@@ -7824,7 +7850,7 @@
       </c>
       <c r="D199" s="7"/>
       <c t="s" r="E199" s="7">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="F199" s="7">
         <v>321</v>
@@ -7833,20 +7859,20 @@
         <v>17</v>
       </c>
       <c t="s" r="H199" s="8">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c t="s" r="I199" s="7">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c t="s" r="J199" s="7">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c t="s" r="K199" s="7">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="L199" s="7"/>
       <c t="s" r="M199" s="7">
-        <v>310</v>
+        <v>313</v>
       </c>
     </row>
     <row r="200" ht="15" customHeight="1">
@@ -7861,29 +7887,29 @@
       </c>
       <c r="D200" s="7"/>
       <c t="s" r="E200" s="7">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="F200" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G200" s="8">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c t="s" r="H200" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I200" s="7">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c t="s" r="J200" s="7">
         <v>48</v>
       </c>
       <c t="s" r="K200" s="7">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="L200" s="7"/>
       <c t="s" r="M200" s="7">
-        <v>224</v>
+        <v>226</v>
       </c>
     </row>
     <row r="201" ht="14.25" customHeight="1">
@@ -7913,27 +7939,27 @@
       </c>
       <c r="D202" s="7"/>
       <c t="s" r="E202" s="7">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="F202" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G202" s="8">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c t="s" r="H202" s="8">
         <v>43</v>
       </c>
       <c t="s" r="I202" s="7">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c t="s" r="J202" s="7">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="K202" s="7"/>
       <c r="L202" s="7"/>
       <c t="s" r="M202" s="7">
-        <v>313</v>
+        <v>316</v>
       </c>
     </row>
     <row r="203" ht="14.25" customHeight="1">
@@ -7948,7 +7974,7 @@
       </c>
       <c r="D203" s="7"/>
       <c t="s" r="E203" s="7">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="F203" s="7">
         <v>321</v>
@@ -7957,17 +7983,19 @@
         <v>43</v>
       </c>
       <c t="s" r="H203" s="8">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c t="s" r="I203" s="7">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c t="s" r="J203" s="7">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="K203" s="7"/>
       <c r="L203" s="7"/>
-      <c r="M203" s="7"/>
+      <c t="s" r="M203" s="7">
+        <v>209</v>
+      </c>
     </row>
     <row r="204" ht="14.25" customHeight="1">
       <c t="s" r="A204" s="6">
@@ -7981,13 +8009,13 @@
       </c>
       <c r="D204" s="7"/>
       <c t="s" r="E204" s="7">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="F204" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G204" s="8">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c t="s" r="H204" s="8">
         <v>43</v>
@@ -8014,7 +8042,7 @@
       </c>
       <c r="D205" s="7"/>
       <c t="s" r="E205" s="7">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="F205" s="7">
         <v>321</v>
@@ -8023,13 +8051,13 @@
         <v>43</v>
       </c>
       <c t="s" r="H205" s="8">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c t="s" r="I205" s="7">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c t="s" r="J205" s="7">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="K205" s="7"/>
       <c r="L205" s="7"/>
@@ -8047,13 +8075,13 @@
       </c>
       <c r="D206" s="7"/>
       <c t="s" r="E206" s="7">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="F206" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G206" s="8">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c t="s" r="H206" s="8">
         <v>43</v>
@@ -8062,7 +8090,7 @@
         <v>59</v>
       </c>
       <c t="s" r="J206" s="7">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="K206" s="7"/>
       <c r="L206" s="7"/>
@@ -8080,7 +8108,7 @@
       </c>
       <c r="D207" s="7"/>
       <c t="s" r="E207" s="7">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="F207" s="7">
         <v>321</v>
@@ -8092,10 +8120,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I207" s="7">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c t="s" r="J207" s="7">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="K207" s="7"/>
       <c r="L207" s="7"/>
@@ -8113,7 +8141,7 @@
       </c>
       <c r="D208" s="7"/>
       <c t="s" r="E208" s="7">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="F208" s="7">
         <v>321</v>
@@ -8125,7 +8153,7 @@
         <v>43</v>
       </c>
       <c t="s" r="I208" s="7">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c t="s" r="J208" s="7">
         <v>60</v>
@@ -8161,7 +8189,7 @@
       </c>
       <c r="D210" s="7"/>
       <c t="s" r="E210" s="7">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="F210" s="7">
         <v>321</v>
@@ -8170,18 +8198,18 @@
         <v>17</v>
       </c>
       <c t="s" r="H210" s="8">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c t="s" r="I210" s="7">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c t="s" r="J210" s="7">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="K210" s="7"/>
       <c r="L210" s="7"/>
       <c t="s" r="M210" s="7">
-        <v>316</v>
+        <v>319</v>
       </c>
     </row>
     <row r="211" ht="14.25" customHeight="1">
@@ -8196,27 +8224,27 @@
       </c>
       <c r="D211" s="7"/>
       <c t="s" r="E211" s="7">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="F211" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G211" s="8">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c t="s" r="H211" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I211" s="7">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c t="s" r="J211" s="7">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="K211" s="7"/>
       <c r="L211" s="7"/>
       <c t="s" r="M211" s="7">
-        <v>318</v>
+        <v>321</v>
       </c>
     </row>
     <row r="212" ht="14.25" customHeight="1">
@@ -8231,7 +8259,7 @@
       </c>
       <c r="D212" s="7"/>
       <c t="s" r="E212" s="7">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="F212" s="7">
         <v>321</v>
@@ -8246,7 +8274,7 @@
         <v>45</v>
       </c>
       <c t="s" r="J212" s="7">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="K212" s="7"/>
       <c r="L212" s="7"/>
@@ -8264,7 +8292,7 @@
       </c>
       <c r="D213" s="7"/>
       <c t="s" r="E213" s="7">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="F213" s="7">
         <v>321</v>
@@ -8276,10 +8304,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I213" s="7">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c t="s" r="J213" s="7">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="K213" s="7"/>
       <c r="L213" s="7"/>
@@ -8297,7 +8325,7 @@
       </c>
       <c r="D214" s="7"/>
       <c t="s" r="E214" s="7">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="F214" s="7">
         <v>321</v>
@@ -8312,7 +8340,7 @@
         <v>25</v>
       </c>
       <c t="s" r="J214" s="7">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="K214" s="7"/>
       <c r="L214" s="7"/>
@@ -8330,7 +8358,7 @@
       </c>
       <c r="D215" s="7"/>
       <c t="s" r="E215" s="7">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="F215" s="7">
         <v>321</v>
@@ -8342,10 +8370,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I215" s="7">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c t="s" r="J215" s="7">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="K215" s="7"/>
       <c r="L215" s="7"/>
@@ -8378,7 +8406,7 @@
       </c>
       <c r="D217" s="7"/>
       <c t="s" r="E217" s="7">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="F217" s="7">
         <v>321</v>
@@ -8390,15 +8418,15 @@
         <v>17</v>
       </c>
       <c t="s" r="I217" s="7">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c t="s" r="J217" s="7">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="K217" s="7"/>
       <c r="L217" s="7"/>
       <c t="s" r="M217" s="7">
-        <v>323</v>
+        <v>326</v>
       </c>
     </row>
     <row r="218" ht="14.25" customHeight="1">
@@ -8413,7 +8441,7 @@
       </c>
       <c r="D218" s="7"/>
       <c t="s" r="E218" s="7">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="F218" s="7">
         <v>321</v>
@@ -8422,17 +8450,19 @@
         <v>17</v>
       </c>
       <c t="s" r="H218" s="8">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c t="s" r="I218" s="7">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c t="s" r="J218" s="7">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="K218" s="7"/>
       <c r="L218" s="7"/>
-      <c r="M218" s="7"/>
+      <c t="s" r="M218" s="7">
+        <v>327</v>
+      </c>
     </row>
     <row r="219" ht="14.25" customHeight="1">
       <c t="s" r="A219" s="6">
@@ -8446,22 +8476,22 @@
       </c>
       <c r="D219" s="7"/>
       <c t="s" r="E219" s="7">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="F219" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G219" s="8">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c t="s" r="H219" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I219" s="7">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c t="s" r="J219" s="7">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="K219" s="7"/>
       <c r="L219" s="7"/>
@@ -8479,7 +8509,7 @@
       </c>
       <c r="D220" s="7"/>
       <c t="s" r="E220" s="7">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="F220" s="7">
         <v>321</v>
@@ -8488,13 +8518,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H220" s="8">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c t="s" r="I220" s="7">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c t="s" r="J220" s="7">
-        <v>324</v>
+        <v>328</v>
       </c>
       <c r="K220" s="7"/>
       <c r="L220" s="7"/>
@@ -8512,22 +8542,22 @@
       </c>
       <c r="D221" s="7"/>
       <c t="s" r="E221" s="7">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="F221" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G221" s="8">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c t="s" r="H221" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I221" s="7">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c t="s" r="J221" s="7">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="K221" s="7"/>
       <c r="L221" s="7"/>
@@ -8560,7 +8590,7 @@
       </c>
       <c r="D223" s="7"/>
       <c t="s" r="E223" s="7">
-        <v>325</v>
+        <v>329</v>
       </c>
       <c r="F223" s="7">
         <v>321</v>
@@ -8569,10 +8599,10 @@
         <v>16</v>
       </c>
       <c t="s" r="H223" s="8">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c t="s" r="I223" s="7">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c t="s" r="J223" s="7">
         <v>66</v>
@@ -8580,7 +8610,7 @@
       <c r="K223" s="7"/>
       <c r="L223" s="7"/>
       <c t="s" r="M223" s="7">
-        <v>326</v>
+        <v>330</v>
       </c>
     </row>
     <row r="224" ht="14.25" customHeight="1">
@@ -8595,27 +8625,27 @@
       </c>
       <c r="D224" s="7"/>
       <c t="s" r="E224" s="7">
-        <v>325</v>
+        <v>329</v>
       </c>
       <c r="F224" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G224" s="8">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c t="s" r="H224" s="8">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c t="s" r="I224" s="7">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c t="s" r="J224" s="7">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="K224" s="7"/>
       <c r="L224" s="7"/>
       <c t="s" r="M224" s="7">
-        <v>328</v>
+        <v>332</v>
       </c>
     </row>
     <row r="225" ht="15" customHeight="1">
@@ -8630,19 +8660,19 @@
       </c>
       <c r="D225" s="7"/>
       <c t="s" r="E225" s="7">
-        <v>325</v>
+        <v>329</v>
       </c>
       <c r="F225" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G225" s="8">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c t="s" r="H225" s="8">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c t="s" r="I225" s="7">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c t="s" r="J225" s="7">
         <v>69</v>
@@ -8663,13 +8693,13 @@
       </c>
       <c r="D226" s="7"/>
       <c t="s" r="E226" s="7">
-        <v>325</v>
+        <v>329</v>
       </c>
       <c r="F226" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G226" s="8">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c t="s" r="H226" s="8">
         <v>17</v>
@@ -8678,7 +8708,7 @@
         <v>24</v>
       </c>
       <c t="s" r="J226" s="7">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="K226" s="7"/>
       <c r="L226" s="7"/>
@@ -8711,7 +8741,7 @@
       </c>
       <c r="D228" s="7"/>
       <c t="s" r="E228" s="7">
-        <v>329</v>
+        <v>333</v>
       </c>
       <c r="F228" s="7">
         <v>321</v>
@@ -8723,7 +8753,7 @@
         <v>43</v>
       </c>
       <c t="s" r="I228" s="7">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c t="s" r="J228" s="7">
         <v>35</v>
@@ -8731,7 +8761,7 @@
       <c r="K228" s="7"/>
       <c r="L228" s="7"/>
       <c t="s" r="M228" s="7">
-        <v>331</v>
+        <v>335</v>
       </c>
     </row>
     <row r="229" ht="14.25" customHeight="1">
@@ -8746,7 +8776,7 @@
       </c>
       <c r="D229" s="7"/>
       <c t="s" r="E229" s="7">
-        <v>329</v>
+        <v>333</v>
       </c>
       <c r="F229" s="7">
         <v>321</v>
@@ -8761,7 +8791,7 @@
         <v>37</v>
       </c>
       <c t="s" r="J229" s="7">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="K229" s="7"/>
       <c r="L229" s="7"/>
@@ -8779,7 +8809,7 @@
       </c>
       <c r="D230" s="7"/>
       <c t="s" r="E230" s="7">
-        <v>329</v>
+        <v>333</v>
       </c>
       <c r="F230" s="7">
         <v>321</v>
@@ -8794,7 +8824,7 @@
         <v>91</v>
       </c>
       <c t="s" r="J230" s="7">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="K230" s="7"/>
       <c r="L230" s="7"/>
@@ -8812,7 +8842,7 @@
       </c>
       <c r="D231" s="7"/>
       <c t="s" r="E231" s="7">
-        <v>329</v>
+        <v>333</v>
       </c>
       <c r="F231" s="7">
         <v>321</v>
@@ -8824,10 +8854,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I231" s="7">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c t="s" r="J231" s="7">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="K231" s="7"/>
       <c r="L231" s="7"/>
@@ -8860,27 +8890,27 @@
       </c>
       <c r="D233" s="7"/>
       <c t="s" r="E233" s="7">
-        <v>332</v>
+        <v>336</v>
       </c>
       <c r="F233" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G233" s="8">
-        <v>333</v>
+        <v>337</v>
       </c>
       <c t="s" r="H233" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I233" s="7">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c t="s" r="J233" s="7">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="K233" s="7"/>
       <c r="L233" s="7"/>
       <c t="s" r="M233" s="7">
-        <v>334</v>
+        <v>338</v>
       </c>
     </row>
     <row r="234" ht="14.25" customHeight="1">
@@ -8895,7 +8925,7 @@
       </c>
       <c r="D234" s="7"/>
       <c t="s" r="E234" s="7">
-        <v>332</v>
+        <v>336</v>
       </c>
       <c r="F234" s="7">
         <v>321</v>
@@ -8904,13 +8934,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H234" s="8">
-        <v>333</v>
+        <v>337</v>
       </c>
       <c t="s" r="I234" s="7">
         <v>71</v>
       </c>
       <c t="s" r="J234" s="7">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="K234" s="7"/>
       <c r="L234" s="7"/>
@@ -8943,7 +8973,7 @@
       </c>
       <c r="D236" s="7"/>
       <c t="s" r="E236" s="7">
-        <v>335</v>
+        <v>339</v>
       </c>
       <c r="F236" s="7">
         <v>321</v>
@@ -8955,7 +8985,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I236" s="7">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c t="s" r="J236" s="7">
         <v>44</v>
@@ -8978,7 +9008,7 @@
       </c>
       <c r="D237" s="7"/>
       <c t="s" r="E237" s="7">
-        <v>335</v>
+        <v>339</v>
       </c>
       <c r="F237" s="7">
         <v>321</v>
@@ -8990,15 +9020,15 @@
         <v>43</v>
       </c>
       <c t="s" r="I237" s="7">
-        <v>336</v>
+        <v>340</v>
       </c>
       <c t="s" r="J237" s="7">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="K237" s="7"/>
       <c r="L237" s="7"/>
       <c t="s" r="M237" s="7">
-        <v>266</v>
+        <v>341</v>
       </c>
     </row>
     <row r="238" ht="14.25" customHeight="1">
@@ -9013,7 +9043,7 @@
       </c>
       <c r="D238" s="7"/>
       <c t="s" r="E238" s="7">
-        <v>335</v>
+        <v>339</v>
       </c>
       <c r="F238" s="7">
         <v>321</v>
@@ -9028,14 +9058,14 @@
         <v>54</v>
       </c>
       <c t="s" r="J238" s="7">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c t="s" r="K238" s="7">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="L238" s="7"/>
       <c t="s" r="M238" s="7">
-        <v>338</v>
+        <v>343</v>
       </c>
     </row>
     <row r="239" ht="14.25" customHeight="1">
@@ -9050,7 +9080,7 @@
       </c>
       <c r="D239" s="7"/>
       <c t="s" r="E239" s="7">
-        <v>335</v>
+        <v>339</v>
       </c>
       <c r="F239" s="7">
         <v>321</v>
@@ -9062,17 +9092,17 @@
         <v>43</v>
       </c>
       <c t="s" r="I239" s="7">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c t="s" r="J239" s="7">
         <v>59</v>
       </c>
       <c t="s" r="K239" s="7">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="L239" s="7"/>
       <c t="s" r="M239" s="7">
-        <v>163</v>
+        <v>164</v>
       </c>
     </row>
     <row r="240" ht="15" customHeight="1">
@@ -9087,7 +9117,7 @@
       </c>
       <c r="D240" s="7"/>
       <c t="s" r="E240" s="7">
-        <v>335</v>
+        <v>339</v>
       </c>
       <c r="F240" s="7">
         <v>321</v>
@@ -9099,14 +9129,18 @@
         <v>98</v>
       </c>
       <c t="s" r="I240" s="7">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c t="s" r="J240" s="7">
         <v>48</v>
       </c>
-      <c r="K240" s="7"/>
+      <c t="s" r="K240" s="7">
+        <v>146</v>
+      </c>
       <c r="L240" s="7"/>
-      <c r="M240" s="7"/>
+      <c t="s" r="M240" s="7">
+        <v>192</v>
+      </c>
     </row>
     <row r="241" ht="14.25" customHeight="1">
       <c t="s" r="A241" s="6">
@@ -9120,7 +9154,7 @@
       </c>
       <c r="D241" s="7"/>
       <c t="s" r="E241" s="7">
-        <v>335</v>
+        <v>339</v>
       </c>
       <c r="F241" s="7">
         <v>321</v>
@@ -9132,14 +9166,18 @@
         <v>43</v>
       </c>
       <c t="s" r="I241" s="7">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c t="s" r="J241" s="7">
-        <v>339</v>
-      </c>
-      <c r="K241" s="7"/>
+        <v>344</v>
+      </c>
+      <c t="s" r="K241" s="7">
+        <v>345</v>
+      </c>
       <c r="L241" s="7"/>
-      <c r="M241" s="7"/>
+      <c t="s" r="M241" s="7">
+        <v>346</v>
+      </c>
     </row>
     <row r="242" ht="14.25" customHeight="1">
       <c t="s" r="A242" s="6">
@@ -9153,7 +9191,7 @@
       </c>
       <c r="D242" s="7"/>
       <c t="s" r="E242" s="7">
-        <v>335</v>
+        <v>339</v>
       </c>
       <c r="F242" s="7">
         <v>321</v>
@@ -9162,13 +9200,13 @@
         <v>43</v>
       </c>
       <c t="s" r="H242" s="8">
-        <v>340</v>
+        <v>347</v>
       </c>
       <c t="s" r="I242" s="7">
-        <v>341</v>
+        <v>348</v>
       </c>
       <c t="s" r="J242" s="7">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="K242" s="7"/>
       <c r="L242" s="7"/>
@@ -9201,27 +9239,27 @@
       </c>
       <c r="D244" s="7"/>
       <c t="s" r="E244" s="7">
-        <v>342</v>
+        <v>349</v>
       </c>
       <c r="F244" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G244" s="8">
-        <v>343</v>
+        <v>350</v>
       </c>
       <c t="s" r="H244" s="8">
         <v>43</v>
       </c>
       <c t="s" r="I244" s="7">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c t="s" r="J244" s="7">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="K244" s="7"/>
       <c r="L244" s="7"/>
       <c t="s" r="M244" s="7">
-        <v>344</v>
+        <v>351</v>
       </c>
     </row>
     <row r="245" ht="15" customHeight="1">
@@ -9236,7 +9274,7 @@
       </c>
       <c r="D245" s="7"/>
       <c t="s" r="E245" s="7">
-        <v>342</v>
+        <v>349</v>
       </c>
       <c r="F245" s="7">
         <v>321</v>
@@ -9245,13 +9283,13 @@
         <v>43</v>
       </c>
       <c t="s" r="H245" s="8">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c t="s" r="I245" s="7">
         <v>18</v>
       </c>
       <c t="s" r="J245" s="7">
-        <v>90</v>
+        <v>77</v>
       </c>
       <c r="K245" s="7"/>
       <c r="L245" s="7"/>
@@ -9269,19 +9307,19 @@
       </c>
       <c r="D246" s="7"/>
       <c t="s" r="E246" s="7">
-        <v>342</v>
+        <v>349</v>
       </c>
       <c r="F246" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G246" s="8">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c t="s" r="H246" s="8">
         <v>43</v>
       </c>
       <c t="s" r="I246" s="7">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c t="s" r="J246" s="7">
         <v>58</v>
@@ -9302,7 +9340,7 @@
       </c>
       <c r="D247" s="7"/>
       <c t="s" r="E247" s="7">
-        <v>342</v>
+        <v>349</v>
       </c>
       <c r="F247" s="7">
         <v>321</v>
@@ -9311,13 +9349,13 @@
         <v>43</v>
       </c>
       <c t="s" r="H247" s="8">
-        <v>345</v>
+        <v>352</v>
       </c>
       <c t="s" r="I247" s="7">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c t="s" r="J247" s="7">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="K247" s="7"/>
       <c r="L247" s="7"/>
@@ -9335,13 +9373,13 @@
       </c>
       <c r="D248" s="7"/>
       <c t="s" r="E248" s="7">
-        <v>342</v>
+        <v>349</v>
       </c>
       <c r="F248" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G248" s="8">
-        <v>345</v>
+        <v>352</v>
       </c>
       <c t="s" r="H248" s="8">
         <v>43</v>
@@ -9350,7 +9388,7 @@
         <v>27</v>
       </c>
       <c t="s" r="J248" s="7">
-        <v>346</v>
+        <v>353</v>
       </c>
       <c r="K248" s="7"/>
       <c r="L248" s="7"/>
@@ -9368,7 +9406,7 @@
       </c>
       <c r="D249" s="7"/>
       <c t="s" r="E249" s="7">
-        <v>342</v>
+        <v>349</v>
       </c>
       <c r="F249" s="7">
         <v>321</v>
@@ -9377,10 +9415,10 @@
         <v>43</v>
       </c>
       <c t="s" r="H249" s="8">
-        <v>343</v>
+        <v>350</v>
       </c>
       <c t="s" r="I249" s="7">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c t="s" r="J249" s="7">
         <v>51</v>
@@ -9416,7 +9454,7 @@
       </c>
       <c r="D251" s="7"/>
       <c t="s" r="E251" s="7">
-        <v>347</v>
+        <v>354</v>
       </c>
       <c r="F251" s="7">
         <v>321</v>
@@ -9425,10 +9463,10 @@
         <v>43</v>
       </c>
       <c t="s" r="H251" s="8">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c t="s" r="I251" s="7">
-        <v>348</v>
+        <v>355</v>
       </c>
       <c t="s" r="J251" s="7">
         <v>63</v>
@@ -9436,7 +9474,7 @@
       <c r="K251" s="7"/>
       <c r="L251" s="7"/>
       <c t="s" r="M251" s="7">
-        <v>349</v>
+        <v>356</v>
       </c>
     </row>
     <row r="252" ht="14.25" customHeight="1">
@@ -9451,22 +9489,22 @@
       </c>
       <c r="D252" s="7"/>
       <c t="s" r="E252" s="7">
-        <v>347</v>
+        <v>354</v>
       </c>
       <c r="F252" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G252" s="8">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c t="s" r="H252" s="8">
-        <v>350</v>
+        <v>357</v>
       </c>
       <c t="s" r="I252" s="7">
         <v>37</v>
       </c>
       <c t="s" r="J252" s="7">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="K252" s="7"/>
       <c r="L252" s="7"/>
@@ -9484,22 +9522,22 @@
       </c>
       <c r="D253" s="7"/>
       <c t="s" r="E253" s="7">
-        <v>347</v>
+        <v>354</v>
       </c>
       <c r="F253" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G253" s="8">
-        <v>350</v>
+        <v>357</v>
       </c>
       <c t="s" r="H253" s="8">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c t="s" r="I253" s="7">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c t="s" r="J253" s="7">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="K253" s="7"/>
       <c r="L253" s="7"/>
@@ -9517,22 +9555,22 @@
       </c>
       <c r="D254" s="7"/>
       <c t="s" r="E254" s="7">
-        <v>347</v>
+        <v>354</v>
       </c>
       <c r="F254" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G254" s="8">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c t="s" r="H254" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I254" s="7">
-        <v>351</v>
+        <v>346</v>
       </c>
       <c t="s" r="J254" s="7">
-        <v>352</v>
+        <v>358</v>
       </c>
       <c r="K254" s="7"/>
       <c r="L254" s="7"/>
@@ -9565,7 +9603,7 @@
       </c>
       <c r="D256" s="7"/>
       <c t="s" r="E256" s="7">
-        <v>353</v>
+        <v>359</v>
       </c>
       <c r="F256" s="7">
         <v>321</v>
@@ -9577,15 +9615,15 @@
         <v>17</v>
       </c>
       <c t="s" r="I256" s="7">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c t="s" r="J256" s="7">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="K256" s="7"/>
       <c r="L256" s="7"/>
       <c t="s" r="M256" s="7">
-        <v>354</v>
+        <v>360</v>
       </c>
     </row>
     <row r="257" ht="14.25" customHeight="1">
@@ -9600,7 +9638,7 @@
       </c>
       <c r="D257" s="7"/>
       <c t="s" r="E257" s="7">
-        <v>353</v>
+        <v>359</v>
       </c>
       <c r="F257" s="7">
         <v>321</v>
@@ -9615,12 +9653,12 @@
         <v>96</v>
       </c>
       <c t="s" r="J257" s="7">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="K257" s="7"/>
       <c r="L257" s="7"/>
       <c t="s" r="M257" s="7">
-        <v>355</v>
+        <v>361</v>
       </c>
     </row>
     <row r="258" ht="14.25" customHeight="1">
@@ -9635,7 +9673,7 @@
       </c>
       <c r="D258" s="7"/>
       <c t="s" r="E258" s="7">
-        <v>353</v>
+        <v>359</v>
       </c>
       <c r="F258" s="7">
         <v>321</v>
@@ -9647,15 +9685,15 @@
         <v>17</v>
       </c>
       <c t="s" r="I258" s="7">
-        <v>344</v>
+        <v>351</v>
       </c>
       <c t="s" r="J258" s="7">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="K258" s="7"/>
       <c r="L258" s="7"/>
       <c t="s" r="M258" s="7">
-        <v>356</v>
+        <v>362</v>
       </c>
     </row>
     <row r="259" ht="14.25" customHeight="1">
@@ -9670,7 +9708,7 @@
       </c>
       <c r="D259" s="7"/>
       <c t="s" r="E259" s="7">
-        <v>353</v>
+        <v>359</v>
       </c>
       <c r="F259" s="7">
         <v>321</v>
@@ -9682,10 +9720,10 @@
         <v>43</v>
       </c>
       <c t="s" r="I259" s="7">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c t="s" r="J259" s="7">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="K259" s="7"/>
       <c r="L259" s="7"/>
@@ -9703,7 +9741,7 @@
       </c>
       <c r="D260" s="7"/>
       <c t="s" r="E260" s="7">
-        <v>353</v>
+        <v>359</v>
       </c>
       <c r="F260" s="7">
         <v>321</v>
@@ -9712,13 +9750,13 @@
         <v>43</v>
       </c>
       <c t="s" r="H260" s="8">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c t="s" r="I260" s="7">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c t="s" r="J260" s="7">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="K260" s="7"/>
       <c r="L260" s="7"/>
@@ -9736,22 +9774,22 @@
       </c>
       <c r="D261" s="7"/>
       <c t="s" r="E261" s="7">
-        <v>353</v>
+        <v>359</v>
       </c>
       <c r="F261" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G261" s="8">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c t="s" r="H261" s="8">
         <v>43</v>
       </c>
       <c t="s" r="I261" s="7">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c t="s" r="J261" s="7">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="K261" s="7"/>
       <c r="L261" s="7"/>
@@ -9769,7 +9807,7 @@
       </c>
       <c r="D262" s="7"/>
       <c t="s" r="E262" s="7">
-        <v>353</v>
+        <v>359</v>
       </c>
       <c r="F262" s="7">
         <v>321</v>
@@ -9781,10 +9819,10 @@
         <v>98</v>
       </c>
       <c t="s" r="I262" s="7">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c t="s" r="J262" s="7">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="K262" s="7"/>
       <c r="L262" s="7"/>
@@ -9802,7 +9840,7 @@
       </c>
       <c r="D263" s="7"/>
       <c t="s" r="E263" s="7">
-        <v>353</v>
+        <v>359</v>
       </c>
       <c r="F263" s="7">
         <v>321</v>
@@ -9814,10 +9852,10 @@
         <v>43</v>
       </c>
       <c t="s" r="I263" s="7">
-        <v>357</v>
+        <v>363</v>
       </c>
       <c t="s" r="J263" s="7">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="K263" s="7"/>
       <c r="L263" s="7"/>
@@ -9850,7 +9888,7 @@
       </c>
       <c r="D265" s="7"/>
       <c t="s" r="E265" s="7">
-        <v>358</v>
+        <v>364</v>
       </c>
       <c r="F265" s="7">
         <v>321</v>
@@ -9862,15 +9900,15 @@
         <v>17</v>
       </c>
       <c t="s" r="I265" s="7">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c t="s" r="J265" s="7">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="K265" s="7"/>
       <c r="L265" s="7"/>
       <c t="s" r="M265" s="7">
-        <v>359</v>
+        <v>365</v>
       </c>
     </row>
     <row r="266" ht="14.25" customHeight="1">
@@ -9885,7 +9923,7 @@
       </c>
       <c r="D266" s="7"/>
       <c t="s" r="E266" s="7">
-        <v>358</v>
+        <v>364</v>
       </c>
       <c r="F266" s="7">
         <v>321</v>
@@ -9894,10 +9932,10 @@
         <v>17</v>
       </c>
       <c t="s" r="H266" s="8">
-        <v>360</v>
+        <v>366</v>
       </c>
       <c t="s" r="I266" s="7">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c t="s" r="J266" s="7">
         <v>71</v>
@@ -9918,22 +9956,22 @@
       </c>
       <c r="D267" s="7"/>
       <c t="s" r="E267" s="7">
-        <v>358</v>
+        <v>364</v>
       </c>
       <c r="F267" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G267" s="8">
-        <v>360</v>
+        <v>366</v>
       </c>
       <c t="s" r="H267" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I267" s="7">
-        <v>361</v>
+        <v>367</v>
       </c>
       <c t="s" r="J267" s="7">
-        <v>362</v>
+        <v>368</v>
       </c>
       <c r="K267" s="7"/>
       <c r="L267" s="7"/>
@@ -9966,7 +10004,7 @@
       </c>
       <c r="D269" s="7"/>
       <c t="s" r="E269" s="7">
-        <v>363</v>
+        <v>369</v>
       </c>
       <c r="F269" s="7">
         <v>321</v>
@@ -9975,7 +10013,7 @@
         <v>43</v>
       </c>
       <c t="s" r="H269" s="8">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c t="s" r="I269" s="7">
         <v>51</v>
@@ -9986,7 +10024,7 @@
       <c r="K269" s="7"/>
       <c r="L269" s="7"/>
       <c t="s" r="M269" s="7">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="270" ht="15" customHeight="1">
@@ -10001,19 +10039,19 @@
       </c>
       <c r="D270" s="7"/>
       <c t="s" r="E270" s="7">
-        <v>363</v>
+        <v>369</v>
       </c>
       <c r="F270" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G270" s="8">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c t="s" r="H270" s="8">
         <v>43</v>
       </c>
       <c t="s" r="I270" s="7">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c t="s" r="J270" s="7">
         <v>74</v>
@@ -10021,7 +10059,7 @@
       <c r="K270" s="7"/>
       <c r="L270" s="7"/>
       <c t="s" r="M270" s="7">
-        <v>364</v>
+        <v>370</v>
       </c>
     </row>
     <row r="271" ht="14.25" customHeight="1">
@@ -10036,7 +10074,7 @@
       </c>
       <c r="D271" s="7"/>
       <c t="s" r="E271" s="7">
-        <v>363</v>
+        <v>369</v>
       </c>
       <c r="F271" s="7">
         <v>321</v>
@@ -10048,10 +10086,10 @@
         <v>21</v>
       </c>
       <c t="s" r="I271" s="7">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c t="s" r="J271" s="7">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="K271" s="7"/>
       <c r="L271" s="7"/>
@@ -10069,7 +10107,7 @@
       </c>
       <c r="D272" s="7"/>
       <c t="s" r="E272" s="7">
-        <v>363</v>
+        <v>369</v>
       </c>
       <c r="F272" s="7">
         <v>321</v>
@@ -10084,7 +10122,7 @@
         <v>37</v>
       </c>
       <c t="s" r="J272" s="7">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="K272" s="7"/>
       <c r="L272" s="7"/>
@@ -10102,7 +10140,7 @@
       </c>
       <c r="D273" s="7"/>
       <c t="s" r="E273" s="7">
-        <v>363</v>
+        <v>369</v>
       </c>
       <c r="F273" s="7">
         <v>321</v>
@@ -10111,13 +10149,13 @@
         <v>43</v>
       </c>
       <c t="s" r="H273" s="8">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c t="s" r="I273" s="7">
         <v>24</v>
       </c>
       <c t="s" r="J273" s="7">
-        <v>365</v>
+        <v>371</v>
       </c>
       <c r="K273" s="7"/>
       <c r="L273" s="7"/>
@@ -10135,22 +10173,22 @@
       </c>
       <c r="D274" s="7"/>
       <c t="s" r="E274" s="7">
-        <v>363</v>
+        <v>369</v>
       </c>
       <c r="F274" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G274" s="8">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c t="s" r="H274" s="8">
         <v>43</v>
       </c>
       <c t="s" r="I274" s="7">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c t="s" r="J274" s="7">
-        <v>366</v>
+        <v>345</v>
       </c>
       <c r="K274" s="7"/>
       <c r="L274" s="7"/>
@@ -10168,7 +10206,7 @@
       </c>
       <c r="D275" s="7"/>
       <c t="s" r="E275" s="7">
-        <v>363</v>
+        <v>369</v>
       </c>
       <c r="F275" s="7">
         <v>321</v>
@@ -10177,10 +10215,10 @@
         <v>43</v>
       </c>
       <c t="s" r="H275" s="8">
-        <v>367</v>
+        <v>372</v>
       </c>
       <c t="s" r="I275" s="7">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c t="s" r="J275" s="7">
         <v>60</v>
@@ -10201,22 +10239,22 @@
       </c>
       <c r="D276" s="7"/>
       <c t="s" r="E276" s="7">
-        <v>363</v>
+        <v>369</v>
       </c>
       <c r="F276" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G276" s="8">
-        <v>367</v>
+        <v>372</v>
       </c>
       <c t="s" r="H276" s="8">
         <v>43</v>
       </c>
       <c t="s" r="I276" s="7">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c t="s" r="J276" s="7">
-        <v>368</v>
+        <v>373</v>
       </c>
       <c r="K276" s="7"/>
       <c r="L276" s="7"/>
@@ -10249,7 +10287,7 @@
       </c>
       <c r="D278" s="7"/>
       <c t="s" r="E278" s="7">
-        <v>369</v>
+        <v>374</v>
       </c>
       <c r="F278" s="7">
         <v>320</v>
@@ -10258,13 +10296,13 @@
         <v>98</v>
       </c>
       <c t="s" r="H278" s="8">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c t="s" r="I278" s="7">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c t="s" r="J278" s="7">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="K278" s="7"/>
       <c r="L278" s="7"/>
@@ -10282,22 +10320,22 @@
       </c>
       <c r="D279" s="7"/>
       <c t="s" r="E279" s="7">
-        <v>369</v>
+        <v>374</v>
       </c>
       <c r="F279" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G279" s="8">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c t="s" r="H279" s="8">
         <v>98</v>
       </c>
       <c t="s" r="I279" s="7">
-        <v>359</v>
+        <v>365</v>
       </c>
       <c t="s" r="J279" s="7">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="K279" s="7"/>
       <c r="L279" s="7"/>
@@ -10330,19 +10368,19 @@
       </c>
       <c r="D281" s="7"/>
       <c t="s" r="E281" s="7">
-        <v>370</v>
+        <v>375</v>
       </c>
       <c r="F281" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G281" s="8">
-        <v>343</v>
+        <v>350</v>
       </c>
       <c t="s" r="H281" s="8">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c t="s" r="I281" s="7">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c t="s" r="J281" s="7">
         <v>35</v>
@@ -10350,7 +10388,7 @@
       <c r="K281" s="7"/>
       <c r="L281" s="7"/>
       <c t="s" r="M281" s="7">
-        <v>90</v>
+        <v>77</v>
       </c>
     </row>
     <row r="282" ht="14.25" customHeight="1">
@@ -10380,7 +10418,7 @@
       </c>
       <c r="D283" s="7"/>
       <c t="s" r="E283" s="7">
-        <v>371</v>
+        <v>376</v>
       </c>
       <c r="F283" s="7">
         <v>320</v>
@@ -10392,7 +10430,7 @@
         <v>43</v>
       </c>
       <c t="s" r="I283" s="7">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c t="s" r="J283" s="7">
         <v>51</v>
@@ -10400,7 +10438,7 @@
       <c r="K283" s="7"/>
       <c r="L283" s="7"/>
       <c t="s" r="M283" s="7">
-        <v>372</v>
+        <v>377</v>
       </c>
     </row>
     <row r="284" ht="14.25" customHeight="1">
@@ -10415,7 +10453,7 @@
       </c>
       <c r="D284" s="7"/>
       <c t="s" r="E284" s="7">
-        <v>371</v>
+        <v>376</v>
       </c>
       <c r="F284" s="7">
         <v>320</v>
@@ -10424,13 +10462,13 @@
         <v>43</v>
       </c>
       <c t="s" r="H284" s="8">
-        <v>373</v>
+        <v>378</v>
       </c>
       <c t="s" r="I284" s="7">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c t="s" r="J284" s="7">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="K284" s="7"/>
       <c r="L284" s="7"/>
@@ -10448,13 +10486,13 @@
       </c>
       <c r="D285" s="7"/>
       <c t="s" r="E285" s="7">
-        <v>371</v>
+        <v>376</v>
       </c>
       <c r="F285" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G285" s="8">
-        <v>373</v>
+        <v>378</v>
       </c>
       <c t="s" r="H285" s="8">
         <v>43</v>
@@ -10463,7 +10501,7 @@
         <v>70</v>
       </c>
       <c t="s" r="J285" s="7">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="K285" s="7"/>
       <c r="L285" s="7"/>
@@ -10481,7 +10519,7 @@
       </c>
       <c r="D286" s="7"/>
       <c t="s" r="E286" s="7">
-        <v>371</v>
+        <v>376</v>
       </c>
       <c r="F286" s="7">
         <v>320</v>
@@ -10490,13 +10528,13 @@
         <v>43</v>
       </c>
       <c t="s" r="H286" s="8">
-        <v>374</v>
+        <v>379</v>
       </c>
       <c t="s" r="I286" s="7">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c t="s" r="J286" s="7">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="K286" s="7"/>
       <c r="L286" s="7"/>
@@ -10514,22 +10552,22 @@
       </c>
       <c r="D287" s="7"/>
       <c t="s" r="E287" s="7">
-        <v>371</v>
+        <v>376</v>
       </c>
       <c r="F287" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G287" s="8">
-        <v>374</v>
+        <v>379</v>
       </c>
       <c t="s" r="H287" s="8">
         <v>43</v>
       </c>
       <c t="s" r="I287" s="7">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c t="s" r="J287" s="7">
-        <v>375</v>
+        <v>380</v>
       </c>
       <c r="K287" s="7"/>
       <c r="L287" s="7"/>
@@ -10562,7 +10600,7 @@
       </c>
       <c r="D289" s="7"/>
       <c t="s" r="E289" s="7">
-        <v>376</v>
+        <v>381</v>
       </c>
       <c r="F289" s="7">
         <v>321</v>
@@ -10571,18 +10609,18 @@
         <v>43</v>
       </c>
       <c t="s" r="H289" s="8">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c t="s" r="I289" s="7">
-        <v>377</v>
+        <v>382</v>
       </c>
       <c t="s" r="J289" s="7">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="K289" s="7"/>
       <c r="L289" s="7"/>
       <c t="s" r="M289" s="7">
-        <v>378</v>
+        <v>263</v>
       </c>
     </row>
     <row r="290" ht="15" customHeight="1">
@@ -10597,27 +10635,27 @@
       </c>
       <c r="D290" s="7"/>
       <c t="s" r="E290" s="7">
-        <v>376</v>
+        <v>381</v>
       </c>
       <c r="F290" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G290" s="8">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c t="s" r="H290" s="8">
         <v>43</v>
       </c>
       <c t="s" r="I290" s="7">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c t="s" r="J290" s="7">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="K290" s="7"/>
       <c r="L290" s="7"/>
       <c t="s" r="M290" s="7">
-        <v>379</v>
+        <v>383</v>
       </c>
     </row>
     <row r="291" ht="14.25" customHeight="1">
@@ -10632,7 +10670,7 @@
       </c>
       <c r="D291" s="7"/>
       <c t="s" r="E291" s="7">
-        <v>376</v>
+        <v>381</v>
       </c>
       <c r="F291" s="7">
         <v>321</v>
@@ -10641,13 +10679,13 @@
         <v>43</v>
       </c>
       <c t="s" r="H291" s="8">
-        <v>380</v>
+        <v>384</v>
       </c>
       <c t="s" r="I291" s="7">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c t="s" r="J291" s="7">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="K291" s="7"/>
       <c r="L291" s="7"/>
@@ -10665,22 +10703,22 @@
       </c>
       <c r="D292" s="7"/>
       <c t="s" r="E292" s="7">
-        <v>376</v>
+        <v>381</v>
       </c>
       <c r="F292" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G292" s="8">
-        <v>380</v>
+        <v>384</v>
       </c>
       <c t="s" r="H292" s="8">
         <v>43</v>
       </c>
       <c t="s" r="I292" s="7">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c t="s" r="J292" s="7">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="K292" s="7"/>
       <c r="L292" s="7"/>
@@ -10713,7 +10751,7 @@
       </c>
       <c r="D294" s="7"/>
       <c t="s" r="E294" s="7">
-        <v>381</v>
+        <v>385</v>
       </c>
       <c r="F294" s="7">
         <v>320</v>
@@ -10722,13 +10760,13 @@
         <v>98</v>
       </c>
       <c t="s" r="H294" s="8">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c t="s" r="I294" s="7">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c t="s" r="J294" s="7">
-        <v>359</v>
+        <v>365</v>
       </c>
       <c r="K294" s="7"/>
       <c r="L294" s="7"/>
@@ -10746,19 +10784,19 @@
       </c>
       <c r="D295" s="7"/>
       <c t="s" r="E295" s="7">
-        <v>381</v>
+        <v>385</v>
       </c>
       <c r="F295" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G295" s="8">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c t="s" r="H295" s="8">
         <v>98</v>
       </c>
       <c t="s" r="I295" s="7">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c t="s" r="J295" s="7">
         <v>23</v>
@@ -10794,7 +10832,7 @@
       </c>
       <c r="D297" s="7"/>
       <c t="s" r="E297" s="7">
-        <v>382</v>
+        <v>386</v>
       </c>
       <c r="F297" s="7">
         <v>320</v>
@@ -10803,18 +10841,18 @@
         <v>17</v>
       </c>
       <c t="s" r="H297" s="8">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c t="s" r="I297" s="7">
         <v>97</v>
       </c>
       <c t="s" r="J297" s="7">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="K297" s="7"/>
       <c r="L297" s="7"/>
       <c t="s" r="M297" s="7">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="298" ht="14.25" customHeight="1">
@@ -10829,26 +10867,28 @@
       </c>
       <c r="D298" s="7"/>
       <c t="s" r="E298" s="7">
-        <v>382</v>
+        <v>386</v>
       </c>
       <c r="F298" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G298" s="8">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c t="s" r="H298" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I298" s="7">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c t="s" r="J298" s="7">
         <v>54</v>
       </c>
       <c r="K298" s="7"/>
       <c r="L298" s="7"/>
-      <c r="M298" s="7"/>
+      <c t="s" r="M298" s="7">
+        <v>311</v>
+      </c>
     </row>
     <row r="299" ht="14.25" customHeight="1">
       <c t="s" r="A299" s="6">
@@ -10862,7 +10902,7 @@
       </c>
       <c r="D299" s="7"/>
       <c t="s" r="E299" s="7">
-        <v>382</v>
+        <v>386</v>
       </c>
       <c r="F299" s="7">
         <v>320</v>
@@ -10871,13 +10911,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H299" s="8">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c t="s" r="I299" s="7">
         <v>37</v>
       </c>
       <c t="s" r="J299" s="7">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="K299" s="7"/>
       <c r="L299" s="7"/>
@@ -10895,19 +10935,19 @@
       </c>
       <c r="D300" s="7"/>
       <c t="s" r="E300" s="7">
-        <v>382</v>
+        <v>386</v>
       </c>
       <c r="F300" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G300" s="8">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c t="s" r="H300" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I300" s="7">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c t="s" r="J300" s="7">
         <v>23</v>
@@ -10928,7 +10968,7 @@
       </c>
       <c r="D301" s="7"/>
       <c t="s" r="E301" s="7">
-        <v>382</v>
+        <v>386</v>
       </c>
       <c r="F301" s="7">
         <v>320</v>
@@ -10937,13 +10977,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H301" s="8">
-        <v>383</v>
+        <v>387</v>
       </c>
       <c t="s" r="I301" s="7">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c t="s" r="J301" s="7">
-        <v>365</v>
+        <v>371</v>
       </c>
       <c r="K301" s="7"/>
       <c r="L301" s="7"/>
@@ -10961,22 +11001,22 @@
       </c>
       <c r="D302" s="7"/>
       <c t="s" r="E302" s="7">
-        <v>382</v>
+        <v>386</v>
       </c>
       <c r="F302" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G302" s="8">
-        <v>383</v>
+        <v>387</v>
       </c>
       <c t="s" r="H302" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I302" s="7">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c t="s" r="J302" s="7">
-        <v>346</v>
+        <v>353</v>
       </c>
       <c r="K302" s="7"/>
       <c r="L302" s="7"/>
@@ -11009,27 +11049,27 @@
       </c>
       <c r="D304" s="7"/>
       <c t="s" r="E304" s="7">
-        <v>384</v>
+        <v>388</v>
       </c>
       <c r="F304" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G304" s="8">
-        <v>343</v>
+        <v>350</v>
       </c>
       <c t="s" r="H304" s="8">
         <v>98</v>
       </c>
       <c t="s" r="I304" s="7">
-        <v>385</v>
+        <v>389</v>
       </c>
       <c t="s" r="J304" s="7">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="K304" s="7"/>
       <c r="L304" s="7"/>
       <c t="s" r="M304" s="7">
-        <v>386</v>
+        <v>390</v>
       </c>
     </row>
     <row r="305" ht="15" customHeight="1">
@@ -11044,7 +11084,7 @@
       </c>
       <c r="D305" s="7"/>
       <c t="s" r="E305" s="7">
-        <v>384</v>
+        <v>388</v>
       </c>
       <c r="F305" s="7">
         <v>321</v>
@@ -11056,10 +11096,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I305" s="7">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c t="s" r="J305" s="7">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="K305" s="7"/>
       <c r="L305" s="7"/>
@@ -11077,7 +11117,7 @@
       </c>
       <c r="D306" s="7"/>
       <c t="s" r="E306" s="7">
-        <v>384</v>
+        <v>388</v>
       </c>
       <c r="F306" s="7">
         <v>321</v>
@@ -11086,10 +11126,10 @@
         <v>17</v>
       </c>
       <c t="s" r="H306" s="8">
-        <v>343</v>
+        <v>350</v>
       </c>
       <c t="s" r="I306" s="7">
-        <v>387</v>
+        <v>391</v>
       </c>
       <c t="s" r="J306" s="7">
         <v>31</v>
@@ -11125,7 +11165,7 @@
       </c>
       <c r="D308" s="7"/>
       <c t="s" r="E308" s="7">
-        <v>388</v>
+        <v>392</v>
       </c>
       <c r="F308" s="7">
         <v>320</v>
@@ -11145,7 +11185,7 @@
       <c r="K308" s="7"/>
       <c r="L308" s="7"/>
       <c t="s" r="M308" s="7">
-        <v>389</v>
+        <v>393</v>
       </c>
     </row>
     <row r="309" ht="14.25" customHeight="1">
@@ -11160,7 +11200,7 @@
       </c>
       <c r="D309" s="7"/>
       <c t="s" r="E309" s="7">
-        <v>388</v>
+        <v>392</v>
       </c>
       <c r="F309" s="7">
         <v>320</v>
@@ -11175,11 +11215,13 @@
         <v>76</v>
       </c>
       <c t="s" r="J309" s="7">
-        <v>90</v>
+        <v>77</v>
       </c>
       <c r="K309" s="7"/>
       <c r="L309" s="7"/>
-      <c r="M309" s="7"/>
+      <c t="s" r="M309" s="7">
+        <v>77</v>
+      </c>
     </row>
     <row r="310" ht="15" customHeight="1">
       <c t="s" r="A310" s="6">
@@ -11193,7 +11235,7 @@
       </c>
       <c r="D310" s="7"/>
       <c t="s" r="E310" s="7">
-        <v>388</v>
+        <v>392</v>
       </c>
       <c r="F310" s="7">
         <v>320</v>
@@ -11202,13 +11244,13 @@
         <v>43</v>
       </c>
       <c t="s" r="H310" s="8">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c t="s" r="I310" s="7">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c t="s" r="J310" s="7">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="K310" s="7"/>
       <c r="L310" s="7"/>
@@ -11226,22 +11268,22 @@
       </c>
       <c r="D311" s="7"/>
       <c t="s" r="E311" s="7">
-        <v>388</v>
+        <v>392</v>
       </c>
       <c r="F311" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G311" s="8">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c t="s" r="H311" s="8">
         <v>43</v>
       </c>
       <c t="s" r="I311" s="7">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c t="s" r="J311" s="7">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="K311" s="7"/>
       <c r="L311" s="7"/>
@@ -11259,7 +11301,7 @@
       </c>
       <c r="D312" s="7"/>
       <c t="s" r="E312" s="7">
-        <v>388</v>
+        <v>392</v>
       </c>
       <c r="F312" s="7">
         <v>320</v>
@@ -11271,10 +11313,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I312" s="7">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c t="s" r="J312" s="7">
-        <v>366</v>
+        <v>345</v>
       </c>
       <c r="K312" s="7"/>
       <c r="L312" s="7"/>
@@ -11292,7 +11334,7 @@
       </c>
       <c r="D313" s="7"/>
       <c t="s" r="E313" s="7">
-        <v>388</v>
+        <v>392</v>
       </c>
       <c r="F313" s="7">
         <v>320</v>
@@ -11304,7 +11346,7 @@
         <v>43</v>
       </c>
       <c t="s" r="I313" s="7">
-        <v>390</v>
+        <v>394</v>
       </c>
       <c t="s" r="J313" s="7">
         <v>93</v>
@@ -11340,7 +11382,7 @@
       </c>
       <c r="D315" s="7"/>
       <c t="s" r="E315" s="7">
-        <v>391</v>
+        <v>395</v>
       </c>
       <c r="F315" s="7">
         <v>321</v>
@@ -11349,13 +11391,13 @@
         <v>43</v>
       </c>
       <c t="s" r="H315" s="8">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c t="s" r="I315" s="7">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c t="s" r="J315" s="7">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="K315" s="7"/>
       <c r="L315" s="7"/>
@@ -11375,26 +11417,28 @@
       </c>
       <c r="D316" s="7"/>
       <c t="s" r="E316" s="7">
-        <v>391</v>
+        <v>395</v>
       </c>
       <c r="F316" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G316" s="8">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c t="s" r="H316" s="8">
         <v>43</v>
       </c>
       <c t="s" r="I316" s="7">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c t="s" r="J316" s="7">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="K316" s="7"/>
       <c r="L316" s="7"/>
-      <c r="M316" s="7"/>
+      <c t="s" r="M316" s="7">
+        <v>396</v>
+      </c>
     </row>
     <row r="317" ht="14.25" customHeight="1">
       <c t="s" r="A317" s="6">
@@ -11408,7 +11452,7 @@
       </c>
       <c r="D317" s="7"/>
       <c t="s" r="E317" s="7">
-        <v>391</v>
+        <v>395</v>
       </c>
       <c r="F317" s="7">
         <v>321</v>
@@ -11417,10 +11461,10 @@
         <v>43</v>
       </c>
       <c t="s" r="H317" s="8">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c t="s" r="I317" s="7">
-        <v>392</v>
+        <v>397</v>
       </c>
       <c t="s" r="J317" s="7">
         <v>19</v>
@@ -11441,22 +11485,22 @@
       </c>
       <c r="D318" s="7"/>
       <c t="s" r="E318" s="7">
-        <v>391</v>
+        <v>395</v>
       </c>
       <c r="F318" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G318" s="8">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c t="s" r="H318" s="8">
         <v>43</v>
       </c>
       <c t="s" r="I318" s="7">
-        <v>338</v>
+        <v>343</v>
       </c>
       <c t="s" r="J318" s="7">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="K318" s="7"/>
       <c r="L318" s="7"/>
@@ -11474,7 +11518,7 @@
       </c>
       <c r="D319" s="7"/>
       <c t="s" r="E319" s="7">
-        <v>391</v>
+        <v>395</v>
       </c>
       <c r="F319" s="7">
         <v>321</v>
@@ -11489,7 +11533,7 @@
         <v>48</v>
       </c>
       <c t="s" r="J319" s="7">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="K319" s="7"/>
       <c r="L319" s="7"/>
@@ -11507,7 +11551,7 @@
       </c>
       <c r="D320" s="7"/>
       <c t="s" r="E320" s="7">
-        <v>391</v>
+        <v>395</v>
       </c>
       <c r="F320" s="7">
         <v>321</v>
@@ -11516,13 +11560,13 @@
         <v>21</v>
       </c>
       <c t="s" r="H320" s="8">
-        <v>343</v>
+        <v>350</v>
       </c>
       <c t="s" r="I320" s="7">
-        <v>393</v>
+        <v>398</v>
       </c>
       <c t="s" r="J320" s="7">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="K320" s="7"/>
       <c r="L320" s="7"/>
@@ -11555,7 +11599,7 @@
       </c>
       <c r="D322" s="7"/>
       <c t="s" r="E322" s="7">
-        <v>394</v>
+        <v>399</v>
       </c>
       <c r="F322" s="7">
         <v>320</v>
@@ -11567,15 +11611,15 @@
         <v>43</v>
       </c>
       <c t="s" r="I322" s="7">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c t="s" r="J322" s="7">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="K322" s="7"/>
       <c r="L322" s="7"/>
       <c t="s" r="M322" s="7">
-        <v>395</v>
+        <v>400</v>
       </c>
     </row>
     <row r="323" ht="14.25" customHeight="1">
@@ -11590,7 +11634,7 @@
       </c>
       <c r="D323" s="7"/>
       <c t="s" r="E323" s="7">
-        <v>394</v>
+        <v>399</v>
       </c>
       <c r="F323" s="7">
         <v>320</v>
@@ -11602,15 +11646,15 @@
         <v>17</v>
       </c>
       <c t="s" r="I323" s="7">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c t="s" r="J323" s="7">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="K323" s="7"/>
       <c r="L323" s="7"/>
       <c t="s" r="M323" s="7">
-        <v>396</v>
+        <v>401</v>
       </c>
     </row>
     <row r="324" ht="14.25" customHeight="1">
@@ -11625,7 +11669,7 @@
       </c>
       <c r="D324" s="7"/>
       <c t="s" r="E324" s="7">
-        <v>394</v>
+        <v>399</v>
       </c>
       <c r="F324" s="7">
         <v>320</v>
@@ -11634,13 +11678,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H324" s="8">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c t="s" r="I324" s="7">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c t="s" r="J324" s="7">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="K324" s="7"/>
       <c r="L324" s="7"/>
@@ -11658,22 +11702,22 @@
       </c>
       <c r="D325" s="7"/>
       <c t="s" r="E325" s="7">
-        <v>394</v>
+        <v>399</v>
       </c>
       <c r="F325" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G325" s="8">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c t="s" r="H325" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I325" s="7">
-        <v>397</v>
+        <v>402</v>
       </c>
       <c t="s" r="J325" s="7">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="K325" s="7"/>
       <c r="L325" s="7"/>
@@ -11691,7 +11735,7 @@
       </c>
       <c r="D326" s="7"/>
       <c t="s" r="E326" s="7">
-        <v>394</v>
+        <v>399</v>
       </c>
       <c r="F326" s="7">
         <v>320</v>
@@ -11700,13 +11744,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H326" s="8">
-        <v>398</v>
+        <v>403</v>
       </c>
       <c t="s" r="I326" s="7">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c t="s" r="J326" s="7">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="K326" s="7"/>
       <c r="L326" s="7"/>
@@ -11724,22 +11768,22 @@
       </c>
       <c r="D327" s="7"/>
       <c t="s" r="E327" s="7">
-        <v>394</v>
+        <v>399</v>
       </c>
       <c r="F327" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G327" s="8">
-        <v>398</v>
+        <v>403</v>
       </c>
       <c t="s" r="H327" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I327" s="7">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c t="s" r="J327" s="7">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="K327" s="7"/>
       <c r="L327" s="7"/>
@@ -11772,7 +11816,7 @@
       </c>
       <c r="D329" s="7"/>
       <c t="s" r="E329" s="7">
-        <v>399</v>
+        <v>404</v>
       </c>
       <c r="F329" s="7">
         <v>320</v>
@@ -11784,7 +11828,7 @@
         <v>21</v>
       </c>
       <c t="s" r="I329" s="7">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c t="s" r="J329" s="7">
         <v>97</v>
@@ -11792,7 +11836,7 @@
       <c r="K329" s="7"/>
       <c r="L329" s="7"/>
       <c t="s" r="M329" s="7">
-        <v>400</v>
+        <v>405</v>
       </c>
     </row>
     <row r="330" ht="15" customHeight="1">
@@ -11807,7 +11851,7 @@
       </c>
       <c r="D330" s="7"/>
       <c t="s" r="E330" s="7">
-        <v>399</v>
+        <v>404</v>
       </c>
       <c r="F330" s="7">
         <v>320</v>
@@ -11819,15 +11863,15 @@
         <v>43</v>
       </c>
       <c t="s" r="I330" s="7">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c t="s" r="J330" s="7">
-        <v>401</v>
+        <v>406</v>
       </c>
       <c r="K330" s="7"/>
       <c r="L330" s="7"/>
       <c t="s" r="M330" s="7">
-        <v>402</v>
+        <v>407</v>
       </c>
     </row>
     <row r="331" ht="14.25" customHeight="1">
@@ -11842,7 +11886,7 @@
       </c>
       <c r="D331" s="7"/>
       <c t="s" r="E331" s="7">
-        <v>399</v>
+        <v>404</v>
       </c>
       <c r="F331" s="7">
         <v>320</v>
@@ -11851,10 +11895,10 @@
         <v>43</v>
       </c>
       <c t="s" r="H331" s="8">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c t="s" r="I331" s="7">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c t="s" r="J331" s="7">
         <v>35</v>
@@ -11875,13 +11919,13 @@
       </c>
       <c r="D332" s="7"/>
       <c t="s" r="E332" s="7">
-        <v>399</v>
+        <v>404</v>
       </c>
       <c r="F332" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G332" s="8">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c t="s" r="H332" s="8">
         <v>43</v>
@@ -11908,7 +11952,7 @@
       </c>
       <c r="D333" s="7"/>
       <c t="s" r="E333" s="7">
-        <v>399</v>
+        <v>404</v>
       </c>
       <c r="F333" s="7">
         <v>320</v>
@@ -11923,11 +11967,15 @@
         <v>91</v>
       </c>
       <c t="s" r="J333" s="7">
-        <v>211</v>
-      </c>
-      <c r="K333" s="7"/>
+        <v>213</v>
+      </c>
+      <c t="s" r="K333" s="7">
+        <v>178</v>
+      </c>
       <c r="L333" s="7"/>
-      <c r="M333" s="7"/>
+      <c t="s" r="M333" s="7">
+        <v>274</v>
+      </c>
     </row>
     <row r="334" ht="14.25" customHeight="1">
       <c t="s" r="A334" s="6">
@@ -11941,7 +11989,7 @@
       </c>
       <c r="D334" s="7"/>
       <c t="s" r="E334" s="7">
-        <v>399</v>
+        <v>404</v>
       </c>
       <c r="F334" s="7">
         <v>320</v>
@@ -11953,14 +12001,18 @@
         <v>43</v>
       </c>
       <c t="s" r="I334" s="7">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c t="s" r="J334" s="7">
-        <v>80</v>
-      </c>
-      <c r="K334" s="7"/>
+        <v>81</v>
+      </c>
+      <c t="s" r="K334" s="7">
+        <v>214</v>
+      </c>
       <c r="L334" s="7"/>
-      <c r="M334" s="7"/>
+      <c t="s" r="M334" s="7">
+        <v>290</v>
+      </c>
     </row>
     <row r="335" ht="15" customHeight="1">
       <c t="s" r="A335" s="6">
@@ -11974,7 +12026,7 @@
       </c>
       <c r="D335" s="7"/>
       <c t="s" r="E335" s="7">
-        <v>399</v>
+        <v>404</v>
       </c>
       <c r="F335" s="7">
         <v>320</v>
@@ -11983,13 +12035,13 @@
         <v>43</v>
       </c>
       <c t="s" r="H335" s="8">
-        <v>403</v>
+        <v>408</v>
       </c>
       <c t="s" r="I335" s="7">
-        <v>357</v>
+        <v>363</v>
       </c>
       <c t="s" r="J335" s="7">
-        <v>404</v>
+        <v>409</v>
       </c>
       <c r="K335" s="7"/>
       <c r="L335" s="7"/>
@@ -12007,22 +12059,22 @@
       </c>
       <c r="D336" s="7"/>
       <c t="s" r="E336" s="7">
-        <v>399</v>
+        <v>404</v>
       </c>
       <c r="F336" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G336" s="8">
-        <v>403</v>
+        <v>408</v>
       </c>
       <c t="s" r="H336" s="8">
         <v>43</v>
       </c>
       <c t="s" r="I336" s="7">
-        <v>405</v>
+        <v>410</v>
       </c>
       <c t="s" r="J336" s="7">
-        <v>406</v>
+        <v>411</v>
       </c>
       <c r="K336" s="7"/>
       <c r="L336" s="7"/>
@@ -12055,7 +12107,7 @@
       </c>
       <c r="D338" s="7"/>
       <c t="s" r="E338" s="7">
-        <v>407</v>
+        <v>412</v>
       </c>
       <c r="F338" s="7">
         <v>321</v>
@@ -12067,7 +12119,7 @@
         <v>98</v>
       </c>
       <c t="s" r="I338" s="7">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c t="s" r="J338" s="7">
         <v>40</v>
@@ -12075,7 +12127,7 @@
       <c r="K338" s="7"/>
       <c r="L338" s="7"/>
       <c t="s" r="M338" s="7">
-        <v>336</v>
+        <v>340</v>
       </c>
     </row>
     <row r="339" ht="14.25" customHeight="1">
@@ -12090,7 +12142,7 @@
       </c>
       <c r="D339" s="7"/>
       <c t="s" r="E339" s="7">
-        <v>407</v>
+        <v>412</v>
       </c>
       <c r="F339" s="7">
         <v>321</v>
@@ -12102,7 +12154,7 @@
         <v>68</v>
       </c>
       <c t="s" r="I339" s="7">
-        <v>392</v>
+        <v>397</v>
       </c>
       <c t="s" r="J339" s="7">
         <v>23</v>
@@ -12123,7 +12175,7 @@
       </c>
       <c r="D340" s="7"/>
       <c t="s" r="E340" s="7">
-        <v>407</v>
+        <v>412</v>
       </c>
       <c r="F340" s="7">
         <v>321</v>
@@ -12135,10 +12187,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I340" s="7">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c t="s" r="J340" s="7">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="K340" s="7"/>
       <c r="L340" s="7"/>
@@ -12156,7 +12208,7 @@
       </c>
       <c r="D341" s="7"/>
       <c t="s" r="E341" s="7">
-        <v>407</v>
+        <v>412</v>
       </c>
       <c r="F341" s="7">
         <v>321</v>
@@ -12165,13 +12217,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H341" s="8">
-        <v>367</v>
+        <v>372</v>
       </c>
       <c t="s" r="I341" s="7">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c t="s" r="J341" s="7">
-        <v>408</v>
+        <v>413</v>
       </c>
       <c r="K341" s="7"/>
       <c r="L341" s="7"/>
@@ -12189,22 +12241,22 @@
       </c>
       <c r="D342" s="7"/>
       <c t="s" r="E342" s="7">
-        <v>407</v>
+        <v>412</v>
       </c>
       <c r="F342" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G342" s="8">
-        <v>367</v>
+        <v>372</v>
       </c>
       <c t="s" r="H342" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I342" s="7">
-        <v>409</v>
+        <v>414</v>
       </c>
       <c t="s" r="J342" s="7">
-        <v>410</v>
+        <v>415</v>
       </c>
       <c r="K342" s="7"/>
       <c r="L342" s="7"/>
@@ -12237,19 +12289,19 @@
       </c>
       <c r="D344" s="7"/>
       <c t="s" r="E344" s="7">
-        <v>411</v>
+        <v>416</v>
       </c>
       <c r="F344" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G344" s="8">
-        <v>340</v>
+        <v>347</v>
       </c>
       <c t="s" r="H344" s="8">
         <v>43</v>
       </c>
       <c t="s" r="I344" s="7">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c t="s" r="J344" s="7">
         <v>76</v>
@@ -12257,7 +12309,7 @@
       <c r="K344" s="7"/>
       <c r="L344" s="7"/>
       <c t="s" r="M344" s="7">
-        <v>330</v>
+        <v>334</v>
       </c>
     </row>
     <row r="345" ht="15" customHeight="1">
@@ -12272,7 +12324,7 @@
       </c>
       <c r="D345" s="7"/>
       <c t="s" r="E345" s="7">
-        <v>411</v>
+        <v>416</v>
       </c>
       <c r="F345" s="7">
         <v>321</v>
@@ -12284,10 +12336,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I345" s="7">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c t="s" r="J345" s="7">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="K345" s="7"/>
       <c r="L345" s="7"/>
@@ -12305,7 +12357,7 @@
       </c>
       <c r="D346" s="7"/>
       <c t="s" r="E346" s="7">
-        <v>411</v>
+        <v>416</v>
       </c>
       <c r="F346" s="7">
         <v>321</v>
@@ -12317,10 +12369,10 @@
         <v>43</v>
       </c>
       <c t="s" r="I346" s="7">
-        <v>397</v>
+        <v>402</v>
       </c>
       <c t="s" r="J346" s="7">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="K346" s="7"/>
       <c r="L346" s="7"/>
@@ -12338,7 +12390,7 @@
       </c>
       <c r="D347" s="7"/>
       <c t="s" r="E347" s="7">
-        <v>411</v>
+        <v>416</v>
       </c>
       <c r="F347" s="7">
         <v>321</v>
@@ -12350,10 +12402,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I347" s="7">
-        <v>412</v>
+        <v>417</v>
       </c>
       <c t="s" r="J347" s="7">
-        <v>357</v>
+        <v>363</v>
       </c>
       <c r="K347" s="7"/>
       <c r="L347" s="7"/>
@@ -12386,7 +12438,7 @@
       </c>
       <c r="D349" s="7"/>
       <c t="s" r="E349" s="7">
-        <v>413</v>
+        <v>418</v>
       </c>
       <c r="F349" s="7">
         <v>321</v>
@@ -12398,15 +12450,15 @@
         <v>17</v>
       </c>
       <c t="s" r="I349" s="7">
-        <v>414</v>
+        <v>419</v>
       </c>
       <c t="s" r="J349" s="7">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="K349" s="7"/>
       <c r="L349" s="7"/>
       <c t="s" r="M349" s="7">
-        <v>415</v>
+        <v>420</v>
       </c>
     </row>
     <row r="350" ht="15" customHeight="1">
@@ -12421,7 +12473,7 @@
       </c>
       <c r="D350" s="7"/>
       <c t="s" r="E350" s="7">
-        <v>413</v>
+        <v>418</v>
       </c>
       <c r="F350" s="7">
         <v>321</v>
@@ -12433,7 +12485,7 @@
         <v>98</v>
       </c>
       <c t="s" r="I350" s="7">
-        <v>416</v>
+        <v>421</v>
       </c>
       <c t="s" r="J350" s="7">
         <v>99</v>
@@ -12456,7 +12508,7 @@
       </c>
       <c r="D351" s="7"/>
       <c t="s" r="E351" s="7">
-        <v>413</v>
+        <v>418</v>
       </c>
       <c r="F351" s="7">
         <v>321</v>
@@ -12465,13 +12517,13 @@
         <v>98</v>
       </c>
       <c t="s" r="H351" s="8">
-        <v>350</v>
+        <v>357</v>
       </c>
       <c t="s" r="I351" s="7">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c t="s" r="J351" s="7">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="K351" s="7"/>
       <c r="L351" s="7"/>
@@ -12489,19 +12541,19 @@
       </c>
       <c r="D352" s="7"/>
       <c t="s" r="E352" s="7">
-        <v>413</v>
+        <v>418</v>
       </c>
       <c r="F352" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G352" s="8">
-        <v>350</v>
+        <v>357</v>
       </c>
       <c t="s" r="H352" s="8">
         <v>98</v>
       </c>
       <c t="s" r="I352" s="7">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c t="s" r="J352" s="7">
         <v>91</v>
@@ -12522,7 +12574,7 @@
       </c>
       <c r="D353" s="7"/>
       <c t="s" r="E353" s="7">
-        <v>413</v>
+        <v>418</v>
       </c>
       <c r="F353" s="7">
         <v>321</v>
@@ -12531,13 +12583,13 @@
         <v>98</v>
       </c>
       <c t="s" r="H353" s="8">
-        <v>350</v>
+        <v>357</v>
       </c>
       <c t="s" r="I353" s="7">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c t="s" r="J353" s="7">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="K353" s="7"/>
       <c r="L353" s="7"/>
@@ -12555,22 +12607,22 @@
       </c>
       <c r="D354" s="7"/>
       <c t="s" r="E354" s="7">
-        <v>413</v>
+        <v>418</v>
       </c>
       <c r="F354" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G354" s="8">
-        <v>350</v>
+        <v>357</v>
       </c>
       <c t="s" r="H354" s="8">
         <v>98</v>
       </c>
       <c t="s" r="I354" s="7">
-        <v>417</v>
+        <v>422</v>
       </c>
       <c t="s" r="J354" s="7">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="K354" s="7"/>
       <c r="L354" s="7"/>
@@ -12588,7 +12640,7 @@
       </c>
       <c r="D355" s="7"/>
       <c t="s" r="E355" s="7">
-        <v>413</v>
+        <v>418</v>
       </c>
       <c r="F355" s="7">
         <v>321</v>
@@ -12600,10 +12652,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I355" s="7">
-        <v>418</v>
+        <v>423</v>
       </c>
       <c t="s" r="J355" s="7">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="K355" s="7"/>
       <c r="L355" s="7"/>
@@ -12636,7 +12688,7 @@
       </c>
       <c r="D357" s="7"/>
       <c t="s" r="E357" s="7">
-        <v>419</v>
+        <v>424</v>
       </c>
       <c r="F357" s="7">
         <v>321</v>
@@ -12651,12 +12703,12 @@
         <v>51</v>
       </c>
       <c t="s" r="J357" s="7">
-        <v>420</v>
+        <v>425</v>
       </c>
       <c r="K357" s="7"/>
       <c r="L357" s="7"/>
       <c t="s" r="M357" s="7">
-        <v>421</v>
+        <v>426</v>
       </c>
     </row>
     <row r="358" ht="14.25" customHeight="1">
@@ -12671,7 +12723,7 @@
       </c>
       <c r="D358" s="7"/>
       <c t="s" r="E358" s="7">
-        <v>419</v>
+        <v>424</v>
       </c>
       <c r="F358" s="7">
         <v>321</v>
@@ -12683,15 +12735,15 @@
         <v>98</v>
       </c>
       <c t="s" r="I358" s="7">
-        <v>401</v>
+        <v>406</v>
       </c>
       <c t="s" r="J358" s="7">
-        <v>392</v>
+        <v>397</v>
       </c>
       <c r="K358" s="7"/>
       <c r="L358" s="7"/>
       <c t="s" r="M358" s="7">
-        <v>422</v>
+        <v>427</v>
       </c>
     </row>
     <row r="359" ht="14.25" customHeight="1">
@@ -12706,7 +12758,7 @@
       </c>
       <c r="D359" s="7"/>
       <c t="s" r="E359" s="7">
-        <v>419</v>
+        <v>424</v>
       </c>
       <c r="F359" s="7">
         <v>321</v>
@@ -12718,7 +12770,7 @@
         <v>21</v>
       </c>
       <c t="s" r="I359" s="7">
-        <v>423</v>
+        <v>428</v>
       </c>
       <c t="s" r="J359" s="7">
         <v>22</v>
@@ -12739,7 +12791,7 @@
       </c>
       <c r="D360" s="7"/>
       <c t="s" r="E360" s="7">
-        <v>419</v>
+        <v>424</v>
       </c>
       <c r="F360" s="7">
         <v>321</v>
@@ -12751,10 +12803,10 @@
         <v>98</v>
       </c>
       <c t="s" r="I360" s="7">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c t="s" r="J360" s="7">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="K360" s="7"/>
       <c r="L360" s="7"/>
@@ -12787,7 +12839,7 @@
       </c>
       <c r="D362" s="7"/>
       <c t="s" r="E362" s="7">
-        <v>424</v>
+        <v>429</v>
       </c>
       <c r="F362" s="7">
         <v>320</v>
@@ -12796,10 +12848,10 @@
         <v>17</v>
       </c>
       <c t="s" r="H362" s="8">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c t="s" r="I362" s="7">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c t="s" r="J362" s="7">
         <v>96</v>
@@ -12807,7 +12859,7 @@
       <c r="K362" s="7"/>
       <c r="L362" s="7"/>
       <c t="s" r="M362" s="7">
-        <v>425</v>
+        <v>430</v>
       </c>
     </row>
     <row r="363" ht="14.25" customHeight="1">
@@ -12822,29 +12874,29 @@
       </c>
       <c r="D363" s="7"/>
       <c t="s" r="E363" s="7">
-        <v>424</v>
+        <v>429</v>
       </c>
       <c r="F363" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G363" s="8">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c t="s" r="H363" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I363" s="7">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c t="s" r="J363" s="7">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c t="s" r="K363" s="7">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="L363" s="7"/>
       <c t="s" r="M363" s="7">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="364" ht="14.25" customHeight="1">
@@ -12859,7 +12911,7 @@
       </c>
       <c r="D364" s="7"/>
       <c t="s" r="E364" s="7">
-        <v>424</v>
+        <v>429</v>
       </c>
       <c r="F364" s="7">
         <v>320</v>
@@ -12868,13 +12920,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H364" s="8">
-        <v>398</v>
+        <v>403</v>
       </c>
       <c t="s" r="I364" s="7">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c t="s" r="J364" s="7">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="K364" s="7"/>
       <c r="L364" s="7"/>
@@ -12892,13 +12944,13 @@
       </c>
       <c r="D365" s="7"/>
       <c t="s" r="E365" s="7">
-        <v>424</v>
+        <v>429</v>
       </c>
       <c r="F365" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G365" s="8">
-        <v>398</v>
+        <v>403</v>
       </c>
       <c t="s" r="H365" s="8">
         <v>17</v>
@@ -12925,7 +12977,7 @@
       </c>
       <c r="D366" s="7"/>
       <c t="s" r="E366" s="7">
-        <v>424</v>
+        <v>429</v>
       </c>
       <c r="F366" s="7">
         <v>320</v>
@@ -12934,13 +12986,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H366" s="8">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c t="s" r="I366" s="7">
         <v>91</v>
       </c>
       <c t="s" r="J366" s="7">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="K366" s="7"/>
       <c r="L366" s="7"/>
@@ -12958,22 +13010,22 @@
       </c>
       <c r="D367" s="7"/>
       <c t="s" r="E367" s="7">
-        <v>424</v>
+        <v>429</v>
       </c>
       <c r="F367" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G367" s="8">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c t="s" r="H367" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I367" s="7">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c t="s" r="J367" s="7">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="K367" s="7"/>
       <c r="L367" s="7"/>
@@ -13006,7 +13058,7 @@
       </c>
       <c r="D369" s="7"/>
       <c t="s" r="E369" s="7">
-        <v>426</v>
+        <v>431</v>
       </c>
       <c r="F369" s="7">
         <v>321</v>
@@ -13021,11 +13073,15 @@
         <v>55</v>
       </c>
       <c t="s" r="J369" s="7">
-        <v>397</v>
-      </c>
-      <c r="K369" s="7"/>
+        <v>402</v>
+      </c>
+      <c t="s" r="K369" s="7">
+        <v>211</v>
+      </c>
       <c r="L369" s="7"/>
-      <c r="M369" s="7"/>
+      <c t="s" r="M369" s="7">
+        <v>212</v>
+      </c>
     </row>
     <row r="370" ht="15" customHeight="1">
       <c t="s" r="A370" s="6">
@@ -13039,7 +13095,7 @@
       </c>
       <c r="D370" s="7"/>
       <c t="s" r="E370" s="7">
-        <v>426</v>
+        <v>431</v>
       </c>
       <c r="F370" s="7">
         <v>321</v>
@@ -13051,14 +13107,18 @@
         <v>43</v>
       </c>
       <c t="s" r="I370" s="7">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c t="s" r="J370" s="7">
-        <v>311</v>
-      </c>
-      <c r="K370" s="7"/>
+        <v>314</v>
+      </c>
+      <c t="s" r="K370" s="7">
+        <v>59</v>
+      </c>
       <c r="L370" s="7"/>
-      <c r="M370" s="7"/>
+      <c t="s" r="M370" s="7">
+        <v>191</v>
+      </c>
     </row>
     <row r="371" ht="14.25" customHeight="1">
       <c r="A371" s="6"/>
@@ -13087,22 +13147,22 @@
       </c>
       <c r="D372" s="7"/>
       <c t="s" r="E372" s="7">
-        <v>427</v>
+        <v>432</v>
       </c>
       <c r="F372" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G372" s="8">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c t="s" r="H372" s="8">
-        <v>428</v>
+        <v>433</v>
       </c>
       <c t="s" r="I372" s="7">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c t="s" r="J372" s="7">
-        <v>429</v>
+        <v>434</v>
       </c>
       <c r="K372" s="7"/>
       <c r="L372" s="7"/>
@@ -13120,22 +13180,22 @@
       </c>
       <c r="D373" s="7"/>
       <c t="s" r="E373" s="7">
-        <v>427</v>
+        <v>432</v>
       </c>
       <c r="F373" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G373" s="8">
-        <v>428</v>
+        <v>433</v>
       </c>
       <c t="s" r="H373" s="8">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c t="s" r="I373" s="7">
-        <v>375</v>
+        <v>380</v>
       </c>
       <c t="s" r="J373" s="7">
-        <v>430</v>
+        <v>435</v>
       </c>
       <c r="K373" s="7"/>
       <c r="L373" s="7"/>
@@ -13168,7 +13228,7 @@
       </c>
       <c r="D375" s="7"/>
       <c t="s" r="E375" s="7">
-        <v>431</v>
+        <v>436</v>
       </c>
       <c r="F375" s="7">
         <v>330</v>
@@ -13177,18 +13237,18 @@
         <v>17</v>
       </c>
       <c t="s" r="H375" s="8">
-        <v>432</v>
+        <v>437</v>
       </c>
       <c t="s" r="I375" s="7">
-        <v>420</v>
+        <v>425</v>
       </c>
       <c t="s" r="J375" s="7">
-        <v>366</v>
+        <v>345</v>
       </c>
       <c r="K375" s="7"/>
       <c r="L375" s="7"/>
       <c t="s" r="M375" s="7">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="376" ht="14.25" customHeight="1">
@@ -13203,22 +13263,22 @@
       </c>
       <c r="D376" s="7"/>
       <c t="s" r="E376" s="7">
-        <v>431</v>
+        <v>436</v>
       </c>
       <c r="F376" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G376" s="8">
-        <v>432</v>
+        <v>437</v>
       </c>
       <c t="s" r="H376" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I376" s="7">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c t="s" r="J376" s="7">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="K376" s="7"/>
       <c r="L376" s="7"/>
@@ -13251,7 +13311,7 @@
       </c>
       <c r="D378" s="7"/>
       <c t="s" r="E378" s="7">
-        <v>433</v>
+        <v>438</v>
       </c>
       <c r="F378" s="7">
         <v>330</v>
@@ -13260,17 +13320,19 @@
         <v>17</v>
       </c>
       <c t="s" r="H378" s="8">
-        <v>434</v>
+        <v>439</v>
       </c>
       <c t="s" r="I378" s="7">
         <v>100</v>
       </c>
       <c t="s" r="J378" s="7">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="K378" s="7"/>
       <c r="L378" s="7"/>
-      <c r="M378" s="7"/>
+      <c t="s" r="M378" s="7">
+        <v>440</v>
+      </c>
     </row>
     <row r="379" ht="14.25" customHeight="1">
       <c t="s" r="A379" s="6">
@@ -13284,22 +13346,22 @@
       </c>
       <c r="D379" s="7"/>
       <c t="s" r="E379" s="7">
-        <v>433</v>
+        <v>438</v>
       </c>
       <c r="F379" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G379" s="8">
-        <v>434</v>
+        <v>439</v>
       </c>
       <c t="s" r="H379" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I379" s="7">
-        <v>408</v>
+        <v>413</v>
       </c>
       <c t="s" r="J379" s="7">
-        <v>414</v>
+        <v>419</v>
       </c>
       <c r="K379" s="7"/>
       <c r="L379" s="7"/>
@@ -13328,31 +13390,31 @@
         <v>5805</v>
       </c>
       <c t="s" r="C381" s="7">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="D381" s="7"/>
       <c t="s" r="E381" s="7">
-        <v>435</v>
+        <v>441</v>
       </c>
       <c r="F381" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G381" s="8">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c t="s" r="H381" s="8">
-        <v>436</v>
+        <v>442</v>
       </c>
       <c t="s" r="I381" s="7">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c t="s" r="J381" s="7">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="K381" s="7"/>
       <c r="L381" s="7"/>
       <c t="s" r="M381" s="7">
-        <v>437</v>
+        <v>443</v>
       </c>
     </row>
     <row r="382" ht="14.25" customHeight="1">
@@ -13363,23 +13425,23 @@
         <v>5806</v>
       </c>
       <c t="s" r="C382" s="7">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="D382" s="7"/>
       <c t="s" r="E382" s="7">
-        <v>435</v>
+        <v>441</v>
       </c>
       <c r="F382" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G382" s="8">
-        <v>436</v>
+        <v>442</v>
       </c>
       <c t="s" r="H382" s="8">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c t="s" r="I382" s="7">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c t="s" r="J382" s="7">
         <v>51</v>
@@ -13415,19 +13477,19 @@
       </c>
       <c r="D384" s="7"/>
       <c t="s" r="E384" s="7">
-        <v>438</v>
+        <v>444</v>
       </c>
       <c r="F384" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G384" s="8">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c t="s" r="H384" s="8">
-        <v>439</v>
+        <v>445</v>
       </c>
       <c t="s" r="I384" s="7">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c t="s" r="J384" s="7">
         <v>55</v>
@@ -13435,7 +13497,7 @@
       <c r="K384" s="7"/>
       <c r="L384" s="7"/>
       <c t="s" r="M384" s="7">
-        <v>440</v>
+        <v>446</v>
       </c>
     </row>
     <row r="385" ht="15" customHeight="1">
@@ -13450,22 +13512,22 @@
       </c>
       <c r="D385" s="7"/>
       <c t="s" r="E385" s="7">
-        <v>438</v>
+        <v>444</v>
       </c>
       <c r="F385" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G385" s="8">
-        <v>439</v>
+        <v>445</v>
       </c>
       <c t="s" r="H385" s="8">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c t="s" r="I385" s="7">
         <v>57</v>
       </c>
       <c t="s" r="J385" s="7">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="K385" s="7"/>
       <c r="L385" s="7"/>
@@ -13498,19 +13560,19 @@
       </c>
       <c r="D387" s="7"/>
       <c t="s" r="E387" s="7">
-        <v>441</v>
+        <v>447</v>
       </c>
       <c r="F387" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G387" s="8">
-        <v>442</v>
+        <v>448</v>
       </c>
       <c t="s" r="H387" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I387" s="7">
-        <v>401</v>
+        <v>406</v>
       </c>
       <c t="s" r="J387" s="7">
         <v>58</v>
@@ -13518,7 +13580,7 @@
       <c r="K387" s="7"/>
       <c r="L387" s="7"/>
       <c t="s" r="M387" s="7">
-        <v>443</v>
+        <v>449</v>
       </c>
     </row>
     <row r="388" ht="14.25" customHeight="1">
@@ -13533,7 +13595,7 @@
       </c>
       <c r="D388" s="7"/>
       <c t="s" r="E388" s="7">
-        <v>441</v>
+        <v>447</v>
       </c>
       <c r="F388" s="7">
         <v>330</v>
@@ -13545,10 +13607,10 @@
         <v>43</v>
       </c>
       <c t="s" r="I388" s="7">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c t="s" r="J388" s="7">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="K388" s="7"/>
       <c r="L388" s="7"/>
@@ -13566,7 +13628,7 @@
       </c>
       <c r="D389" s="7"/>
       <c t="s" r="E389" s="7">
-        <v>441</v>
+        <v>447</v>
       </c>
       <c r="F389" s="7">
         <v>330</v>
@@ -13578,10 +13640,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I389" s="7">
-        <v>417</v>
+        <v>422</v>
       </c>
       <c t="s" r="J389" s="7">
-        <v>387</v>
+        <v>391</v>
       </c>
       <c r="K389" s="7"/>
       <c r="L389" s="7"/>
@@ -13589,7 +13651,7 @@
     </row>
     <row r="390" ht="16.5" customHeight="1">
       <c t="s" r="A390" s="9">
-        <v>444</v>
+        <v>450</v>
       </c>
       <c r="B390" s="9"/>
       <c r="C390" s="9"/>
@@ -13609,7 +13671,7 @@
     <row r="391" ht="65.25" customHeight="1"/>
     <row r="392" ht="16.5" customHeight="1">
       <c t="s" r="A392" s="10">
-        <v>445</v>
+        <v>451</v>
       </c>
       <c r="B392" s="10"/>
       <c r="C392" s="10"/>
@@ -13622,7 +13684,7 @@
       <c r="J392" s="10"/>
       <c r="K392" s="10"/>
       <c t="s" r="L392" s="11">
-        <v>446</v>
+        <v>452</v>
       </c>
       <c r="M392" s="11"/>
       <c r="N392" s="11"/>

--- a/Data/FlightPlan/FPL_23OCT26.xlsx
+++ b/Data/FlightPlan/FPL_23OCT26.xlsx
@@ -221,6 +221,9 @@
     <t>14:45</t>
   </si>
   <si>
+    <t>14:53</t>
+  </si>
+  <si>
     <t>17:00</t>
   </si>
   <si>
@@ -242,48 +245,51 @@
     <t>11:25</t>
   </si>
   <si>
+    <t>13:40</t>
+  </si>
+  <si>
+    <t>HPH</t>
+  </si>
+  <si>
+    <t>15:15</t>
+  </si>
+  <si>
+    <t>17:15</t>
+  </si>
+  <si>
+    <t>19:45</t>
+  </si>
+  <si>
+    <t>20:30</t>
+  </si>
+  <si>
+    <t>22:40</t>
+  </si>
+  <si>
+    <t>01:40</t>
+  </si>
+  <si>
+    <t>07:55</t>
+  </si>
+  <si>
+    <t>VN-A526</t>
+  </si>
+  <si>
+    <t>09:00</t>
+  </si>
+  <si>
+    <t>11:00</t>
+  </si>
+  <si>
+    <t>11:09</t>
+  </si>
+  <si>
+    <t>11:30</t>
+  </si>
+  <si>
     <t>13:30</t>
   </si>
   <si>
-    <t>HPH</t>
-  </si>
-  <si>
-    <t>15:15</t>
-  </si>
-  <si>
-    <t>17:15</t>
-  </si>
-  <si>
-    <t>19:45</t>
-  </si>
-  <si>
-    <t>20:30</t>
-  </si>
-  <si>
-    <t>22:40</t>
-  </si>
-  <si>
-    <t>01:40</t>
-  </si>
-  <si>
-    <t>07:55</t>
-  </si>
-  <si>
-    <t>VN-A526</t>
-  </si>
-  <si>
-    <t>09:00</t>
-  </si>
-  <si>
-    <t>11:00</t>
-  </si>
-  <si>
-    <t>11:09</t>
-  </si>
-  <si>
-    <t>11:30</t>
-  </si>
-  <si>
     <t>16:35</t>
   </si>
   <si>
@@ -320,7 +326,7 @@
     <t>13:25</t>
   </si>
   <si>
-    <t>12:52</t>
+    <t>13:26</t>
   </si>
   <si>
     <t>14:00</t>
@@ -467,6 +473,9 @@
     <t>10:49</t>
   </si>
   <si>
+    <t>12:57</t>
+  </si>
+  <si>
     <t>13:15</t>
   </si>
   <si>
@@ -575,7 +584,7 @@
     <t>11:50</t>
   </si>
   <si>
-    <t>12:50</t>
+    <t>12:47</t>
   </si>
   <si>
     <t>15:05</t>
@@ -707,6 +716,9 @@
     <t>11:45</t>
   </si>
   <si>
+    <t>13:01</t>
+  </si>
+  <si>
     <t>14:40</t>
   </si>
   <si>
@@ -947,9 +959,6 @@
     <t>13:09</t>
   </si>
   <si>
-    <t>13:40</t>
-  </si>
-  <si>
     <t>20:00</t>
   </si>
   <si>
@@ -992,7 +1001,7 @@
     <t>10:29</t>
   </si>
   <si>
-    <t>13:39</t>
+    <t>13:36</t>
   </si>
   <si>
     <t>17:50</t>
@@ -1100,6 +1109,9 @@
     <t>11:52</t>
   </si>
   <si>
+    <t>14:23</t>
+  </si>
+  <si>
     <t>21:15</t>
   </si>
   <si>
@@ -1124,6 +1136,9 @@
     <t>10:58</t>
   </si>
   <si>
+    <t>13:42</t>
+  </si>
+  <si>
     <t>19:15</t>
   </si>
   <si>
@@ -1148,6 +1163,9 @@
     <t>TXN</t>
   </si>
   <si>
+    <t>15:53</t>
+  </si>
+  <si>
     <t>PKX</t>
   </si>
   <si>
@@ -1160,7 +1178,7 @@
     <t>07:25</t>
   </si>
   <si>
-    <t>14:44</t>
+    <t>14:51</t>
   </si>
   <si>
     <t>KHH</t>
@@ -1172,138 +1190,147 @@
     <t>VN-A669</t>
   </si>
   <si>
+    <t>13:27</t>
+  </si>
+  <si>
+    <t>16:15</t>
+  </si>
+  <si>
+    <t>VCL</t>
+  </si>
+  <si>
+    <t>VN-A670</t>
+  </si>
+  <si>
+    <t>07:45</t>
+  </si>
+  <si>
+    <t>10:17</t>
+  </si>
+  <si>
+    <t>00:05</t>
+  </si>
+  <si>
+    <t>VN-A672</t>
+  </si>
+  <si>
+    <t>10:39</t>
+  </si>
+  <si>
+    <t>22:15</t>
+  </si>
+  <si>
+    <t>VN-A674</t>
+  </si>
+  <si>
+    <t>12:32</t>
+  </si>
+  <si>
+    <t>13:10</t>
+  </si>
+  <si>
+    <t>23:10</t>
+  </si>
+  <si>
+    <t>VN-A675</t>
+  </si>
+  <si>
+    <t>08:57</t>
+  </si>
+  <si>
+    <t>12:23</t>
+  </si>
+  <si>
+    <t>VN-A676</t>
+  </si>
+  <si>
+    <t>08:34</t>
+  </si>
+  <si>
+    <t>11:15</t>
+  </si>
+  <si>
+    <t>11:29</t>
+  </si>
+  <si>
+    <t>14:04</t>
+  </si>
+  <si>
+    <t>PVG</t>
+  </si>
+  <si>
+    <t>01:15</t>
+  </si>
+  <si>
+    <t>02:20</t>
+  </si>
+  <si>
+    <t>04:50</t>
+  </si>
+  <si>
+    <t>VN-A677</t>
+  </si>
+  <si>
+    <t>01:30</t>
+  </si>
+  <si>
+    <t>02:30</t>
+  </si>
+  <si>
+    <t>04:10</t>
+  </si>
+  <si>
+    <t>VN-A683</t>
+  </si>
+  <si>
+    <t>14:33</t>
+  </si>
+  <si>
+    <t>19:05</t>
+  </si>
+  <si>
+    <t>VN-A684</t>
+  </si>
+  <si>
+    <t>06:05</t>
+  </si>
+  <si>
+    <t>07:33</t>
+  </si>
+  <si>
+    <t>08:05</t>
+  </si>
+  <si>
+    <t>21:55</t>
+  </si>
+  <si>
+    <t>23:45</t>
+  </si>
+  <si>
+    <t>VN-A685</t>
+  </si>
+  <si>
+    <t>10:15</t>
+  </si>
+  <si>
+    <t>10:57</t>
+  </si>
+  <si>
+    <t>12:53</t>
+  </si>
+  <si>
+    <t>14:10</t>
+  </si>
+  <si>
+    <t>VN-A689</t>
+  </si>
+  <si>
+    <t>09:36</t>
+  </si>
+  <si>
     <t>VDH</t>
   </si>
   <si>
-    <t>VN-A670</t>
-  </si>
-  <si>
-    <t>07:45</t>
-  </si>
-  <si>
-    <t>10:17</t>
-  </si>
-  <si>
-    <t>00:05</t>
-  </si>
-  <si>
-    <t>VN-A672</t>
-  </si>
-  <si>
-    <t>10:39</t>
-  </si>
-  <si>
-    <t>22:15</t>
-  </si>
-  <si>
-    <t>VN-A674</t>
-  </si>
-  <si>
-    <t>12:32</t>
-  </si>
-  <si>
-    <t>13:10</t>
-  </si>
-  <si>
-    <t>23:10</t>
-  </si>
-  <si>
-    <t>VN-A675</t>
-  </si>
-  <si>
-    <t>08:57</t>
-  </si>
-  <si>
-    <t>12:23</t>
-  </si>
-  <si>
-    <t>16:15</t>
-  </si>
-  <si>
-    <t>VCL</t>
-  </si>
-  <si>
-    <t>VN-A676</t>
-  </si>
-  <si>
-    <t>08:34</t>
-  </si>
-  <si>
-    <t>11:15</t>
-  </si>
-  <si>
-    <t>11:29</t>
-  </si>
-  <si>
-    <t>PVG</t>
-  </si>
-  <si>
-    <t>01:15</t>
-  </si>
-  <si>
-    <t>02:20</t>
-  </si>
-  <si>
-    <t>04:50</t>
-  </si>
-  <si>
-    <t>VN-A677</t>
-  </si>
-  <si>
-    <t>01:30</t>
-  </si>
-  <si>
-    <t>02:30</t>
-  </si>
-  <si>
-    <t>04:10</t>
-  </si>
-  <si>
-    <t>VN-A683</t>
-  </si>
-  <si>
-    <t>19:05</t>
-  </si>
-  <si>
-    <t>VN-A684</t>
-  </si>
-  <si>
-    <t>06:05</t>
-  </si>
-  <si>
-    <t>07:33</t>
-  </si>
-  <si>
-    <t>08:05</t>
-  </si>
-  <si>
-    <t>21:55</t>
-  </si>
-  <si>
-    <t>23:45</t>
-  </si>
-  <si>
-    <t>VN-A685</t>
-  </si>
-  <si>
-    <t>10:15</t>
-  </si>
-  <si>
-    <t>10:57</t>
-  </si>
-  <si>
-    <t>12:53</t>
-  </si>
-  <si>
-    <t>14:10</t>
-  </si>
-  <si>
-    <t>VN-A689</t>
-  </si>
-  <si>
-    <t>09:36</t>
-  </si>
-  <si>
     <t>VN-A697</t>
   </si>
   <si>
@@ -1331,7 +1358,7 @@
     <t>MEL</t>
   </si>
   <si>
-    <t>00:01</t>
+    <t>00:19</t>
   </si>
   <si>
     <t>VN-A815</t>
@@ -1349,9 +1376,6 @@
     <t>SVO</t>
   </si>
   <si>
-    <t>13:54</t>
-  </si>
-  <si>
     <t>VN-A820</t>
   </si>
   <si>
@@ -1364,7 +1388,7 @@
     <t>Total Record(s): 316</t>
   </si>
   <si>
-    <t xml:space="preserve">Generated on  Oct 23, 2026 11:39</t>
+    <t xml:space="preserve">Generated on  Oct 23, 2026 12:38</t>
   </si>
   <si>
     <t>Page 1 of 1</t>
@@ -2561,7 +2585,9 @@
       </c>
       <c r="K27" s="7"/>
       <c r="L27" s="7"/>
-      <c r="M27" s="7"/>
+      <c t="s" r="M27" s="7">
+        <v>70</v>
+      </c>
     </row>
     <row r="28" ht="14.25" customHeight="1">
       <c t="s" r="A28" s="6">
@@ -2590,7 +2616,7 @@
         <v>22</v>
       </c>
       <c t="s" r="J28" s="7">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="K28" s="7"/>
       <c r="L28" s="7"/>
@@ -2620,7 +2646,7 @@
         <v>53</v>
       </c>
       <c t="s" r="I29" s="7">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c t="s" r="J29" s="7">
         <v>65</v>
@@ -2656,7 +2682,7 @@
       </c>
       <c r="D31" s="7"/>
       <c t="s" r="E31" s="7">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="F31" s="7">
         <v>321</v>
@@ -2668,15 +2694,15 @@
         <v>43</v>
       </c>
       <c t="s" r="I31" s="7">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c t="s" r="J31" s="7">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="K31" s="7"/>
       <c r="L31" s="7"/>
       <c t="s" r="M31" s="7">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="32" ht="14.25" customHeight="1">
@@ -2691,7 +2717,7 @@
       </c>
       <c r="D32" s="7"/>
       <c t="s" r="E32" s="7">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="F32" s="7">
         <v>321</v>
@@ -2703,7 +2729,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I32" s="7">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c t="s" r="J32" s="7">
         <v>35</v>
@@ -2711,7 +2737,7 @@
       <c r="K32" s="7"/>
       <c r="L32" s="7"/>
       <c t="s" r="M32" s="7">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="33" ht="14.25" customHeight="1">
@@ -2726,7 +2752,7 @@
       </c>
       <c r="D33" s="7"/>
       <c t="s" r="E33" s="7">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="F33" s="7">
         <v>321</v>
@@ -2735,13 +2761,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H33" s="8">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c t="s" r="I33" s="7">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c t="s" r="J33" s="7">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="K33" s="7"/>
       <c r="L33" s="7"/>
@@ -2759,13 +2785,13 @@
       </c>
       <c r="D34" s="7"/>
       <c t="s" r="E34" s="7">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="F34" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G34" s="8">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c t="s" r="H34" s="8">
         <v>17</v>
@@ -2774,7 +2800,7 @@
         <v>59</v>
       </c>
       <c t="s" r="J34" s="7">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="K34" s="7"/>
       <c r="L34" s="7"/>
@@ -2792,7 +2818,7 @@
       </c>
       <c r="D35" s="7"/>
       <c t="s" r="E35" s="7">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="F35" s="7">
         <v>321</v>
@@ -2804,10 +2830,10 @@
         <v>43</v>
       </c>
       <c t="s" r="I35" s="7">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c t="s" r="J35" s="7">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="K35" s="7"/>
       <c r="L35" s="7"/>
@@ -2825,7 +2851,7 @@
       </c>
       <c r="D36" s="7"/>
       <c t="s" r="E36" s="7">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="F36" s="7">
         <v>321</v>
@@ -2837,10 +2863,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I36" s="7">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c t="s" r="J36" s="7">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="K36" s="7"/>
       <c r="L36" s="7"/>
@@ -2873,7 +2899,7 @@
       </c>
       <c r="D38" s="7"/>
       <c t="s" r="E38" s="7">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="F38" s="7">
         <v>321</v>
@@ -2882,18 +2908,18 @@
         <v>17</v>
       </c>
       <c t="s" r="H38" s="8">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c t="s" r="I38" s="7">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c t="s" r="J38" s="7">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="K38" s="7"/>
       <c r="L38" s="7"/>
       <c t="s" r="M38" s="7">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="39" ht="14.25" customHeight="1">
@@ -2908,26 +2934,28 @@
       </c>
       <c r="D39" s="7"/>
       <c t="s" r="E39" s="7">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="F39" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G39" s="8">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c t="s" r="H39" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I39" s="7">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c t="s" r="J39" s="7">
-        <v>77</v>
+        <v>92</v>
       </c>
       <c r="K39" s="7"/>
       <c r="L39" s="7"/>
-      <c r="M39" s="7"/>
+      <c t="s" r="M39" s="7">
+        <v>55</v>
+      </c>
     </row>
     <row r="40" ht="15" customHeight="1">
       <c t="s" r="A40" s="6">
@@ -2941,7 +2969,7 @@
       </c>
       <c r="D40" s="7"/>
       <c t="s" r="E40" s="7">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="F40" s="7">
         <v>321</v>
@@ -2950,7 +2978,7 @@
         <v>17</v>
       </c>
       <c t="s" r="H40" s="8">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c t="s" r="I40" s="7">
         <v>55</v>
@@ -2974,19 +3002,19 @@
       </c>
       <c r="D41" s="7"/>
       <c t="s" r="E41" s="7">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="F41" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G41" s="8">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c t="s" r="H41" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I41" s="7">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c t="s" r="J41" s="7">
         <v>25</v>
@@ -3007,7 +3035,7 @@
       </c>
       <c r="D42" s="7"/>
       <c t="s" r="E42" s="7">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="F42" s="7">
         <v>321</v>
@@ -3016,10 +3044,10 @@
         <v>17</v>
       </c>
       <c t="s" r="H42" s="8">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c t="s" r="I42" s="7">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c t="s" r="J42" s="7">
         <v>28</v>
@@ -3040,19 +3068,19 @@
       </c>
       <c r="D43" s="7"/>
       <c t="s" r="E43" s="7">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="F43" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G43" s="8">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c t="s" r="H43" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I43" s="7">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c t="s" r="J43" s="7">
         <v>31</v>
@@ -3088,7 +3116,7 @@
       </c>
       <c r="D45" s="7"/>
       <c t="s" r="E45" s="7">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="F45" s="7">
         <v>321</v>
@@ -3100,15 +3128,15 @@
         <v>21</v>
       </c>
       <c t="s" r="I45" s="7">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c t="s" r="J45" s="7">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="K45" s="7"/>
       <c r="L45" s="7"/>
       <c t="s" r="M45" s="7">
-        <v>97</v>
+        <v>99</v>
       </c>
     </row>
     <row r="46" ht="14.25" customHeight="1">
@@ -3123,7 +3151,7 @@
       </c>
       <c r="D46" s="7"/>
       <c t="s" r="E46" s="7">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="F46" s="7">
         <v>321</v>
@@ -3132,18 +3160,18 @@
         <v>21</v>
       </c>
       <c t="s" r="H46" s="8">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c t="s" r="I46" s="7">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c t="s" r="J46" s="7">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="K46" s="7"/>
       <c r="L46" s="7"/>
       <c t="s" r="M46" s="7">
-        <v>101</v>
+        <v>103</v>
       </c>
     </row>
     <row r="47" ht="14.25" customHeight="1">
@@ -3158,13 +3186,13 @@
       </c>
       <c r="D47" s="7"/>
       <c t="s" r="E47" s="7">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="F47" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G47" s="8">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c t="s" r="H47" s="8">
         <v>21</v>
@@ -3173,12 +3201,12 @@
         <v>18</v>
       </c>
       <c t="s" r="J47" s="7">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="K47" s="7"/>
       <c r="L47" s="7"/>
       <c t="s" r="M47" s="7">
-        <v>103</v>
+        <v>105</v>
       </c>
     </row>
     <row r="48" ht="14.25" customHeight="1">
@@ -3193,7 +3221,7 @@
       </c>
       <c r="D48" s="7"/>
       <c t="s" r="E48" s="7">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="F48" s="7">
         <v>321</v>
@@ -3205,7 +3233,7 @@
         <v>43</v>
       </c>
       <c t="s" r="I48" s="7">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c t="s" r="J48" s="7">
         <v>58</v>
@@ -3226,7 +3254,7 @@
       </c>
       <c r="D49" s="7"/>
       <c t="s" r="E49" s="7">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="F49" s="7">
         <v>321</v>
@@ -3238,10 +3266,10 @@
         <v>21</v>
       </c>
       <c t="s" r="I49" s="7">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c t="s" r="J49" s="7">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="K49" s="7"/>
       <c r="L49" s="7"/>
@@ -3259,7 +3287,7 @@
       </c>
       <c r="D50" s="7"/>
       <c t="s" r="E50" s="7">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="F50" s="7">
         <v>321</v>
@@ -3271,10 +3299,10 @@
         <v>43</v>
       </c>
       <c t="s" r="I50" s="7">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c t="s" r="J50" s="7">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="K50" s="7"/>
       <c r="L50" s="7"/>
@@ -3307,7 +3335,7 @@
       </c>
       <c r="D52" s="7"/>
       <c t="s" r="E52" s="7">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="F52" s="7">
         <v>321</v>
@@ -3316,18 +3344,18 @@
         <v>17</v>
       </c>
       <c t="s" r="H52" s="8">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c t="s" r="I52" s="7">
         <v>66</v>
       </c>
       <c t="s" r="J52" s="7">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="K52" s="7"/>
       <c r="L52" s="7"/>
       <c t="s" r="M52" s="7">
-        <v>112</v>
+        <v>114</v>
       </c>
     </row>
     <row r="53" ht="14.25" customHeight="1">
@@ -3342,22 +3370,22 @@
       </c>
       <c r="D53" s="7"/>
       <c t="s" r="E53" s="7">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="F53" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G53" s="8">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c t="s" r="H53" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I53" s="7">
-        <v>77</v>
+        <v>92</v>
       </c>
       <c t="s" r="J53" s="7">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="K53" s="7"/>
       <c r="L53" s="7"/>
@@ -3375,22 +3403,22 @@
       </c>
       <c r="D54" s="7"/>
       <c t="s" r="E54" s="7">
+        <v>111</v>
+      </c>
+      <c r="F54" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G54" s="8">
+        <v>17</v>
+      </c>
+      <c t="s" r="H54" s="8">
+        <v>116</v>
+      </c>
+      <c t="s" r="I54" s="7">
         <v>109</v>
       </c>
-      <c r="F54" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G54" s="8">
-        <v>17</v>
-      </c>
-      <c t="s" r="H54" s="8">
-        <v>114</v>
-      </c>
-      <c t="s" r="I54" s="7">
-        <v>107</v>
-      </c>
       <c t="s" r="J54" s="7">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="K54" s="7"/>
       <c r="L54" s="7"/>
@@ -3408,22 +3436,22 @@
       </c>
       <c r="D55" s="7"/>
       <c t="s" r="E55" s="7">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="F55" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G55" s="8">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c t="s" r="H55" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I55" s="7">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c t="s" r="J55" s="7">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="K55" s="7"/>
       <c r="L55" s="7"/>
@@ -3456,7 +3484,7 @@
       </c>
       <c r="D57" s="7"/>
       <c t="s" r="E57" s="7">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="F57" s="7">
         <v>321</v>
@@ -3465,13 +3493,13 @@
         <v>43</v>
       </c>
       <c t="s" r="H57" s="8">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c t="s" r="I57" s="7">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c t="s" r="J57" s="7">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="K57" s="7"/>
       <c r="L57" s="7"/>
@@ -3491,13 +3519,13 @@
       </c>
       <c r="D58" s="7"/>
       <c t="s" r="E58" s="7">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="F58" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G58" s="8">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c t="s" r="H58" s="8">
         <v>43</v>
@@ -3511,7 +3539,7 @@
       <c r="K58" s="7"/>
       <c r="L58" s="7"/>
       <c t="s" r="M58" s="7">
-        <v>122</v>
+        <v>124</v>
       </c>
     </row>
     <row r="59" ht="14.25" customHeight="1">
@@ -3526,7 +3554,7 @@
       </c>
       <c r="D59" s="7"/>
       <c t="s" r="E59" s="7">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="F59" s="7">
         <v>321</v>
@@ -3535,13 +3563,13 @@
         <v>43</v>
       </c>
       <c t="s" r="H59" s="8">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c t="s" r="I59" s="7">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c t="s" r="J59" s="7">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="K59" s="7"/>
       <c r="L59" s="7"/>
@@ -3559,13 +3587,13 @@
       </c>
       <c r="D60" s="7"/>
       <c t="s" r="E60" s="7">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="F60" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G60" s="8">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c t="s" r="H60" s="8">
         <v>43</v>
@@ -3574,7 +3602,7 @@
         <v>56</v>
       </c>
       <c t="s" r="J60" s="7">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="K60" s="7"/>
       <c r="L60" s="7"/>
@@ -3592,7 +3620,7 @@
       </c>
       <c r="D61" s="7"/>
       <c t="s" r="E61" s="7">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="F61" s="7">
         <v>321</v>
@@ -3601,13 +3629,13 @@
         <v>43</v>
       </c>
       <c t="s" r="H61" s="8">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c t="s" r="I61" s="7">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c t="s" r="J61" s="7">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="K61" s="7"/>
       <c r="L61" s="7"/>
@@ -3625,22 +3653,22 @@
       </c>
       <c r="D62" s="7"/>
       <c t="s" r="E62" s="7">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="F62" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G62" s="8">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c t="s" r="H62" s="8">
         <v>43</v>
       </c>
       <c t="s" r="I62" s="7">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c t="s" r="J62" s="7">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="K62" s="7"/>
       <c r="L62" s="7"/>
@@ -3673,7 +3701,7 @@
       </c>
       <c r="D64" s="7"/>
       <c t="s" r="E64" s="7">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="F64" s="7">
         <v>321</v>
@@ -3685,15 +3713,15 @@
         <v>42</v>
       </c>
       <c t="s" r="I64" s="7">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c t="s" r="J64" s="7">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="K64" s="7"/>
       <c r="L64" s="7"/>
       <c t="s" r="M64" s="7">
-        <v>132</v>
+        <v>134</v>
       </c>
     </row>
     <row r="65" ht="15" customHeight="1">
@@ -3708,7 +3736,7 @@
       </c>
       <c r="D65" s="7"/>
       <c t="s" r="E65" s="7">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="F65" s="7">
         <v>321</v>
@@ -3720,7 +3748,7 @@
         <v>43</v>
       </c>
       <c t="s" r="I65" s="7">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c t="s" r="J65" s="7">
         <v>48</v>
@@ -3756,7 +3784,7 @@
       </c>
       <c r="D67" s="7"/>
       <c t="s" r="E67" s="7">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="F67" s="7">
         <v>321</v>
@@ -3765,18 +3793,18 @@
         <v>17</v>
       </c>
       <c t="s" r="H67" s="8">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c t="s" r="I67" s="7">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c t="s" r="J67" s="7">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="K67" s="7"/>
       <c r="L67" s="7"/>
       <c t="s" r="M67" s="7">
-        <v>138</v>
+        <v>140</v>
       </c>
     </row>
     <row r="68" ht="14.25" customHeight="1">
@@ -3791,27 +3819,27 @@
       </c>
       <c r="D68" s="7"/>
       <c t="s" r="E68" s="7">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="F68" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G68" s="8">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c t="s" r="H68" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I68" s="7">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c t="s" r="J68" s="7">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="K68" s="7"/>
       <c r="L68" s="7"/>
       <c t="s" r="M68" s="7">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="69" ht="14.25" customHeight="1">
@@ -3841,7 +3869,7 @@
       </c>
       <c r="D70" s="7"/>
       <c t="s" r="E70" s="7">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="F70" s="7">
         <v>321</v>
@@ -3853,15 +3881,15 @@
         <v>43</v>
       </c>
       <c t="s" r="I70" s="7">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c t="s" r="J70" s="7">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="K70" s="7"/>
       <c r="L70" s="7"/>
       <c t="s" r="M70" s="7">
-        <v>111</v>
+        <v>113</v>
       </c>
     </row>
     <row r="71" ht="14.25" customHeight="1">
@@ -3876,7 +3904,7 @@
       </c>
       <c r="D71" s="7"/>
       <c t="s" r="E71" s="7">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="F71" s="7">
         <v>321</v>
@@ -3888,10 +3916,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I71" s="7">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c t="s" r="J71" s="7">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="K71" s="7"/>
       <c r="L71" s="7"/>
@@ -3909,7 +3937,7 @@
       </c>
       <c r="D72" s="7"/>
       <c t="s" r="E72" s="7">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="F72" s="7">
         <v>321</v>
@@ -3921,17 +3949,17 @@
         <v>43</v>
       </c>
       <c t="s" r="I72" s="7">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c t="s" r="J72" s="7">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c t="s" r="K72" s="7">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="L72" s="7"/>
       <c t="s" r="M72" s="7">
-        <v>146</v>
+        <v>148</v>
       </c>
     </row>
     <row r="73" ht="14.25" customHeight="1">
@@ -3946,7 +3974,7 @@
       </c>
       <c r="D73" s="7"/>
       <c t="s" r="E73" s="7">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="F73" s="7">
         <v>321</v>
@@ -3958,10 +3986,10 @@
         <v>53</v>
       </c>
       <c t="s" r="I73" s="7">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c t="s" r="J73" s="7">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="K73" s="7"/>
       <c r="L73" s="7"/>
@@ -3994,7 +4022,7 @@
       </c>
       <c r="D75" s="7"/>
       <c t="s" r="E75" s="7">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="F75" s="7">
         <v>321</v>
@@ -4003,18 +4031,18 @@
         <v>43</v>
       </c>
       <c t="s" r="H75" s="8">
+        <v>100</v>
+      </c>
+      <c t="s" r="I75" s="7">
+        <v>139</v>
+      </c>
+      <c t="s" r="J75" s="7">
         <v>98</v>
-      </c>
-      <c t="s" r="I75" s="7">
-        <v>137</v>
-      </c>
-      <c t="s" r="J75" s="7">
-        <v>96</v>
       </c>
       <c r="K75" s="7"/>
       <c r="L75" s="7"/>
       <c t="s" r="M75" s="7">
-        <v>149</v>
+        <v>151</v>
       </c>
     </row>
     <row r="76" ht="14.25" customHeight="1">
@@ -4029,27 +4057,27 @@
       </c>
       <c r="D76" s="7"/>
       <c t="s" r="E76" s="7">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="F76" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G76" s="8">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c t="s" r="H76" s="8">
         <v>43</v>
       </c>
       <c t="s" r="I76" s="7">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c t="s" r="J76" s="7">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="K76" s="7"/>
       <c r="L76" s="7"/>
       <c t="s" r="M76" s="7">
-        <v>151</v>
+        <v>153</v>
       </c>
     </row>
     <row r="77" ht="14.25" customHeight="1">
@@ -4064,7 +4092,7 @@
       </c>
       <c r="D77" s="7"/>
       <c t="s" r="E77" s="7">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="F77" s="7">
         <v>321</v>
@@ -4073,17 +4101,19 @@
         <v>43</v>
       </c>
       <c t="s" r="H77" s="8">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c t="s" r="I77" s="7">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c t="s" r="J77" s="7">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="K77" s="7"/>
       <c r="L77" s="7"/>
-      <c r="M77" s="7"/>
+      <c t="s" r="M77" s="7">
+        <v>154</v>
+      </c>
     </row>
     <row r="78" ht="14.25" customHeight="1">
       <c t="s" r="A78" s="6">
@@ -4097,19 +4127,19 @@
       </c>
       <c r="D78" s="7"/>
       <c t="s" r="E78" s="7">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="F78" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G78" s="8">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c t="s" r="H78" s="8">
         <v>43</v>
       </c>
       <c t="s" r="I78" s="7">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c t="s" r="J78" s="7">
         <v>37</v>
@@ -4130,7 +4160,7 @@
       </c>
       <c r="D79" s="7"/>
       <c t="s" r="E79" s="7">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="F79" s="7">
         <v>321</v>
@@ -4139,10 +4169,10 @@
         <v>43</v>
       </c>
       <c t="s" r="H79" s="8">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c t="s" r="I79" s="7">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c t="s" r="J79" s="7">
         <v>24</v>
@@ -4163,22 +4193,22 @@
       </c>
       <c r="D80" s="7"/>
       <c t="s" r="E80" s="7">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="F80" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G80" s="8">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c t="s" r="H80" s="8">
         <v>43</v>
       </c>
       <c t="s" r="I80" s="7">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c t="s" r="J80" s="7">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="K80" s="7"/>
       <c r="L80" s="7"/>
@@ -4196,7 +4226,7 @@
       </c>
       <c r="D81" s="7"/>
       <c t="s" r="E81" s="7">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="F81" s="7">
         <v>321</v>
@@ -4208,10 +4238,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I81" s="7">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c t="s" r="J81" s="7">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="K81" s="7"/>
       <c r="L81" s="7"/>
@@ -4244,7 +4274,7 @@
       </c>
       <c r="D83" s="7"/>
       <c t="s" r="E83" s="7">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="F83" s="7">
         <v>321</v>
@@ -4256,17 +4286,17 @@
         <v>33</v>
       </c>
       <c t="s" r="I83" s="7">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c t="s" r="J83" s="7">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c t="s" r="K83" s="7">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="L83" s="7"/>
       <c t="s" r="M83" s="7">
-        <v>145</v>
+        <v>59</v>
       </c>
     </row>
     <row r="84" ht="14.25" customHeight="1">
@@ -4281,7 +4311,7 @@
       </c>
       <c r="D84" s="7"/>
       <c t="s" r="E84" s="7">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="F84" s="7">
         <v>321</v>
@@ -4296,14 +4326,14 @@
         <v>24</v>
       </c>
       <c t="s" r="J84" s="7">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c t="s" r="K84" s="7">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="L84" s="7"/>
       <c t="s" r="M84" s="7">
-        <v>165</v>
+        <v>168</v>
       </c>
     </row>
     <row r="85" ht="15" customHeight="1">
@@ -4318,7 +4348,7 @@
       </c>
       <c r="D85" s="7"/>
       <c t="s" r="E85" s="7">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="F85" s="7">
         <v>321</v>
@@ -4330,10 +4360,10 @@
         <v>42</v>
       </c>
       <c t="s" r="I85" s="7">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c t="s" r="J85" s="7">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="K85" s="7"/>
       <c r="L85" s="7"/>
@@ -4366,7 +4396,7 @@
       </c>
       <c r="D87" s="7"/>
       <c t="s" r="E87" s="7">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="F87" s="7">
         <v>321</v>
@@ -4375,18 +4405,18 @@
         <v>17</v>
       </c>
       <c t="s" r="H87" s="8">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c t="s" r="I87" s="7">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c t="s" r="J87" s="7">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="K87" s="7"/>
       <c r="L87" s="7"/>
       <c t="s" r="M87" s="7">
-        <v>169</v>
+        <v>172</v>
       </c>
     </row>
     <row r="88" ht="14.25" customHeight="1">
@@ -4401,27 +4431,27 @@
       </c>
       <c r="D88" s="7"/>
       <c t="s" r="E88" s="7">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="F88" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G88" s="8">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c t="s" r="H88" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I88" s="7">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c t="s" r="J88" s="7">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="K88" s="7"/>
       <c r="L88" s="7"/>
       <c t="s" r="M88" s="7">
-        <v>171</v>
+        <v>174</v>
       </c>
     </row>
     <row r="89" ht="14.25" customHeight="1">
@@ -4436,7 +4466,7 @@
       </c>
       <c r="D89" s="7"/>
       <c t="s" r="E89" s="7">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="F89" s="7">
         <v>321</v>
@@ -4445,18 +4475,18 @@
         <v>17</v>
       </c>
       <c t="s" r="H89" s="8">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c t="s" r="I89" s="7">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c t="s" r="J89" s="7">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="K89" s="7"/>
       <c r="L89" s="7"/>
       <c t="s" r="M89" s="7">
-        <v>175</v>
+        <v>178</v>
       </c>
     </row>
     <row r="90" ht="15" customHeight="1">
@@ -4471,22 +4501,22 @@
       </c>
       <c r="D90" s="7"/>
       <c t="s" r="E90" s="7">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="F90" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G90" s="8">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c t="s" r="H90" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I90" s="7">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c t="s" r="J90" s="7">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="K90" s="7"/>
       <c r="L90" s="7"/>
@@ -4504,7 +4534,7 @@
       </c>
       <c r="D91" s="7"/>
       <c t="s" r="E91" s="7">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="F91" s="7">
         <v>321</v>
@@ -4513,13 +4543,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H91" s="8">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c t="s" r="I91" s="7">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c t="s" r="J91" s="7">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="K91" s="7"/>
       <c r="L91" s="7"/>
@@ -4537,22 +4567,22 @@
       </c>
       <c r="D92" s="7"/>
       <c t="s" r="E92" s="7">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="F92" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G92" s="8">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c t="s" r="H92" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I92" s="7">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c t="s" r="J92" s="7">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="K92" s="7"/>
       <c r="L92" s="7"/>
@@ -4570,7 +4600,7 @@
       </c>
       <c r="D93" s="7"/>
       <c t="s" r="E93" s="7">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="F93" s="7">
         <v>321</v>
@@ -4579,13 +4609,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H93" s="8">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c t="s" r="I93" s="7">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c t="s" r="J93" s="7">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="K93" s="7"/>
       <c r="L93" s="7"/>
@@ -4618,7 +4648,7 @@
       </c>
       <c r="D95" s="7"/>
       <c t="s" r="E95" s="7">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="F95" s="7">
         <v>321</v>
@@ -4627,10 +4657,10 @@
         <v>17</v>
       </c>
       <c t="s" r="H95" s="8">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c t="s" r="I95" s="7">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c t="s" r="J95" s="7">
         <v>66</v>
@@ -4638,7 +4668,7 @@
       <c r="K95" s="7"/>
       <c r="L95" s="7"/>
       <c t="s" r="M95" s="7">
-        <v>184</v>
+        <v>187</v>
       </c>
     </row>
     <row r="96" ht="14.25" customHeight="1">
@@ -4653,27 +4683,27 @@
       </c>
       <c r="D96" s="7"/>
       <c t="s" r="E96" s="7">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="F96" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G96" s="8">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c t="s" r="H96" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I96" s="7">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c t="s" r="J96" s="7">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="K96" s="7"/>
       <c r="L96" s="7"/>
       <c t="s" r="M96" s="7">
-        <v>186</v>
+        <v>189</v>
       </c>
     </row>
     <row r="97" ht="14.25" customHeight="1">
@@ -4688,7 +4718,7 @@
       </c>
       <c r="D97" s="7"/>
       <c t="s" r="E97" s="7">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="F97" s="7">
         <v>321</v>
@@ -4700,17 +4730,17 @@
         <v>21</v>
       </c>
       <c t="s" r="I97" s="7">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c t="s" r="J97" s="7">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c t="s" r="K97" s="7">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="L97" s="7"/>
       <c t="s" r="M97" s="7">
-        <v>188</v>
+        <v>191</v>
       </c>
     </row>
     <row r="98" ht="14.25" customHeight="1">
@@ -4725,7 +4755,7 @@
       </c>
       <c r="D98" s="7"/>
       <c t="s" r="E98" s="7">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="F98" s="7">
         <v>321</v>
@@ -4734,20 +4764,20 @@
         <v>21</v>
       </c>
       <c t="s" r="H98" s="8">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c t="s" r="I98" s="7">
         <v>54</v>
       </c>
       <c t="s" r="J98" s="7">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c t="s" r="K98" s="7">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="L98" s="7"/>
       <c t="s" r="M98" s="7">
-        <v>131</v>
+        <v>133</v>
       </c>
     </row>
     <row r="99" ht="14.25" customHeight="1">
@@ -4762,19 +4792,19 @@
       </c>
       <c r="D99" s="7"/>
       <c t="s" r="E99" s="7">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="F99" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G99" s="8">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c t="s" r="H99" s="8">
         <v>21</v>
       </c>
       <c t="s" r="I99" s="7">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c t="s" r="J99" s="7">
         <v>59</v>
@@ -4784,7 +4814,7 @@
       </c>
       <c r="L99" s="7"/>
       <c t="s" r="M99" s="7">
-        <v>127</v>
+        <v>129</v>
       </c>
     </row>
     <row r="100" ht="15" customHeight="1">
@@ -4799,7 +4829,7 @@
       </c>
       <c r="D100" s="7"/>
       <c t="s" r="E100" s="7">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="F100" s="7">
         <v>321</v>
@@ -4811,17 +4841,17 @@
         <v>17</v>
       </c>
       <c t="s" r="I100" s="7">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c t="s" r="J100" s="7">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c t="s" r="K100" s="7">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="L100" s="7"/>
       <c t="s" r="M100" s="7">
-        <v>191</v>
+        <v>194</v>
       </c>
     </row>
     <row r="101" ht="14.25" customHeight="1">
@@ -4836,7 +4866,7 @@
       </c>
       <c r="D101" s="7"/>
       <c t="s" r="E101" s="7">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="F101" s="7">
         <v>321</v>
@@ -4848,17 +4878,17 @@
         <v>43</v>
       </c>
       <c t="s" r="I101" s="7">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c t="s" r="J101" s="7">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c t="s" r="K101" s="7">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="L101" s="7"/>
       <c t="s" r="M101" s="7">
-        <v>193</v>
+        <v>196</v>
       </c>
     </row>
     <row r="102" ht="14.25" customHeight="1">
@@ -4873,7 +4903,7 @@
       </c>
       <c r="D102" s="7"/>
       <c t="s" r="E102" s="7">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="F102" s="7">
         <v>321</v>
@@ -4882,13 +4912,13 @@
         <v>43</v>
       </c>
       <c t="s" r="H102" s="8">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c t="s" r="I102" s="7">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c t="s" r="J102" s="7">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="K102" s="7"/>
       <c r="L102" s="7"/>
@@ -4921,7 +4951,7 @@
       </c>
       <c r="D104" s="7"/>
       <c t="s" r="E104" s="7">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="F104" s="7">
         <v>321</v>
@@ -4930,18 +4960,18 @@
         <v>17</v>
       </c>
       <c t="s" r="H104" s="8">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c t="s" r="I104" s="7">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c t="s" r="J104" s="7">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="K104" s="7"/>
       <c r="L104" s="7"/>
       <c t="s" r="M104" s="7">
-        <v>198</v>
+        <v>201</v>
       </c>
     </row>
     <row r="105" ht="15" customHeight="1">
@@ -4956,22 +4986,22 @@
       </c>
       <c r="D105" s="7"/>
       <c t="s" r="E105" s="7">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="F105" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G105" s="8">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c t="s" r="H105" s="8">
         <v>43</v>
       </c>
       <c t="s" r="I105" s="7">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c t="s" r="J105" s="7">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="K105" s="7"/>
       <c r="L105" s="7"/>
@@ -4989,7 +5019,7 @@
       </c>
       <c r="D106" s="7"/>
       <c t="s" r="E106" s="7">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="F106" s="7">
         <v>321</v>
@@ -4998,7 +5028,7 @@
         <v>43</v>
       </c>
       <c t="s" r="H106" s="8">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c t="s" r="I106" s="7">
         <v>37</v>
@@ -5022,22 +5052,22 @@
       </c>
       <c r="D107" s="7"/>
       <c t="s" r="E107" s="7">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="F107" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G107" s="8">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c t="s" r="H107" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I107" s="7">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c t="s" r="J107" s="7">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="K107" s="7"/>
       <c r="L107" s="7"/>
@@ -5055,7 +5085,7 @@
       </c>
       <c r="D108" s="7"/>
       <c t="s" r="E108" s="7">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="F108" s="7">
         <v>321</v>
@@ -5064,13 +5094,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H108" s="8">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c t="s" r="I108" s="7">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c t="s" r="J108" s="7">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="K108" s="7"/>
       <c r="L108" s="7"/>
@@ -5088,22 +5118,22 @@
       </c>
       <c r="D109" s="7"/>
       <c t="s" r="E109" s="7">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="F109" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G109" s="8">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c t="s" r="H109" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I109" s="7">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c t="s" r="J109" s="7">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="K109" s="7"/>
       <c r="L109" s="7"/>
@@ -5121,7 +5151,7 @@
       </c>
       <c r="D110" s="7"/>
       <c t="s" r="E110" s="7">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="F110" s="7">
         <v>321</v>
@@ -5133,17 +5163,17 @@
         <v>43</v>
       </c>
       <c t="s" r="I110" s="7">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c t="s" r="J110" s="7">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c t="s" r="K110" s="7">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="L110" s="7"/>
       <c t="s" r="M110" s="7">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="111" ht="14.25" customHeight="1">
@@ -5173,7 +5203,7 @@
       </c>
       <c r="D112" s="7"/>
       <c t="s" r="E112" s="7">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="F112" s="7">
         <v>321</v>
@@ -5182,18 +5212,18 @@
         <v>43</v>
       </c>
       <c t="s" r="H112" s="8">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c t="s" r="I112" s="7">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c t="s" r="J112" s="7">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="K112" s="7"/>
       <c r="L112" s="7"/>
       <c t="s" r="M112" s="7">
-        <v>208</v>
+        <v>211</v>
       </c>
     </row>
     <row r="113" ht="14.25" customHeight="1">
@@ -5208,22 +5238,22 @@
       </c>
       <c r="D113" s="7"/>
       <c t="s" r="E113" s="7">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="F113" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G113" s="8">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c t="s" r="H113" s="8">
         <v>43</v>
       </c>
       <c t="s" r="I113" s="7">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c t="s" r="J113" s="7">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="K113" s="7"/>
       <c r="L113" s="7"/>
@@ -5241,7 +5271,7 @@
       </c>
       <c r="D114" s="7"/>
       <c t="s" r="E114" s="7">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="F114" s="7">
         <v>321</v>
@@ -5253,10 +5283,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I114" s="7">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c t="s" r="J114" s="7">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="K114" s="7"/>
       <c r="L114" s="7"/>
@@ -5274,7 +5304,7 @@
       </c>
       <c r="D115" s="7"/>
       <c t="s" r="E115" s="7">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="F115" s="7">
         <v>321</v>
@@ -5283,13 +5313,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H115" s="8">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c t="s" r="I115" s="7">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c t="s" r="J115" s="7">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="K115" s="7"/>
       <c r="L115" s="7"/>
@@ -5307,22 +5337,22 @@
       </c>
       <c r="D116" s="7"/>
       <c t="s" r="E116" s="7">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="F116" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G116" s="8">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c t="s" r="H116" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I116" s="7">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c t="s" r="J116" s="7">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="K116" s="7"/>
       <c r="L116" s="7"/>
@@ -5340,7 +5370,7 @@
       </c>
       <c r="D117" s="7"/>
       <c t="s" r="E117" s="7">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="F117" s="7">
         <v>321</v>
@@ -5349,13 +5379,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H117" s="8">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c t="s" r="I117" s="7">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c t="s" r="J117" s="7">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="K117" s="7"/>
       <c r="L117" s="7"/>
@@ -5373,22 +5403,22 @@
       </c>
       <c r="D118" s="7"/>
       <c t="s" r="E118" s="7">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="F118" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G118" s="8">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c t="s" r="H118" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I118" s="7">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c t="s" r="J118" s="7">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="K118" s="7"/>
       <c r="L118" s="7"/>
@@ -5421,7 +5451,7 @@
       </c>
       <c r="D120" s="7"/>
       <c t="s" r="E120" s="7">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="F120" s="7">
         <v>321</v>
@@ -5430,18 +5460,18 @@
         <v>17</v>
       </c>
       <c t="s" r="H120" s="8">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c t="s" r="I120" s="7">
         <v>44</v>
       </c>
       <c t="s" r="J120" s="7">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="K120" s="7"/>
       <c r="L120" s="7"/>
       <c t="s" r="M120" s="7">
-        <v>224</v>
+        <v>227</v>
       </c>
     </row>
     <row r="121" ht="14.25" customHeight="1">
@@ -5456,13 +5486,13 @@
       </c>
       <c r="D121" s="7"/>
       <c t="s" r="E121" s="7">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="F121" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G121" s="8">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c t="s" r="H121" s="8">
         <v>17</v>
@@ -5471,7 +5501,7 @@
         <v>35</v>
       </c>
       <c t="s" r="J121" s="7">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="K121" s="7"/>
       <c r="L121" s="7"/>
@@ -5489,7 +5519,7 @@
       </c>
       <c r="D122" s="7"/>
       <c t="s" r="E122" s="7">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="F122" s="7">
         <v>321</v>
@@ -5498,13 +5528,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H122" s="8">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c t="s" r="I122" s="7">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c t="s" r="J122" s="7">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="K122" s="7"/>
       <c r="L122" s="7"/>
@@ -5522,13 +5552,13 @@
       </c>
       <c r="D123" s="7"/>
       <c t="s" r="E123" s="7">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="F123" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G123" s="8">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c t="s" r="H123" s="8">
         <v>17</v>
@@ -5537,7 +5567,7 @@
         <v>48</v>
       </c>
       <c t="s" r="J123" s="7">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="K123" s="7"/>
       <c r="L123" s="7"/>
@@ -5570,27 +5600,27 @@
       </c>
       <c r="D125" s="7"/>
       <c t="s" r="E125" s="7">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="F125" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G125" s="8">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c t="s" r="H125" s="8">
         <v>43</v>
       </c>
       <c t="s" r="I125" s="7">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c t="s" r="J125" s="7">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="K125" s="7"/>
       <c r="L125" s="7"/>
       <c t="s" r="M125" s="7">
-        <v>230</v>
+        <v>233</v>
       </c>
     </row>
     <row r="126" ht="14.25" customHeight="1">
@@ -5605,7 +5635,7 @@
       </c>
       <c r="D126" s="7"/>
       <c t="s" r="E126" s="7">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="F126" s="7">
         <v>321</v>
@@ -5620,12 +5650,12 @@
         <v>44</v>
       </c>
       <c t="s" r="J126" s="7">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="K126" s="7"/>
       <c r="L126" s="7"/>
       <c t="s" r="M126" s="7">
-        <v>231</v>
+        <v>234</v>
       </c>
     </row>
     <row r="127" ht="14.25" customHeight="1">
@@ -5640,7 +5670,7 @@
       </c>
       <c r="D127" s="7"/>
       <c t="s" r="E127" s="7">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="F127" s="7">
         <v>321</v>
@@ -5659,7 +5689,9 @@
       </c>
       <c r="K127" s="7"/>
       <c r="L127" s="7"/>
-      <c r="M127" s="7"/>
+      <c t="s" r="M127" s="7">
+        <v>235</v>
+      </c>
     </row>
     <row r="128" ht="14.25" customHeight="1">
       <c t="s" r="A128" s="6">
@@ -5673,7 +5705,7 @@
       </c>
       <c r="D128" s="7"/>
       <c t="s" r="E128" s="7">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="F128" s="7">
         <v>321</v>
@@ -5682,13 +5714,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H128" s="8">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c t="s" r="I128" s="7">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c t="s" r="J128" s="7">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="K128" s="7"/>
       <c r="L128" s="7"/>
@@ -5706,22 +5738,22 @@
       </c>
       <c r="D129" s="7"/>
       <c t="s" r="E129" s="7">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="F129" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G129" s="8">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c t="s" r="H129" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I129" s="7">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c t="s" r="J129" s="7">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="K129" s="7"/>
       <c r="L129" s="7"/>
@@ -5739,7 +5771,7 @@
       </c>
       <c r="D130" s="7"/>
       <c t="s" r="E130" s="7">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="F130" s="7">
         <v>321</v>
@@ -5751,10 +5783,10 @@
         <v>43</v>
       </c>
       <c t="s" r="I130" s="7">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c t="s" r="J130" s="7">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="K130" s="7"/>
       <c r="L130" s="7"/>
@@ -5772,7 +5804,7 @@
       </c>
       <c r="D131" s="7"/>
       <c t="s" r="E131" s="7">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="F131" s="7">
         <v>321</v>
@@ -5784,10 +5816,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I131" s="7">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c t="s" r="J131" s="7">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="K131" s="7"/>
       <c r="L131" s="7"/>
@@ -5820,7 +5852,7 @@
       </c>
       <c r="D133" s="7"/>
       <c t="s" r="E133" s="7">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="F133" s="7">
         <v>321</v>
@@ -5829,18 +5861,18 @@
         <v>17</v>
       </c>
       <c t="s" r="H133" s="8">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c t="s" r="I133" s="7">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c t="s" r="J133" s="7">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="K133" s="7"/>
       <c r="L133" s="7"/>
       <c t="s" r="M133" s="7">
-        <v>238</v>
+        <v>242</v>
       </c>
     </row>
     <row r="134" ht="14.25" customHeight="1">
@@ -5855,19 +5887,19 @@
       </c>
       <c r="D134" s="7"/>
       <c t="s" r="E134" s="7">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="F134" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G134" s="8">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c t="s" r="H134" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I134" s="7">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c t="s" r="J134" s="7">
         <v>44</v>
@@ -5875,7 +5907,7 @@
       <c r="K134" s="7"/>
       <c r="L134" s="7"/>
       <c t="s" r="M134" s="7">
-        <v>184</v>
+        <v>187</v>
       </c>
     </row>
     <row r="135" ht="15" customHeight="1">
@@ -5890,7 +5922,7 @@
       </c>
       <c r="D135" s="7"/>
       <c t="s" r="E135" s="7">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="F135" s="7">
         <v>321</v>
@@ -5899,18 +5931,18 @@
         <v>17</v>
       </c>
       <c t="s" r="H135" s="8">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c t="s" r="I135" s="7">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c t="s" r="J135" s="7">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="K135" s="7"/>
       <c r="L135" s="7"/>
       <c t="s" r="M135" s="7">
-        <v>240</v>
+        <v>244</v>
       </c>
     </row>
     <row r="136" ht="14.25" customHeight="1">
@@ -5925,19 +5957,19 @@
       </c>
       <c r="D136" s="7"/>
       <c t="s" r="E136" s="7">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="F136" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G136" s="8">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c t="s" r="H136" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I136" s="7">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c t="s" r="J136" s="7">
         <v>37</v>
@@ -5958,7 +5990,7 @@
       </c>
       <c r="D137" s="7"/>
       <c t="s" r="E137" s="7">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="F137" s="7">
         <v>321</v>
@@ -5967,13 +5999,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H137" s="8">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c t="s" r="I137" s="7">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c t="s" r="J137" s="7">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="K137" s="7"/>
       <c r="L137" s="7"/>
@@ -5991,22 +6023,22 @@
       </c>
       <c r="D138" s="7"/>
       <c t="s" r="E138" s="7">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="F138" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G138" s="8">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c t="s" r="H138" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I138" s="7">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c t="s" r="J138" s="7">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="K138" s="7"/>
       <c r="L138" s="7"/>
@@ -6035,31 +6067,31 @@
         <v>7615</v>
       </c>
       <c t="s" r="C140" s="7">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="D140" s="7"/>
       <c t="s" r="E140" s="7">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="F140" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G140" s="8">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c t="s" r="H140" s="8">
         <v>43</v>
       </c>
       <c t="s" r="I140" s="7">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c t="s" r="J140" s="7">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="K140" s="7"/>
       <c r="L140" s="7"/>
       <c t="s" r="M140" s="7">
-        <v>247</v>
+        <v>251</v>
       </c>
     </row>
     <row r="141" ht="14.25" customHeight="1">
@@ -6070,11 +6102,11 @@
         <v>7615</v>
       </c>
       <c t="s" r="C141" s="7">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="D141" s="7"/>
       <c t="s" r="E141" s="7">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="F141" s="7">
         <v>321</v>
@@ -6083,13 +6115,13 @@
         <v>43</v>
       </c>
       <c t="s" r="H141" s="8">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c t="s" r="I141" s="7">
-        <v>248</v>
+        <v>252</v>
       </c>
       <c t="s" r="J141" s="7">
-        <v>249</v>
+        <v>253</v>
       </c>
       <c r="K141" s="7"/>
       <c r="L141" s="7"/>
@@ -6103,26 +6135,26 @@
         <v>7706</v>
       </c>
       <c t="s" r="C142" s="7">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="D142" s="7"/>
       <c t="s" r="E142" s="7">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="F142" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G142" s="8">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c t="s" r="H142" s="8">
         <v>43</v>
       </c>
       <c t="s" r="I142" s="7">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c t="s" r="J142" s="7">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="K142" s="7"/>
       <c r="L142" s="7"/>
@@ -6136,11 +6168,11 @@
         <v>7706</v>
       </c>
       <c t="s" r="C143" s="7">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="D143" s="7"/>
       <c t="s" r="E143" s="7">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="F143" s="7">
         <v>321</v>
@@ -6149,13 +6181,13 @@
         <v>43</v>
       </c>
       <c t="s" r="H143" s="8">
-        <v>250</v>
+        <v>254</v>
       </c>
       <c t="s" r="I143" s="7">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c t="s" r="J143" s="7">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="K143" s="7"/>
       <c r="L143" s="7"/>
@@ -6181,14 +6213,14 @@
         <v>13</v>
       </c>
       <c t="s" r="B145" s="7">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c t="s" r="C145" s="7">
         <v>14</v>
       </c>
       <c r="D145" s="7"/>
       <c t="s" r="E145" s="7">
-        <v>254</v>
+        <v>258</v>
       </c>
       <c r="F145" s="7">
         <v>321</v>
@@ -6203,12 +6235,12 @@
         <v>31</v>
       </c>
       <c t="s" r="J145" s="7">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c r="K145" s="7"/>
       <c r="L145" s="7"/>
       <c t="s" r="M145" s="7">
-        <v>256</v>
+        <v>260</v>
       </c>
     </row>
     <row r="146" ht="14.25" customHeight="1">
@@ -6223,7 +6255,7 @@
       </c>
       <c r="D146" s="7"/>
       <c t="s" r="E146" s="7">
-        <v>254</v>
+        <v>258</v>
       </c>
       <c r="F146" s="7">
         <v>321</v>
@@ -6232,18 +6264,18 @@
         <v>43</v>
       </c>
       <c t="s" r="H146" s="8">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c t="s" r="I146" s="7">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c t="s" r="J146" s="7">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="K146" s="7"/>
       <c r="L146" s="7"/>
       <c t="s" r="M146" s="7">
-        <v>258</v>
+        <v>262</v>
       </c>
     </row>
     <row r="147" ht="14.25" customHeight="1">
@@ -6258,13 +6290,13 @@
       </c>
       <c r="D147" s="7"/>
       <c t="s" r="E147" s="7">
-        <v>254</v>
+        <v>258</v>
       </c>
       <c r="F147" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G147" s="8">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c t="s" r="H147" s="8">
         <v>43</v>
@@ -6273,7 +6305,7 @@
         <v>54</v>
       </c>
       <c t="s" r="J147" s="7">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="K147" s="7"/>
       <c r="L147" s="7"/>
@@ -6291,7 +6323,7 @@
       </c>
       <c r="D148" s="7"/>
       <c t="s" r="E148" s="7">
-        <v>254</v>
+        <v>258</v>
       </c>
       <c r="F148" s="7">
         <v>321</v>
@@ -6300,13 +6332,13 @@
         <v>43</v>
       </c>
       <c t="s" r="H148" s="8">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c t="s" r="I148" s="7">
         <v>22</v>
       </c>
       <c t="s" r="J148" s="7">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="K148" s="7"/>
       <c r="L148" s="7"/>
@@ -6324,22 +6356,22 @@
       </c>
       <c r="D149" s="7"/>
       <c t="s" r="E149" s="7">
-        <v>254</v>
+        <v>258</v>
       </c>
       <c r="F149" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G149" s="8">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c t="s" r="H149" s="8">
         <v>43</v>
       </c>
       <c t="s" r="I149" s="7">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c t="s" r="J149" s="7">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="K149" s="7"/>
       <c r="L149" s="7"/>
@@ -6372,7 +6404,7 @@
       </c>
       <c r="D151" s="7"/>
       <c t="s" r="E151" s="7">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="F151" s="7">
         <v>321</v>
@@ -6384,15 +6416,15 @@
         <v>21</v>
       </c>
       <c t="s" r="I151" s="7">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c t="s" r="J151" s="7">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="K151" s="7"/>
       <c r="L151" s="7"/>
       <c t="s" r="M151" s="7">
-        <v>262</v>
+        <v>266</v>
       </c>
     </row>
     <row r="152" ht="14.25" customHeight="1">
@@ -6407,7 +6439,7 @@
       </c>
       <c r="D152" s="7"/>
       <c t="s" r="E152" s="7">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="F152" s="7">
         <v>321</v>
@@ -6419,15 +6451,15 @@
         <v>17</v>
       </c>
       <c t="s" r="I152" s="7">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c t="s" r="J152" s="7">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="K152" s="7"/>
       <c r="L152" s="7"/>
       <c t="s" r="M152" s="7">
-        <v>263</v>
+        <v>267</v>
       </c>
     </row>
     <row r="153" ht="14.25" customHeight="1">
@@ -6442,7 +6474,7 @@
       </c>
       <c r="D153" s="7"/>
       <c t="s" r="E153" s="7">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="F153" s="7">
         <v>321</v>
@@ -6451,13 +6483,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H153" s="8">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c t="s" r="I153" s="7">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c t="s" r="J153" s="7">
-        <v>77</v>
+        <v>92</v>
       </c>
       <c r="K153" s="7"/>
       <c r="L153" s="7"/>
@@ -6471,17 +6503,17 @@
         <v>5068</v>
       </c>
       <c t="s" r="C154" s="7">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="D154" s="7"/>
       <c t="s" r="E154" s="7">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="F154" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G154" s="8">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c t="s" r="H154" s="8">
         <v>43</v>
@@ -6490,7 +6522,7 @@
         <v>37</v>
       </c>
       <c t="s" r="J154" s="7">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="K154" s="7"/>
       <c r="L154" s="7"/>
@@ -6504,11 +6536,11 @@
         <v>5068</v>
       </c>
       <c t="s" r="C155" s="7">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="D155" s="7"/>
       <c t="s" r="E155" s="7">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="F155" s="7">
         <v>321</v>
@@ -6517,13 +6549,13 @@
         <v>43</v>
       </c>
       <c t="s" r="H155" s="8">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c t="s" r="I155" s="7">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c t="s" r="J155" s="7">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="K155" s="7"/>
       <c r="L155" s="7"/>
@@ -6537,17 +6569,17 @@
         <v>5069</v>
       </c>
       <c t="s" r="C156" s="7">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="D156" s="7"/>
       <c t="s" r="E156" s="7">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="F156" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G156" s="8">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c t="s" r="H156" s="8">
         <v>43</v>
@@ -6556,7 +6588,7 @@
         <v>30</v>
       </c>
       <c t="s" r="J156" s="7">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="K156" s="7"/>
       <c r="L156" s="7"/>
@@ -6589,7 +6621,7 @@
       </c>
       <c r="D158" s="7"/>
       <c t="s" r="E158" s="7">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c r="F158" s="7">
         <v>321</v>
@@ -6601,15 +6633,15 @@
         <v>33</v>
       </c>
       <c t="s" r="I158" s="7">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c t="s" r="J158" s="7">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="K158" s="7"/>
       <c r="L158" s="7"/>
       <c t="s" r="M158" s="7">
-        <v>269</v>
+        <v>273</v>
       </c>
     </row>
     <row r="159" ht="14.25" customHeight="1">
@@ -6624,7 +6656,7 @@
       </c>
       <c r="D159" s="7"/>
       <c t="s" r="E159" s="7">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c r="F159" s="7">
         <v>321</v>
@@ -6636,10 +6668,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I159" s="7">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c t="s" r="J159" s="7">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="K159" s="7"/>
       <c r="L159" s="7"/>
@@ -6657,7 +6689,7 @@
       </c>
       <c r="D160" s="7"/>
       <c t="s" r="E160" s="7">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c r="F160" s="7">
         <v>321</v>
@@ -6669,10 +6701,10 @@
         <v>42</v>
       </c>
       <c t="s" r="I160" s="7">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c t="s" r="J160" s="7">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="K160" s="7"/>
       <c r="L160" s="7"/>
@@ -6705,7 +6737,7 @@
       </c>
       <c r="D162" s="7"/>
       <c t="s" r="E162" s="7">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="F162" s="7">
         <v>321</v>
@@ -6714,18 +6746,18 @@
         <v>17</v>
       </c>
       <c t="s" r="H162" s="8">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c t="s" r="I162" s="7">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c t="s" r="J162" s="7">
-        <v>77</v>
+        <v>92</v>
       </c>
       <c r="K162" s="7"/>
       <c r="L162" s="7"/>
       <c t="s" r="M162" s="7">
-        <v>272</v>
+        <v>276</v>
       </c>
     </row>
     <row r="163" ht="14.25" customHeight="1">
@@ -6740,22 +6772,22 @@
       </c>
       <c r="D163" s="7"/>
       <c t="s" r="E163" s="7">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="F163" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G163" s="8">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c t="s" r="H163" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I163" s="7">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c t="s" r="J163" s="7">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="K163" s="7"/>
       <c r="L163" s="7"/>
@@ -6773,7 +6805,7 @@
       </c>
       <c r="D164" s="7"/>
       <c t="s" r="E164" s="7">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="F164" s="7">
         <v>321</v>
@@ -6782,13 +6814,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H164" s="8">
-        <v>273</v>
+        <v>277</v>
       </c>
       <c t="s" r="I164" s="7">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c t="s" r="J164" s="7">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="K164" s="7"/>
       <c r="L164" s="7"/>
@@ -6806,22 +6838,22 @@
       </c>
       <c r="D165" s="7"/>
       <c t="s" r="E165" s="7">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="F165" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G165" s="8">
-        <v>273</v>
+        <v>277</v>
       </c>
       <c t="s" r="H165" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I165" s="7">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c t="s" r="J165" s="7">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="K165" s="7"/>
       <c r="L165" s="7"/>
@@ -6839,7 +6871,7 @@
       </c>
       <c r="D166" s="7"/>
       <c t="s" r="E166" s="7">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="F166" s="7">
         <v>321</v>
@@ -6848,13 +6880,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H166" s="8">
-        <v>276</v>
+        <v>280</v>
       </c>
       <c t="s" r="I166" s="7">
-        <v>277</v>
+        <v>281</v>
       </c>
       <c t="s" r="J166" s="7">
-        <v>278</v>
+        <v>282</v>
       </c>
       <c r="K166" s="7"/>
       <c r="L166" s="7"/>
@@ -6872,22 +6904,22 @@
       </c>
       <c r="D167" s="7"/>
       <c t="s" r="E167" s="7">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="F167" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G167" s="8">
-        <v>276</v>
+        <v>280</v>
       </c>
       <c t="s" r="H167" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I167" s="7">
-        <v>279</v>
+        <v>283</v>
       </c>
       <c t="s" r="J167" s="7">
-        <v>280</v>
+        <v>284</v>
       </c>
       <c r="K167" s="7"/>
       <c r="L167" s="7"/>
@@ -6920,7 +6952,7 @@
       </c>
       <c r="D169" s="7"/>
       <c t="s" r="E169" s="7">
-        <v>281</v>
+        <v>285</v>
       </c>
       <c r="F169" s="7">
         <v>321</v>
@@ -6932,15 +6964,15 @@
         <v>17</v>
       </c>
       <c t="s" r="I169" s="7">
-        <v>282</v>
+        <v>286</v>
       </c>
       <c t="s" r="J169" s="7">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="K169" s="7"/>
       <c r="L169" s="7"/>
       <c t="s" r="M169" s="7">
-        <v>283</v>
+        <v>287</v>
       </c>
     </row>
     <row r="170" ht="15" customHeight="1">
@@ -6970,7 +7002,7 @@
       </c>
       <c r="D171" s="7"/>
       <c t="s" r="E171" s="7">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="F171" s="7">
         <v>321</v>
@@ -6982,15 +7014,15 @@
         <v>17</v>
       </c>
       <c t="s" r="I171" s="7">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c t="s" r="J171" s="7">
-        <v>285</v>
+        <v>289</v>
       </c>
       <c r="K171" s="7"/>
       <c r="L171" s="7"/>
       <c t="s" r="M171" s="7">
-        <v>286</v>
+        <v>290</v>
       </c>
     </row>
     <row r="172" ht="14.25" customHeight="1">
@@ -7005,7 +7037,7 @@
       </c>
       <c r="D172" s="7"/>
       <c t="s" r="E172" s="7">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="F172" s="7">
         <v>321</v>
@@ -7014,18 +7046,18 @@
         <v>17</v>
       </c>
       <c t="s" r="H172" s="8">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c t="s" r="I172" s="7">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c t="s" r="J172" s="7">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="K172" s="7"/>
       <c r="L172" s="7"/>
       <c t="s" r="M172" s="7">
-        <v>287</v>
+        <v>291</v>
       </c>
     </row>
     <row r="173" ht="14.25" customHeight="1">
@@ -7040,27 +7072,27 @@
       </c>
       <c r="D173" s="7"/>
       <c t="s" r="E173" s="7">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="F173" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G173" s="8">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c t="s" r="H173" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I173" s="7">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c t="s" r="J173" s="7">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="K173" s="7"/>
       <c r="L173" s="7"/>
       <c t="s" r="M173" s="7">
-        <v>223</v>
+        <v>226</v>
       </c>
     </row>
     <row r="174" ht="14.25" customHeight="1">
@@ -7075,7 +7107,7 @@
       </c>
       <c r="D174" s="7"/>
       <c t="s" r="E174" s="7">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="F174" s="7">
         <v>321</v>
@@ -7084,10 +7116,10 @@
         <v>17</v>
       </c>
       <c t="s" r="H174" s="8">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c t="s" r="I174" s="7">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c t="s" r="J174" s="7">
         <v>69</v>
@@ -7108,22 +7140,22 @@
       </c>
       <c r="D175" s="7"/>
       <c t="s" r="E175" s="7">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="F175" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G175" s="8">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c t="s" r="H175" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I175" s="7">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c t="s" r="J175" s="7">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="K175" s="7"/>
       <c r="L175" s="7"/>
@@ -7141,7 +7173,7 @@
       </c>
       <c r="D176" s="7"/>
       <c t="s" r="E176" s="7">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="F176" s="7">
         <v>321</v>
@@ -7150,13 +7182,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H176" s="8">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c t="s" r="I176" s="7">
-        <v>289</v>
+        <v>293</v>
       </c>
       <c t="s" r="J176" s="7">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="K176" s="7"/>
       <c r="L176" s="7"/>
@@ -7174,22 +7206,22 @@
       </c>
       <c r="D177" s="7"/>
       <c t="s" r="E177" s="7">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="F177" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G177" s="8">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c t="s" r="H177" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I177" s="7">
-        <v>291</v>
+        <v>295</v>
       </c>
       <c t="s" r="J177" s="7">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="K177" s="7"/>
       <c r="L177" s="7"/>
@@ -7222,7 +7254,7 @@
       </c>
       <c r="D179" s="7"/>
       <c t="s" r="E179" s="7">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c r="F179" s="7">
         <v>321</v>
@@ -7231,10 +7263,10 @@
         <v>43</v>
       </c>
       <c t="s" r="H179" s="8">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c t="s" r="I179" s="7">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c t="s" r="J179" s="7">
         <v>54</v>
@@ -7242,7 +7274,7 @@
       <c r="K179" s="7"/>
       <c r="L179" s="7"/>
       <c t="s" r="M179" s="7">
-        <v>293</v>
+        <v>297</v>
       </c>
     </row>
     <row r="180" ht="15" customHeight="1">
@@ -7257,22 +7289,22 @@
       </c>
       <c r="D180" s="7"/>
       <c t="s" r="E180" s="7">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c r="F180" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G180" s="8">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c t="s" r="H180" s="8">
         <v>43</v>
       </c>
       <c t="s" r="I180" s="7">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c t="s" r="J180" s="7">
-        <v>289</v>
+        <v>293</v>
       </c>
       <c r="K180" s="7"/>
       <c r="L180" s="7"/>
@@ -7290,7 +7322,7 @@
       </c>
       <c r="D181" s="7"/>
       <c t="s" r="E181" s="7">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c r="F181" s="7">
         <v>321</v>
@@ -7305,7 +7337,7 @@
         <v>28</v>
       </c>
       <c t="s" r="J181" s="7">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="K181" s="7"/>
       <c r="L181" s="7"/>
@@ -7338,7 +7370,7 @@
       </c>
       <c r="D183" s="7"/>
       <c t="s" r="E183" s="7">
-        <v>294</v>
+        <v>298</v>
       </c>
       <c r="F183" s="7">
         <v>321</v>
@@ -7347,18 +7379,18 @@
         <v>17</v>
       </c>
       <c t="s" r="H183" s="8">
-        <v>295</v>
+        <v>299</v>
       </c>
       <c t="s" r="I183" s="7">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c t="s" r="J183" s="7">
-        <v>296</v>
+        <v>300</v>
       </c>
       <c r="K183" s="7"/>
       <c r="L183" s="7"/>
       <c t="s" r="M183" s="7">
-        <v>297</v>
+        <v>301</v>
       </c>
     </row>
     <row r="184" ht="14.25" customHeight="1">
@@ -7373,22 +7405,22 @@
       </c>
       <c r="D184" s="7"/>
       <c t="s" r="E184" s="7">
-        <v>294</v>
+        <v>298</v>
       </c>
       <c r="F184" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G184" s="8">
-        <v>295</v>
+        <v>299</v>
       </c>
       <c t="s" r="H184" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I184" s="7">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c t="s" r="J184" s="7">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="K184" s="7"/>
       <c r="L184" s="7"/>
@@ -7406,7 +7438,7 @@
       </c>
       <c r="D185" s="7"/>
       <c t="s" r="E185" s="7">
-        <v>294</v>
+        <v>298</v>
       </c>
       <c r="F185" s="7">
         <v>321</v>
@@ -7418,17 +7450,17 @@
         <v>43</v>
       </c>
       <c t="s" r="I185" s="7">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c t="s" r="J185" s="7">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c t="s" r="K185" s="7">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="L185" s="7"/>
       <c t="s" r="M185" s="7">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="186" ht="14.25" customHeight="1">
@@ -7443,7 +7475,7 @@
       </c>
       <c r="D186" s="7"/>
       <c t="s" r="E186" s="7">
-        <v>294</v>
+        <v>298</v>
       </c>
       <c r="F186" s="7">
         <v>321</v>
@@ -7458,7 +7490,7 @@
         <v>24</v>
       </c>
       <c t="s" r="J186" s="7">
-        <v>298</v>
+        <v>302</v>
       </c>
       <c r="K186" s="7"/>
       <c r="L186" s="7"/>
@@ -7476,7 +7508,7 @@
       </c>
       <c r="D187" s="7"/>
       <c t="s" r="E187" s="7">
-        <v>294</v>
+        <v>298</v>
       </c>
       <c r="F187" s="7">
         <v>321</v>
@@ -7488,17 +7520,17 @@
         <v>43</v>
       </c>
       <c t="s" r="I187" s="7">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c t="s" r="J187" s="7">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c t="s" r="K187" s="7">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="L187" s="7"/>
       <c t="s" r="M187" s="7">
-        <v>203</v>
+        <v>206</v>
       </c>
     </row>
     <row r="188" ht="14.25" customHeight="1">
@@ -7528,7 +7560,7 @@
       </c>
       <c r="D189" s="7"/>
       <c t="s" r="E189" s="7">
-        <v>299</v>
+        <v>303</v>
       </c>
       <c r="F189" s="7">
         <v>321</v>
@@ -7537,18 +7569,18 @@
         <v>16</v>
       </c>
       <c t="s" r="H189" s="8">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c t="s" r="I189" s="7">
-        <v>300</v>
+        <v>304</v>
       </c>
       <c t="s" r="J189" s="7">
-        <v>301</v>
+        <v>305</v>
       </c>
       <c r="K189" s="7"/>
       <c r="L189" s="7"/>
       <c t="s" r="M189" s="7">
-        <v>302</v>
+        <v>306</v>
       </c>
     </row>
     <row r="190" ht="15" customHeight="1">
@@ -7563,22 +7595,22 @@
       </c>
       <c r="D190" s="7"/>
       <c t="s" r="E190" s="7">
-        <v>299</v>
+        <v>303</v>
       </c>
       <c r="F190" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G190" s="8">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c t="s" r="H190" s="8">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c t="s" r="I190" s="7">
-        <v>303</v>
+        <v>307</v>
       </c>
       <c t="s" r="J190" s="7">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="K190" s="7"/>
       <c r="L190" s="7"/>
@@ -7596,22 +7628,22 @@
       </c>
       <c r="D191" s="7"/>
       <c t="s" r="E191" s="7">
-        <v>299</v>
+        <v>303</v>
       </c>
       <c r="F191" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G191" s="8">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c t="s" r="H191" s="8">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c t="s" r="I191" s="7">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c t="s" r="J191" s="7">
-        <v>304</v>
+        <v>308</v>
       </c>
       <c r="K191" s="7"/>
       <c r="L191" s="7"/>
@@ -7644,7 +7676,7 @@
       </c>
       <c r="D193" s="7"/>
       <c t="s" r="E193" s="7">
-        <v>305</v>
+        <v>309</v>
       </c>
       <c r="F193" s="7">
         <v>321</v>
@@ -7653,18 +7685,18 @@
         <v>17</v>
       </c>
       <c t="s" r="H193" s="8">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c t="s" r="I193" s="7">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c t="s" r="J193" s="7">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="K193" s="7"/>
       <c r="L193" s="7"/>
       <c t="s" r="M193" s="7">
-        <v>308</v>
+        <v>312</v>
       </c>
     </row>
     <row r="194" ht="14.25" customHeight="1">
@@ -7679,19 +7711,19 @@
       </c>
       <c r="D194" s="7"/>
       <c t="s" r="E194" s="7">
-        <v>305</v>
+        <v>309</v>
       </c>
       <c r="F194" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G194" s="8">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c t="s" r="H194" s="8">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c t="s" r="I194" s="7">
-        <v>309</v>
+        <v>313</v>
       </c>
       <c t="s" r="J194" s="7">
         <v>34</v>
@@ -7699,7 +7731,7 @@
       <c r="K194" s="7"/>
       <c r="L194" s="7"/>
       <c t="s" r="M194" s="7">
-        <v>121</v>
+        <v>123</v>
       </c>
     </row>
     <row r="195" ht="15" customHeight="1">
@@ -7714,27 +7746,27 @@
       </c>
       <c r="D195" s="7"/>
       <c t="s" r="E195" s="7">
-        <v>305</v>
+        <v>309</v>
       </c>
       <c r="F195" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G195" s="8">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c t="s" r="H195" s="8">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c t="s" r="I195" s="7">
-        <v>310</v>
+        <v>314</v>
       </c>
       <c t="s" r="J195" s="7">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="K195" s="7"/>
       <c r="L195" s="7"/>
       <c t="s" r="M195" s="7">
-        <v>151</v>
+        <v>153</v>
       </c>
     </row>
     <row r="196" ht="14.25" customHeight="1">
@@ -7749,19 +7781,19 @@
       </c>
       <c r="D196" s="7"/>
       <c t="s" r="E196" s="7">
-        <v>305</v>
+        <v>309</v>
       </c>
       <c r="F196" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G196" s="8">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c t="s" r="H196" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I196" s="7">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c t="s" r="J196" s="7">
         <v>54</v>
@@ -7769,7 +7801,7 @@
       <c r="K196" s="7"/>
       <c r="L196" s="7"/>
       <c t="s" r="M196" s="7">
-        <v>311</v>
+        <v>315</v>
       </c>
     </row>
     <row r="197" ht="14.25" customHeight="1">
@@ -7784,7 +7816,7 @@
       </c>
       <c r="D197" s="7"/>
       <c t="s" r="E197" s="7">
-        <v>305</v>
+        <v>309</v>
       </c>
       <c r="F197" s="7">
         <v>321</v>
@@ -7793,13 +7825,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H197" s="8">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c t="s" r="I197" s="7">
-        <v>312</v>
+        <v>78</v>
       </c>
       <c t="s" r="J197" s="7">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="K197" s="7"/>
       <c r="L197" s="7"/>
@@ -7817,22 +7849,22 @@
       </c>
       <c r="D198" s="7"/>
       <c t="s" r="E198" s="7">
-        <v>305</v>
+        <v>309</v>
       </c>
       <c r="F198" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G198" s="8">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c t="s" r="H198" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I198" s="7">
-        <v>303</v>
+        <v>307</v>
       </c>
       <c t="s" r="J198" s="7">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="K198" s="7"/>
       <c r="L198" s="7"/>
@@ -7850,7 +7882,7 @@
       </c>
       <c r="D199" s="7"/>
       <c t="s" r="E199" s="7">
-        <v>305</v>
+        <v>309</v>
       </c>
       <c r="F199" s="7">
         <v>321</v>
@@ -7859,20 +7891,20 @@
         <v>17</v>
       </c>
       <c t="s" r="H199" s="8">
+        <v>185</v>
+      </c>
+      <c t="s" r="I199" s="7">
+        <v>147</v>
+      </c>
+      <c t="s" r="J199" s="7">
         <v>182</v>
       </c>
-      <c t="s" r="I199" s="7">
-        <v>145</v>
-      </c>
-      <c t="s" r="J199" s="7">
-        <v>179</v>
-      </c>
       <c t="s" r="K199" s="7">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="L199" s="7"/>
       <c t="s" r="M199" s="7">
-        <v>313</v>
+        <v>316</v>
       </c>
     </row>
     <row r="200" ht="15" customHeight="1">
@@ -7887,29 +7919,29 @@
       </c>
       <c r="D200" s="7"/>
       <c t="s" r="E200" s="7">
-        <v>305</v>
+        <v>309</v>
       </c>
       <c r="F200" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G200" s="8">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c t="s" r="H200" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I200" s="7">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c t="s" r="J200" s="7">
         <v>48</v>
       </c>
       <c t="s" r="K200" s="7">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="L200" s="7"/>
       <c t="s" r="M200" s="7">
-        <v>226</v>
+        <v>229</v>
       </c>
     </row>
     <row r="201" ht="14.25" customHeight="1">
@@ -7939,27 +7971,27 @@
       </c>
       <c r="D202" s="7"/>
       <c t="s" r="E202" s="7">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="F202" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G202" s="8">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c t="s" r="H202" s="8">
         <v>43</v>
       </c>
       <c t="s" r="I202" s="7">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c t="s" r="J202" s="7">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="K202" s="7"/>
       <c r="L202" s="7"/>
       <c t="s" r="M202" s="7">
-        <v>316</v>
+        <v>319</v>
       </c>
     </row>
     <row r="203" ht="14.25" customHeight="1">
@@ -7974,7 +8006,7 @@
       </c>
       <c r="D203" s="7"/>
       <c t="s" r="E203" s="7">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="F203" s="7">
         <v>321</v>
@@ -7983,18 +8015,18 @@
         <v>43</v>
       </c>
       <c t="s" r="H203" s="8">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c t="s" r="I203" s="7">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c t="s" r="J203" s="7">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="K203" s="7"/>
       <c r="L203" s="7"/>
       <c t="s" r="M203" s="7">
-        <v>209</v>
+        <v>212</v>
       </c>
     </row>
     <row r="204" ht="14.25" customHeight="1">
@@ -8009,13 +8041,13 @@
       </c>
       <c r="D204" s="7"/>
       <c t="s" r="E204" s="7">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="F204" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G204" s="8">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c t="s" r="H204" s="8">
         <v>43</v>
@@ -8042,7 +8074,7 @@
       </c>
       <c r="D205" s="7"/>
       <c t="s" r="E205" s="7">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="F205" s="7">
         <v>321</v>
@@ -8051,13 +8083,13 @@
         <v>43</v>
       </c>
       <c t="s" r="H205" s="8">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c t="s" r="I205" s="7">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c t="s" r="J205" s="7">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="K205" s="7"/>
       <c r="L205" s="7"/>
@@ -8075,13 +8107,13 @@
       </c>
       <c r="D206" s="7"/>
       <c t="s" r="E206" s="7">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="F206" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G206" s="8">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c t="s" r="H206" s="8">
         <v>43</v>
@@ -8090,7 +8122,7 @@
         <v>59</v>
       </c>
       <c t="s" r="J206" s="7">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="K206" s="7"/>
       <c r="L206" s="7"/>
@@ -8108,7 +8140,7 @@
       </c>
       <c r="D207" s="7"/>
       <c t="s" r="E207" s="7">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="F207" s="7">
         <v>321</v>
@@ -8120,10 +8152,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I207" s="7">
-        <v>304</v>
+        <v>308</v>
       </c>
       <c t="s" r="J207" s="7">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="K207" s="7"/>
       <c r="L207" s="7"/>
@@ -8141,7 +8173,7 @@
       </c>
       <c r="D208" s="7"/>
       <c t="s" r="E208" s="7">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="F208" s="7">
         <v>321</v>
@@ -8153,7 +8185,7 @@
         <v>43</v>
       </c>
       <c t="s" r="I208" s="7">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c t="s" r="J208" s="7">
         <v>60</v>
@@ -8189,7 +8221,7 @@
       </c>
       <c r="D210" s="7"/>
       <c t="s" r="E210" s="7">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="F210" s="7">
         <v>321</v>
@@ -8198,18 +8230,18 @@
         <v>17</v>
       </c>
       <c t="s" r="H210" s="8">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c t="s" r="I210" s="7">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c t="s" r="J210" s="7">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="K210" s="7"/>
       <c r="L210" s="7"/>
       <c t="s" r="M210" s="7">
-        <v>319</v>
+        <v>322</v>
       </c>
     </row>
     <row r="211" ht="14.25" customHeight="1">
@@ -8224,27 +8256,27 @@
       </c>
       <c r="D211" s="7"/>
       <c t="s" r="E211" s="7">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="F211" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G211" s="8">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c t="s" r="H211" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I211" s="7">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c t="s" r="J211" s="7">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="K211" s="7"/>
       <c r="L211" s="7"/>
       <c t="s" r="M211" s="7">
-        <v>321</v>
+        <v>324</v>
       </c>
     </row>
     <row r="212" ht="14.25" customHeight="1">
@@ -8259,7 +8291,7 @@
       </c>
       <c r="D212" s="7"/>
       <c t="s" r="E212" s="7">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="F212" s="7">
         <v>321</v>
@@ -8274,7 +8306,7 @@
         <v>45</v>
       </c>
       <c t="s" r="J212" s="7">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="K212" s="7"/>
       <c r="L212" s="7"/>
@@ -8292,7 +8324,7 @@
       </c>
       <c r="D213" s="7"/>
       <c t="s" r="E213" s="7">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="F213" s="7">
         <v>321</v>
@@ -8304,10 +8336,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I213" s="7">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c t="s" r="J213" s="7">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="K213" s="7"/>
       <c r="L213" s="7"/>
@@ -8325,7 +8357,7 @@
       </c>
       <c r="D214" s="7"/>
       <c t="s" r="E214" s="7">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="F214" s="7">
         <v>321</v>
@@ -8334,13 +8366,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H214" s="8">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c t="s" r="I214" s="7">
         <v>25</v>
       </c>
       <c t="s" r="J214" s="7">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="K214" s="7"/>
       <c r="L214" s="7"/>
@@ -8358,22 +8390,22 @@
       </c>
       <c r="D215" s="7"/>
       <c t="s" r="E215" s="7">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="F215" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G215" s="8">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c t="s" r="H215" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I215" s="7">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c t="s" r="J215" s="7">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="K215" s="7"/>
       <c r="L215" s="7"/>
@@ -8406,7 +8438,7 @@
       </c>
       <c r="D217" s="7"/>
       <c t="s" r="E217" s="7">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="F217" s="7">
         <v>321</v>
@@ -8418,15 +8450,15 @@
         <v>17</v>
       </c>
       <c t="s" r="I217" s="7">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c t="s" r="J217" s="7">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="K217" s="7"/>
       <c r="L217" s="7"/>
       <c t="s" r="M217" s="7">
-        <v>326</v>
+        <v>329</v>
       </c>
     </row>
     <row r="218" ht="14.25" customHeight="1">
@@ -8441,7 +8473,7 @@
       </c>
       <c r="D218" s="7"/>
       <c t="s" r="E218" s="7">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="F218" s="7">
         <v>321</v>
@@ -8450,18 +8482,18 @@
         <v>17</v>
       </c>
       <c t="s" r="H218" s="8">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c t="s" r="I218" s="7">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c t="s" r="J218" s="7">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="K218" s="7"/>
       <c r="L218" s="7"/>
       <c t="s" r="M218" s="7">
-        <v>327</v>
+        <v>330</v>
       </c>
     </row>
     <row r="219" ht="14.25" customHeight="1">
@@ -8476,22 +8508,22 @@
       </c>
       <c r="D219" s="7"/>
       <c t="s" r="E219" s="7">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="F219" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G219" s="8">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c t="s" r="H219" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I219" s="7">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c t="s" r="J219" s="7">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="K219" s="7"/>
       <c r="L219" s="7"/>
@@ -8509,7 +8541,7 @@
       </c>
       <c r="D220" s="7"/>
       <c t="s" r="E220" s="7">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="F220" s="7">
         <v>321</v>
@@ -8518,13 +8550,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H220" s="8">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c t="s" r="I220" s="7">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c t="s" r="J220" s="7">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="K220" s="7"/>
       <c r="L220" s="7"/>
@@ -8542,22 +8574,22 @@
       </c>
       <c r="D221" s="7"/>
       <c t="s" r="E221" s="7">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="F221" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G221" s="8">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c t="s" r="H221" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I221" s="7">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c t="s" r="J221" s="7">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="K221" s="7"/>
       <c r="L221" s="7"/>
@@ -8590,7 +8622,7 @@
       </c>
       <c r="D223" s="7"/>
       <c t="s" r="E223" s="7">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="F223" s="7">
         <v>321</v>
@@ -8599,10 +8631,10 @@
         <v>16</v>
       </c>
       <c t="s" r="H223" s="8">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c t="s" r="I223" s="7">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c t="s" r="J223" s="7">
         <v>66</v>
@@ -8610,7 +8642,7 @@
       <c r="K223" s="7"/>
       <c r="L223" s="7"/>
       <c t="s" r="M223" s="7">
-        <v>330</v>
+        <v>333</v>
       </c>
     </row>
     <row r="224" ht="14.25" customHeight="1">
@@ -8625,27 +8657,27 @@
       </c>
       <c r="D224" s="7"/>
       <c t="s" r="E224" s="7">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="F224" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G224" s="8">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c t="s" r="H224" s="8">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c t="s" r="I224" s="7">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c t="s" r="J224" s="7">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="K224" s="7"/>
       <c r="L224" s="7"/>
       <c t="s" r="M224" s="7">
-        <v>332</v>
+        <v>335</v>
       </c>
     </row>
     <row r="225" ht="15" customHeight="1">
@@ -8660,19 +8692,19 @@
       </c>
       <c r="D225" s="7"/>
       <c t="s" r="E225" s="7">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="F225" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G225" s="8">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c t="s" r="H225" s="8">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c t="s" r="I225" s="7">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c t="s" r="J225" s="7">
         <v>69</v>
@@ -8693,13 +8725,13 @@
       </c>
       <c r="D226" s="7"/>
       <c t="s" r="E226" s="7">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="F226" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G226" s="8">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c t="s" r="H226" s="8">
         <v>17</v>
@@ -8708,7 +8740,7 @@
         <v>24</v>
       </c>
       <c t="s" r="J226" s="7">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="K226" s="7"/>
       <c r="L226" s="7"/>
@@ -8741,7 +8773,7 @@
       </c>
       <c r="D228" s="7"/>
       <c t="s" r="E228" s="7">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="F228" s="7">
         <v>321</v>
@@ -8753,7 +8785,7 @@
         <v>43</v>
       </c>
       <c t="s" r="I228" s="7">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c t="s" r="J228" s="7">
         <v>35</v>
@@ -8761,7 +8793,7 @@
       <c r="K228" s="7"/>
       <c r="L228" s="7"/>
       <c t="s" r="M228" s="7">
-        <v>335</v>
+        <v>338</v>
       </c>
     </row>
     <row r="229" ht="14.25" customHeight="1">
@@ -8776,7 +8808,7 @@
       </c>
       <c r="D229" s="7"/>
       <c t="s" r="E229" s="7">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="F229" s="7">
         <v>321</v>
@@ -8785,13 +8817,13 @@
         <v>43</v>
       </c>
       <c t="s" r="H229" s="8">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c t="s" r="I229" s="7">
         <v>37</v>
       </c>
       <c t="s" r="J229" s="7">
-        <v>249</v>
+        <v>253</v>
       </c>
       <c r="K229" s="7"/>
       <c r="L229" s="7"/>
@@ -8809,22 +8841,22 @@
       </c>
       <c r="D230" s="7"/>
       <c t="s" r="E230" s="7">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="F230" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G230" s="8">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c t="s" r="H230" s="8">
         <v>43</v>
       </c>
       <c t="s" r="I230" s="7">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c t="s" r="J230" s="7">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="K230" s="7"/>
       <c r="L230" s="7"/>
@@ -8842,7 +8874,7 @@
       </c>
       <c r="D231" s="7"/>
       <c t="s" r="E231" s="7">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="F231" s="7">
         <v>321</v>
@@ -8854,10 +8886,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I231" s="7">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c t="s" r="J231" s="7">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="K231" s="7"/>
       <c r="L231" s="7"/>
@@ -8890,27 +8922,27 @@
       </c>
       <c r="D233" s="7"/>
       <c t="s" r="E233" s="7">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="F233" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G233" s="8">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c t="s" r="H233" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I233" s="7">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c t="s" r="J233" s="7">
-        <v>303</v>
+        <v>307</v>
       </c>
       <c r="K233" s="7"/>
       <c r="L233" s="7"/>
       <c t="s" r="M233" s="7">
-        <v>338</v>
+        <v>341</v>
       </c>
     </row>
     <row r="234" ht="14.25" customHeight="1">
@@ -8925,7 +8957,7 @@
       </c>
       <c r="D234" s="7"/>
       <c t="s" r="E234" s="7">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="F234" s="7">
         <v>321</v>
@@ -8934,13 +8966,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H234" s="8">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c t="s" r="I234" s="7">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c t="s" r="J234" s="7">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="K234" s="7"/>
       <c r="L234" s="7"/>
@@ -8973,7 +9005,7 @@
       </c>
       <c r="D236" s="7"/>
       <c t="s" r="E236" s="7">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="F236" s="7">
         <v>321</v>
@@ -8985,7 +9017,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I236" s="7">
-        <v>309</v>
+        <v>313</v>
       </c>
       <c t="s" r="J236" s="7">
         <v>44</v>
@@ -9008,7 +9040,7 @@
       </c>
       <c r="D237" s="7"/>
       <c t="s" r="E237" s="7">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="F237" s="7">
         <v>321</v>
@@ -9020,15 +9052,15 @@
         <v>43</v>
       </c>
       <c t="s" r="I237" s="7">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c t="s" r="J237" s="7">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="K237" s="7"/>
       <c r="L237" s="7"/>
       <c t="s" r="M237" s="7">
-        <v>341</v>
+        <v>344</v>
       </c>
     </row>
     <row r="238" ht="14.25" customHeight="1">
@@ -9043,7 +9075,7 @@
       </c>
       <c r="D238" s="7"/>
       <c t="s" r="E238" s="7">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="F238" s="7">
         <v>321</v>
@@ -9058,14 +9090,14 @@
         <v>54</v>
       </c>
       <c t="s" r="J238" s="7">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c t="s" r="K238" s="7">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="L238" s="7"/>
       <c t="s" r="M238" s="7">
-        <v>343</v>
+        <v>346</v>
       </c>
     </row>
     <row r="239" ht="14.25" customHeight="1">
@@ -9080,7 +9112,7 @@
       </c>
       <c r="D239" s="7"/>
       <c t="s" r="E239" s="7">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="F239" s="7">
         <v>321</v>
@@ -9092,17 +9124,17 @@
         <v>43</v>
       </c>
       <c t="s" r="I239" s="7">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c t="s" r="J239" s="7">
         <v>59</v>
       </c>
       <c t="s" r="K239" s="7">
-        <v>249</v>
+        <v>253</v>
       </c>
       <c r="L239" s="7"/>
       <c t="s" r="M239" s="7">
-        <v>164</v>
+        <v>167</v>
       </c>
     </row>
     <row r="240" ht="15" customHeight="1">
@@ -9117,7 +9149,7 @@
       </c>
       <c r="D240" s="7"/>
       <c t="s" r="E240" s="7">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="F240" s="7">
         <v>321</v>
@@ -9126,20 +9158,20 @@
         <v>43</v>
       </c>
       <c t="s" r="H240" s="8">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c t="s" r="I240" s="7">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c t="s" r="J240" s="7">
         <v>48</v>
       </c>
       <c t="s" r="K240" s="7">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="L240" s="7"/>
       <c t="s" r="M240" s="7">
-        <v>192</v>
+        <v>195</v>
       </c>
     </row>
     <row r="241" ht="14.25" customHeight="1">
@@ -9154,29 +9186,29 @@
       </c>
       <c r="D241" s="7"/>
       <c t="s" r="E241" s="7">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="F241" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G241" s="8">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c t="s" r="H241" s="8">
         <v>43</v>
       </c>
       <c t="s" r="I241" s="7">
-        <v>291</v>
+        <v>295</v>
       </c>
       <c t="s" r="J241" s="7">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c t="s" r="K241" s="7">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="L241" s="7"/>
       <c t="s" r="M241" s="7">
-        <v>346</v>
+        <v>349</v>
       </c>
     </row>
     <row r="242" ht="14.25" customHeight="1">
@@ -9191,7 +9223,7 @@
       </c>
       <c r="D242" s="7"/>
       <c t="s" r="E242" s="7">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="F242" s="7">
         <v>321</v>
@@ -9200,13 +9232,13 @@
         <v>43</v>
       </c>
       <c t="s" r="H242" s="8">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c t="s" r="I242" s="7">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c t="s" r="J242" s="7">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="K242" s="7"/>
       <c r="L242" s="7"/>
@@ -9239,27 +9271,27 @@
       </c>
       <c r="D244" s="7"/>
       <c t="s" r="E244" s="7">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="F244" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G244" s="8">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c t="s" r="H244" s="8">
         <v>43</v>
       </c>
       <c t="s" r="I244" s="7">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c t="s" r="J244" s="7">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="K244" s="7"/>
       <c r="L244" s="7"/>
       <c t="s" r="M244" s="7">
-        <v>351</v>
+        <v>354</v>
       </c>
     </row>
     <row r="245" ht="15" customHeight="1">
@@ -9274,7 +9306,7 @@
       </c>
       <c r="D245" s="7"/>
       <c t="s" r="E245" s="7">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="F245" s="7">
         <v>321</v>
@@ -9283,17 +9315,19 @@
         <v>43</v>
       </c>
       <c t="s" r="H245" s="8">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c t="s" r="I245" s="7">
         <v>18</v>
       </c>
       <c t="s" r="J245" s="7">
-        <v>77</v>
+        <v>92</v>
       </c>
       <c r="K245" s="7"/>
       <c r="L245" s="7"/>
-      <c r="M245" s="7"/>
+      <c t="s" r="M245" s="7">
+        <v>250</v>
+      </c>
     </row>
     <row r="246" ht="14.25" customHeight="1">
       <c t="s" r="A246" s="6">
@@ -9307,19 +9341,19 @@
       </c>
       <c r="D246" s="7"/>
       <c t="s" r="E246" s="7">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="F246" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G246" s="8">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c t="s" r="H246" s="8">
         <v>43</v>
       </c>
       <c t="s" r="I246" s="7">
-        <v>248</v>
+        <v>252</v>
       </c>
       <c t="s" r="J246" s="7">
         <v>58</v>
@@ -9340,7 +9374,7 @@
       </c>
       <c r="D247" s="7"/>
       <c t="s" r="E247" s="7">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="F247" s="7">
         <v>321</v>
@@ -9349,13 +9383,13 @@
         <v>43</v>
       </c>
       <c t="s" r="H247" s="8">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c t="s" r="I247" s="7">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c t="s" r="J247" s="7">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="K247" s="7"/>
       <c r="L247" s="7"/>
@@ -9373,13 +9407,13 @@
       </c>
       <c r="D248" s="7"/>
       <c t="s" r="E248" s="7">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="F248" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G248" s="8">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c t="s" r="H248" s="8">
         <v>43</v>
@@ -9388,7 +9422,7 @@
         <v>27</v>
       </c>
       <c t="s" r="J248" s="7">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="K248" s="7"/>
       <c r="L248" s="7"/>
@@ -9406,7 +9440,7 @@
       </c>
       <c r="D249" s="7"/>
       <c t="s" r="E249" s="7">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="F249" s="7">
         <v>321</v>
@@ -9415,10 +9449,10 @@
         <v>43</v>
       </c>
       <c t="s" r="H249" s="8">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c t="s" r="I249" s="7">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c t="s" r="J249" s="7">
         <v>51</v>
@@ -9454,7 +9488,7 @@
       </c>
       <c r="D251" s="7"/>
       <c t="s" r="E251" s="7">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="F251" s="7">
         <v>321</v>
@@ -9463,10 +9497,10 @@
         <v>43</v>
       </c>
       <c t="s" r="H251" s="8">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c t="s" r="I251" s="7">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c t="s" r="J251" s="7">
         <v>63</v>
@@ -9474,7 +9508,7 @@
       <c r="K251" s="7"/>
       <c r="L251" s="7"/>
       <c t="s" r="M251" s="7">
-        <v>356</v>
+        <v>359</v>
       </c>
     </row>
     <row r="252" ht="14.25" customHeight="1">
@@ -9489,22 +9523,22 @@
       </c>
       <c r="D252" s="7"/>
       <c t="s" r="E252" s="7">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="F252" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G252" s="8">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c t="s" r="H252" s="8">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c t="s" r="I252" s="7">
         <v>37</v>
       </c>
       <c t="s" r="J252" s="7">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="K252" s="7"/>
       <c r="L252" s="7"/>
@@ -9522,22 +9556,22 @@
       </c>
       <c r="D253" s="7"/>
       <c t="s" r="E253" s="7">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="F253" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G253" s="8">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c t="s" r="H253" s="8">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c t="s" r="I253" s="7">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c t="s" r="J253" s="7">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="K253" s="7"/>
       <c r="L253" s="7"/>
@@ -9555,22 +9589,22 @@
       </c>
       <c r="D254" s="7"/>
       <c t="s" r="E254" s="7">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="F254" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G254" s="8">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c t="s" r="H254" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I254" s="7">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c t="s" r="J254" s="7">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="K254" s="7"/>
       <c r="L254" s="7"/>
@@ -9603,7 +9637,7 @@
       </c>
       <c r="D256" s="7"/>
       <c t="s" r="E256" s="7">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="F256" s="7">
         <v>321</v>
@@ -9615,15 +9649,15 @@
         <v>17</v>
       </c>
       <c t="s" r="I256" s="7">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c t="s" r="J256" s="7">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="K256" s="7"/>
       <c r="L256" s="7"/>
       <c t="s" r="M256" s="7">
-        <v>360</v>
+        <v>363</v>
       </c>
     </row>
     <row r="257" ht="14.25" customHeight="1">
@@ -9638,7 +9672,7 @@
       </c>
       <c r="D257" s="7"/>
       <c t="s" r="E257" s="7">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="F257" s="7">
         <v>321</v>
@@ -9650,15 +9684,15 @@
         <v>21</v>
       </c>
       <c t="s" r="I257" s="7">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c t="s" r="J257" s="7">
-        <v>301</v>
+        <v>305</v>
       </c>
       <c r="K257" s="7"/>
       <c r="L257" s="7"/>
       <c t="s" r="M257" s="7">
-        <v>361</v>
+        <v>364</v>
       </c>
     </row>
     <row r="258" ht="14.25" customHeight="1">
@@ -9673,7 +9707,7 @@
       </c>
       <c r="D258" s="7"/>
       <c t="s" r="E258" s="7">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="F258" s="7">
         <v>321</v>
@@ -9685,15 +9719,15 @@
         <v>17</v>
       </c>
       <c t="s" r="I258" s="7">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c t="s" r="J258" s="7">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="K258" s="7"/>
       <c r="L258" s="7"/>
       <c t="s" r="M258" s="7">
-        <v>362</v>
+        <v>365</v>
       </c>
     </row>
     <row r="259" ht="14.25" customHeight="1">
@@ -9708,7 +9742,7 @@
       </c>
       <c r="D259" s="7"/>
       <c t="s" r="E259" s="7">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="F259" s="7">
         <v>321</v>
@@ -9720,14 +9754,16 @@
         <v>43</v>
       </c>
       <c t="s" r="I259" s="7">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c t="s" r="J259" s="7">
-        <v>248</v>
+        <v>252</v>
       </c>
       <c r="K259" s="7"/>
       <c r="L259" s="7"/>
-      <c r="M259" s="7"/>
+      <c t="s" r="M259" s="7">
+        <v>366</v>
+      </c>
     </row>
     <row r="260" ht="15" customHeight="1">
       <c t="s" r="A260" s="6">
@@ -9741,7 +9777,7 @@
       </c>
       <c r="D260" s="7"/>
       <c t="s" r="E260" s="7">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="F260" s="7">
         <v>321</v>
@@ -9750,13 +9786,13 @@
         <v>43</v>
       </c>
       <c t="s" r="H260" s="8">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c t="s" r="I260" s="7">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c t="s" r="J260" s="7">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="K260" s="7"/>
       <c r="L260" s="7"/>
@@ -9774,22 +9810,22 @@
       </c>
       <c r="D261" s="7"/>
       <c t="s" r="E261" s="7">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="F261" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G261" s="8">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c t="s" r="H261" s="8">
         <v>43</v>
       </c>
       <c t="s" r="I261" s="7">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c t="s" r="J261" s="7">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="K261" s="7"/>
       <c r="L261" s="7"/>
@@ -9807,7 +9843,7 @@
       </c>
       <c r="D262" s="7"/>
       <c t="s" r="E262" s="7">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="F262" s="7">
         <v>321</v>
@@ -9816,13 +9852,13 @@
         <v>43</v>
       </c>
       <c t="s" r="H262" s="8">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c t="s" r="I262" s="7">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c t="s" r="J262" s="7">
-        <v>291</v>
+        <v>295</v>
       </c>
       <c r="K262" s="7"/>
       <c r="L262" s="7"/>
@@ -9840,22 +9876,22 @@
       </c>
       <c r="D263" s="7"/>
       <c t="s" r="E263" s="7">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="F263" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G263" s="8">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c t="s" r="H263" s="8">
         <v>43</v>
       </c>
       <c t="s" r="I263" s="7">
-        <v>363</v>
+        <v>367</v>
       </c>
       <c t="s" r="J263" s="7">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="K263" s="7"/>
       <c r="L263" s="7"/>
@@ -9888,7 +9924,7 @@
       </c>
       <c r="D265" s="7"/>
       <c t="s" r="E265" s="7">
-        <v>364</v>
+        <v>368</v>
       </c>
       <c r="F265" s="7">
         <v>321</v>
@@ -9900,15 +9936,15 @@
         <v>17</v>
       </c>
       <c t="s" r="I265" s="7">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c t="s" r="J265" s="7">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="K265" s="7"/>
       <c r="L265" s="7"/>
       <c t="s" r="M265" s="7">
-        <v>365</v>
+        <v>369</v>
       </c>
     </row>
     <row r="266" ht="14.25" customHeight="1">
@@ -9923,7 +9959,7 @@
       </c>
       <c r="D266" s="7"/>
       <c t="s" r="E266" s="7">
-        <v>364</v>
+        <v>368</v>
       </c>
       <c r="F266" s="7">
         <v>321</v>
@@ -9932,13 +9968,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H266" s="8">
-        <v>366</v>
+        <v>370</v>
       </c>
       <c t="s" r="I266" s="7">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c t="s" r="J266" s="7">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="K266" s="7"/>
       <c r="L266" s="7"/>
@@ -9956,22 +9992,22 @@
       </c>
       <c r="D267" s="7"/>
       <c t="s" r="E267" s="7">
-        <v>364</v>
+        <v>368</v>
       </c>
       <c r="F267" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G267" s="8">
-        <v>366</v>
+        <v>370</v>
       </c>
       <c t="s" r="H267" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I267" s="7">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c t="s" r="J267" s="7">
-        <v>368</v>
+        <v>372</v>
       </c>
       <c r="K267" s="7"/>
       <c r="L267" s="7"/>
@@ -10004,7 +10040,7 @@
       </c>
       <c r="D269" s="7"/>
       <c t="s" r="E269" s="7">
-        <v>369</v>
+        <v>373</v>
       </c>
       <c r="F269" s="7">
         <v>321</v>
@@ -10013,7 +10049,7 @@
         <v>43</v>
       </c>
       <c t="s" r="H269" s="8">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c t="s" r="I269" s="7">
         <v>51</v>
@@ -10024,7 +10060,7 @@
       <c r="K269" s="7"/>
       <c r="L269" s="7"/>
       <c t="s" r="M269" s="7">
-        <v>149</v>
+        <v>151</v>
       </c>
     </row>
     <row r="270" ht="15" customHeight="1">
@@ -10039,27 +10075,27 @@
       </c>
       <c r="D270" s="7"/>
       <c t="s" r="E270" s="7">
-        <v>369</v>
+        <v>373</v>
       </c>
       <c r="F270" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G270" s="8">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c t="s" r="H270" s="8">
         <v>43</v>
       </c>
       <c t="s" r="I270" s="7">
-        <v>310</v>
+        <v>314</v>
       </c>
       <c t="s" r="J270" s="7">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="K270" s="7"/>
       <c r="L270" s="7"/>
       <c t="s" r="M270" s="7">
-        <v>370</v>
+        <v>374</v>
       </c>
     </row>
     <row r="271" ht="14.25" customHeight="1">
@@ -10074,7 +10110,7 @@
       </c>
       <c r="D271" s="7"/>
       <c t="s" r="E271" s="7">
-        <v>369</v>
+        <v>373</v>
       </c>
       <c r="F271" s="7">
         <v>321</v>
@@ -10086,14 +10122,16 @@
         <v>21</v>
       </c>
       <c t="s" r="I271" s="7">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c t="s" r="J271" s="7">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="K271" s="7"/>
       <c r="L271" s="7"/>
-      <c r="M271" s="7"/>
+      <c t="s" r="M271" s="7">
+        <v>375</v>
+      </c>
     </row>
     <row r="272" ht="14.25" customHeight="1">
       <c t="s" r="A272" s="6">
@@ -10107,7 +10145,7 @@
       </c>
       <c r="D272" s="7"/>
       <c t="s" r="E272" s="7">
-        <v>369</v>
+        <v>373</v>
       </c>
       <c r="F272" s="7">
         <v>321</v>
@@ -10122,7 +10160,7 @@
         <v>37</v>
       </c>
       <c t="s" r="J272" s="7">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="K272" s="7"/>
       <c r="L272" s="7"/>
@@ -10140,7 +10178,7 @@
       </c>
       <c r="D273" s="7"/>
       <c t="s" r="E273" s="7">
-        <v>369</v>
+        <v>373</v>
       </c>
       <c r="F273" s="7">
         <v>321</v>
@@ -10149,13 +10187,13 @@
         <v>43</v>
       </c>
       <c t="s" r="H273" s="8">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c t="s" r="I273" s="7">
         <v>24</v>
       </c>
       <c t="s" r="J273" s="7">
-        <v>371</v>
+        <v>376</v>
       </c>
       <c r="K273" s="7"/>
       <c r="L273" s="7"/>
@@ -10173,22 +10211,22 @@
       </c>
       <c r="D274" s="7"/>
       <c t="s" r="E274" s="7">
-        <v>369</v>
+        <v>373</v>
       </c>
       <c r="F274" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G274" s="8">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c t="s" r="H274" s="8">
         <v>43</v>
       </c>
       <c t="s" r="I274" s="7">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c t="s" r="J274" s="7">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="K274" s="7"/>
       <c r="L274" s="7"/>
@@ -10206,7 +10244,7 @@
       </c>
       <c r="D275" s="7"/>
       <c t="s" r="E275" s="7">
-        <v>369</v>
+        <v>373</v>
       </c>
       <c r="F275" s="7">
         <v>321</v>
@@ -10215,10 +10253,10 @@
         <v>43</v>
       </c>
       <c t="s" r="H275" s="8">
-        <v>372</v>
+        <v>377</v>
       </c>
       <c t="s" r="I275" s="7">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c t="s" r="J275" s="7">
         <v>60</v>
@@ -10239,22 +10277,22 @@
       </c>
       <c r="D276" s="7"/>
       <c t="s" r="E276" s="7">
-        <v>369</v>
+        <v>373</v>
       </c>
       <c r="F276" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G276" s="8">
-        <v>372</v>
+        <v>377</v>
       </c>
       <c t="s" r="H276" s="8">
         <v>43</v>
       </c>
       <c t="s" r="I276" s="7">
-        <v>278</v>
+        <v>282</v>
       </c>
       <c t="s" r="J276" s="7">
-        <v>373</v>
+        <v>378</v>
       </c>
       <c r="K276" s="7"/>
       <c r="L276" s="7"/>
@@ -10287,22 +10325,22 @@
       </c>
       <c r="D278" s="7"/>
       <c t="s" r="E278" s="7">
-        <v>374</v>
+        <v>379</v>
       </c>
       <c r="F278" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G278" s="8">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c t="s" r="H278" s="8">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c t="s" r="I278" s="7">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c t="s" r="J278" s="7">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="K278" s="7"/>
       <c r="L278" s="7"/>
@@ -10320,22 +10358,22 @@
       </c>
       <c r="D279" s="7"/>
       <c t="s" r="E279" s="7">
-        <v>374</v>
+        <v>379</v>
       </c>
       <c r="F279" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G279" s="8">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c t="s" r="H279" s="8">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c t="s" r="I279" s="7">
-        <v>365</v>
+        <v>369</v>
       </c>
       <c t="s" r="J279" s="7">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="K279" s="7"/>
       <c r="L279" s="7"/>
@@ -10368,19 +10406,19 @@
       </c>
       <c r="D281" s="7"/>
       <c t="s" r="E281" s="7">
-        <v>375</v>
+        <v>380</v>
       </c>
       <c r="F281" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G281" s="8">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c t="s" r="H281" s="8">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c t="s" r="I281" s="7">
-        <v>296</v>
+        <v>300</v>
       </c>
       <c t="s" r="J281" s="7">
         <v>35</v>
@@ -10388,7 +10426,7 @@
       <c r="K281" s="7"/>
       <c r="L281" s="7"/>
       <c t="s" r="M281" s="7">
-        <v>77</v>
+        <v>92</v>
       </c>
     </row>
     <row r="282" ht="14.25" customHeight="1">
@@ -10418,7 +10456,7 @@
       </c>
       <c r="D283" s="7"/>
       <c t="s" r="E283" s="7">
-        <v>376</v>
+        <v>381</v>
       </c>
       <c r="F283" s="7">
         <v>320</v>
@@ -10430,7 +10468,7 @@
         <v>43</v>
       </c>
       <c t="s" r="I283" s="7">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c t="s" r="J283" s="7">
         <v>51</v>
@@ -10438,7 +10476,7 @@
       <c r="K283" s="7"/>
       <c r="L283" s="7"/>
       <c t="s" r="M283" s="7">
-        <v>377</v>
+        <v>382</v>
       </c>
     </row>
     <row r="284" ht="14.25" customHeight="1">
@@ -10453,7 +10491,7 @@
       </c>
       <c r="D284" s="7"/>
       <c t="s" r="E284" s="7">
-        <v>376</v>
+        <v>381</v>
       </c>
       <c r="F284" s="7">
         <v>320</v>
@@ -10462,17 +10500,19 @@
         <v>43</v>
       </c>
       <c t="s" r="H284" s="8">
-        <v>378</v>
+        <v>383</v>
       </c>
       <c t="s" r="I284" s="7">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c t="s" r="J284" s="7">
-        <v>249</v>
+        <v>253</v>
       </c>
       <c r="K284" s="7"/>
       <c r="L284" s="7"/>
-      <c r="M284" s="7"/>
+      <c t="s" r="M284" s="7">
+        <v>384</v>
+      </c>
     </row>
     <row r="285" ht="15" customHeight="1">
       <c t="s" r="A285" s="6">
@@ -10486,22 +10526,22 @@
       </c>
       <c r="D285" s="7"/>
       <c t="s" r="E285" s="7">
-        <v>376</v>
+        <v>381</v>
       </c>
       <c r="F285" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G285" s="8">
-        <v>378</v>
+        <v>383</v>
       </c>
       <c t="s" r="H285" s="8">
         <v>43</v>
       </c>
       <c t="s" r="I285" s="7">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c t="s" r="J285" s="7">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="K285" s="7"/>
       <c r="L285" s="7"/>
@@ -10519,7 +10559,7 @@
       </c>
       <c r="D286" s="7"/>
       <c t="s" r="E286" s="7">
-        <v>376</v>
+        <v>381</v>
       </c>
       <c r="F286" s="7">
         <v>320</v>
@@ -10528,13 +10568,13 @@
         <v>43</v>
       </c>
       <c t="s" r="H286" s="8">
-        <v>379</v>
+        <v>385</v>
       </c>
       <c t="s" r="I286" s="7">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c t="s" r="J286" s="7">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="K286" s="7"/>
       <c r="L286" s="7"/>
@@ -10552,22 +10592,22 @@
       </c>
       <c r="D287" s="7"/>
       <c t="s" r="E287" s="7">
-        <v>376</v>
+        <v>381</v>
       </c>
       <c r="F287" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G287" s="8">
-        <v>379</v>
+        <v>385</v>
       </c>
       <c t="s" r="H287" s="8">
         <v>43</v>
       </c>
       <c t="s" r="I287" s="7">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c t="s" r="J287" s="7">
-        <v>380</v>
+        <v>386</v>
       </c>
       <c r="K287" s="7"/>
       <c r="L287" s="7"/>
@@ -10600,7 +10640,7 @@
       </c>
       <c r="D289" s="7"/>
       <c t="s" r="E289" s="7">
-        <v>381</v>
+        <v>387</v>
       </c>
       <c r="F289" s="7">
         <v>321</v>
@@ -10609,18 +10649,18 @@
         <v>43</v>
       </c>
       <c t="s" r="H289" s="8">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c t="s" r="I289" s="7">
-        <v>382</v>
+        <v>388</v>
       </c>
       <c t="s" r="J289" s="7">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="K289" s="7"/>
       <c r="L289" s="7"/>
       <c t="s" r="M289" s="7">
-        <v>263</v>
+        <v>267</v>
       </c>
     </row>
     <row r="290" ht="15" customHeight="1">
@@ -10635,27 +10675,27 @@
       </c>
       <c r="D290" s="7"/>
       <c t="s" r="E290" s="7">
-        <v>381</v>
+        <v>387</v>
       </c>
       <c r="F290" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G290" s="8">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c t="s" r="H290" s="8">
         <v>43</v>
       </c>
       <c t="s" r="I290" s="7">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c t="s" r="J290" s="7">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="K290" s="7"/>
       <c r="L290" s="7"/>
       <c t="s" r="M290" s="7">
-        <v>383</v>
+        <v>389</v>
       </c>
     </row>
     <row r="291" ht="14.25" customHeight="1">
@@ -10670,7 +10710,7 @@
       </c>
       <c r="D291" s="7"/>
       <c t="s" r="E291" s="7">
-        <v>381</v>
+        <v>387</v>
       </c>
       <c r="F291" s="7">
         <v>321</v>
@@ -10679,13 +10719,13 @@
         <v>43</v>
       </c>
       <c t="s" r="H291" s="8">
-        <v>384</v>
+        <v>390</v>
       </c>
       <c t="s" r="I291" s="7">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c t="s" r="J291" s="7">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="K291" s="7"/>
       <c r="L291" s="7"/>
@@ -10703,22 +10743,22 @@
       </c>
       <c r="D292" s="7"/>
       <c t="s" r="E292" s="7">
-        <v>381</v>
+        <v>387</v>
       </c>
       <c r="F292" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G292" s="8">
-        <v>384</v>
+        <v>390</v>
       </c>
       <c t="s" r="H292" s="8">
         <v>43</v>
       </c>
       <c t="s" r="I292" s="7">
-        <v>298</v>
+        <v>302</v>
       </c>
       <c t="s" r="J292" s="7">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="K292" s="7"/>
       <c r="L292" s="7"/>
@@ -10751,22 +10791,22 @@
       </c>
       <c r="D294" s="7"/>
       <c t="s" r="E294" s="7">
-        <v>385</v>
+        <v>391</v>
       </c>
       <c r="F294" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G294" s="8">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c t="s" r="H294" s="8">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c t="s" r="I294" s="7">
-        <v>248</v>
+        <v>252</v>
       </c>
       <c t="s" r="J294" s="7">
-        <v>365</v>
+        <v>369</v>
       </c>
       <c r="K294" s="7"/>
       <c r="L294" s="7"/>
@@ -10784,19 +10824,19 @@
       </c>
       <c r="D295" s="7"/>
       <c t="s" r="E295" s="7">
-        <v>385</v>
+        <v>391</v>
       </c>
       <c r="F295" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G295" s="8">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c t="s" r="H295" s="8">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c t="s" r="I295" s="7">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c t="s" r="J295" s="7">
         <v>23</v>
@@ -10832,7 +10872,7 @@
       </c>
       <c r="D297" s="7"/>
       <c t="s" r="E297" s="7">
-        <v>386</v>
+        <v>392</v>
       </c>
       <c r="F297" s="7">
         <v>320</v>
@@ -10841,18 +10881,18 @@
         <v>17</v>
       </c>
       <c t="s" r="H297" s="8">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c t="s" r="I297" s="7">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c t="s" r="J297" s="7">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="K297" s="7"/>
       <c r="L297" s="7"/>
       <c t="s" r="M297" s="7">
-        <v>185</v>
+        <v>188</v>
       </c>
     </row>
     <row r="298" ht="14.25" customHeight="1">
@@ -10867,19 +10907,19 @@
       </c>
       <c r="D298" s="7"/>
       <c t="s" r="E298" s="7">
-        <v>386</v>
+        <v>392</v>
       </c>
       <c r="F298" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G298" s="8">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c t="s" r="H298" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I298" s="7">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c t="s" r="J298" s="7">
         <v>54</v>
@@ -10887,7 +10927,7 @@
       <c r="K298" s="7"/>
       <c r="L298" s="7"/>
       <c t="s" r="M298" s="7">
-        <v>311</v>
+        <v>393</v>
       </c>
     </row>
     <row r="299" ht="14.25" customHeight="1">
@@ -10895,14 +10935,14 @@
         <v>13</v>
       </c>
       <c r="B299" s="7">
-        <v>362</v>
+        <v>308</v>
       </c>
       <c t="s" r="C299" s="7">
         <v>14</v>
       </c>
       <c r="D299" s="7"/>
       <c t="s" r="E299" s="7">
-        <v>386</v>
+        <v>392</v>
       </c>
       <c r="F299" s="7">
         <v>320</v>
@@ -10911,13 +10951,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H299" s="8">
-        <v>153</v>
+        <v>175</v>
       </c>
       <c t="s" r="I299" s="7">
-        <v>37</v>
+        <v>213</v>
       </c>
       <c t="s" r="J299" s="7">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="K299" s="7"/>
       <c r="L299" s="7"/>
@@ -10928,29 +10968,29 @@
         <v>13</v>
       </c>
       <c r="B300" s="7">
-        <v>363</v>
+        <v>307</v>
       </c>
       <c t="s" r="C300" s="7">
         <v>14</v>
       </c>
       <c r="D300" s="7"/>
       <c t="s" r="E300" s="7">
-        <v>386</v>
+        <v>392</v>
       </c>
       <c r="F300" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G300" s="8">
-        <v>153</v>
+        <v>175</v>
       </c>
       <c t="s" r="H300" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I300" s="7">
-        <v>249</v>
+        <v>394</v>
       </c>
       <c t="s" r="J300" s="7">
-        <v>23</v>
+        <v>263</v>
       </c>
       <c r="K300" s="7"/>
       <c r="L300" s="7"/>
@@ -10961,14 +11001,14 @@
         <v>13</v>
       </c>
       <c r="B301" s="7">
-        <v>262</v>
+        <v>376</v>
       </c>
       <c t="s" r="C301" s="7">
         <v>14</v>
       </c>
       <c r="D301" s="7"/>
       <c t="s" r="E301" s="7">
-        <v>386</v>
+        <v>392</v>
       </c>
       <c r="F301" s="7">
         <v>320</v>
@@ -10977,13 +11017,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H301" s="8">
-        <v>387</v>
+        <v>395</v>
       </c>
       <c t="s" r="I301" s="7">
-        <v>259</v>
+        <v>278</v>
       </c>
       <c t="s" r="J301" s="7">
-        <v>371</v>
+        <v>82</v>
       </c>
       <c r="K301" s="7"/>
       <c r="L301" s="7"/>
@@ -10994,29 +11034,29 @@
         <v>13</v>
       </c>
       <c r="B302" s="7">
-        <v>263</v>
+        <v>377</v>
       </c>
       <c t="s" r="C302" s="7">
         <v>14</v>
       </c>
       <c r="D302" s="7"/>
       <c t="s" r="E302" s="7">
-        <v>386</v>
+        <v>392</v>
       </c>
       <c r="F302" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G302" s="8">
-        <v>387</v>
+        <v>395</v>
       </c>
       <c t="s" r="H302" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I302" s="7">
-        <v>81</v>
+        <v>294</v>
       </c>
       <c t="s" r="J302" s="7">
-        <v>353</v>
+        <v>166</v>
       </c>
       <c r="K302" s="7"/>
       <c r="L302" s="7"/>
@@ -11049,27 +11089,27 @@
       </c>
       <c r="D304" s="7"/>
       <c t="s" r="E304" s="7">
-        <v>388</v>
+        <v>396</v>
       </c>
       <c r="F304" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G304" s="8">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c t="s" r="H304" s="8">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c t="s" r="I304" s="7">
-        <v>389</v>
+        <v>397</v>
       </c>
       <c t="s" r="J304" s="7">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="K304" s="7"/>
       <c r="L304" s="7"/>
       <c t="s" r="M304" s="7">
-        <v>390</v>
+        <v>398</v>
       </c>
     </row>
     <row r="305" ht="15" customHeight="1">
@@ -11084,22 +11124,22 @@
       </c>
       <c r="D305" s="7"/>
       <c t="s" r="E305" s="7">
-        <v>388</v>
+        <v>396</v>
       </c>
       <c r="F305" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G305" s="8">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c t="s" r="H305" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I305" s="7">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c t="s" r="J305" s="7">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="K305" s="7"/>
       <c r="L305" s="7"/>
@@ -11117,7 +11157,7 @@
       </c>
       <c r="D306" s="7"/>
       <c t="s" r="E306" s="7">
-        <v>388</v>
+        <v>396</v>
       </c>
       <c r="F306" s="7">
         <v>321</v>
@@ -11126,10 +11166,10 @@
         <v>17</v>
       </c>
       <c t="s" r="H306" s="8">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c t="s" r="I306" s="7">
-        <v>391</v>
+        <v>399</v>
       </c>
       <c t="s" r="J306" s="7">
         <v>31</v>
@@ -11165,7 +11205,7 @@
       </c>
       <c r="D308" s="7"/>
       <c t="s" r="E308" s="7">
-        <v>392</v>
+        <v>400</v>
       </c>
       <c r="F308" s="7">
         <v>320</v>
@@ -11180,12 +11220,12 @@
         <v>34</v>
       </c>
       <c t="s" r="J308" s="7">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="K308" s="7"/>
       <c r="L308" s="7"/>
       <c t="s" r="M308" s="7">
-        <v>393</v>
+        <v>401</v>
       </c>
     </row>
     <row r="309" ht="14.25" customHeight="1">
@@ -11200,7 +11240,7 @@
       </c>
       <c r="D309" s="7"/>
       <c t="s" r="E309" s="7">
-        <v>392</v>
+        <v>400</v>
       </c>
       <c r="F309" s="7">
         <v>320</v>
@@ -11212,15 +11252,15 @@
         <v>43</v>
       </c>
       <c t="s" r="I309" s="7">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c t="s" r="J309" s="7">
-        <v>77</v>
+        <v>92</v>
       </c>
       <c r="K309" s="7"/>
       <c r="L309" s="7"/>
       <c t="s" r="M309" s="7">
-        <v>77</v>
+        <v>92</v>
       </c>
     </row>
     <row r="310" ht="15" customHeight="1">
@@ -11235,7 +11275,7 @@
       </c>
       <c r="D310" s="7"/>
       <c t="s" r="E310" s="7">
-        <v>392</v>
+        <v>400</v>
       </c>
       <c r="F310" s="7">
         <v>320</v>
@@ -11244,13 +11284,13 @@
         <v>43</v>
       </c>
       <c t="s" r="H310" s="8">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c t="s" r="I310" s="7">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c t="s" r="J310" s="7">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="K310" s="7"/>
       <c r="L310" s="7"/>
@@ -11268,22 +11308,22 @@
       </c>
       <c r="D311" s="7"/>
       <c t="s" r="E311" s="7">
-        <v>392</v>
+        <v>400</v>
       </c>
       <c r="F311" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G311" s="8">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c t="s" r="H311" s="8">
         <v>43</v>
       </c>
       <c t="s" r="I311" s="7">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c t="s" r="J311" s="7">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="K311" s="7"/>
       <c r="L311" s="7"/>
@@ -11301,7 +11341,7 @@
       </c>
       <c r="D312" s="7"/>
       <c t="s" r="E312" s="7">
-        <v>392</v>
+        <v>400</v>
       </c>
       <c r="F312" s="7">
         <v>320</v>
@@ -11313,10 +11353,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I312" s="7">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c t="s" r="J312" s="7">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="K312" s="7"/>
       <c r="L312" s="7"/>
@@ -11334,7 +11374,7 @@
       </c>
       <c r="D313" s="7"/>
       <c t="s" r="E313" s="7">
-        <v>392</v>
+        <v>400</v>
       </c>
       <c r="F313" s="7">
         <v>320</v>
@@ -11346,10 +11386,10 @@
         <v>43</v>
       </c>
       <c t="s" r="I313" s="7">
-        <v>394</v>
+        <v>402</v>
       </c>
       <c t="s" r="J313" s="7">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="K313" s="7"/>
       <c r="L313" s="7"/>
@@ -11382,7 +11422,7 @@
       </c>
       <c r="D315" s="7"/>
       <c t="s" r="E315" s="7">
-        <v>395</v>
+        <v>403</v>
       </c>
       <c r="F315" s="7">
         <v>321</v>
@@ -11391,18 +11431,18 @@
         <v>43</v>
       </c>
       <c t="s" r="H315" s="8">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c t="s" r="I315" s="7">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c t="s" r="J315" s="7">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="K315" s="7"/>
       <c r="L315" s="7"/>
       <c t="s" r="M315" s="7">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="316" ht="14.25" customHeight="1">
@@ -11417,27 +11457,27 @@
       </c>
       <c r="D316" s="7"/>
       <c t="s" r="E316" s="7">
-        <v>395</v>
+        <v>403</v>
       </c>
       <c r="F316" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G316" s="8">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c t="s" r="H316" s="8">
         <v>43</v>
       </c>
       <c t="s" r="I316" s="7">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c t="s" r="J316" s="7">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="K316" s="7"/>
       <c r="L316" s="7"/>
       <c t="s" r="M316" s="7">
-        <v>396</v>
+        <v>404</v>
       </c>
     </row>
     <row r="317" ht="14.25" customHeight="1">
@@ -11452,7 +11492,7 @@
       </c>
       <c r="D317" s="7"/>
       <c t="s" r="E317" s="7">
-        <v>395</v>
+        <v>403</v>
       </c>
       <c r="F317" s="7">
         <v>321</v>
@@ -11461,10 +11501,10 @@
         <v>43</v>
       </c>
       <c t="s" r="H317" s="8">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c t="s" r="I317" s="7">
-        <v>397</v>
+        <v>405</v>
       </c>
       <c t="s" r="J317" s="7">
         <v>19</v>
@@ -11485,22 +11525,22 @@
       </c>
       <c r="D318" s="7"/>
       <c t="s" r="E318" s="7">
-        <v>395</v>
+        <v>403</v>
       </c>
       <c r="F318" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G318" s="8">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c t="s" r="H318" s="8">
         <v>43</v>
       </c>
       <c t="s" r="I318" s="7">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c t="s" r="J318" s="7">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="K318" s="7"/>
       <c r="L318" s="7"/>
@@ -11518,7 +11558,7 @@
       </c>
       <c r="D319" s="7"/>
       <c t="s" r="E319" s="7">
-        <v>395</v>
+        <v>403</v>
       </c>
       <c r="F319" s="7">
         <v>321</v>
@@ -11533,7 +11573,7 @@
         <v>48</v>
       </c>
       <c t="s" r="J319" s="7">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="K319" s="7"/>
       <c r="L319" s="7"/>
@@ -11551,7 +11591,7 @@
       </c>
       <c r="D320" s="7"/>
       <c t="s" r="E320" s="7">
-        <v>395</v>
+        <v>403</v>
       </c>
       <c r="F320" s="7">
         <v>321</v>
@@ -11560,13 +11600,13 @@
         <v>21</v>
       </c>
       <c t="s" r="H320" s="8">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c t="s" r="I320" s="7">
-        <v>398</v>
+        <v>406</v>
       </c>
       <c t="s" r="J320" s="7">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="K320" s="7"/>
       <c r="L320" s="7"/>
@@ -11599,7 +11639,7 @@
       </c>
       <c r="D322" s="7"/>
       <c t="s" r="E322" s="7">
-        <v>399</v>
+        <v>407</v>
       </c>
       <c r="F322" s="7">
         <v>320</v>
@@ -11611,15 +11651,15 @@
         <v>43</v>
       </c>
       <c t="s" r="I322" s="7">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c t="s" r="J322" s="7">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="K322" s="7"/>
       <c r="L322" s="7"/>
       <c t="s" r="M322" s="7">
-        <v>400</v>
+        <v>408</v>
       </c>
     </row>
     <row r="323" ht="14.25" customHeight="1">
@@ -11634,7 +11674,7 @@
       </c>
       <c r="D323" s="7"/>
       <c t="s" r="E323" s="7">
-        <v>399</v>
+        <v>407</v>
       </c>
       <c r="F323" s="7">
         <v>320</v>
@@ -11646,15 +11686,15 @@
         <v>17</v>
       </c>
       <c t="s" r="I323" s="7">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c t="s" r="J323" s="7">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="K323" s="7"/>
       <c r="L323" s="7"/>
       <c t="s" r="M323" s="7">
-        <v>401</v>
+        <v>409</v>
       </c>
     </row>
     <row r="324" ht="14.25" customHeight="1">
@@ -11662,14 +11702,14 @@
         <v>13</v>
       </c>
       <c r="B324" s="7">
-        <v>308</v>
+        <v>374</v>
       </c>
       <c t="s" r="C324" s="7">
         <v>14</v>
       </c>
       <c r="D324" s="7"/>
       <c t="s" r="E324" s="7">
-        <v>399</v>
+        <v>407</v>
       </c>
       <c r="F324" s="7">
         <v>320</v>
@@ -11678,13 +11718,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H324" s="8">
-        <v>172</v>
+        <v>395</v>
       </c>
       <c t="s" r="I324" s="7">
-        <v>210</v>
+        <v>272</v>
       </c>
       <c t="s" r="J324" s="7">
-        <v>124</v>
+        <v>252</v>
       </c>
       <c r="K324" s="7"/>
       <c r="L324" s="7"/>
@@ -11695,29 +11735,29 @@
         <v>13</v>
       </c>
       <c r="B325" s="7">
-        <v>307</v>
+        <v>375</v>
       </c>
       <c t="s" r="C325" s="7">
         <v>14</v>
       </c>
       <c r="D325" s="7"/>
       <c t="s" r="E325" s="7">
-        <v>399</v>
+        <v>407</v>
       </c>
       <c r="F325" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G325" s="8">
-        <v>172</v>
+        <v>395</v>
       </c>
       <c t="s" r="H325" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I325" s="7">
-        <v>402</v>
+        <v>69</v>
       </c>
       <c t="s" r="J325" s="7">
-        <v>259</v>
+        <v>58</v>
       </c>
       <c r="K325" s="7"/>
       <c r="L325" s="7"/>
@@ -11728,14 +11768,14 @@
         <v>13</v>
       </c>
       <c r="B326" s="7">
-        <v>376</v>
+        <v>310</v>
       </c>
       <c t="s" r="C326" s="7">
         <v>14</v>
       </c>
       <c r="D326" s="7"/>
       <c t="s" r="E326" s="7">
-        <v>399</v>
+        <v>407</v>
       </c>
       <c r="F326" s="7">
         <v>320</v>
@@ -11744,13 +11784,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H326" s="8">
-        <v>403</v>
+        <v>175</v>
       </c>
       <c t="s" r="I326" s="7">
-        <v>274</v>
+        <v>93</v>
       </c>
       <c t="s" r="J326" s="7">
-        <v>81</v>
+        <v>158</v>
       </c>
       <c r="K326" s="7"/>
       <c r="L326" s="7"/>
@@ -11761,29 +11801,29 @@
         <v>13</v>
       </c>
       <c r="B327" s="7">
-        <v>377</v>
+        <v>309</v>
       </c>
       <c t="s" r="C327" s="7">
         <v>14</v>
       </c>
       <c r="D327" s="7"/>
       <c t="s" r="E327" s="7">
-        <v>399</v>
+        <v>407</v>
       </c>
       <c r="F327" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G327" s="8">
-        <v>403</v>
+        <v>175</v>
       </c>
       <c t="s" r="H327" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I327" s="7">
-        <v>290</v>
+        <v>182</v>
       </c>
       <c t="s" r="J327" s="7">
-        <v>163</v>
+        <v>194</v>
       </c>
       <c r="K327" s="7"/>
       <c r="L327" s="7"/>
@@ -11816,7 +11856,7 @@
       </c>
       <c r="D329" s="7"/>
       <c t="s" r="E329" s="7">
-        <v>404</v>
+        <v>410</v>
       </c>
       <c r="F329" s="7">
         <v>320</v>
@@ -11828,15 +11868,15 @@
         <v>21</v>
       </c>
       <c t="s" r="I329" s="7">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c t="s" r="J329" s="7">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="K329" s="7"/>
       <c r="L329" s="7"/>
       <c t="s" r="M329" s="7">
-        <v>405</v>
+        <v>411</v>
       </c>
     </row>
     <row r="330" ht="15" customHeight="1">
@@ -11851,7 +11891,7 @@
       </c>
       <c r="D330" s="7"/>
       <c t="s" r="E330" s="7">
-        <v>404</v>
+        <v>410</v>
       </c>
       <c r="F330" s="7">
         <v>320</v>
@@ -11863,15 +11903,15 @@
         <v>43</v>
       </c>
       <c t="s" r="I330" s="7">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c t="s" r="J330" s="7">
-        <v>406</v>
+        <v>412</v>
       </c>
       <c r="K330" s="7"/>
       <c r="L330" s="7"/>
       <c t="s" r="M330" s="7">
-        <v>407</v>
+        <v>413</v>
       </c>
     </row>
     <row r="331" ht="14.25" customHeight="1">
@@ -11886,7 +11926,7 @@
       </c>
       <c r="D331" s="7"/>
       <c t="s" r="E331" s="7">
-        <v>404</v>
+        <v>410</v>
       </c>
       <c r="F331" s="7">
         <v>320</v>
@@ -11895,17 +11935,19 @@
         <v>43</v>
       </c>
       <c t="s" r="H331" s="8">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c t="s" r="I331" s="7">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c t="s" r="J331" s="7">
         <v>35</v>
       </c>
       <c r="K331" s="7"/>
       <c r="L331" s="7"/>
-      <c r="M331" s="7"/>
+      <c t="s" r="M331" s="7">
+        <v>414</v>
+      </c>
     </row>
     <row r="332" ht="14.25" customHeight="1">
       <c t="s" r="A332" s="6">
@@ -11919,13 +11961,13 @@
       </c>
       <c r="D332" s="7"/>
       <c t="s" r="E332" s="7">
-        <v>404</v>
+        <v>410</v>
       </c>
       <c r="F332" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G332" s="8">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c t="s" r="H332" s="8">
         <v>43</v>
@@ -11952,7 +11994,7 @@
       </c>
       <c r="D333" s="7"/>
       <c t="s" r="E333" s="7">
-        <v>404</v>
+        <v>410</v>
       </c>
       <c r="F333" s="7">
         <v>320</v>
@@ -11961,20 +12003,20 @@
         <v>43</v>
       </c>
       <c t="s" r="H333" s="8">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c t="s" r="I333" s="7">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c t="s" r="J333" s="7">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c t="s" r="K333" s="7">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="L333" s="7"/>
       <c t="s" r="M333" s="7">
-        <v>274</v>
+        <v>278</v>
       </c>
     </row>
     <row r="334" ht="14.25" customHeight="1">
@@ -11989,29 +12031,29 @@
       </c>
       <c r="D334" s="7"/>
       <c t="s" r="E334" s="7">
-        <v>404</v>
+        <v>410</v>
       </c>
       <c r="F334" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G334" s="8">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c t="s" r="H334" s="8">
         <v>43</v>
       </c>
       <c t="s" r="I334" s="7">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c t="s" r="J334" s="7">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c t="s" r="K334" s="7">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="L334" s="7"/>
       <c t="s" r="M334" s="7">
-        <v>290</v>
+        <v>294</v>
       </c>
     </row>
     <row r="335" ht="15" customHeight="1">
@@ -12026,7 +12068,7 @@
       </c>
       <c r="D335" s="7"/>
       <c t="s" r="E335" s="7">
-        <v>404</v>
+        <v>410</v>
       </c>
       <c r="F335" s="7">
         <v>320</v>
@@ -12035,13 +12077,13 @@
         <v>43</v>
       </c>
       <c t="s" r="H335" s="8">
-        <v>408</v>
+        <v>415</v>
       </c>
       <c t="s" r="I335" s="7">
-        <v>363</v>
+        <v>367</v>
       </c>
       <c t="s" r="J335" s="7">
-        <v>409</v>
+        <v>416</v>
       </c>
       <c r="K335" s="7"/>
       <c r="L335" s="7"/>
@@ -12059,22 +12101,22 @@
       </c>
       <c r="D336" s="7"/>
       <c t="s" r="E336" s="7">
-        <v>404</v>
+        <v>410</v>
       </c>
       <c r="F336" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G336" s="8">
-        <v>408</v>
+        <v>415</v>
       </c>
       <c t="s" r="H336" s="8">
         <v>43</v>
       </c>
       <c t="s" r="I336" s="7">
-        <v>410</v>
+        <v>417</v>
       </c>
       <c t="s" r="J336" s="7">
-        <v>411</v>
+        <v>418</v>
       </c>
       <c r="K336" s="7"/>
       <c r="L336" s="7"/>
@@ -12107,7 +12149,7 @@
       </c>
       <c r="D338" s="7"/>
       <c t="s" r="E338" s="7">
-        <v>412</v>
+        <v>419</v>
       </c>
       <c r="F338" s="7">
         <v>321</v>
@@ -12116,10 +12158,10 @@
         <v>16</v>
       </c>
       <c t="s" r="H338" s="8">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c t="s" r="I338" s="7">
-        <v>282</v>
+        <v>286</v>
       </c>
       <c t="s" r="J338" s="7">
         <v>40</v>
@@ -12127,7 +12169,7 @@
       <c r="K338" s="7"/>
       <c r="L338" s="7"/>
       <c t="s" r="M338" s="7">
-        <v>340</v>
+        <v>343</v>
       </c>
     </row>
     <row r="339" ht="14.25" customHeight="1">
@@ -12142,19 +12184,19 @@
       </c>
       <c r="D339" s="7"/>
       <c t="s" r="E339" s="7">
-        <v>412</v>
+        <v>419</v>
       </c>
       <c r="F339" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G339" s="8">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c t="s" r="H339" s="8">
         <v>68</v>
       </c>
       <c t="s" r="I339" s="7">
-        <v>397</v>
+        <v>405</v>
       </c>
       <c t="s" r="J339" s="7">
         <v>23</v>
@@ -12175,7 +12217,7 @@
       </c>
       <c r="D340" s="7"/>
       <c t="s" r="E340" s="7">
-        <v>412</v>
+        <v>419</v>
       </c>
       <c r="F340" s="7">
         <v>321</v>
@@ -12187,10 +12229,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I340" s="7">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c t="s" r="J340" s="7">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="K340" s="7"/>
       <c r="L340" s="7"/>
@@ -12208,7 +12250,7 @@
       </c>
       <c r="D341" s="7"/>
       <c t="s" r="E341" s="7">
-        <v>412</v>
+        <v>419</v>
       </c>
       <c r="F341" s="7">
         <v>321</v>
@@ -12217,13 +12259,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H341" s="8">
-        <v>372</v>
+        <v>377</v>
       </c>
       <c t="s" r="I341" s="7">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c t="s" r="J341" s="7">
-        <v>413</v>
+        <v>420</v>
       </c>
       <c r="K341" s="7"/>
       <c r="L341" s="7"/>
@@ -12241,22 +12283,22 @@
       </c>
       <c r="D342" s="7"/>
       <c t="s" r="E342" s="7">
-        <v>412</v>
+        <v>419</v>
       </c>
       <c r="F342" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G342" s="8">
-        <v>372</v>
+        <v>377</v>
       </c>
       <c t="s" r="H342" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I342" s="7">
-        <v>414</v>
+        <v>421</v>
       </c>
       <c t="s" r="J342" s="7">
-        <v>415</v>
+        <v>422</v>
       </c>
       <c r="K342" s="7"/>
       <c r="L342" s="7"/>
@@ -12289,27 +12331,27 @@
       </c>
       <c r="D344" s="7"/>
       <c t="s" r="E344" s="7">
-        <v>416</v>
+        <v>423</v>
       </c>
       <c r="F344" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G344" s="8">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c t="s" r="H344" s="8">
         <v>43</v>
       </c>
       <c t="s" r="I344" s="7">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c t="s" r="J344" s="7">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="K344" s="7"/>
       <c r="L344" s="7"/>
       <c t="s" r="M344" s="7">
-        <v>334</v>
+        <v>337</v>
       </c>
     </row>
     <row r="345" ht="15" customHeight="1">
@@ -12324,7 +12366,7 @@
       </c>
       <c r="D345" s="7"/>
       <c t="s" r="E345" s="7">
-        <v>416</v>
+        <v>423</v>
       </c>
       <c r="F345" s="7">
         <v>321</v>
@@ -12336,14 +12378,16 @@
         <v>17</v>
       </c>
       <c t="s" r="I345" s="7">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c t="s" r="J345" s="7">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="K345" s="7"/>
       <c r="L345" s="7"/>
-      <c r="M345" s="7"/>
+      <c t="s" r="M345" s="7">
+        <v>424</v>
+      </c>
     </row>
     <row r="346" ht="14.25" customHeight="1">
       <c t="s" r="A346" s="6">
@@ -12357,7 +12401,7 @@
       </c>
       <c r="D346" s="7"/>
       <c t="s" r="E346" s="7">
-        <v>416</v>
+        <v>423</v>
       </c>
       <c r="F346" s="7">
         <v>321</v>
@@ -12369,10 +12413,10 @@
         <v>43</v>
       </c>
       <c t="s" r="I346" s="7">
-        <v>402</v>
+        <v>394</v>
       </c>
       <c t="s" r="J346" s="7">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="K346" s="7"/>
       <c r="L346" s="7"/>
@@ -12390,7 +12434,7 @@
       </c>
       <c r="D347" s="7"/>
       <c t="s" r="E347" s="7">
-        <v>416</v>
+        <v>423</v>
       </c>
       <c r="F347" s="7">
         <v>321</v>
@@ -12402,10 +12446,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I347" s="7">
-        <v>417</v>
+        <v>425</v>
       </c>
       <c t="s" r="J347" s="7">
-        <v>363</v>
+        <v>367</v>
       </c>
       <c r="K347" s="7"/>
       <c r="L347" s="7"/>
@@ -12438,27 +12482,27 @@
       </c>
       <c r="D349" s="7"/>
       <c t="s" r="E349" s="7">
-        <v>418</v>
+        <v>426</v>
       </c>
       <c r="F349" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G349" s="8">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c t="s" r="H349" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I349" s="7">
-        <v>419</v>
+        <v>427</v>
       </c>
       <c t="s" r="J349" s="7">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="K349" s="7"/>
       <c r="L349" s="7"/>
       <c t="s" r="M349" s="7">
-        <v>420</v>
+        <v>428</v>
       </c>
     </row>
     <row r="350" ht="15" customHeight="1">
@@ -12473,7 +12517,7 @@
       </c>
       <c r="D350" s="7"/>
       <c t="s" r="E350" s="7">
-        <v>418</v>
+        <v>426</v>
       </c>
       <c r="F350" s="7">
         <v>321</v>
@@ -12482,13 +12526,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H350" s="8">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c t="s" r="I350" s="7">
-        <v>421</v>
+        <v>429</v>
       </c>
       <c t="s" r="J350" s="7">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="K350" s="7"/>
       <c r="L350" s="7"/>
@@ -12508,26 +12552,28 @@
       </c>
       <c r="D351" s="7"/>
       <c t="s" r="E351" s="7">
-        <v>418</v>
+        <v>426</v>
       </c>
       <c r="F351" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G351" s="8">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c t="s" r="H351" s="8">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c t="s" r="I351" s="7">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c t="s" r="J351" s="7">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="K351" s="7"/>
       <c r="L351" s="7"/>
-      <c r="M351" s="7"/>
+      <c t="s" r="M351" s="7">
+        <v>146</v>
+      </c>
     </row>
     <row r="352" ht="14.25" customHeight="1">
       <c t="s" r="A352" s="6">
@@ -12541,22 +12587,22 @@
       </c>
       <c r="D352" s="7"/>
       <c t="s" r="E352" s="7">
-        <v>418</v>
+        <v>426</v>
       </c>
       <c r="F352" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G352" s="8">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c t="s" r="H352" s="8">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c t="s" r="I352" s="7">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c t="s" r="J352" s="7">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="K352" s="7"/>
       <c r="L352" s="7"/>
@@ -12574,22 +12620,22 @@
       </c>
       <c r="D353" s="7"/>
       <c t="s" r="E353" s="7">
-        <v>418</v>
+        <v>426</v>
       </c>
       <c r="F353" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G353" s="8">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c t="s" r="H353" s="8">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c t="s" r="I353" s="7">
-        <v>289</v>
+        <v>293</v>
       </c>
       <c t="s" r="J353" s="7">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="K353" s="7"/>
       <c r="L353" s="7"/>
@@ -12607,22 +12653,22 @@
       </c>
       <c r="D354" s="7"/>
       <c t="s" r="E354" s="7">
-        <v>418</v>
+        <v>426</v>
       </c>
       <c r="F354" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G354" s="8">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c t="s" r="H354" s="8">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c t="s" r="I354" s="7">
-        <v>422</v>
+        <v>430</v>
       </c>
       <c t="s" r="J354" s="7">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="K354" s="7"/>
       <c r="L354" s="7"/>
@@ -12640,22 +12686,22 @@
       </c>
       <c r="D355" s="7"/>
       <c t="s" r="E355" s="7">
-        <v>418</v>
+        <v>426</v>
       </c>
       <c r="F355" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G355" s="8">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c t="s" r="H355" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I355" s="7">
-        <v>423</v>
+        <v>431</v>
       </c>
       <c t="s" r="J355" s="7">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="K355" s="7"/>
       <c r="L355" s="7"/>
@@ -12688,7 +12734,7 @@
       </c>
       <c r="D357" s="7"/>
       <c t="s" r="E357" s="7">
-        <v>424</v>
+        <v>432</v>
       </c>
       <c r="F357" s="7">
         <v>321</v>
@@ -12703,12 +12749,12 @@
         <v>51</v>
       </c>
       <c t="s" r="J357" s="7">
-        <v>425</v>
+        <v>433</v>
       </c>
       <c r="K357" s="7"/>
       <c r="L357" s="7"/>
       <c t="s" r="M357" s="7">
-        <v>426</v>
+        <v>434</v>
       </c>
     </row>
     <row r="358" ht="14.25" customHeight="1">
@@ -12723,7 +12769,7 @@
       </c>
       <c r="D358" s="7"/>
       <c t="s" r="E358" s="7">
-        <v>424</v>
+        <v>432</v>
       </c>
       <c r="F358" s="7">
         <v>321</v>
@@ -12732,18 +12778,18 @@
         <v>68</v>
       </c>
       <c t="s" r="H358" s="8">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c t="s" r="I358" s="7">
-        <v>406</v>
+        <v>412</v>
       </c>
       <c t="s" r="J358" s="7">
-        <v>397</v>
+        <v>405</v>
       </c>
       <c r="K358" s="7"/>
       <c r="L358" s="7"/>
       <c t="s" r="M358" s="7">
-        <v>427</v>
+        <v>435</v>
       </c>
     </row>
     <row r="359" ht="14.25" customHeight="1">
@@ -12758,19 +12804,19 @@
       </c>
       <c r="D359" s="7"/>
       <c t="s" r="E359" s="7">
-        <v>424</v>
+        <v>432</v>
       </c>
       <c r="F359" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G359" s="8">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c t="s" r="H359" s="8">
         <v>21</v>
       </c>
       <c t="s" r="I359" s="7">
-        <v>428</v>
+        <v>436</v>
       </c>
       <c t="s" r="J359" s="7">
         <v>22</v>
@@ -12791,7 +12837,7 @@
       </c>
       <c r="D360" s="7"/>
       <c t="s" r="E360" s="7">
-        <v>424</v>
+        <v>432</v>
       </c>
       <c r="F360" s="7">
         <v>321</v>
@@ -12800,13 +12846,13 @@
         <v>21</v>
       </c>
       <c t="s" r="H360" s="8">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c t="s" r="I360" s="7">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c t="s" r="J360" s="7">
-        <v>289</v>
+        <v>293</v>
       </c>
       <c r="K360" s="7"/>
       <c r="L360" s="7"/>
@@ -12839,7 +12885,7 @@
       </c>
       <c r="D362" s="7"/>
       <c t="s" r="E362" s="7">
-        <v>429</v>
+        <v>437</v>
       </c>
       <c r="F362" s="7">
         <v>320</v>
@@ -12848,18 +12894,18 @@
         <v>17</v>
       </c>
       <c t="s" r="H362" s="8">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c t="s" r="I362" s="7">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c t="s" r="J362" s="7">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="K362" s="7"/>
       <c r="L362" s="7"/>
       <c t="s" r="M362" s="7">
-        <v>430</v>
+        <v>438</v>
       </c>
     </row>
     <row r="363" ht="14.25" customHeight="1">
@@ -12874,29 +12920,29 @@
       </c>
       <c r="D363" s="7"/>
       <c t="s" r="E363" s="7">
-        <v>429</v>
+        <v>437</v>
       </c>
       <c r="F363" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G363" s="8">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c t="s" r="H363" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I363" s="7">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c t="s" r="J363" s="7">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c t="s" r="K363" s="7">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="L363" s="7"/>
       <c t="s" r="M363" s="7">
-        <v>197</v>
+        <v>200</v>
       </c>
     </row>
     <row r="364" ht="14.25" customHeight="1">
@@ -12904,14 +12950,14 @@
         <v>13</v>
       </c>
       <c r="B364" s="7">
-        <v>374</v>
+        <v>362</v>
       </c>
       <c t="s" r="C364" s="7">
         <v>14</v>
       </c>
       <c r="D364" s="7"/>
       <c t="s" r="E364" s="7">
-        <v>429</v>
+        <v>437</v>
       </c>
       <c r="F364" s="7">
         <v>320</v>
@@ -12920,13 +12966,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H364" s="8">
-        <v>403</v>
+        <v>156</v>
       </c>
       <c t="s" r="I364" s="7">
-        <v>268</v>
+        <v>37</v>
       </c>
       <c t="s" r="J364" s="7">
-        <v>248</v>
+        <v>133</v>
       </c>
       <c r="K364" s="7"/>
       <c r="L364" s="7"/>
@@ -12937,29 +12983,29 @@
         <v>13</v>
       </c>
       <c r="B365" s="7">
-        <v>375</v>
+        <v>363</v>
       </c>
       <c t="s" r="C365" s="7">
         <v>14</v>
       </c>
       <c r="D365" s="7"/>
       <c t="s" r="E365" s="7">
-        <v>429</v>
+        <v>437</v>
       </c>
       <c r="F365" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G365" s="8">
-        <v>403</v>
+        <v>156</v>
       </c>
       <c t="s" r="H365" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I365" s="7">
-        <v>69</v>
+        <v>253</v>
       </c>
       <c t="s" r="J365" s="7">
-        <v>58</v>
+        <v>23</v>
       </c>
       <c r="K365" s="7"/>
       <c r="L365" s="7"/>
@@ -12970,14 +13016,14 @@
         <v>13</v>
       </c>
       <c r="B366" s="7">
-        <v>310</v>
+        <v>262</v>
       </c>
       <c t="s" r="C366" s="7">
         <v>14</v>
       </c>
       <c r="D366" s="7"/>
       <c t="s" r="E366" s="7">
-        <v>429</v>
+        <v>437</v>
       </c>
       <c r="F366" s="7">
         <v>320</v>
@@ -12986,13 +13032,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H366" s="8">
-        <v>172</v>
+        <v>439</v>
       </c>
       <c t="s" r="I366" s="7">
-        <v>91</v>
+        <v>263</v>
       </c>
       <c t="s" r="J366" s="7">
-        <v>155</v>
+        <v>376</v>
       </c>
       <c r="K366" s="7"/>
       <c r="L366" s="7"/>
@@ -13003,29 +13049,29 @@
         <v>13</v>
       </c>
       <c r="B367" s="7">
-        <v>309</v>
+        <v>263</v>
       </c>
       <c t="s" r="C367" s="7">
         <v>14</v>
       </c>
       <c r="D367" s="7"/>
       <c t="s" r="E367" s="7">
-        <v>429</v>
+        <v>437</v>
       </c>
       <c r="F367" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G367" s="8">
-        <v>172</v>
+        <v>439</v>
       </c>
       <c t="s" r="H367" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I367" s="7">
-        <v>179</v>
+        <v>82</v>
       </c>
       <c t="s" r="J367" s="7">
-        <v>191</v>
+        <v>356</v>
       </c>
       <c r="K367" s="7"/>
       <c r="L367" s="7"/>
@@ -13058,7 +13104,7 @@
       </c>
       <c r="D369" s="7"/>
       <c t="s" r="E369" s="7">
-        <v>431</v>
+        <v>440</v>
       </c>
       <c r="F369" s="7">
         <v>321</v>
@@ -13073,14 +13119,14 @@
         <v>55</v>
       </c>
       <c t="s" r="J369" s="7">
-        <v>402</v>
+        <v>394</v>
       </c>
       <c t="s" r="K369" s="7">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="L369" s="7"/>
       <c t="s" r="M369" s="7">
-        <v>212</v>
+        <v>215</v>
       </c>
     </row>
     <row r="370" ht="15" customHeight="1">
@@ -13095,7 +13141,7 @@
       </c>
       <c r="D370" s="7"/>
       <c t="s" r="E370" s="7">
-        <v>431</v>
+        <v>440</v>
       </c>
       <c r="F370" s="7">
         <v>321</v>
@@ -13107,17 +13153,17 @@
         <v>43</v>
       </c>
       <c t="s" r="I370" s="7">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c t="s" r="J370" s="7">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c t="s" r="K370" s="7">
         <v>59</v>
       </c>
       <c r="L370" s="7"/>
       <c t="s" r="M370" s="7">
-        <v>191</v>
+        <v>194</v>
       </c>
     </row>
     <row r="371" ht="14.25" customHeight="1">
@@ -13147,22 +13193,22 @@
       </c>
       <c r="D372" s="7"/>
       <c t="s" r="E372" s="7">
-        <v>432</v>
+        <v>441</v>
       </c>
       <c r="F372" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G372" s="8">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c t="s" r="H372" s="8">
-        <v>433</v>
+        <v>442</v>
       </c>
       <c t="s" r="I372" s="7">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c t="s" r="J372" s="7">
-        <v>434</v>
+        <v>443</v>
       </c>
       <c r="K372" s="7"/>
       <c r="L372" s="7"/>
@@ -13180,22 +13226,22 @@
       </c>
       <c r="D373" s="7"/>
       <c t="s" r="E373" s="7">
-        <v>432</v>
+        <v>441</v>
       </c>
       <c r="F373" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G373" s="8">
-        <v>433</v>
+        <v>442</v>
       </c>
       <c t="s" r="H373" s="8">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c t="s" r="I373" s="7">
-        <v>380</v>
+        <v>386</v>
       </c>
       <c t="s" r="J373" s="7">
-        <v>435</v>
+        <v>444</v>
       </c>
       <c r="K373" s="7"/>
       <c r="L373" s="7"/>
@@ -13228,7 +13274,7 @@
       </c>
       <c r="D375" s="7"/>
       <c t="s" r="E375" s="7">
-        <v>436</v>
+        <v>445</v>
       </c>
       <c r="F375" s="7">
         <v>330</v>
@@ -13237,18 +13283,18 @@
         <v>17</v>
       </c>
       <c t="s" r="H375" s="8">
-        <v>437</v>
+        <v>446</v>
       </c>
       <c t="s" r="I375" s="7">
-        <v>425</v>
+        <v>433</v>
       </c>
       <c t="s" r="J375" s="7">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="K375" s="7"/>
       <c r="L375" s="7"/>
       <c t="s" r="M375" s="7">
-        <v>163</v>
+        <v>166</v>
       </c>
     </row>
     <row r="376" ht="14.25" customHeight="1">
@@ -13263,22 +13309,22 @@
       </c>
       <c r="D376" s="7"/>
       <c t="s" r="E376" s="7">
-        <v>436</v>
+        <v>445</v>
       </c>
       <c r="F376" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G376" s="8">
-        <v>437</v>
+        <v>446</v>
       </c>
       <c t="s" r="H376" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I376" s="7">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c t="s" r="J376" s="7">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c r="K376" s="7"/>
       <c r="L376" s="7"/>
@@ -13311,7 +13357,7 @@
       </c>
       <c r="D378" s="7"/>
       <c t="s" r="E378" s="7">
-        <v>438</v>
+        <v>447</v>
       </c>
       <c r="F378" s="7">
         <v>330</v>
@@ -13320,18 +13366,18 @@
         <v>17</v>
       </c>
       <c t="s" r="H378" s="8">
-        <v>439</v>
+        <v>448</v>
       </c>
       <c t="s" r="I378" s="7">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c t="s" r="J378" s="7">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="K378" s="7"/>
       <c r="L378" s="7"/>
       <c t="s" r="M378" s="7">
-        <v>440</v>
+        <v>449</v>
       </c>
     </row>
     <row r="379" ht="14.25" customHeight="1">
@@ -13346,22 +13392,22 @@
       </c>
       <c r="D379" s="7"/>
       <c t="s" r="E379" s="7">
-        <v>438</v>
+        <v>447</v>
       </c>
       <c r="F379" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G379" s="8">
-        <v>439</v>
+        <v>448</v>
       </c>
       <c t="s" r="H379" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I379" s="7">
-        <v>413</v>
+        <v>420</v>
       </c>
       <c t="s" r="J379" s="7">
-        <v>419</v>
+        <v>427</v>
       </c>
       <c r="K379" s="7"/>
       <c r="L379" s="7"/>
@@ -13390,31 +13436,31 @@
         <v>5805</v>
       </c>
       <c t="s" r="C381" s="7">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="D381" s="7"/>
       <c t="s" r="E381" s="7">
-        <v>441</v>
+        <v>450</v>
       </c>
       <c r="F381" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G381" s="8">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c t="s" r="H381" s="8">
-        <v>442</v>
+        <v>451</v>
       </c>
       <c t="s" r="I381" s="7">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c t="s" r="J381" s="7">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="K381" s="7"/>
       <c r="L381" s="7"/>
       <c t="s" r="M381" s="7">
-        <v>443</v>
+        <v>452</v>
       </c>
     </row>
     <row r="382" ht="14.25" customHeight="1">
@@ -13425,23 +13471,23 @@
         <v>5806</v>
       </c>
       <c t="s" r="C382" s="7">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="D382" s="7"/>
       <c t="s" r="E382" s="7">
-        <v>441</v>
+        <v>450</v>
       </c>
       <c r="F382" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G382" s="8">
-        <v>442</v>
+        <v>451</v>
       </c>
       <c t="s" r="H382" s="8">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c t="s" r="I382" s="7">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c t="s" r="J382" s="7">
         <v>51</v>
@@ -13477,19 +13523,19 @@
       </c>
       <c r="D384" s="7"/>
       <c t="s" r="E384" s="7">
-        <v>444</v>
+        <v>453</v>
       </c>
       <c r="F384" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G384" s="8">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c t="s" r="H384" s="8">
-        <v>445</v>
+        <v>454</v>
       </c>
       <c t="s" r="I384" s="7">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c t="s" r="J384" s="7">
         <v>55</v>
@@ -13497,7 +13543,7 @@
       <c r="K384" s="7"/>
       <c r="L384" s="7"/>
       <c t="s" r="M384" s="7">
-        <v>446</v>
+        <v>250</v>
       </c>
     </row>
     <row r="385" ht="15" customHeight="1">
@@ -13512,22 +13558,22 @@
       </c>
       <c r="D385" s="7"/>
       <c t="s" r="E385" s="7">
-        <v>444</v>
+        <v>453</v>
       </c>
       <c r="F385" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G385" s="8">
-        <v>445</v>
+        <v>454</v>
       </c>
       <c t="s" r="H385" s="8">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c t="s" r="I385" s="7">
         <v>57</v>
       </c>
       <c t="s" r="J385" s="7">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="K385" s="7"/>
       <c r="L385" s="7"/>
@@ -13560,19 +13606,19 @@
       </c>
       <c r="D387" s="7"/>
       <c t="s" r="E387" s="7">
-        <v>447</v>
+        <v>455</v>
       </c>
       <c r="F387" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G387" s="8">
-        <v>448</v>
+        <v>456</v>
       </c>
       <c t="s" r="H387" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I387" s="7">
-        <v>406</v>
+        <v>412</v>
       </c>
       <c t="s" r="J387" s="7">
         <v>58</v>
@@ -13580,7 +13626,7 @@
       <c r="K387" s="7"/>
       <c r="L387" s="7"/>
       <c t="s" r="M387" s="7">
-        <v>449</v>
+        <v>457</v>
       </c>
     </row>
     <row r="388" ht="14.25" customHeight="1">
@@ -13595,7 +13641,7 @@
       </c>
       <c r="D388" s="7"/>
       <c t="s" r="E388" s="7">
-        <v>447</v>
+        <v>455</v>
       </c>
       <c r="F388" s="7">
         <v>330</v>
@@ -13607,10 +13653,10 @@
         <v>43</v>
       </c>
       <c t="s" r="I388" s="7">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c t="s" r="J388" s="7">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="K388" s="7"/>
       <c r="L388" s="7"/>
@@ -13628,7 +13674,7 @@
       </c>
       <c r="D389" s="7"/>
       <c t="s" r="E389" s="7">
-        <v>447</v>
+        <v>455</v>
       </c>
       <c r="F389" s="7">
         <v>330</v>
@@ -13640,10 +13686,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I389" s="7">
-        <v>422</v>
+        <v>430</v>
       </c>
       <c t="s" r="J389" s="7">
-        <v>391</v>
+        <v>399</v>
       </c>
       <c r="K389" s="7"/>
       <c r="L389" s="7"/>
@@ -13651,7 +13697,7 @@
     </row>
     <row r="390" ht="16.5" customHeight="1">
       <c t="s" r="A390" s="9">
-        <v>450</v>
+        <v>458</v>
       </c>
       <c r="B390" s="9"/>
       <c r="C390" s="9"/>
@@ -13671,7 +13717,7 @@
     <row r="391" ht="65.25" customHeight="1"/>
     <row r="392" ht="16.5" customHeight="1">
       <c t="s" r="A392" s="10">
-        <v>451</v>
+        <v>459</v>
       </c>
       <c r="B392" s="10"/>
       <c r="C392" s="10"/>
@@ -13684,7 +13730,7 @@
       <c r="J392" s="10"/>
       <c r="K392" s="10"/>
       <c t="s" r="L392" s="11">
-        <v>452</v>
+        <v>460</v>
       </c>
       <c r="M392" s="11"/>
       <c r="N392" s="11"/>

--- a/Data/FlightPlan/FPL_23OCT26.xlsx
+++ b/Data/FlightPlan/FPL_23OCT26.xlsx
@@ -314,834 +314,846 @@
     <t>16:35</t>
   </si>
   <si>
+    <t>19:21</t>
+  </si>
+  <si>
+    <t>DEL</t>
+  </si>
+  <si>
+    <t>20:15</t>
+  </si>
+  <si>
+    <t>23:45</t>
+  </si>
+  <si>
+    <t>00:25</t>
+  </si>
+  <si>
+    <t>VN-A528</t>
+  </si>
+  <si>
+    <t>07:50</t>
+  </si>
+  <si>
+    <t>08:50</t>
+  </si>
+  <si>
+    <t>08:35</t>
+  </si>
+  <si>
+    <t>DAD</t>
+  </si>
+  <si>
+    <t>09:25</t>
+  </si>
+  <si>
+    <t>11:10</t>
+  </si>
+  <si>
+    <t>11:11</t>
+  </si>
+  <si>
+    <t>13:25</t>
+  </si>
+  <si>
+    <t>13:26</t>
+  </si>
+  <si>
+    <t>14:00</t>
+  </si>
+  <si>
+    <t>16:21</t>
+  </si>
+  <si>
+    <t>16:45</t>
+  </si>
+  <si>
+    <t>18:50</t>
+  </si>
+  <si>
+    <t>19:09</t>
+  </si>
+  <si>
+    <t>19:20</t>
+  </si>
+  <si>
+    <t>21:25</t>
+  </si>
+  <si>
+    <t>VN-A529</t>
+  </si>
+  <si>
+    <t>CGK</t>
+  </si>
+  <si>
+    <t>12:30</t>
+  </si>
+  <si>
+    <t>12:34</t>
+  </si>
+  <si>
+    <t>16:40</t>
+  </si>
+  <si>
+    <t>16:44</t>
+  </si>
+  <si>
+    <t>BLR</t>
+  </si>
+  <si>
+    <t>22:35</t>
+  </si>
+  <si>
+    <t>06:00</t>
+  </si>
+  <si>
+    <t>VN-A530</t>
+  </si>
+  <si>
+    <t>VCA</t>
+  </si>
+  <si>
+    <t>06:45</t>
+  </si>
+  <si>
+    <t>08:55</t>
+  </si>
+  <si>
+    <t>11:53</t>
+  </si>
+  <si>
+    <t>13:50</t>
+  </si>
+  <si>
+    <t>13:58</t>
+  </si>
+  <si>
+    <t>15:45</t>
+  </si>
+  <si>
+    <t>15:48</t>
+  </si>
+  <si>
+    <t>CXR</t>
+  </si>
+  <si>
+    <t>16:20</t>
+  </si>
+  <si>
+    <t>18:10</t>
+  </si>
+  <si>
+    <t>18:21</t>
+  </si>
+  <si>
+    <t>18:45</t>
+  </si>
+  <si>
+    <t>20:35</t>
+  </si>
+  <si>
+    <t>VN-A532</t>
+  </si>
+  <si>
+    <t>15:30</t>
+  </si>
+  <si>
+    <t>15:04</t>
+  </si>
+  <si>
+    <t>16:30</t>
+  </si>
+  <si>
+    <t>20:32</t>
+  </si>
+  <si>
+    <t>VN-A534</t>
+  </si>
+  <si>
+    <t>BMV</t>
+  </si>
+  <si>
+    <t>06:30</t>
+  </si>
+  <si>
+    <t>07:30</t>
+  </si>
+  <si>
+    <t>07:12</t>
+  </si>
+  <si>
+    <t>08:00</t>
+  </si>
+  <si>
+    <t>VN-A535</t>
+  </si>
+  <si>
+    <t>09:20</t>
+  </si>
+  <si>
+    <t>12:20</t>
+  </si>
+  <si>
+    <t>14:30</t>
+  </si>
+  <si>
+    <t>16:36</t>
+  </si>
+  <si>
+    <t>14:50</t>
+  </si>
+  <si>
+    <t>17:20</t>
+  </si>
+  <si>
+    <t>19:26</t>
+  </si>
+  <si>
+    <t>01:20</t>
+  </si>
+  <si>
+    <t>VN-A536</t>
+  </si>
+  <si>
+    <t>09:10</t>
+  </si>
+  <si>
+    <t>10:40</t>
+  </si>
+  <si>
+    <t>10:49</t>
+  </si>
+  <si>
+    <t>12:57</t>
+  </si>
+  <si>
+    <t>13:15</t>
+  </si>
+  <si>
+    <t>14:46</t>
+  </si>
+  <si>
+    <t>DLI</t>
+  </si>
+  <si>
+    <t>15:40</t>
+  </si>
+  <si>
+    <t>17:47</t>
+  </si>
+  <si>
+    <t>18:00</t>
+  </si>
+  <si>
+    <t>19:50</t>
+  </si>
+  <si>
+    <t>23:25</t>
+  </si>
+  <si>
+    <t>01:35</t>
+  </si>
+  <si>
+    <t>VN-A542</t>
+  </si>
+  <si>
+    <t>10:25</t>
+  </si>
+  <si>
+    <t>16:25</t>
+  </si>
+  <si>
+    <t>11:20</t>
+  </si>
+  <si>
+    <t>21:35</t>
+  </si>
+  <si>
+    <t>18:05</t>
+  </si>
+  <si>
+    <t>22:10</t>
+  </si>
+  <si>
+    <t>00:30</t>
+  </si>
+  <si>
+    <t>VN-A543</t>
+  </si>
+  <si>
+    <t>05:30</t>
+  </si>
+  <si>
+    <t>07:28</t>
+  </si>
+  <si>
+    <t>10:00</t>
+  </si>
+  <si>
+    <t>10:14</t>
+  </si>
+  <si>
+    <t>HUI</t>
+  </si>
+  <si>
+    <t>10:35</t>
+  </si>
+  <si>
+    <t>12:00</t>
+  </si>
+  <si>
+    <t>12:17</t>
+  </si>
+  <si>
+    <t>13:55</t>
+  </si>
+  <si>
+    <t>14:21</t>
+  </si>
+  <si>
+    <t>15:10</t>
+  </si>
+  <si>
+    <t>17:05</t>
+  </si>
+  <si>
+    <t>18:30</t>
+  </si>
+  <si>
+    <t>20:40</t>
+  </si>
+  <si>
+    <t>VN-A544</t>
+  </si>
+  <si>
+    <t>UIH</t>
+  </si>
+  <si>
+    <t>08:25</t>
+  </si>
+  <si>
+    <t>09:24</t>
+  </si>
+  <si>
+    <t>10:05</t>
+  </si>
+  <si>
+    <t>11:07</t>
+  </si>
+  <si>
+    <t>11:50</t>
+  </si>
+  <si>
+    <t>12:47</t>
+  </si>
+  <si>
+    <t>15:05</t>
+  </si>
+  <si>
+    <t>15:33</t>
+  </si>
+  <si>
+    <t>18:17</t>
+  </si>
+  <si>
+    <t>18:20</t>
+  </si>
+  <si>
+    <t>20:55</t>
+  </si>
+  <si>
+    <t>22:45</t>
+  </si>
+  <si>
+    <t>NGO</t>
+  </si>
+  <si>
+    <t>VN-A549</t>
+  </si>
+  <si>
+    <t>10:45</t>
+  </si>
+  <si>
+    <t>12:05</t>
+  </si>
+  <si>
+    <t>12:11</t>
+  </si>
+  <si>
+    <t>12:40</t>
+  </si>
+  <si>
+    <t>14:14</t>
+  </si>
+  <si>
+    <t>18:43</t>
+  </si>
+  <si>
+    <t>VII</t>
+  </si>
+  <si>
+    <t>18:40</t>
+  </si>
+  <si>
+    <t>19:10</t>
+  </si>
+  <si>
+    <t>21:00</t>
+  </si>
+  <si>
+    <t>22:50</t>
+  </si>
+  <si>
+    <t>VN-A551</t>
+  </si>
+  <si>
+    <t>12:15</t>
+  </si>
+  <si>
+    <t>12:12</t>
+  </si>
+  <si>
+    <t>12:45</t>
+  </si>
+  <si>
+    <t>14:20</t>
+  </si>
+  <si>
+    <t>14:47</t>
+  </si>
+  <si>
+    <t>15:00</t>
+  </si>
+  <si>
+    <t>17:10</t>
+  </si>
+  <si>
+    <t>17:55</t>
+  </si>
+  <si>
+    <t>18:55</t>
+  </si>
+  <si>
+    <t>19:25</t>
+  </si>
+  <si>
+    <t>20:25</t>
+  </si>
+  <si>
+    <t>21:10</t>
+  </si>
+  <si>
+    <t>22:30</t>
+  </si>
+  <si>
+    <t>21:40</t>
+  </si>
+  <si>
+    <t>23:00</t>
+  </si>
+  <si>
+    <t>00:20</t>
+  </si>
+  <si>
+    <t>VN-A552</t>
+  </si>
+  <si>
+    <t>KUL</t>
+  </si>
+  <si>
+    <t>12:35</t>
+  </si>
+  <si>
+    <t>12:39</t>
+  </si>
+  <si>
+    <t>14:27</t>
+  </si>
+  <si>
+    <t>HKG</t>
+  </si>
+  <si>
+    <t>21:45</t>
+  </si>
+  <si>
+    <t>VN-A553</t>
+  </si>
+  <si>
+    <t>VVO</t>
+  </si>
+  <si>
+    <t>06:20</t>
+  </si>
+  <si>
+    <t>09:07</t>
+  </si>
+  <si>
+    <t>11:45</t>
+  </si>
+  <si>
+    <t>14:07</t>
+  </si>
+  <si>
+    <t>14:40</t>
+  </si>
+  <si>
+    <t>18:47</t>
+  </si>
+  <si>
+    <t>21:50</t>
+  </si>
+  <si>
+    <t>VN-A554</t>
+  </si>
+  <si>
+    <t>PXU</t>
+  </si>
+  <si>
+    <t>06:40</t>
+  </si>
+  <si>
+    <t>07:27</t>
+  </si>
+  <si>
+    <t>08:20</t>
+  </si>
+  <si>
+    <t>11:55</t>
+  </si>
+  <si>
+    <t>14:51</t>
+  </si>
+  <si>
+    <t>15:25</t>
+  </si>
+  <si>
+    <t>16:22</t>
+  </si>
+  <si>
+    <t>16:00</t>
+  </si>
+  <si>
+    <t>17:38</t>
+  </si>
+  <si>
+    <t>THD</t>
+  </si>
+  <si>
+    <t>20:50</t>
+  </si>
+  <si>
+    <t>21:05</t>
+  </si>
+  <si>
+    <t>23:10</t>
+  </si>
+  <si>
+    <t>C</t>
+  </si>
+  <si>
+    <t>VN-A575</t>
+  </si>
+  <si>
+    <t>BQS</t>
+  </si>
+  <si>
+    <t>13:45</t>
+  </si>
+  <si>
+    <t>13:37</t>
+  </si>
+  <si>
+    <t>14:15</t>
+  </si>
+  <si>
+    <t>16:02</t>
+  </si>
+  <si>
+    <t>KHV</t>
+  </si>
+  <si>
+    <t>01:05</t>
+  </si>
+  <si>
+    <t>09:50</t>
+  </si>
+  <si>
+    <t>122A</t>
+  </si>
+  <si>
+    <t>VN-A578</t>
+  </si>
+  <si>
+    <t>09:05</t>
+  </si>
+  <si>
+    <t>09:09</t>
+  </si>
+  <si>
+    <t>10:20</t>
+  </si>
+  <si>
+    <t>12:51</t>
+  </si>
+  <si>
+    <t>17:51</t>
+  </si>
+  <si>
+    <t>17:40</t>
+  </si>
+  <si>
+    <t>22:25</t>
+  </si>
+  <si>
+    <t>00:50</t>
+  </si>
+  <si>
+    <t>23:30</t>
+  </si>
+  <si>
+    <t>VN-A580</t>
+  </si>
+  <si>
+    <t>10:10</t>
+  </si>
+  <si>
+    <t>10:07</t>
+  </si>
+  <si>
+    <t>11:47</t>
+  </si>
+  <si>
+    <t>16:49</t>
+  </si>
+  <si>
+    <t>NOZ</t>
+  </si>
+  <si>
+    <t>23:05</t>
+  </si>
+  <si>
+    <t>06:15</t>
+  </si>
+  <si>
+    <t>VN-A607</t>
+  </si>
+  <si>
+    <t>12:55</t>
+  </si>
+  <si>
+    <t>12:54</t>
+  </si>
+  <si>
+    <t>16:50</t>
+  </si>
+  <si>
+    <t>VN-A629</t>
+  </si>
+  <si>
+    <t>13:24</t>
+  </si>
+  <si>
+    <t>VTE</t>
+  </si>
+  <si>
+    <t>18:25</t>
+  </si>
+  <si>
+    <t>18:33</t>
+  </si>
+  <si>
+    <t>MNL</t>
+  </si>
+  <si>
+    <t>02:10</t>
+  </si>
+  <si>
+    <t>03:00</t>
+  </si>
+  <si>
+    <t>04:35</t>
+  </si>
+  <si>
+    <t>VN-A630</t>
+  </si>
+  <si>
+    <t>07:00</t>
+  </si>
+  <si>
+    <t>10:03</t>
+  </si>
+  <si>
+    <t>VN-A632</t>
+  </si>
+  <si>
+    <t>07:40</t>
+  </si>
+  <si>
+    <t>07:48</t>
+  </si>
+  <si>
+    <t>10:32</t>
+  </si>
+  <si>
+    <t>BKK</t>
+  </si>
+  <si>
+    <t>15:03</t>
+  </si>
+  <si>
+    <t>17:49</t>
+  </si>
+  <si>
+    <t>VDH</t>
+  </si>
+  <si>
     <t>19:15</t>
   </si>
   <si>
-    <t>DEL</t>
-  </si>
-  <si>
-    <t>20:15</t>
-  </si>
-  <si>
-    <t>23:45</t>
-  </si>
-  <si>
-    <t>00:25</t>
-  </si>
-  <si>
-    <t>VN-A528</t>
-  </si>
-  <si>
-    <t>07:50</t>
-  </si>
-  <si>
-    <t>08:50</t>
-  </si>
-  <si>
-    <t>08:35</t>
-  </si>
-  <si>
-    <t>DAD</t>
-  </si>
-  <si>
-    <t>09:25</t>
-  </si>
-  <si>
-    <t>11:10</t>
-  </si>
-  <si>
-    <t>11:11</t>
-  </si>
-  <si>
-    <t>13:25</t>
-  </si>
-  <si>
-    <t>13:26</t>
-  </si>
-  <si>
-    <t>14:00</t>
-  </si>
-  <si>
-    <t>16:21</t>
-  </si>
-  <si>
-    <t>16:45</t>
-  </si>
-  <si>
-    <t>18:50</t>
+    <t>21:20</t>
+  </si>
+  <si>
+    <t>20:45</t>
+  </si>
+  <si>
+    <t>VN-A633</t>
+  </si>
+  <si>
+    <t>13:04</t>
+  </si>
+  <si>
+    <t>18:15</t>
+  </si>
+  <si>
+    <t>18:09</t>
+  </si>
+  <si>
+    <t>VN-A634</t>
+  </si>
+  <si>
+    <t>HKT</t>
+  </si>
+  <si>
+    <t>10:55</t>
+  </si>
+  <si>
+    <t>11:16</t>
+  </si>
+  <si>
+    <t>14:57</t>
+  </si>
+  <si>
+    <t>19:40</t>
+  </si>
+  <si>
+    <t>21:30</t>
+  </si>
+  <si>
+    <t>VN-A636</t>
+  </si>
+  <si>
+    <t>07:15</t>
+  </si>
+  <si>
+    <t>09:55</t>
+  </si>
+  <si>
+    <t>09:34</t>
+  </si>
+  <si>
+    <t>16:10</t>
+  </si>
+  <si>
+    <t>17:44</t>
+  </si>
+  <si>
+    <t>20:10</t>
+  </si>
+  <si>
+    <t>VN-A637</t>
+  </si>
+  <si>
+    <t>05:00</t>
+  </si>
+  <si>
+    <t>06:50</t>
+  </si>
+  <si>
+    <t>06:48</t>
+  </si>
+  <si>
+    <t>07:20</t>
+  </si>
+  <si>
+    <t>09:15</t>
+  </si>
+  <si>
+    <t>13:09</t>
+  </si>
+  <si>
+    <t>15:34</t>
+  </si>
+  <si>
+    <t>20:00</t>
+  </si>
+  <si>
+    <t>19:00</t>
+  </si>
+  <si>
+    <t>VN-A639</t>
+  </si>
+  <si>
+    <t>10:31</t>
+  </si>
+  <si>
+    <t>17:26</t>
   </si>
   <si>
     <t>19:11</t>
   </si>
   <si>
-    <t>19:20</t>
-  </si>
-  <si>
-    <t>21:25</t>
-  </si>
-  <si>
-    <t>VN-A529</t>
-  </si>
-  <si>
-    <t>CGK</t>
-  </si>
-  <si>
-    <t>12:30</t>
-  </si>
-  <si>
-    <t>12:34</t>
-  </si>
-  <si>
-    <t>16:40</t>
-  </si>
-  <si>
-    <t>16:44</t>
-  </si>
-  <si>
-    <t>BLR</t>
-  </si>
-  <si>
-    <t>22:35</t>
-  </si>
-  <si>
-    <t>06:00</t>
-  </si>
-  <si>
-    <t>VN-A530</t>
-  </si>
-  <si>
-    <t>VCA</t>
-  </si>
-  <si>
-    <t>06:45</t>
-  </si>
-  <si>
-    <t>08:55</t>
-  </si>
-  <si>
-    <t>11:53</t>
-  </si>
-  <si>
-    <t>13:50</t>
-  </si>
-  <si>
-    <t>13:58</t>
-  </si>
-  <si>
-    <t>15:45</t>
-  </si>
-  <si>
-    <t>15:48</t>
-  </si>
-  <si>
-    <t>CXR</t>
-  </si>
-  <si>
-    <t>16:20</t>
-  </si>
-  <si>
-    <t>18:10</t>
-  </si>
-  <si>
-    <t>18:21</t>
-  </si>
-  <si>
-    <t>18:45</t>
-  </si>
-  <si>
-    <t>20:35</t>
-  </si>
-  <si>
-    <t>VN-A532</t>
-  </si>
-  <si>
-    <t>15:30</t>
-  </si>
-  <si>
-    <t>15:04</t>
-  </si>
-  <si>
-    <t>16:30</t>
-  </si>
-  <si>
-    <t>20:32</t>
-  </si>
-  <si>
-    <t>VN-A534</t>
-  </si>
-  <si>
-    <t>BMV</t>
-  </si>
-  <si>
-    <t>06:30</t>
-  </si>
-  <si>
-    <t>07:30</t>
-  </si>
-  <si>
-    <t>07:12</t>
-  </si>
-  <si>
-    <t>08:00</t>
-  </si>
-  <si>
-    <t>VN-A535</t>
-  </si>
-  <si>
-    <t>09:20</t>
-  </si>
-  <si>
-    <t>12:20</t>
-  </si>
-  <si>
-    <t>14:30</t>
-  </si>
-  <si>
-    <t>16:36</t>
-  </si>
-  <si>
-    <t>14:50</t>
-  </si>
-  <si>
-    <t>17:20</t>
+    <t>22:20</t>
+  </si>
+  <si>
+    <t>VN-A640</t>
+  </si>
+  <si>
+    <t>09:47</t>
+  </si>
+  <si>
+    <t>12:10</t>
+  </si>
+  <si>
+    <t>12:16</t>
+  </si>
+  <si>
+    <t>SAI</t>
+  </si>
+  <si>
+    <t>00:55</t>
+  </si>
+  <si>
+    <t>VN-A642</t>
+  </si>
+  <si>
+    <t>08:10</t>
+  </si>
+  <si>
+    <t>10:29</t>
+  </si>
+  <si>
+    <t>13:36</t>
+  </si>
+  <si>
+    <t>17:50</t>
+  </si>
+  <si>
+    <t>18:16</t>
   </si>
   <si>
     <t>19:30</t>
   </si>
   <si>
-    <t>01:20</t>
-  </si>
-  <si>
-    <t>VN-A536</t>
-  </si>
-  <si>
-    <t>09:10</t>
-  </si>
-  <si>
-    <t>10:40</t>
-  </si>
-  <si>
-    <t>10:49</t>
-  </si>
-  <si>
-    <t>12:57</t>
-  </si>
-  <si>
-    <t>13:15</t>
-  </si>
-  <si>
-    <t>14:46</t>
-  </si>
-  <si>
-    <t>DLI</t>
-  </si>
-  <si>
-    <t>15:40</t>
-  </si>
-  <si>
-    <t>17:47</t>
-  </si>
-  <si>
-    <t>18:00</t>
-  </si>
-  <si>
-    <t>19:50</t>
-  </si>
-  <si>
-    <t>23:25</t>
-  </si>
-  <si>
-    <t>01:35</t>
-  </si>
-  <si>
-    <t>VN-A542</t>
-  </si>
-  <si>
-    <t>10:25</t>
-  </si>
-  <si>
-    <t>16:25</t>
-  </si>
-  <si>
-    <t>11:20</t>
-  </si>
-  <si>
-    <t>21:35</t>
-  </si>
-  <si>
-    <t>18:05</t>
-  </si>
-  <si>
-    <t>22:10</t>
-  </si>
-  <si>
-    <t>00:30</t>
-  </si>
-  <si>
-    <t>VN-A543</t>
-  </si>
-  <si>
-    <t>05:30</t>
-  </si>
-  <si>
-    <t>07:28</t>
-  </si>
-  <si>
-    <t>10:00</t>
-  </si>
-  <si>
-    <t>10:14</t>
-  </si>
-  <si>
-    <t>HUI</t>
-  </si>
-  <si>
-    <t>10:35</t>
-  </si>
-  <si>
-    <t>12:00</t>
-  </si>
-  <si>
-    <t>12:17</t>
-  </si>
-  <si>
-    <t>13:55</t>
-  </si>
-  <si>
-    <t>14:21</t>
-  </si>
-  <si>
-    <t>15:10</t>
-  </si>
-  <si>
-    <t>17:05</t>
-  </si>
-  <si>
-    <t>18:30</t>
-  </si>
-  <si>
-    <t>20:40</t>
-  </si>
-  <si>
-    <t>VN-A544</t>
-  </si>
-  <si>
-    <t>UIH</t>
-  </si>
-  <si>
-    <t>08:25</t>
-  </si>
-  <si>
-    <t>09:24</t>
-  </si>
-  <si>
-    <t>10:05</t>
-  </si>
-  <si>
-    <t>11:07</t>
-  </si>
-  <si>
-    <t>11:50</t>
-  </si>
-  <si>
-    <t>12:47</t>
-  </si>
-  <si>
-    <t>15:05</t>
-  </si>
-  <si>
-    <t>15:33</t>
-  </si>
-  <si>
-    <t>18:17</t>
-  </si>
-  <si>
-    <t>18:20</t>
-  </si>
-  <si>
-    <t>20:55</t>
-  </si>
-  <si>
-    <t>22:45</t>
-  </si>
-  <si>
-    <t>NGO</t>
-  </si>
-  <si>
-    <t>VN-A549</t>
-  </si>
-  <si>
-    <t>10:45</t>
-  </si>
-  <si>
-    <t>12:05</t>
-  </si>
-  <si>
-    <t>12:11</t>
-  </si>
-  <si>
-    <t>12:40</t>
-  </si>
-  <si>
-    <t>14:14</t>
-  </si>
-  <si>
-    <t>VII</t>
-  </si>
-  <si>
-    <t>18:40</t>
-  </si>
-  <si>
-    <t>19:10</t>
-  </si>
-  <si>
-    <t>21:00</t>
-  </si>
-  <si>
-    <t>22:50</t>
-  </si>
-  <si>
-    <t>VN-A551</t>
-  </si>
-  <si>
-    <t>12:15</t>
-  </si>
-  <si>
-    <t>12:12</t>
-  </si>
-  <si>
-    <t>12:45</t>
-  </si>
-  <si>
-    <t>14:20</t>
-  </si>
-  <si>
-    <t>14:47</t>
-  </si>
-  <si>
-    <t>15:00</t>
-  </si>
-  <si>
-    <t>17:10</t>
-  </si>
-  <si>
-    <t>17:55</t>
-  </si>
-  <si>
-    <t>18:55</t>
-  </si>
-  <si>
-    <t>19:25</t>
-  </si>
-  <si>
-    <t>20:25</t>
-  </si>
-  <si>
-    <t>21:10</t>
-  </si>
-  <si>
-    <t>22:30</t>
-  </si>
-  <si>
-    <t>21:40</t>
-  </si>
-  <si>
-    <t>23:00</t>
-  </si>
-  <si>
-    <t>00:20</t>
-  </si>
-  <si>
-    <t>VN-A552</t>
-  </si>
-  <si>
-    <t>KUL</t>
-  </si>
-  <si>
-    <t>12:35</t>
-  </si>
-  <si>
-    <t>12:39</t>
-  </si>
-  <si>
-    <t>14:27</t>
-  </si>
-  <si>
-    <t>HKG</t>
-  </si>
-  <si>
-    <t>21:45</t>
-  </si>
-  <si>
-    <t>VN-A553</t>
-  </si>
-  <si>
-    <t>VVO</t>
-  </si>
-  <si>
-    <t>06:20</t>
-  </si>
-  <si>
-    <t>09:07</t>
-  </si>
-  <si>
-    <t>11:45</t>
-  </si>
-  <si>
-    <t>14:07</t>
-  </si>
-  <si>
-    <t>14:40</t>
-  </si>
-  <si>
-    <t>18:47</t>
-  </si>
-  <si>
-    <t>21:50</t>
-  </si>
-  <si>
-    <t>VN-A554</t>
-  </si>
-  <si>
-    <t>PXU</t>
-  </si>
-  <si>
-    <t>06:40</t>
-  </si>
-  <si>
-    <t>07:27</t>
-  </si>
-  <si>
-    <t>08:20</t>
-  </si>
-  <si>
-    <t>11:55</t>
-  </si>
-  <si>
-    <t>14:51</t>
-  </si>
-  <si>
-    <t>15:25</t>
-  </si>
-  <si>
-    <t>16:22</t>
-  </si>
-  <si>
-    <t>16:00</t>
-  </si>
-  <si>
-    <t>17:38</t>
-  </si>
-  <si>
-    <t>THD</t>
-  </si>
-  <si>
-    <t>20:50</t>
-  </si>
-  <si>
-    <t>21:05</t>
-  </si>
-  <si>
-    <t>23:10</t>
-  </si>
-  <si>
-    <t>C</t>
-  </si>
-  <si>
-    <t>VN-A575</t>
-  </si>
-  <si>
-    <t>BQS</t>
-  </si>
-  <si>
-    <t>13:45</t>
-  </si>
-  <si>
-    <t>13:37</t>
-  </si>
-  <si>
-    <t>14:15</t>
-  </si>
-  <si>
-    <t>16:02</t>
-  </si>
-  <si>
-    <t>KHV</t>
-  </si>
-  <si>
-    <t>01:05</t>
-  </si>
-  <si>
-    <t>09:50</t>
-  </si>
-  <si>
-    <t>122A</t>
-  </si>
-  <si>
-    <t>VN-A578</t>
-  </si>
-  <si>
-    <t>09:05</t>
-  </si>
-  <si>
-    <t>09:09</t>
-  </si>
-  <si>
-    <t>10:20</t>
-  </si>
-  <si>
-    <t>12:51</t>
-  </si>
-  <si>
-    <t>17:51</t>
-  </si>
-  <si>
-    <t>17:40</t>
-  </si>
-  <si>
-    <t>20:00</t>
-  </si>
-  <si>
-    <t>00:50</t>
-  </si>
-  <si>
-    <t>23:30</t>
-  </si>
-  <si>
-    <t>VN-A580</t>
-  </si>
-  <si>
-    <t>10:10</t>
-  </si>
-  <si>
-    <t>10:07</t>
-  </si>
-  <si>
-    <t>11:47</t>
-  </si>
-  <si>
-    <t>16:49</t>
-  </si>
-  <si>
-    <t>NOZ</t>
-  </si>
-  <si>
-    <t>23:05</t>
-  </si>
-  <si>
-    <t>06:15</t>
-  </si>
-  <si>
-    <t>VN-A607</t>
-  </si>
-  <si>
-    <t>12:55</t>
-  </si>
-  <si>
-    <t>12:54</t>
-  </si>
-  <si>
-    <t>16:50</t>
-  </si>
-  <si>
-    <t>VN-A629</t>
-  </si>
-  <si>
-    <t>13:24</t>
-  </si>
-  <si>
-    <t>VTE</t>
-  </si>
-  <si>
-    <t>18:25</t>
-  </si>
-  <si>
-    <t>18:33</t>
-  </si>
-  <si>
-    <t>MNL</t>
-  </si>
-  <si>
-    <t>22:25</t>
-  </si>
-  <si>
-    <t>02:10</t>
-  </si>
-  <si>
-    <t>03:00</t>
-  </si>
-  <si>
-    <t>04:35</t>
-  </si>
-  <si>
-    <t>VN-A630</t>
-  </si>
-  <si>
-    <t>07:00</t>
-  </si>
-  <si>
-    <t>10:03</t>
-  </si>
-  <si>
-    <t>VN-A632</t>
-  </si>
-  <si>
-    <t>07:40</t>
-  </si>
-  <si>
-    <t>07:48</t>
-  </si>
-  <si>
-    <t>10:32</t>
-  </si>
-  <si>
-    <t>BKK</t>
-  </si>
-  <si>
-    <t>15:03</t>
-  </si>
-  <si>
-    <t>17:49</t>
-  </si>
-  <si>
-    <t>VDH</t>
-  </si>
-  <si>
-    <t>21:20</t>
-  </si>
-  <si>
-    <t>20:45</t>
-  </si>
-  <si>
-    <t>VN-A633</t>
-  </si>
-  <si>
-    <t>13:04</t>
-  </si>
-  <si>
-    <t>18:15</t>
-  </si>
-  <si>
-    <t>18:09</t>
-  </si>
-  <si>
-    <t>VN-A634</t>
-  </si>
-  <si>
-    <t>HKT</t>
-  </si>
-  <si>
-    <t>10:55</t>
-  </si>
-  <si>
-    <t>11:16</t>
-  </si>
-  <si>
-    <t>14:57</t>
-  </si>
-  <si>
-    <t>19:40</t>
-  </si>
-  <si>
-    <t>21:30</t>
-  </si>
-  <si>
-    <t>VN-A636</t>
-  </si>
-  <si>
-    <t>07:15</t>
-  </si>
-  <si>
-    <t>09:55</t>
-  </si>
-  <si>
-    <t>09:34</t>
-  </si>
-  <si>
-    <t>16:10</t>
-  </si>
-  <si>
-    <t>17:44</t>
-  </si>
-  <si>
-    <t>20:10</t>
-  </si>
-  <si>
-    <t>VN-A637</t>
-  </si>
-  <si>
-    <t>05:00</t>
-  </si>
-  <si>
-    <t>06:50</t>
-  </si>
-  <si>
-    <t>06:48</t>
-  </si>
-  <si>
-    <t>07:20</t>
-  </si>
-  <si>
-    <t>09:15</t>
-  </si>
-  <si>
-    <t>13:09</t>
-  </si>
-  <si>
-    <t>15:34</t>
-  </si>
-  <si>
-    <t>19:00</t>
-  </si>
-  <si>
-    <t>VN-A639</t>
-  </si>
-  <si>
-    <t>10:31</t>
-  </si>
-  <si>
-    <t>17:26</t>
-  </si>
-  <si>
-    <t>22:20</t>
-  </si>
-  <si>
-    <t>VN-A640</t>
-  </si>
-  <si>
-    <t>09:47</t>
-  </si>
-  <si>
-    <t>12:10</t>
-  </si>
-  <si>
-    <t>12:16</t>
-  </si>
-  <si>
-    <t>SAI</t>
-  </si>
-  <si>
-    <t>00:55</t>
-  </si>
-  <si>
-    <t>VN-A642</t>
-  </si>
-  <si>
-    <t>08:10</t>
-  </si>
-  <si>
-    <t>10:29</t>
-  </si>
-  <si>
-    <t>13:36</t>
-  </si>
-  <si>
-    <t>17:50</t>
-  </si>
-  <si>
-    <t>18:22</t>
-  </si>
-  <si>
     <t>VN-A644</t>
   </si>
   <si>
@@ -1154,6 +1166,9 @@
     <t>12:29</t>
   </si>
   <si>
+    <t>18:39</t>
+  </si>
+  <si>
     <t>21:15</t>
   </si>
   <si>
@@ -1169,6 +1184,9 @@
     <t>14:09</t>
   </si>
   <si>
+    <t>18:59</t>
+  </si>
+  <si>
     <t>PUS</t>
   </si>
   <si>
@@ -1241,9 +1259,6 @@
     <t>17:36</t>
   </si>
   <si>
-    <t>18:42</t>
-  </si>
-  <si>
     <t>05:35</t>
   </si>
   <si>
@@ -1289,6 +1304,9 @@
     <t>16:32</t>
   </si>
   <si>
+    <t>19:13</t>
+  </si>
+  <si>
     <t>CAN</t>
   </si>
   <si>
@@ -1397,6 +1415,9 @@
     <t>14:43</t>
   </si>
   <si>
+    <t>18:44</t>
+  </si>
+  <si>
     <t>VN-A676</t>
   </si>
   <si>
@@ -1421,24 +1442,27 @@
     <t>01:15</t>
   </si>
   <si>
+    <t>01:45</t>
+  </si>
+  <si>
     <t>02:20</t>
   </si>
   <si>
     <t>04:50</t>
   </si>
   <si>
+    <t>02:30</t>
+  </si>
+  <si>
     <t>VN-A677</t>
   </si>
   <si>
-    <t>19:07</t>
+    <t>19:05</t>
   </si>
   <si>
     <t>01:30</t>
   </si>
   <si>
-    <t>02:30</t>
-  </si>
-  <si>
     <t>04:10</t>
   </si>
   <si>
@@ -1451,9 +1475,6 @@
     <t>18:27</t>
   </si>
   <si>
-    <t>19:05</t>
-  </si>
-  <si>
     <t>VN-A684</t>
   </si>
   <si>
@@ -1535,6 +1556,9 @@
     <t>KZN</t>
   </si>
   <si>
+    <t>16:01</t>
+  </si>
+  <si>
     <t>VN-A817</t>
   </si>
   <si>
@@ -1550,7 +1574,7 @@
     <t>Total Record(s): 316</t>
   </si>
   <si>
-    <t xml:space="preserve">Generated on  Oct 23, 2026 17:14</t>
+    <t xml:space="preserve">Generated on  Oct 23, 2026 17:40</t>
   </si>
   <si>
     <t>Page 1 of 1</t>
@@ -5283,7 +5307,9 @@
       </c>
       <c r="K107" s="7"/>
       <c r="L107" s="7"/>
-      <c r="M107" s="7"/>
+      <c t="s" r="M107" s="7">
+        <v>225</v>
+      </c>
     </row>
     <row r="108" ht="14.25" customHeight="1">
       <c t="s" r="A108" s="6">
@@ -5306,20 +5332,20 @@
         <v>17</v>
       </c>
       <c t="s" r="H108" s="8">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c t="s" r="I108" s="7">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c t="s" r="J108" s="7">
         <v>88</v>
       </c>
       <c t="s" r="K108" s="7">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="L108" s="7"/>
       <c t="s" r="M108" s="7">
-        <v>228</v>
+        <v>229</v>
       </c>
     </row>
     <row r="109" ht="14.25" customHeight="1">
@@ -5340,16 +5366,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G109" s="8">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c t="s" r="H109" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I109" s="7">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c t="s" r="J109" s="7">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c t="s" r="K109" s="7">
         <v>185</v>
@@ -5386,7 +5412,7 @@
       </c>
       <c r="D111" s="7"/>
       <c t="s" r="E111" s="7">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="F111" s="7">
         <v>321</v>
@@ -5401,12 +5427,12 @@
         <v>182</v>
       </c>
       <c t="s" r="J111" s="7">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="K111" s="7"/>
       <c r="L111" s="7"/>
       <c t="s" r="M111" s="7">
-        <v>232</v>
+        <v>233</v>
       </c>
     </row>
     <row r="112" ht="14.25" customHeight="1">
@@ -5421,7 +5447,7 @@
       </c>
       <c r="D112" s="7"/>
       <c t="s" r="E112" s="7">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="F112" s="7">
         <v>321</v>
@@ -5433,15 +5459,15 @@
         <v>48</v>
       </c>
       <c t="s" r="I112" s="7">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c t="s" r="J112" s="7">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="K112" s="7"/>
       <c r="L112" s="7"/>
       <c t="s" r="M112" s="7">
-        <v>235</v>
+        <v>236</v>
       </c>
     </row>
     <row r="113" ht="14.25" customHeight="1">
@@ -5456,7 +5482,7 @@
       </c>
       <c r="D113" s="7"/>
       <c t="s" r="E113" s="7">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="F113" s="7">
         <v>321</v>
@@ -5468,10 +5494,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I113" s="7">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c t="s" r="J113" s="7">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="K113" s="7"/>
       <c r="L113" s="7"/>
@@ -5491,7 +5517,7 @@
       </c>
       <c r="D114" s="7"/>
       <c t="s" r="E114" s="7">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="F114" s="7">
         <v>321</v>
@@ -5503,10 +5529,10 @@
         <v>153</v>
       </c>
       <c t="s" r="I114" s="7">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c t="s" r="J114" s="7">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="K114" s="7"/>
       <c r="L114" s="7"/>
@@ -5524,7 +5550,7 @@
       </c>
       <c r="D115" s="7"/>
       <c t="s" r="E115" s="7">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="F115" s="7">
         <v>321</v>
@@ -5536,10 +5562,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I115" s="7">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c t="s" r="J115" s="7">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="K115" s="7"/>
       <c r="L115" s="7"/>
@@ -5557,7 +5583,7 @@
       </c>
       <c r="D116" s="7"/>
       <c t="s" r="E116" s="7">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="F116" s="7">
         <v>321</v>
@@ -5569,17 +5595,17 @@
         <v>110</v>
       </c>
       <c t="s" r="I116" s="7">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c t="s" r="J116" s="7">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c t="s" r="K116" s="7">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="L116" s="7"/>
       <c t="s" r="M116" s="7">
-        <v>245</v>
+        <v>246</v>
       </c>
     </row>
     <row r="117" ht="14.25" customHeight="1">
@@ -5594,7 +5620,7 @@
       </c>
       <c r="D117" s="7"/>
       <c t="s" r="E117" s="7">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="F117" s="7">
         <v>321</v>
@@ -5606,10 +5632,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I117" s="7">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c t="s" r="J117" s="7">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c t="s" r="K117" s="7">
         <v>31</v>
@@ -5646,7 +5672,7 @@
       </c>
       <c r="D119" s="7"/>
       <c t="s" r="E119" s="7">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="F119" s="7">
         <v>321</v>
@@ -5655,18 +5681,18 @@
         <v>17</v>
       </c>
       <c t="s" r="H119" s="8">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c t="s" r="I119" s="7">
         <v>49</v>
       </c>
       <c t="s" r="J119" s="7">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="K119" s="7"/>
       <c r="L119" s="7"/>
       <c t="s" r="M119" s="7">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="120" ht="15" customHeight="1">
@@ -5681,13 +5707,13 @@
       </c>
       <c r="D120" s="7"/>
       <c t="s" r="E120" s="7">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="F120" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G120" s="8">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c t="s" r="H120" s="8">
         <v>17</v>
@@ -5696,12 +5722,12 @@
         <v>38</v>
       </c>
       <c t="s" r="J120" s="7">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="K120" s="7"/>
       <c r="L120" s="7"/>
       <c t="s" r="M120" s="7">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="121" ht="14.25" customHeight="1">
@@ -5716,7 +5742,7 @@
       </c>
       <c r="D121" s="7"/>
       <c t="s" r="E121" s="7">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="F121" s="7">
         <v>321</v>
@@ -5725,7 +5751,7 @@
         <v>17</v>
       </c>
       <c t="s" r="H121" s="8">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c t="s" r="I121" s="7">
         <v>175</v>
@@ -5751,13 +5777,13 @@
       </c>
       <c r="D122" s="7"/>
       <c t="s" r="E122" s="7">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="F122" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G122" s="8">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c t="s" r="H122" s="8">
         <v>17</v>
@@ -5766,7 +5792,7 @@
         <v>53</v>
       </c>
       <c t="s" r="J122" s="7">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="K122" s="7"/>
       <c r="L122" s="7"/>
@@ -5799,19 +5825,19 @@
       </c>
       <c r="D124" s="7"/>
       <c t="s" r="E124" s="7">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="F124" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G124" s="8">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c t="s" r="H124" s="8">
         <v>48</v>
       </c>
       <c t="s" r="I124" s="7">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c t="s" r="J124" s="7">
         <v>93</v>
@@ -5819,7 +5845,7 @@
       <c r="K124" s="7"/>
       <c r="L124" s="7"/>
       <c t="s" r="M124" s="7">
-        <v>257</v>
+        <v>258</v>
       </c>
     </row>
     <row r="125" ht="15" customHeight="1">
@@ -5834,7 +5860,7 @@
       </c>
       <c r="D125" s="7"/>
       <c t="s" r="E125" s="7">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="F125" s="7">
         <v>321</v>
@@ -5854,7 +5880,7 @@
       <c r="K125" s="7"/>
       <c r="L125" s="7"/>
       <c t="s" r="M125" s="7">
-        <v>258</v>
+        <v>259</v>
       </c>
     </row>
     <row r="126" ht="14.25" customHeight="1">
@@ -5869,7 +5895,7 @@
       </c>
       <c r="D126" s="7"/>
       <c t="s" r="E126" s="7">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="F126" s="7">
         <v>321</v>
@@ -5889,7 +5915,7 @@
       <c r="K126" s="7"/>
       <c r="L126" s="7"/>
       <c t="s" r="M126" s="7">
-        <v>259</v>
+        <v>260</v>
       </c>
     </row>
     <row r="127" ht="14.25" customHeight="1">
@@ -5904,7 +5930,7 @@
       </c>
       <c r="D127" s="7"/>
       <c t="s" r="E127" s="7">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="F127" s="7">
         <v>321</v>
@@ -5913,10 +5939,10 @@
         <v>17</v>
       </c>
       <c t="s" r="H127" s="8">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c t="s" r="I127" s="7">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c t="s" r="J127" s="7">
         <v>150</v>
@@ -5939,13 +5965,13 @@
       </c>
       <c r="D128" s="7"/>
       <c t="s" r="E128" s="7">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="F128" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G128" s="8">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c t="s" r="H128" s="8">
         <v>17</v>
@@ -5959,7 +5985,7 @@
       <c r="K128" s="7"/>
       <c r="L128" s="7"/>
       <c t="s" r="M128" s="7">
-        <v>261</v>
+        <v>262</v>
       </c>
     </row>
     <row r="129" ht="14.25" customHeight="1">
@@ -5974,7 +6000,7 @@
       </c>
       <c r="D129" s="7"/>
       <c t="s" r="E129" s="7">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="F129" s="7">
         <v>321</v>
@@ -5989,7 +6015,7 @@
         <v>87</v>
       </c>
       <c t="s" r="J129" s="7">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="K129" s="7"/>
       <c r="L129" s="7"/>
@@ -6022,7 +6048,7 @@
       </c>
       <c r="D131" s="7"/>
       <c t="s" r="E131" s="7">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="F131" s="7">
         <v>321</v>
@@ -6031,10 +6057,10 @@
         <v>17</v>
       </c>
       <c t="s" r="H131" s="8">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c t="s" r="I131" s="7">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c t="s" r="J131" s="7">
         <v>107</v>
@@ -6042,7 +6068,7 @@
       <c r="K131" s="7"/>
       <c r="L131" s="7"/>
       <c t="s" r="M131" s="7">
-        <v>266</v>
+        <v>267</v>
       </c>
     </row>
     <row r="132" ht="14.25" customHeight="1">
@@ -6057,19 +6083,19 @@
       </c>
       <c r="D132" s="7"/>
       <c t="s" r="E132" s="7">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="F132" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G132" s="8">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c t="s" r="H132" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I132" s="7">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c t="s" r="J132" s="7">
         <v>49</v>
@@ -6092,7 +6118,7 @@
       </c>
       <c r="D133" s="7"/>
       <c t="s" r="E133" s="7">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="F133" s="7">
         <v>321</v>
@@ -6112,7 +6138,7 @@
       <c r="K133" s="7"/>
       <c r="L133" s="7"/>
       <c t="s" r="M133" s="7">
-        <v>268</v>
+        <v>269</v>
       </c>
     </row>
     <row r="134" ht="14.25" customHeight="1">
@@ -6127,7 +6153,7 @@
       </c>
       <c r="D134" s="7"/>
       <c t="s" r="E134" s="7">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="F134" s="7">
         <v>321</v>
@@ -6139,7 +6165,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I134" s="7">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c t="s" r="J134" s="7">
         <v>40</v>
@@ -6147,7 +6173,7 @@
       <c r="K134" s="7"/>
       <c r="L134" s="7"/>
       <c t="s" r="M134" s="7">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="135" ht="15" customHeight="1">
@@ -6162,7 +6188,7 @@
       </c>
       <c r="D135" s="7"/>
       <c t="s" r="E135" s="7">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="F135" s="7">
         <v>321</v>
@@ -6180,11 +6206,11 @@
         <v>148</v>
       </c>
       <c t="s" r="K135" s="7">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="L135" s="7"/>
       <c t="s" r="M135" s="7">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="136" ht="14.25" customHeight="1">
@@ -6199,7 +6225,7 @@
       </c>
       <c r="D136" s="7"/>
       <c t="s" r="E136" s="7">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="F136" s="7">
         <v>321</v>
@@ -6211,7 +6237,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I136" s="7">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c t="s" r="J136" s="7">
         <v>23</v>
@@ -6221,7 +6247,7 @@
       </c>
       <c r="L136" s="7"/>
       <c t="s" r="M136" s="7">
-        <v>273</v>
+        <v>274</v>
       </c>
     </row>
     <row r="137" ht="14.25" customHeight="1">
@@ -6236,7 +6262,7 @@
       </c>
       <c r="D137" s="7"/>
       <c t="s" r="E137" s="7">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="F137" s="7">
         <v>321</v>
@@ -6245,7 +6271,7 @@
         <v>17</v>
       </c>
       <c t="s" r="H137" s="8">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c t="s" r="I137" s="7">
         <v>142</v>
@@ -6273,13 +6299,13 @@
       </c>
       <c r="D138" s="7"/>
       <c t="s" r="E138" s="7">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="F138" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G138" s="8">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c t="s" r="H138" s="8">
         <v>17</v>
@@ -6288,14 +6314,14 @@
         <v>119</v>
       </c>
       <c t="s" r="J138" s="7">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c t="s" r="K138" s="7">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="L138" s="7"/>
       <c t="s" r="M138" s="7">
-        <v>277</v>
+        <v>278</v>
       </c>
     </row>
     <row r="139" ht="14.25" customHeight="1">
@@ -6321,17 +6347,17 @@
         <v>7615</v>
       </c>
       <c t="s" r="C140" s="7">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="D140" s="7"/>
       <c t="s" r="E140" s="7">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="F140" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G140" s="8">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c t="s" r="H140" s="8">
         <v>48</v>
@@ -6340,12 +6366,12 @@
         <v>208</v>
       </c>
       <c t="s" r="J140" s="7">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="K140" s="7"/>
       <c r="L140" s="7"/>
       <c t="s" r="M140" s="7">
-        <v>282</v>
+        <v>283</v>
       </c>
     </row>
     <row r="141" ht="14.25" customHeight="1">
@@ -6356,11 +6382,11 @@
         <v>7615</v>
       </c>
       <c t="s" r="C141" s="7">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="D141" s="7"/>
       <c t="s" r="E141" s="7">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="F141" s="7">
         <v>321</v>
@@ -6372,15 +6398,15 @@
         <v>141</v>
       </c>
       <c t="s" r="I141" s="7">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c t="s" r="J141" s="7">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="K141" s="7"/>
       <c r="L141" s="7"/>
       <c t="s" r="M141" s="7">
-        <v>284</v>
+        <v>285</v>
       </c>
     </row>
     <row r="142" ht="14.25" customHeight="1">
@@ -6391,11 +6417,11 @@
         <v>7706</v>
       </c>
       <c t="s" r="C142" s="7">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="D142" s="7"/>
       <c t="s" r="E142" s="7">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="F142" s="7">
         <v>321</v>
@@ -6424,11 +6450,11 @@
         <v>7706</v>
       </c>
       <c t="s" r="C143" s="7">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="D143" s="7"/>
       <c t="s" r="E143" s="7">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="F143" s="7">
         <v>321</v>
@@ -6437,13 +6463,13 @@
         <v>48</v>
       </c>
       <c t="s" r="H143" s="8">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c t="s" r="I143" s="7">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c t="s" r="J143" s="7">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="K143" s="7"/>
       <c r="L143" s="7"/>
@@ -6469,14 +6495,14 @@
         <v>13</v>
       </c>
       <c t="s" r="B145" s="7">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c t="s" r="C145" s="7">
         <v>14</v>
       </c>
       <c r="D145" s="7"/>
       <c t="s" r="E145" s="7">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="F145" s="7">
         <v>321</v>
@@ -6491,12 +6517,12 @@
         <v>34</v>
       </c>
       <c t="s" r="J145" s="7">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="K145" s="7"/>
       <c r="L145" s="7"/>
       <c t="s" r="M145" s="7">
-        <v>291</v>
+        <v>292</v>
       </c>
     </row>
     <row r="146" ht="14.25" customHeight="1">
@@ -6511,7 +6537,7 @@
       </c>
       <c r="D146" s="7"/>
       <c t="s" r="E146" s="7">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="F146" s="7">
         <v>321</v>
@@ -6523,7 +6549,7 @@
         <v>133</v>
       </c>
       <c t="s" r="I146" s="7">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c t="s" r="J146" s="7">
         <v>125</v>
@@ -6531,7 +6557,7 @@
       <c r="K146" s="7"/>
       <c r="L146" s="7"/>
       <c t="s" r="M146" s="7">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="147" ht="14.25" customHeight="1">
@@ -6546,7 +6572,7 @@
       </c>
       <c r="D147" s="7"/>
       <c t="s" r="E147" s="7">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="F147" s="7">
         <v>321</v>
@@ -6581,7 +6607,7 @@
       </c>
       <c r="D148" s="7"/>
       <c t="s" r="E148" s="7">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="F148" s="7">
         <v>321</v>
@@ -6596,12 +6622,12 @@
         <v>22</v>
       </c>
       <c t="s" r="J148" s="7">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="K148" s="7"/>
       <c r="L148" s="7"/>
       <c t="s" r="M148" s="7">
-        <v>294</v>
+        <v>295</v>
       </c>
     </row>
     <row r="149" ht="14.25" customHeight="1">
@@ -6616,7 +6642,7 @@
       </c>
       <c r="D149" s="7"/>
       <c t="s" r="E149" s="7">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="F149" s="7">
         <v>321</v>
@@ -6628,10 +6654,10 @@
         <v>48</v>
       </c>
       <c t="s" r="I149" s="7">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c t="s" r="J149" s="7">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="K149" s="7"/>
       <c r="L149" s="7"/>
@@ -6649,7 +6675,7 @@
       </c>
       <c r="D150" s="7"/>
       <c t="s" r="E150" s="7">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="F150" s="7">
         <v>321</v>
@@ -6667,11 +6693,11 @@
         <v>146</v>
       </c>
       <c t="s" r="K150" s="7">
-        <v>296</v>
+        <v>242</v>
       </c>
       <c r="L150" s="7"/>
       <c t="s" r="M150" s="7">
-        <v>187</v>
+        <v>297</v>
       </c>
     </row>
     <row r="151" ht="14.25" customHeight="1">
@@ -6686,7 +6712,7 @@
       </c>
       <c r="D151" s="7"/>
       <c t="s" r="E151" s="7">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="F151" s="7">
         <v>321</v>
@@ -6701,10 +6727,10 @@
         <v>89</v>
       </c>
       <c t="s" r="J151" s="7">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c t="s" r="K151" s="7">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="L151" s="7"/>
       <c t="s" r="M151" s="7">
@@ -6738,7 +6764,7 @@
       </c>
       <c r="D153" s="7"/>
       <c t="s" r="E153" s="7">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="F153" s="7">
         <v>321</v>
@@ -6753,12 +6779,12 @@
         <v>168</v>
       </c>
       <c t="s" r="J153" s="7">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="K153" s="7"/>
       <c r="L153" s="7"/>
       <c t="s" r="M153" s="7">
-        <v>301</v>
+        <v>302</v>
       </c>
     </row>
     <row r="154" ht="14.25" customHeight="1">
@@ -6773,7 +6799,7 @@
       </c>
       <c r="D154" s="7"/>
       <c t="s" r="E154" s="7">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="F154" s="7">
         <v>321</v>
@@ -6788,12 +6814,12 @@
         <v>79</v>
       </c>
       <c t="s" r="J154" s="7">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="K154" s="7"/>
       <c r="L154" s="7"/>
       <c t="s" r="M154" s="7">
-        <v>302</v>
+        <v>303</v>
       </c>
     </row>
     <row r="155" ht="15" customHeight="1">
@@ -6808,7 +6834,7 @@
       </c>
       <c r="D155" s="7"/>
       <c t="s" r="E155" s="7">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="F155" s="7">
         <v>321</v>
@@ -6839,11 +6865,11 @@
         <v>5068</v>
       </c>
       <c t="s" r="C156" s="7">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="D156" s="7"/>
       <c t="s" r="E156" s="7">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="F156" s="7">
         <v>321</v>
@@ -6863,7 +6889,7 @@
       <c r="K156" s="7"/>
       <c r="L156" s="7"/>
       <c t="s" r="M156" s="7">
-        <v>303</v>
+        <v>304</v>
       </c>
     </row>
     <row r="157" ht="14.25" customHeight="1">
@@ -6874,11 +6900,11 @@
         <v>5068</v>
       </c>
       <c t="s" r="C157" s="7">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="D157" s="7"/>
       <c t="s" r="E157" s="7">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="F157" s="7">
         <v>321</v>
@@ -6887,13 +6913,13 @@
         <v>48</v>
       </c>
       <c t="s" r="H157" s="8">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c t="s" r="I157" s="7">
         <v>74</v>
       </c>
       <c t="s" r="J157" s="7">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="K157" s="7"/>
       <c r="L157" s="7"/>
@@ -6907,17 +6933,17 @@
         <v>5069</v>
       </c>
       <c t="s" r="C158" s="7">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="D158" s="7"/>
       <c t="s" r="E158" s="7">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="F158" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G158" s="8">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c t="s" r="H158" s="8">
         <v>48</v>
@@ -6926,7 +6952,7 @@
         <v>33</v>
       </c>
       <c t="s" r="J158" s="7">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="K158" s="7"/>
       <c r="L158" s="7"/>
@@ -6959,7 +6985,7 @@
       </c>
       <c r="D160" s="7"/>
       <c t="s" r="E160" s="7">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="F160" s="7">
         <v>321</v>
@@ -6974,12 +7000,12 @@
         <v>91</v>
       </c>
       <c t="s" r="J160" s="7">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="K160" s="7"/>
       <c r="L160" s="7"/>
       <c t="s" r="M160" s="7">
-        <v>309</v>
+        <v>310</v>
       </c>
     </row>
     <row r="161" ht="14.25" customHeight="1">
@@ -6994,7 +7020,7 @@
       </c>
       <c r="D161" s="7"/>
       <c t="s" r="E161" s="7">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="F161" s="7">
         <v>321</v>
@@ -7009,12 +7035,12 @@
         <v>116</v>
       </c>
       <c t="s" r="J161" s="7">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="K161" s="7"/>
       <c r="L161" s="7"/>
       <c t="s" r="M161" s="7">
-        <v>310</v>
+        <v>311</v>
       </c>
     </row>
     <row r="162" ht="14.25" customHeight="1">
@@ -7029,7 +7055,7 @@
       </c>
       <c r="D162" s="7"/>
       <c t="s" r="E162" s="7">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="F162" s="7">
         <v>321</v>
@@ -7077,7 +7103,7 @@
       </c>
       <c r="D164" s="7"/>
       <c t="s" r="E164" s="7">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="F164" s="7">
         <v>321</v>
@@ -7086,7 +7112,7 @@
         <v>17</v>
       </c>
       <c t="s" r="H164" s="8">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c t="s" r="I164" s="7">
         <v>182</v>
@@ -7097,7 +7123,7 @@
       <c r="K164" s="7"/>
       <c r="L164" s="7"/>
       <c t="s" r="M164" s="7">
-        <v>312</v>
+        <v>313</v>
       </c>
     </row>
     <row r="165" ht="15" customHeight="1">
@@ -7112,13 +7138,13 @@
       </c>
       <c r="D165" s="7"/>
       <c t="s" r="E165" s="7">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="F165" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G165" s="8">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c t="s" r="H165" s="8">
         <v>17</v>
@@ -7132,7 +7158,7 @@
       <c r="K165" s="7"/>
       <c r="L165" s="7"/>
       <c t="s" r="M165" s="7">
-        <v>270</v>
+        <v>271</v>
       </c>
     </row>
     <row r="166" ht="14.25" customHeight="1">
@@ -7147,7 +7173,7 @@
       </c>
       <c r="D166" s="7"/>
       <c t="s" r="E166" s="7">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="F166" s="7">
         <v>321</v>
@@ -7156,18 +7182,18 @@
         <v>17</v>
       </c>
       <c t="s" r="H166" s="8">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c t="s" r="I166" s="7">
         <v>183</v>
       </c>
       <c t="s" r="J166" s="7">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="K166" s="7"/>
       <c r="L166" s="7"/>
       <c t="s" r="M166" s="7">
-        <v>315</v>
+        <v>316</v>
       </c>
     </row>
     <row r="167" ht="14.25" customHeight="1">
@@ -7182,22 +7208,22 @@
       </c>
       <c r="D167" s="7"/>
       <c t="s" r="E167" s="7">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="F167" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G167" s="8">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c t="s" r="H167" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I167" s="7">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c t="s" r="J167" s="7">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="K167" s="7"/>
       <c r="L167" s="7"/>
@@ -7215,7 +7241,7 @@
       </c>
       <c r="D168" s="7"/>
       <c t="s" r="E168" s="7">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="F168" s="7">
         <v>321</v>
@@ -7224,10 +7250,10 @@
         <v>17</v>
       </c>
       <c t="s" r="H168" s="8">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c t="s" r="I168" s="7">
-        <v>317</v>
+        <v>297</v>
       </c>
       <c t="s" r="J168" s="7">
         <v>318</v>
@@ -7248,13 +7274,13 @@
       </c>
       <c r="D169" s="7"/>
       <c t="s" r="E169" s="7">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="F169" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G169" s="8">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c t="s" r="H169" s="8">
         <v>17</v>
@@ -7396,7 +7422,7 @@
         <v>93</v>
       </c>
       <c t="s" r="J174" s="7">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="K174" s="7"/>
       <c r="L174" s="7"/>
@@ -7431,12 +7457,12 @@
         <v>79</v>
       </c>
       <c t="s" r="J175" s="7">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="K175" s="7"/>
       <c r="L175" s="7"/>
       <c t="s" r="M175" s="7">
-        <v>249</v>
+        <v>250</v>
       </c>
     </row>
     <row r="176" ht="14.25" customHeight="1">
@@ -7533,13 +7559,13 @@
         <v>331</v>
       </c>
       <c t="s" r="I178" s="7">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c t="s" r="J178" s="7">
-        <v>101</v>
+        <v>332</v>
       </c>
       <c t="s" r="K178" s="7">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="L178" s="7"/>
       <c t="s" r="M178" s="7">
@@ -7573,14 +7599,14 @@
         <v>87</v>
       </c>
       <c t="s" r="J179" s="7">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c t="s" r="K179" s="7">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="L179" s="7"/>
       <c t="s" r="M179" s="7">
-        <v>317</v>
+        <v>297</v>
       </c>
     </row>
     <row r="180" ht="15" customHeight="1">
@@ -7610,7 +7636,7 @@
       </c>
       <c r="D181" s="7"/>
       <c t="s" r="E181" s="7">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="F181" s="7">
         <v>321</v>
@@ -7630,7 +7656,7 @@
       <c r="K181" s="7"/>
       <c r="L181" s="7"/>
       <c t="s" r="M181" s="7">
-        <v>335</v>
+        <v>336</v>
       </c>
     </row>
     <row r="182" ht="14.25" customHeight="1">
@@ -7645,7 +7671,7 @@
       </c>
       <c r="D182" s="7"/>
       <c t="s" r="E182" s="7">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="F182" s="7">
         <v>321</v>
@@ -7660,12 +7686,12 @@
         <v>116</v>
       </c>
       <c t="s" r="J182" s="7">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="K182" s="7"/>
       <c r="L182" s="7"/>
       <c t="s" r="M182" s="7">
-        <v>337</v>
+        <v>338</v>
       </c>
     </row>
     <row r="183" ht="14.25" customHeight="1">
@@ -7680,7 +7706,7 @@
       </c>
       <c r="D183" s="7"/>
       <c t="s" r="E183" s="7">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="F183" s="7">
         <v>321</v>
@@ -7728,7 +7754,7 @@
       </c>
       <c r="D185" s="7"/>
       <c t="s" r="E185" s="7">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="F185" s="7">
         <v>321</v>
@@ -7737,18 +7763,18 @@
         <v>17</v>
       </c>
       <c t="s" r="H185" s="8">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c t="s" r="I185" s="7">
         <v>108</v>
       </c>
       <c t="s" r="J185" s="7">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="K185" s="7"/>
       <c r="L185" s="7"/>
       <c t="s" r="M185" s="7">
-        <v>341</v>
+        <v>342</v>
       </c>
     </row>
     <row r="186" ht="14.25" customHeight="1">
@@ -7763,19 +7789,19 @@
       </c>
       <c r="D186" s="7"/>
       <c t="s" r="E186" s="7">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="F186" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G186" s="8">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c t="s" r="H186" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I186" s="7">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c t="s" r="J186" s="7">
         <v>137</v>
@@ -7783,7 +7809,7 @@
       <c r="K186" s="7"/>
       <c r="L186" s="7"/>
       <c t="s" r="M186" s="7">
-        <v>342</v>
+        <v>343</v>
       </c>
     </row>
     <row r="187" ht="14.25" customHeight="1">
@@ -7798,7 +7824,7 @@
       </c>
       <c r="D187" s="7"/>
       <c t="s" r="E187" s="7">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="F187" s="7">
         <v>321</v>
@@ -7810,17 +7836,17 @@
         <v>48</v>
       </c>
       <c t="s" r="I187" s="7">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c t="s" r="J187" s="7">
         <v>198</v>
       </c>
       <c t="s" r="K187" s="7">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="L187" s="7"/>
       <c t="s" r="M187" s="7">
-        <v>337</v>
+        <v>338</v>
       </c>
     </row>
     <row r="188" ht="14.25" customHeight="1">
@@ -7835,7 +7861,7 @@
       </c>
       <c r="D188" s="7"/>
       <c t="s" r="E188" s="7">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="F188" s="7">
         <v>321</v>
@@ -7850,7 +7876,7 @@
         <v>25</v>
       </c>
       <c t="s" r="J188" s="7">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c t="s" r="K188" s="7">
         <v>145</v>
@@ -7872,7 +7898,7 @@
       </c>
       <c r="D189" s="7"/>
       <c t="s" r="E189" s="7">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="F189" s="7">
         <v>321</v>
@@ -7884,13 +7910,13 @@
         <v>48</v>
       </c>
       <c t="s" r="I189" s="7">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c t="s" r="J189" s="7">
         <v>121</v>
       </c>
       <c t="s" r="K189" s="7">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="L189" s="7"/>
       <c t="s" r="M189" s="7">
@@ -7924,7 +7950,7 @@
       </c>
       <c r="D191" s="7"/>
       <c t="s" r="E191" s="7">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="F191" s="7">
         <v>321</v>
@@ -7936,15 +7962,15 @@
         <v>83</v>
       </c>
       <c t="s" r="I191" s="7">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c t="s" r="J191" s="7">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="K191" s="7"/>
       <c r="L191" s="7"/>
       <c t="s" r="M191" s="7">
-        <v>348</v>
+        <v>349</v>
       </c>
     </row>
     <row r="192" ht="14.25" customHeight="1">
@@ -7959,7 +7985,7 @@
       </c>
       <c r="D192" s="7"/>
       <c t="s" r="E192" s="7">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="F192" s="7">
         <v>321</v>
@@ -7971,15 +7997,15 @@
         <v>174</v>
       </c>
       <c t="s" r="I192" s="7">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c t="s" r="J192" s="7">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="K192" s="7"/>
       <c r="L192" s="7"/>
       <c t="s" r="M192" s="7">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="193" ht="14.25" customHeight="1">
@@ -7994,7 +8020,7 @@
       </c>
       <c r="D193" s="7"/>
       <c t="s" r="E193" s="7">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="F193" s="7">
         <v>321</v>
@@ -8006,10 +8032,10 @@
         <v>83</v>
       </c>
       <c t="s" r="I193" s="7">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c t="s" r="J193" s="7">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="K193" s="7"/>
       <c r="L193" s="7"/>
@@ -8042,7 +8068,7 @@
       </c>
       <c r="D195" s="7"/>
       <c t="s" r="E195" s="7">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="F195" s="7">
         <v>321</v>
@@ -8051,18 +8077,18 @@
         <v>17</v>
       </c>
       <c t="s" r="H195" s="8">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c t="s" r="I195" s="7">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c t="s" r="J195" s="7">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="K195" s="7"/>
       <c r="L195" s="7"/>
       <c t="s" r="M195" s="7">
-        <v>355</v>
+        <v>356</v>
       </c>
     </row>
     <row r="196" ht="14.25" customHeight="1">
@@ -8077,19 +8103,19 @@
       </c>
       <c r="D196" s="7"/>
       <c t="s" r="E196" s="7">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="F196" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G196" s="8">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c t="s" r="H196" s="8">
         <v>153</v>
       </c>
       <c t="s" r="I196" s="7">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c t="s" r="J196" s="7">
         <v>37</v>
@@ -8112,7 +8138,7 @@
       </c>
       <c r="D197" s="7"/>
       <c t="s" r="E197" s="7">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="F197" s="7">
         <v>321</v>
@@ -8121,10 +8147,10 @@
         <v>153</v>
       </c>
       <c t="s" r="H197" s="8">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c t="s" r="I197" s="7">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c t="s" r="J197" s="7">
         <v>169</v>
@@ -8147,13 +8173,13 @@
       </c>
       <c r="D198" s="7"/>
       <c t="s" r="E198" s="7">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="F198" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G198" s="8">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c t="s" r="H198" s="8">
         <v>17</v>
@@ -8167,7 +8193,7 @@
       <c r="K198" s="7"/>
       <c r="L198" s="7"/>
       <c t="s" r="M198" s="7">
-        <v>358</v>
+        <v>359</v>
       </c>
     </row>
     <row r="199" ht="14.25" customHeight="1">
@@ -8182,7 +8208,7 @@
       </c>
       <c r="D199" s="7"/>
       <c t="s" r="E199" s="7">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="F199" s="7">
         <v>321</v>
@@ -8191,7 +8217,7 @@
         <v>17</v>
       </c>
       <c t="s" r="H199" s="8">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c t="s" r="I199" s="7">
         <v>82</v>
@@ -8202,7 +8228,7 @@
       <c r="K199" s="7"/>
       <c r="L199" s="7"/>
       <c t="s" r="M199" s="7">
-        <v>359</v>
+        <v>360</v>
       </c>
     </row>
     <row r="200" ht="15" customHeight="1">
@@ -8217,19 +8243,19 @@
       </c>
       <c r="D200" s="7"/>
       <c t="s" r="E200" s="7">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="F200" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G200" s="8">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c t="s" r="H200" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I200" s="7">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c t="s" r="J200" s="7">
         <v>143</v>
@@ -8252,7 +8278,7 @@
       </c>
       <c r="D201" s="7"/>
       <c t="s" r="E201" s="7">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="F201" s="7">
         <v>321</v>
@@ -8274,7 +8300,7 @@
       </c>
       <c r="L201" s="7"/>
       <c t="s" r="M201" s="7">
-        <v>296</v>
+        <v>361</v>
       </c>
     </row>
     <row r="202" ht="14.25" customHeight="1">
@@ -8289,7 +8315,7 @@
       </c>
       <c r="D202" s="7"/>
       <c t="s" r="E202" s="7">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="F202" s="7">
         <v>321</v>
@@ -8301,7 +8327,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I202" s="7">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c t="s" r="J202" s="7">
         <v>53</v>
@@ -8311,7 +8337,7 @@
       </c>
       <c r="L202" s="7"/>
       <c t="s" r="M202" s="7">
-        <v>253</v>
+        <v>254</v>
       </c>
     </row>
     <row r="203" ht="14.25" customHeight="1">
@@ -8341,7 +8367,7 @@
       </c>
       <c r="D204" s="7"/>
       <c t="s" r="E204" s="7">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="F204" s="7">
         <v>321</v>
@@ -8353,15 +8379,15 @@
         <v>48</v>
       </c>
       <c t="s" r="I204" s="7">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c t="s" r="J204" s="7">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="K204" s="7"/>
       <c r="L204" s="7"/>
       <c t="s" r="M204" s="7">
-        <v>362</v>
+        <v>364</v>
       </c>
     </row>
     <row r="205" ht="15" customHeight="1">
@@ -8376,7 +8402,7 @@
       </c>
       <c r="D205" s="7"/>
       <c t="s" r="E205" s="7">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="F205" s="7">
         <v>321</v>
@@ -8396,7 +8422,7 @@
       <c r="K205" s="7"/>
       <c r="L205" s="7"/>
       <c t="s" r="M205" s="7">
-        <v>233</v>
+        <v>234</v>
       </c>
     </row>
     <row r="206" ht="14.25" customHeight="1">
@@ -8411,7 +8437,7 @@
       </c>
       <c r="D206" s="7"/>
       <c t="s" r="E206" s="7">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="F206" s="7">
         <v>321</v>
@@ -8431,7 +8457,7 @@
       <c r="K206" s="7"/>
       <c r="L206" s="7"/>
       <c t="s" r="M206" s="7">
-        <v>342</v>
+        <v>343</v>
       </c>
     </row>
     <row r="207" ht="14.25" customHeight="1">
@@ -8446,7 +8472,7 @@
       </c>
       <c r="D207" s="7"/>
       <c t="s" r="E207" s="7">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="F207" s="7">
         <v>321</v>
@@ -8466,7 +8492,7 @@
       <c r="K207" s="7"/>
       <c r="L207" s="7"/>
       <c t="s" r="M207" s="7">
-        <v>363</v>
+        <v>365</v>
       </c>
     </row>
     <row r="208" ht="14.25" customHeight="1">
@@ -8481,7 +8507,7 @@
       </c>
       <c r="D208" s="7"/>
       <c t="s" r="E208" s="7">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="F208" s="7">
         <v>321</v>
@@ -8496,11 +8522,13 @@
         <v>63</v>
       </c>
       <c t="s" r="J208" s="7">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="K208" s="7"/>
       <c r="L208" s="7"/>
-      <c r="M208" s="7"/>
+      <c t="s" r="M208" s="7">
+        <v>366</v>
+      </c>
     </row>
     <row r="209" ht="14.25" customHeight="1">
       <c t="s" r="A209" s="6">
@@ -8514,7 +8542,7 @@
       </c>
       <c r="D209" s="7"/>
       <c t="s" r="E209" s="7">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="F209" s="7">
         <v>321</v>
@@ -8526,10 +8554,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I209" s="7">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c t="s" r="J209" s="7">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="K209" s="7"/>
       <c r="L209" s="7"/>
@@ -8547,7 +8575,7 @@
       </c>
       <c r="D210" s="7"/>
       <c t="s" r="E210" s="7">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="F210" s="7">
         <v>321</v>
@@ -8559,7 +8587,7 @@
         <v>48</v>
       </c>
       <c t="s" r="I210" s="7">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c t="s" r="J210" s="7">
         <v>64</v>
@@ -8595,7 +8623,7 @@
       </c>
       <c r="D212" s="7"/>
       <c t="s" r="E212" s="7">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="F212" s="7">
         <v>321</v>
@@ -8604,18 +8632,18 @@
         <v>17</v>
       </c>
       <c t="s" r="H212" s="8">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c t="s" r="I212" s="7">
         <v>157</v>
       </c>
       <c t="s" r="J212" s="7">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="K212" s="7"/>
       <c r="L212" s="7"/>
       <c t="s" r="M212" s="7">
-        <v>366</v>
+        <v>369</v>
       </c>
     </row>
     <row r="213" ht="14.25" customHeight="1">
@@ -8630,27 +8658,27 @@
       </c>
       <c r="D213" s="7"/>
       <c t="s" r="E213" s="7">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="F213" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G213" s="8">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c t="s" r="H213" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I213" s="7">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c t="s" r="J213" s="7">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="K213" s="7"/>
       <c r="L213" s="7"/>
       <c t="s" r="M213" s="7">
-        <v>368</v>
+        <v>371</v>
       </c>
     </row>
     <row r="214" ht="14.25" customHeight="1">
@@ -8665,7 +8693,7 @@
       </c>
       <c r="D214" s="7"/>
       <c t="s" r="E214" s="7">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="F214" s="7">
         <v>321</v>
@@ -8700,7 +8728,7 @@
       </c>
       <c r="D215" s="7"/>
       <c t="s" r="E215" s="7">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="F215" s="7">
         <v>321</v>
@@ -8709,7 +8737,7 @@
         <v>48</v>
       </c>
       <c t="s" r="H215" s="8">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c t="s" r="I215" s="7">
         <v>201</v>
@@ -8719,7 +8747,9 @@
       </c>
       <c r="K215" s="7"/>
       <c r="L215" s="7"/>
-      <c r="M215" s="7"/>
+      <c t="s" r="M215" s="7">
+        <v>240</v>
+      </c>
     </row>
     <row r="216" ht="14.25" customHeight="1">
       <c t="s" r="A216" s="6">
@@ -8733,13 +8763,13 @@
       </c>
       <c r="D216" s="7"/>
       <c t="s" r="E216" s="7">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="F216" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G216" s="8">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c t="s" r="H216" s="8">
         <v>48</v>
@@ -8748,7 +8778,7 @@
         <v>28</v>
       </c>
       <c t="s" r="J216" s="7">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="K216" s="7"/>
       <c r="L216" s="7"/>
@@ -8766,7 +8796,7 @@
       </c>
       <c r="D217" s="7"/>
       <c t="s" r="E217" s="7">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="F217" s="7">
         <v>321</v>
@@ -8781,7 +8811,7 @@
         <v>217</v>
       </c>
       <c t="s" r="J217" s="7">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="K217" s="7"/>
       <c r="L217" s="7"/>
@@ -8814,7 +8844,7 @@
       </c>
       <c r="D219" s="7"/>
       <c t="s" r="E219" s="7">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="F219" s="7">
         <v>321</v>
@@ -8826,15 +8856,15 @@
         <v>17</v>
       </c>
       <c t="s" r="I219" s="7">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c t="s" r="J219" s="7">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="K219" s="7"/>
       <c r="L219" s="7"/>
       <c t="s" r="M219" s="7">
-        <v>373</v>
+        <v>376</v>
       </c>
     </row>
     <row r="220" ht="15" customHeight="1">
@@ -8849,7 +8879,7 @@
       </c>
       <c r="D220" s="7"/>
       <c t="s" r="E220" s="7">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="F220" s="7">
         <v>321</v>
@@ -8858,18 +8888,18 @@
         <v>17</v>
       </c>
       <c t="s" r="H220" s="8">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c t="s" r="I220" s="7">
         <v>220</v>
       </c>
       <c t="s" r="J220" s="7">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="K220" s="7"/>
       <c r="L220" s="7"/>
       <c t="s" r="M220" s="7">
-        <v>374</v>
+        <v>377</v>
       </c>
     </row>
     <row r="221" ht="14.25" customHeight="1">
@@ -8884,13 +8914,13 @@
       </c>
       <c r="D221" s="7"/>
       <c t="s" r="E221" s="7">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="F221" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G221" s="8">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c t="s" r="H221" s="8">
         <v>17</v>
@@ -8904,7 +8934,7 @@
       <c r="K221" s="7"/>
       <c r="L221" s="7"/>
       <c t="s" r="M221" s="7">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="222" ht="14.25" customHeight="1">
@@ -8919,7 +8949,7 @@
       </c>
       <c r="D222" s="7"/>
       <c t="s" r="E222" s="7">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="F222" s="7">
         <v>321</v>
@@ -8928,18 +8958,18 @@
         <v>17</v>
       </c>
       <c t="s" r="H222" s="8">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c t="s" r="I222" s="7">
         <v>127</v>
       </c>
       <c t="s" r="J222" s="7">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="K222" s="7"/>
       <c r="L222" s="7"/>
       <c t="s" r="M222" s="7">
-        <v>376</v>
+        <v>379</v>
       </c>
     </row>
     <row r="223" ht="14.25" customHeight="1">
@@ -8954,13 +8984,13 @@
       </c>
       <c r="D223" s="7"/>
       <c t="s" r="E223" s="7">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="F223" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G223" s="8">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c t="s" r="H223" s="8">
         <v>17</v>
@@ -8969,7 +8999,7 @@
         <v>215</v>
       </c>
       <c t="s" r="J223" s="7">
-        <v>165</v>
+        <v>380</v>
       </c>
       <c r="K223" s="7"/>
       <c r="L223" s="7"/>
@@ -9002,7 +9032,7 @@
       </c>
       <c r="D225" s="7"/>
       <c t="s" r="E225" s="7">
-        <v>377</v>
+        <v>381</v>
       </c>
       <c r="F225" s="7">
         <v>321</v>
@@ -9022,7 +9052,7 @@
       <c r="K225" s="7"/>
       <c r="L225" s="7"/>
       <c t="s" r="M225" s="7">
-        <v>378</v>
+        <v>382</v>
       </c>
     </row>
     <row r="226" ht="14.25" customHeight="1">
@@ -9037,7 +9067,7 @@
       </c>
       <c r="D226" s="7"/>
       <c t="s" r="E226" s="7">
-        <v>377</v>
+        <v>381</v>
       </c>
       <c r="F226" s="7">
         <v>321</v>
@@ -9052,12 +9082,12 @@
         <v>195</v>
       </c>
       <c t="s" r="J226" s="7">
-        <v>379</v>
+        <v>383</v>
       </c>
       <c r="K226" s="7"/>
       <c r="L226" s="7"/>
       <c t="s" r="M226" s="7">
-        <v>380</v>
+        <v>384</v>
       </c>
     </row>
     <row r="227" ht="14.25" customHeight="1">
@@ -9072,7 +9102,7 @@
       </c>
       <c r="D227" s="7"/>
       <c t="s" r="E227" s="7">
-        <v>377</v>
+        <v>381</v>
       </c>
       <c r="F227" s="7">
         <v>321</v>
@@ -9084,7 +9114,7 @@
         <v>141</v>
       </c>
       <c t="s" r="I227" s="7">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c t="s" r="J227" s="7">
         <v>72</v>
@@ -9107,7 +9137,7 @@
       </c>
       <c r="D228" s="7"/>
       <c t="s" r="E228" s="7">
-        <v>377</v>
+        <v>381</v>
       </c>
       <c r="F228" s="7">
         <v>321</v>
@@ -9126,7 +9156,9 @@
       </c>
       <c r="K228" s="7"/>
       <c r="L228" s="7"/>
-      <c r="M228" s="7"/>
+      <c t="s" r="M228" s="7">
+        <v>385</v>
+      </c>
     </row>
     <row r="229" ht="14.25" customHeight="1">
       <c t="s" r="A229" s="6">
@@ -9140,7 +9172,7 @@
       </c>
       <c r="D229" s="7"/>
       <c t="s" r="E229" s="7">
-        <v>377</v>
+        <v>381</v>
       </c>
       <c r="F229" s="7">
         <v>321</v>
@@ -9152,17 +9184,17 @@
         <v>83</v>
       </c>
       <c t="s" r="I229" s="7">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c t="s" r="J229" s="7">
         <v>103</v>
       </c>
       <c t="s" r="K229" s="7">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="L229" s="7"/>
       <c t="s" r="M229" s="7">
-        <v>381</v>
+        <v>386</v>
       </c>
     </row>
     <row r="230" ht="15" customHeight="1">
@@ -9177,7 +9209,7 @@
       </c>
       <c r="D230" s="7"/>
       <c t="s" r="E230" s="7">
-        <v>377</v>
+        <v>381</v>
       </c>
       <c r="F230" s="7">
         <v>321</v>
@@ -9189,17 +9221,17 @@
         <v>17</v>
       </c>
       <c t="s" r="I230" s="7">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c t="s" r="J230" s="7">
         <v>217</v>
       </c>
       <c t="s" r="K230" s="7">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="L230" s="7"/>
       <c t="s" r="M230" s="7">
-        <v>382</v>
+        <v>387</v>
       </c>
     </row>
     <row r="231" ht="14.25" customHeight="1">
@@ -9229,7 +9261,7 @@
       </c>
       <c r="D232" s="7"/>
       <c t="s" r="E232" s="7">
-        <v>383</v>
+        <v>388</v>
       </c>
       <c r="F232" s="7">
         <v>321</v>
@@ -9241,7 +9273,7 @@
         <v>48</v>
       </c>
       <c t="s" r="I232" s="7">
-        <v>384</v>
+        <v>389</v>
       </c>
       <c t="s" r="J232" s="7">
         <v>38</v>
@@ -9249,7 +9281,7 @@
       <c r="K232" s="7"/>
       <c r="L232" s="7"/>
       <c t="s" r="M232" s="7">
-        <v>385</v>
+        <v>390</v>
       </c>
     </row>
     <row r="233" ht="14.25" customHeight="1">
@@ -9264,7 +9296,7 @@
       </c>
       <c r="D233" s="7"/>
       <c t="s" r="E233" s="7">
-        <v>383</v>
+        <v>388</v>
       </c>
       <c r="F233" s="7">
         <v>321</v>
@@ -9273,7 +9305,7 @@
         <v>48</v>
       </c>
       <c t="s" r="H233" s="8">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c t="s" r="I233" s="7">
         <v>212</v>
@@ -9284,7 +9316,7 @@
       <c r="K233" s="7"/>
       <c r="L233" s="7"/>
       <c t="s" r="M233" s="7">
-        <v>310</v>
+        <v>311</v>
       </c>
     </row>
     <row r="234" ht="14.25" customHeight="1">
@@ -9299,26 +9331,28 @@
       </c>
       <c r="D234" s="7"/>
       <c t="s" r="E234" s="7">
-        <v>383</v>
+        <v>388</v>
       </c>
       <c r="F234" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G234" s="8">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c t="s" r="H234" s="8">
         <v>48</v>
       </c>
       <c t="s" r="I234" s="7">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c t="s" r="J234" s="7">
         <v>145</v>
       </c>
       <c r="K234" s="7"/>
       <c r="L234" s="7"/>
-      <c r="M234" s="7"/>
+      <c t="s" r="M234" s="7">
+        <v>391</v>
+      </c>
     </row>
     <row r="235" ht="15" customHeight="1">
       <c t="s" r="A235" s="6">
@@ -9332,7 +9366,7 @@
       </c>
       <c r="D235" s="7"/>
       <c t="s" r="E235" s="7">
-        <v>383</v>
+        <v>388</v>
       </c>
       <c r="F235" s="7">
         <v>321</v>
@@ -9344,10 +9378,10 @@
         <v>110</v>
       </c>
       <c t="s" r="I235" s="7">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c t="s" r="J235" s="7">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="K235" s="7"/>
       <c r="L235" s="7"/>
@@ -9365,7 +9399,7 @@
       </c>
       <c r="D236" s="7"/>
       <c t="s" r="E236" s="7">
-        <v>383</v>
+        <v>388</v>
       </c>
       <c r="F236" s="7">
         <v>321</v>
@@ -9377,7 +9411,7 @@
         <v>48</v>
       </c>
       <c t="s" r="I236" s="7">
-        <v>381</v>
+        <v>386</v>
       </c>
       <c t="s" r="J236" s="7">
         <v>130</v>
@@ -9398,7 +9432,7 @@
       </c>
       <c r="D237" s="7"/>
       <c t="s" r="E237" s="7">
-        <v>383</v>
+        <v>388</v>
       </c>
       <c r="F237" s="7">
         <v>321</v>
@@ -9407,10 +9441,10 @@
         <v>48</v>
       </c>
       <c t="s" r="H237" s="8">
-        <v>386</v>
+        <v>392</v>
       </c>
       <c t="s" r="I237" s="7">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c t="s" r="J237" s="7">
         <v>56</v>
@@ -9446,13 +9480,13 @@
       </c>
       <c r="D239" s="7"/>
       <c t="s" r="E239" s="7">
-        <v>387</v>
+        <v>393</v>
       </c>
       <c r="F239" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G239" s="8">
-        <v>388</v>
+        <v>394</v>
       </c>
       <c t="s" r="H239" s="8">
         <v>17</v>
@@ -9461,12 +9495,12 @@
         <v>195</v>
       </c>
       <c t="s" r="J239" s="7">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="K239" s="7"/>
       <c r="L239" s="7"/>
       <c t="s" r="M239" s="7">
-        <v>389</v>
+        <v>395</v>
       </c>
     </row>
     <row r="240" ht="15" customHeight="1">
@@ -9481,7 +9515,7 @@
       </c>
       <c r="D240" s="7"/>
       <c t="s" r="E240" s="7">
-        <v>387</v>
+        <v>393</v>
       </c>
       <c r="F240" s="7">
         <v>321</v>
@@ -9490,7 +9524,7 @@
         <v>17</v>
       </c>
       <c t="s" r="H240" s="8">
-        <v>388</v>
+        <v>394</v>
       </c>
       <c t="s" r="I240" s="7">
         <v>44</v>
@@ -9529,7 +9563,7 @@
       </c>
       <c r="D242" s="7"/>
       <c t="s" r="E242" s="7">
-        <v>390</v>
+        <v>396</v>
       </c>
       <c r="F242" s="7">
         <v>321</v>
@@ -9541,7 +9575,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I242" s="7">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c t="s" r="J242" s="7">
         <v>49</v>
@@ -9564,7 +9598,7 @@
       </c>
       <c r="D243" s="7"/>
       <c t="s" r="E243" s="7">
-        <v>390</v>
+        <v>396</v>
       </c>
       <c r="F243" s="7">
         <v>321</v>
@@ -9576,15 +9610,15 @@
         <v>48</v>
       </c>
       <c t="s" r="I243" s="7">
-        <v>391</v>
+        <v>397</v>
       </c>
       <c t="s" r="J243" s="7">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="K243" s="7"/>
       <c r="L243" s="7"/>
       <c t="s" r="M243" s="7">
-        <v>392</v>
+        <v>398</v>
       </c>
     </row>
     <row r="244" ht="14.25" customHeight="1">
@@ -9599,7 +9633,7 @@
       </c>
       <c r="D244" s="7"/>
       <c t="s" r="E244" s="7">
-        <v>390</v>
+        <v>396</v>
       </c>
       <c r="F244" s="7">
         <v>321</v>
@@ -9617,11 +9651,11 @@
         <v>212</v>
       </c>
       <c t="s" r="K244" s="7">
-        <v>393</v>
+        <v>399</v>
       </c>
       <c r="L244" s="7"/>
       <c t="s" r="M244" s="7">
-        <v>394</v>
+        <v>400</v>
       </c>
     </row>
     <row r="245" ht="15" customHeight="1">
@@ -9636,7 +9670,7 @@
       </c>
       <c r="D245" s="7"/>
       <c t="s" r="E245" s="7">
-        <v>390</v>
+        <v>396</v>
       </c>
       <c r="F245" s="7">
         <v>321</v>
@@ -9654,11 +9688,11 @@
         <v>63</v>
       </c>
       <c t="s" r="K245" s="7">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="L245" s="7"/>
       <c t="s" r="M245" s="7">
-        <v>395</v>
+        <v>401</v>
       </c>
     </row>
     <row r="246" ht="14.25" customHeight="1">
@@ -9673,7 +9707,7 @@
       </c>
       <c r="D246" s="7"/>
       <c t="s" r="E246" s="7">
-        <v>390</v>
+        <v>396</v>
       </c>
       <c r="F246" s="7">
         <v>321</v>
@@ -9691,7 +9725,7 @@
         <v>53</v>
       </c>
       <c t="s" r="K246" s="7">
-        <v>165</v>
+        <v>380</v>
       </c>
       <c r="L246" s="7"/>
       <c t="s" r="M246" s="7">
@@ -9710,7 +9744,7 @@
       </c>
       <c r="D247" s="7"/>
       <c t="s" r="E247" s="7">
-        <v>390</v>
+        <v>396</v>
       </c>
       <c r="F247" s="7">
         <v>321</v>
@@ -9722,17 +9756,17 @@
         <v>48</v>
       </c>
       <c t="s" r="I247" s="7">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c t="s" r="J247" s="7">
-        <v>396</v>
+        <v>402</v>
       </c>
       <c t="s" r="K247" s="7">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="L247" s="7"/>
       <c t="s" r="M247" s="7">
-        <v>397</v>
+        <v>403</v>
       </c>
     </row>
     <row r="248" ht="14.25" customHeight="1">
@@ -9747,7 +9781,7 @@
       </c>
       <c r="D248" s="7"/>
       <c t="s" r="E248" s="7">
-        <v>390</v>
+        <v>396</v>
       </c>
       <c r="F248" s="7">
         <v>321</v>
@@ -9756,10 +9790,10 @@
         <v>48</v>
       </c>
       <c t="s" r="H248" s="8">
-        <v>398</v>
+        <v>404</v>
       </c>
       <c t="s" r="I248" s="7">
-        <v>399</v>
+        <v>405</v>
       </c>
       <c t="s" r="J248" s="7">
         <v>91</v>
@@ -9795,19 +9829,19 @@
       </c>
       <c r="D250" s="7"/>
       <c t="s" r="E250" s="7">
-        <v>400</v>
+        <v>406</v>
       </c>
       <c r="F250" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G250" s="8">
-        <v>386</v>
+        <v>392</v>
       </c>
       <c t="s" r="H250" s="8">
         <v>48</v>
       </c>
       <c t="s" r="I250" s="7">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c t="s" r="J250" s="7">
         <v>169</v>
@@ -9815,7 +9849,7 @@
       <c r="K250" s="7"/>
       <c r="L250" s="7"/>
       <c t="s" r="M250" s="7">
-        <v>401</v>
+        <v>407</v>
       </c>
     </row>
     <row r="251" ht="14.25" customHeight="1">
@@ -9830,7 +9864,7 @@
       </c>
       <c r="D251" s="7"/>
       <c t="s" r="E251" s="7">
-        <v>400</v>
+        <v>406</v>
       </c>
       <c r="F251" s="7">
         <v>321</v>
@@ -9850,7 +9884,7 @@
       <c r="K251" s="7"/>
       <c r="L251" s="7"/>
       <c t="s" r="M251" s="7">
-        <v>281</v>
+        <v>282</v>
       </c>
     </row>
     <row r="252" ht="14.25" customHeight="1">
@@ -9865,7 +9899,7 @@
       </c>
       <c r="D252" s="7"/>
       <c t="s" r="E252" s="7">
-        <v>400</v>
+        <v>406</v>
       </c>
       <c r="F252" s="7">
         <v>321</v>
@@ -9877,7 +9911,7 @@
         <v>48</v>
       </c>
       <c t="s" r="I252" s="7">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c t="s" r="J252" s="7">
         <v>98</v>
@@ -9885,7 +9919,7 @@
       <c r="K252" s="7"/>
       <c r="L252" s="7"/>
       <c t="s" r="M252" s="7">
-        <v>402</v>
+        <v>408</v>
       </c>
     </row>
     <row r="253" ht="14.25" customHeight="1">
@@ -9900,7 +9934,7 @@
       </c>
       <c r="D253" s="7"/>
       <c t="s" r="E253" s="7">
-        <v>400</v>
+        <v>406</v>
       </c>
       <c r="F253" s="7">
         <v>321</v>
@@ -9912,7 +9946,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I253" s="7">
-        <v>403</v>
+        <v>409</v>
       </c>
       <c t="s" r="J253" s="7">
         <v>177</v>
@@ -9922,7 +9956,7 @@
       </c>
       <c r="L253" s="7"/>
       <c t="s" r="M253" s="7">
-        <v>240</v>
+        <v>241</v>
       </c>
     </row>
     <row r="254" ht="14.25" customHeight="1">
@@ -9937,7 +9971,7 @@
       </c>
       <c r="D254" s="7"/>
       <c t="s" r="E254" s="7">
-        <v>400</v>
+        <v>406</v>
       </c>
       <c r="F254" s="7">
         <v>321</v>
@@ -9974,7 +10008,7 @@
       </c>
       <c r="D255" s="7"/>
       <c t="s" r="E255" s="7">
-        <v>400</v>
+        <v>406</v>
       </c>
       <c r="F255" s="7">
         <v>321</v>
@@ -9989,10 +10023,10 @@
         <v>146</v>
       </c>
       <c t="s" r="J255" s="7">
-        <v>404</v>
+        <v>410</v>
       </c>
       <c t="s" r="K255" s="7">
-        <v>404</v>
+        <v>410</v>
       </c>
       <c r="L255" s="7"/>
       <c t="s" r="M255" s="7">
@@ -10026,7 +10060,7 @@
       </c>
       <c r="D257" s="7"/>
       <c t="s" r="E257" s="7">
-        <v>405</v>
+        <v>411</v>
       </c>
       <c r="F257" s="7">
         <v>321</v>
@@ -10038,7 +10072,7 @@
         <v>141</v>
       </c>
       <c t="s" r="I257" s="7">
-        <v>406</v>
+        <v>412</v>
       </c>
       <c t="s" r="J257" s="7">
         <v>67</v>
@@ -10046,7 +10080,7 @@
       <c r="K257" s="7"/>
       <c r="L257" s="7"/>
       <c t="s" r="M257" s="7">
-        <v>407</v>
+        <v>413</v>
       </c>
     </row>
     <row r="258" ht="14.25" customHeight="1">
@@ -10061,7 +10095,7 @@
       </c>
       <c r="D258" s="7"/>
       <c t="s" r="E258" s="7">
-        <v>405</v>
+        <v>411</v>
       </c>
       <c r="F258" s="7">
         <v>321</v>
@@ -10070,18 +10104,18 @@
         <v>141</v>
       </c>
       <c t="s" r="H258" s="8">
-        <v>408</v>
+        <v>414</v>
       </c>
       <c t="s" r="I258" s="7">
         <v>40</v>
       </c>
       <c t="s" r="J258" s="7">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="K258" s="7"/>
       <c r="L258" s="7"/>
       <c t="s" r="M258" s="7">
-        <v>409</v>
+        <v>415</v>
       </c>
     </row>
     <row r="259" ht="14.25" customHeight="1">
@@ -10096,27 +10130,27 @@
       </c>
       <c r="D259" s="7"/>
       <c t="s" r="E259" s="7">
-        <v>405</v>
+        <v>411</v>
       </c>
       <c r="F259" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G259" s="8">
-        <v>408</v>
+        <v>414</v>
       </c>
       <c t="s" r="H259" s="8">
         <v>141</v>
       </c>
       <c t="s" r="I259" s="7">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c t="s" r="J259" s="7">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="K259" s="7"/>
       <c r="L259" s="7"/>
       <c t="s" r="M259" s="7">
-        <v>410</v>
+        <v>121</v>
       </c>
     </row>
     <row r="260" ht="15" customHeight="1">
@@ -10131,7 +10165,7 @@
       </c>
       <c r="D260" s="7"/>
       <c t="s" r="E260" s="7">
-        <v>405</v>
+        <v>411</v>
       </c>
       <c r="F260" s="7">
         <v>321</v>
@@ -10143,10 +10177,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I260" s="7">
-        <v>397</v>
+        <v>403</v>
       </c>
       <c t="s" r="J260" s="7">
-        <v>411</v>
+        <v>416</v>
       </c>
       <c r="K260" s="7"/>
       <c r="L260" s="7"/>
@@ -10179,7 +10213,7 @@
       </c>
       <c r="D262" s="7"/>
       <c t="s" r="E262" s="7">
-        <v>412</v>
+        <v>417</v>
       </c>
       <c r="F262" s="7">
         <v>321</v>
@@ -10194,12 +10228,12 @@
         <v>131</v>
       </c>
       <c t="s" r="J262" s="7">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="K262" s="7"/>
       <c r="L262" s="7"/>
       <c t="s" r="M262" s="7">
-        <v>413</v>
+        <v>418</v>
       </c>
     </row>
     <row r="263" ht="14.25" customHeight="1">
@@ -10214,7 +10248,7 @@
       </c>
       <c r="D263" s="7"/>
       <c t="s" r="E263" s="7">
-        <v>412</v>
+        <v>417</v>
       </c>
       <c r="F263" s="7">
         <v>321</v>
@@ -10229,12 +10263,12 @@
         <v>108</v>
       </c>
       <c t="s" r="J263" s="7">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="K263" s="7"/>
       <c r="L263" s="7"/>
       <c t="s" r="M263" s="7">
-        <v>414</v>
+        <v>419</v>
       </c>
     </row>
     <row r="264" ht="14.25" customHeight="1">
@@ -10249,7 +10283,7 @@
       </c>
       <c r="D264" s="7"/>
       <c t="s" r="E264" s="7">
-        <v>412</v>
+        <v>417</v>
       </c>
       <c r="F264" s="7">
         <v>321</v>
@@ -10261,7 +10295,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I264" s="7">
-        <v>401</v>
+        <v>407</v>
       </c>
       <c t="s" r="J264" s="7">
         <v>96</v>
@@ -10269,7 +10303,7 @@
       <c r="K264" s="7"/>
       <c r="L264" s="7"/>
       <c t="s" r="M264" s="7">
-        <v>415</v>
+        <v>420</v>
       </c>
     </row>
     <row r="265" ht="15" customHeight="1">
@@ -10284,7 +10318,7 @@
       </c>
       <c r="D265" s="7"/>
       <c t="s" r="E265" s="7">
-        <v>412</v>
+        <v>417</v>
       </c>
       <c r="F265" s="7">
         <v>321</v>
@@ -10299,12 +10333,12 @@
         <v>221</v>
       </c>
       <c t="s" r="J265" s="7">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="K265" s="7"/>
       <c r="L265" s="7"/>
       <c t="s" r="M265" s="7">
-        <v>416</v>
+        <v>421</v>
       </c>
     </row>
     <row r="266" ht="14.25" customHeight="1">
@@ -10334,7 +10368,7 @@
       </c>
       <c r="D267" s="7"/>
       <c t="s" r="E267" s="7">
-        <v>417</v>
+        <v>422</v>
       </c>
       <c r="F267" s="7">
         <v>321</v>
@@ -10349,12 +10383,12 @@
         <v>135</v>
       </c>
       <c t="s" r="J267" s="7">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="K267" s="7"/>
       <c r="L267" s="7"/>
       <c t="s" r="M267" s="7">
-        <v>418</v>
+        <v>423</v>
       </c>
     </row>
     <row r="268" ht="14.25" customHeight="1">
@@ -10369,7 +10403,7 @@
       </c>
       <c r="D268" s="7"/>
       <c t="s" r="E268" s="7">
-        <v>417</v>
+        <v>422</v>
       </c>
       <c r="F268" s="7">
         <v>321</v>
@@ -10378,7 +10412,7 @@
         <v>17</v>
       </c>
       <c t="s" r="H268" s="8">
-        <v>419</v>
+        <v>424</v>
       </c>
       <c t="s" r="I268" s="7">
         <v>150</v>
@@ -10404,22 +10438,22 @@
       </c>
       <c r="D269" s="7"/>
       <c t="s" r="E269" s="7">
-        <v>417</v>
+        <v>422</v>
       </c>
       <c r="F269" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G269" s="8">
-        <v>419</v>
+        <v>424</v>
       </c>
       <c t="s" r="H269" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I269" s="7">
-        <v>420</v>
+        <v>425</v>
       </c>
       <c t="s" r="J269" s="7">
-        <v>421</v>
+        <v>426</v>
       </c>
       <c r="K269" s="7"/>
       <c r="L269" s="7"/>
@@ -10452,7 +10486,7 @@
       </c>
       <c r="D271" s="7"/>
       <c t="s" r="E271" s="7">
-        <v>422</v>
+        <v>427</v>
       </c>
       <c r="F271" s="7">
         <v>321</v>
@@ -10461,7 +10495,7 @@
         <v>48</v>
       </c>
       <c t="s" r="H271" s="8">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c t="s" r="I271" s="7">
         <v>56</v>
@@ -10487,19 +10521,19 @@
       </c>
       <c r="D272" s="7"/>
       <c t="s" r="E272" s="7">
-        <v>422</v>
+        <v>427</v>
       </c>
       <c r="F272" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G272" s="8">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c t="s" r="H272" s="8">
         <v>48</v>
       </c>
       <c t="s" r="I272" s="7">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c t="s" r="J272" s="7">
         <v>79</v>
@@ -10507,7 +10541,7 @@
       <c r="K272" s="7"/>
       <c r="L272" s="7"/>
       <c t="s" r="M272" s="7">
-        <v>423</v>
+        <v>428</v>
       </c>
     </row>
     <row r="273" ht="14.25" customHeight="1">
@@ -10522,7 +10556,7 @@
       </c>
       <c r="D273" s="7"/>
       <c t="s" r="E273" s="7">
-        <v>422</v>
+        <v>427</v>
       </c>
       <c r="F273" s="7">
         <v>321</v>
@@ -10534,7 +10568,7 @@
         <v>21</v>
       </c>
       <c t="s" r="I273" s="7">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c t="s" r="J273" s="7">
         <v>198</v>
@@ -10542,7 +10576,7 @@
       <c r="K273" s="7"/>
       <c r="L273" s="7"/>
       <c t="s" r="M273" s="7">
-        <v>424</v>
+        <v>429</v>
       </c>
     </row>
     <row r="274" ht="14.25" customHeight="1">
@@ -10557,7 +10591,7 @@
       </c>
       <c r="D274" s="7"/>
       <c t="s" r="E274" s="7">
-        <v>422</v>
+        <v>427</v>
       </c>
       <c r="F274" s="7">
         <v>321</v>
@@ -10577,7 +10611,7 @@
       <c r="K274" s="7"/>
       <c r="L274" s="7"/>
       <c t="s" r="M274" s="7">
-        <v>425</v>
+        <v>430</v>
       </c>
     </row>
     <row r="275" ht="15" customHeight="1">
@@ -10592,7 +10626,7 @@
       </c>
       <c r="D275" s="7"/>
       <c t="s" r="E275" s="7">
-        <v>422</v>
+        <v>427</v>
       </c>
       <c r="F275" s="7">
         <v>321</v>
@@ -10607,11 +10641,13 @@
         <v>25</v>
       </c>
       <c t="s" r="J275" s="7">
-        <v>101</v>
+        <v>332</v>
       </c>
       <c r="K275" s="7"/>
       <c r="L275" s="7"/>
-      <c r="M275" s="7"/>
+      <c t="s" r="M275" s="7">
+        <v>431</v>
+      </c>
     </row>
     <row r="276" ht="14.25" customHeight="1">
       <c t="s" r="A276" s="6">
@@ -10625,7 +10661,7 @@
       </c>
       <c r="D276" s="7"/>
       <c t="s" r="E276" s="7">
-        <v>422</v>
+        <v>427</v>
       </c>
       <c r="F276" s="7">
         <v>321</v>
@@ -10640,7 +10676,7 @@
         <v>87</v>
       </c>
       <c t="s" r="J276" s="7">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="K276" s="7"/>
       <c r="L276" s="7"/>
@@ -10658,7 +10694,7 @@
       </c>
       <c r="D277" s="7"/>
       <c t="s" r="E277" s="7">
-        <v>422</v>
+        <v>427</v>
       </c>
       <c r="F277" s="7">
         <v>321</v>
@@ -10667,10 +10703,10 @@
         <v>48</v>
       </c>
       <c t="s" r="H277" s="8">
-        <v>426</v>
+        <v>432</v>
       </c>
       <c t="s" r="I277" s="7">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c t="s" r="J277" s="7">
         <v>64</v>
@@ -10691,13 +10727,13 @@
       </c>
       <c r="D278" s="7"/>
       <c t="s" r="E278" s="7">
-        <v>422</v>
+        <v>427</v>
       </c>
       <c r="F278" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G278" s="8">
-        <v>426</v>
+        <v>432</v>
       </c>
       <c t="s" r="H278" s="8">
         <v>48</v>
@@ -10706,7 +10742,7 @@
         <v>318</v>
       </c>
       <c t="s" r="J278" s="7">
-        <v>427</v>
+        <v>433</v>
       </c>
       <c r="K278" s="7"/>
       <c r="L278" s="7"/>
@@ -10739,7 +10775,7 @@
       </c>
       <c r="D280" s="7"/>
       <c t="s" r="E280" s="7">
-        <v>428</v>
+        <v>434</v>
       </c>
       <c r="F280" s="7">
         <v>320</v>
@@ -10751,7 +10787,7 @@
         <v>133</v>
       </c>
       <c t="s" r="I280" s="7">
-        <v>393</v>
+        <v>399</v>
       </c>
       <c t="s" r="J280" s="7">
         <v>163</v>
@@ -10759,7 +10795,7 @@
       <c r="K280" s="7"/>
       <c r="L280" s="7"/>
       <c t="s" r="M280" s="7">
-        <v>235</v>
+        <v>236</v>
       </c>
     </row>
     <row r="281" ht="14.25" customHeight="1">
@@ -10774,7 +10810,7 @@
       </c>
       <c r="D281" s="7"/>
       <c t="s" r="E281" s="7">
-        <v>428</v>
+        <v>434</v>
       </c>
       <c r="F281" s="7">
         <v>320</v>
@@ -10786,10 +10822,10 @@
         <v>110</v>
       </c>
       <c t="s" r="I281" s="7">
-        <v>418</v>
+        <v>423</v>
       </c>
       <c t="s" r="J281" s="7">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="K281" s="7"/>
       <c r="L281" s="7"/>
@@ -10824,19 +10860,19 @@
       </c>
       <c r="D283" s="7"/>
       <c t="s" r="E283" s="7">
-        <v>429</v>
+        <v>435</v>
       </c>
       <c r="F283" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G283" s="8">
-        <v>386</v>
+        <v>392</v>
       </c>
       <c t="s" r="H283" s="8">
         <v>141</v>
       </c>
       <c t="s" r="I283" s="7">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c t="s" r="J283" s="7">
         <v>38</v>
@@ -10874,7 +10910,7 @@
       </c>
       <c r="D285" s="7"/>
       <c t="s" r="E285" s="7">
-        <v>430</v>
+        <v>436</v>
       </c>
       <c r="F285" s="7">
         <v>320</v>
@@ -10886,7 +10922,7 @@
         <v>48</v>
       </c>
       <c t="s" r="I285" s="7">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c t="s" r="J285" s="7">
         <v>56</v>
@@ -10894,7 +10930,7 @@
       <c r="K285" s="7"/>
       <c r="L285" s="7"/>
       <c t="s" r="M285" s="7">
-        <v>431</v>
+        <v>437</v>
       </c>
     </row>
     <row r="286" ht="14.25" customHeight="1">
@@ -10909,7 +10945,7 @@
       </c>
       <c r="D286" s="7"/>
       <c t="s" r="E286" s="7">
-        <v>430</v>
+        <v>436</v>
       </c>
       <c r="F286" s="7">
         <v>320</v>
@@ -10918,18 +10954,18 @@
         <v>48</v>
       </c>
       <c t="s" r="H286" s="8">
-        <v>432</v>
+        <v>438</v>
       </c>
       <c t="s" r="I286" s="7">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c t="s" r="J286" s="7">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="K286" s="7"/>
       <c r="L286" s="7"/>
       <c t="s" r="M286" s="7">
-        <v>433</v>
+        <v>439</v>
       </c>
     </row>
     <row r="287" ht="14.25" customHeight="1">
@@ -10944,13 +10980,13 @@
       </c>
       <c r="D287" s="7"/>
       <c t="s" r="E287" s="7">
-        <v>430</v>
+        <v>436</v>
       </c>
       <c r="F287" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G287" s="8">
-        <v>432</v>
+        <v>438</v>
       </c>
       <c t="s" r="H287" s="8">
         <v>48</v>
@@ -10959,12 +10995,12 @@
         <v>74</v>
       </c>
       <c t="s" r="J287" s="7">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="K287" s="7"/>
       <c r="L287" s="7"/>
       <c t="s" r="M287" s="7">
-        <v>434</v>
+        <v>440</v>
       </c>
     </row>
     <row r="288" ht="14.25" customHeight="1">
@@ -10979,7 +11015,7 @@
       </c>
       <c r="D288" s="7"/>
       <c t="s" r="E288" s="7">
-        <v>430</v>
+        <v>436</v>
       </c>
       <c r="F288" s="7">
         <v>320</v>
@@ -10988,13 +11024,13 @@
         <v>48</v>
       </c>
       <c t="s" r="H288" s="8">
-        <v>435</v>
+        <v>441</v>
       </c>
       <c t="s" r="I288" s="7">
         <v>30</v>
       </c>
       <c t="s" r="J288" s="7">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="K288" s="7"/>
       <c r="L288" s="7"/>
@@ -11012,13 +11048,13 @@
       </c>
       <c r="D289" s="7"/>
       <c t="s" r="E289" s="7">
-        <v>430</v>
+        <v>436</v>
       </c>
       <c r="F289" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G289" s="8">
-        <v>435</v>
+        <v>441</v>
       </c>
       <c t="s" r="H289" s="8">
         <v>48</v>
@@ -11027,7 +11063,7 @@
         <v>166</v>
       </c>
       <c t="s" r="J289" s="7">
-        <v>436</v>
+        <v>442</v>
       </c>
       <c r="K289" s="7"/>
       <c r="L289" s="7"/>
@@ -11060,7 +11096,7 @@
       </c>
       <c r="D291" s="7"/>
       <c t="s" r="E291" s="7">
-        <v>437</v>
+        <v>443</v>
       </c>
       <c r="F291" s="7">
         <v>321</v>
@@ -11069,10 +11105,10 @@
         <v>48</v>
       </c>
       <c t="s" r="H291" s="8">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c t="s" r="I291" s="7">
-        <v>438</v>
+        <v>444</v>
       </c>
       <c t="s" r="J291" s="7">
         <v>96</v>
@@ -11080,7 +11116,7 @@
       <c r="K291" s="7"/>
       <c r="L291" s="7"/>
       <c t="s" r="M291" s="7">
-        <v>302</v>
+        <v>303</v>
       </c>
     </row>
     <row r="292" ht="14.25" customHeight="1">
@@ -11095,13 +11131,13 @@
       </c>
       <c r="D292" s="7"/>
       <c t="s" r="E292" s="7">
-        <v>437</v>
+        <v>443</v>
       </c>
       <c r="F292" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G292" s="8">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c t="s" r="H292" s="8">
         <v>48</v>
@@ -11110,12 +11146,12 @@
         <v>125</v>
       </c>
       <c t="s" r="J292" s="7">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="K292" s="7"/>
       <c r="L292" s="7"/>
       <c t="s" r="M292" s="7">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="293" ht="14.25" customHeight="1">
@@ -11130,7 +11166,7 @@
       </c>
       <c r="D293" s="7"/>
       <c t="s" r="E293" s="7">
-        <v>437</v>
+        <v>443</v>
       </c>
       <c r="F293" s="7">
         <v>321</v>
@@ -11139,18 +11175,18 @@
         <v>48</v>
       </c>
       <c t="s" r="H293" s="8">
-        <v>439</v>
+        <v>445</v>
       </c>
       <c t="s" r="I293" s="7">
         <v>175</v>
       </c>
       <c t="s" r="J293" s="7">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="K293" s="7"/>
       <c r="L293" s="7"/>
       <c t="s" r="M293" s="7">
-        <v>440</v>
+        <v>446</v>
       </c>
     </row>
     <row r="294" ht="14.25" customHeight="1">
@@ -11165,19 +11201,19 @@
       </c>
       <c r="D294" s="7"/>
       <c t="s" r="E294" s="7">
-        <v>437</v>
+        <v>443</v>
       </c>
       <c r="F294" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G294" s="8">
-        <v>439</v>
+        <v>445</v>
       </c>
       <c t="s" r="H294" s="8">
         <v>48</v>
       </c>
       <c t="s" r="I294" s="7">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c t="s" r="J294" s="7">
         <v>122</v>
@@ -11213,7 +11249,7 @@
       </c>
       <c r="D296" s="7"/>
       <c t="s" r="E296" s="7">
-        <v>441</v>
+        <v>447</v>
       </c>
       <c r="F296" s="7">
         <v>320</v>
@@ -11225,10 +11261,10 @@
         <v>174</v>
       </c>
       <c t="s" r="I296" s="7">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c t="s" r="J296" s="7">
-        <v>418</v>
+        <v>423</v>
       </c>
       <c r="K296" s="7"/>
       <c r="L296" s="7"/>
@@ -11248,7 +11284,7 @@
       </c>
       <c r="D297" s="7"/>
       <c t="s" r="E297" s="7">
-        <v>441</v>
+        <v>447</v>
       </c>
       <c r="F297" s="7">
         <v>320</v>
@@ -11260,7 +11296,7 @@
         <v>110</v>
       </c>
       <c t="s" r="I297" s="7">
-        <v>403</v>
+        <v>409</v>
       </c>
       <c t="s" r="J297" s="7">
         <v>23</v>
@@ -11268,7 +11304,7 @@
       <c r="K297" s="7"/>
       <c r="L297" s="7"/>
       <c t="s" r="M297" s="7">
-        <v>442</v>
+        <v>448</v>
       </c>
     </row>
     <row r="298" ht="14.25" customHeight="1">
@@ -11298,7 +11334,7 @@
       </c>
       <c r="D299" s="7"/>
       <c t="s" r="E299" s="7">
-        <v>443</v>
+        <v>449</v>
       </c>
       <c r="F299" s="7">
         <v>320</v>
@@ -11333,7 +11369,7 @@
       </c>
       <c r="D300" s="7"/>
       <c t="s" r="E300" s="7">
-        <v>443</v>
+        <v>449</v>
       </c>
       <c r="F300" s="7">
         <v>320</v>
@@ -11353,7 +11389,7 @@
       <c r="K300" s="7"/>
       <c r="L300" s="7"/>
       <c t="s" r="M300" s="7">
-        <v>444</v>
+        <v>450</v>
       </c>
     </row>
     <row r="301" ht="14.25" customHeight="1">
@@ -11368,7 +11404,7 @@
       </c>
       <c r="D301" s="7"/>
       <c t="s" r="E301" s="7">
-        <v>443</v>
+        <v>449</v>
       </c>
       <c r="F301" s="7">
         <v>320</v>
@@ -11380,7 +11416,7 @@
         <v>194</v>
       </c>
       <c t="s" r="I301" s="7">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c t="s" r="J301" s="7">
         <v>139</v>
@@ -11403,7 +11439,7 @@
       </c>
       <c r="D302" s="7"/>
       <c t="s" r="E302" s="7">
-        <v>443</v>
+        <v>449</v>
       </c>
       <c r="F302" s="7">
         <v>320</v>
@@ -11415,15 +11451,15 @@
         <v>17</v>
       </c>
       <c t="s" r="I302" s="7">
-        <v>445</v>
+        <v>451</v>
       </c>
       <c t="s" r="J302" s="7">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="K302" s="7"/>
       <c r="L302" s="7"/>
       <c t="s" r="M302" s="7">
-        <v>238</v>
+        <v>239</v>
       </c>
     </row>
     <row r="303" ht="14.25" customHeight="1">
@@ -11438,7 +11474,7 @@
       </c>
       <c r="D303" s="7"/>
       <c t="s" r="E303" s="7">
-        <v>443</v>
+        <v>449</v>
       </c>
       <c r="F303" s="7">
         <v>320</v>
@@ -11447,10 +11483,10 @@
         <v>17</v>
       </c>
       <c t="s" r="H303" s="8">
-        <v>446</v>
+        <v>452</v>
       </c>
       <c t="s" r="I303" s="7">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c t="s" r="J303" s="7">
         <v>87</v>
@@ -11471,13 +11507,13 @@
       </c>
       <c r="D304" s="7"/>
       <c t="s" r="E304" s="7">
-        <v>443</v>
+        <v>449</v>
       </c>
       <c r="F304" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G304" s="8">
-        <v>446</v>
+        <v>452</v>
       </c>
       <c t="s" r="H304" s="8">
         <v>17</v>
@@ -11519,27 +11555,27 @@
       </c>
       <c r="D306" s="7"/>
       <c t="s" r="E306" s="7">
-        <v>447</v>
+        <v>453</v>
       </c>
       <c r="F306" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G306" s="8">
-        <v>386</v>
+        <v>392</v>
       </c>
       <c t="s" r="H306" s="8">
         <v>110</v>
       </c>
       <c t="s" r="I306" s="7">
-        <v>448</v>
+        <v>454</v>
       </c>
       <c t="s" r="J306" s="7">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="K306" s="7"/>
       <c r="L306" s="7"/>
       <c t="s" r="M306" s="7">
-        <v>449</v>
+        <v>455</v>
       </c>
     </row>
     <row r="307" ht="14.25" customHeight="1">
@@ -11554,7 +11590,7 @@
       </c>
       <c r="D307" s="7"/>
       <c t="s" r="E307" s="7">
-        <v>447</v>
+        <v>453</v>
       </c>
       <c r="F307" s="7">
         <v>321</v>
@@ -11569,14 +11605,14 @@
         <v>100</v>
       </c>
       <c t="s" r="J307" s="7">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c t="s" r="K307" s="7">
         <v>186</v>
       </c>
       <c r="L307" s="7"/>
       <c t="s" r="M307" s="7">
-        <v>240</v>
+        <v>241</v>
       </c>
     </row>
     <row r="308" ht="14.25" customHeight="1">
@@ -11591,7 +11627,7 @@
       </c>
       <c r="D308" s="7"/>
       <c t="s" r="E308" s="7">
-        <v>447</v>
+        <v>453</v>
       </c>
       <c r="F308" s="7">
         <v>321</v>
@@ -11606,14 +11642,14 @@
         <v>40</v>
       </c>
       <c t="s" r="J308" s="7">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c t="s" r="K308" s="7">
-        <v>296</v>
+        <v>361</v>
       </c>
       <c r="L308" s="7"/>
       <c t="s" r="M308" s="7">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="309" ht="14.25" customHeight="1">
@@ -11643,7 +11679,7 @@
       </c>
       <c r="D310" s="7"/>
       <c t="s" r="E310" s="7">
-        <v>450</v>
+        <v>456</v>
       </c>
       <c r="F310" s="7">
         <v>320</v>
@@ -11663,7 +11699,7 @@
       <c r="K310" s="7"/>
       <c r="L310" s="7"/>
       <c t="s" r="M310" s="7">
-        <v>451</v>
+        <v>457</v>
       </c>
     </row>
     <row r="311" ht="14.25" customHeight="1">
@@ -11678,7 +11714,7 @@
       </c>
       <c r="D311" s="7"/>
       <c t="s" r="E311" s="7">
-        <v>450</v>
+        <v>456</v>
       </c>
       <c r="F311" s="7">
         <v>320</v>
@@ -11713,7 +11749,7 @@
       </c>
       <c r="D312" s="7"/>
       <c t="s" r="E312" s="7">
-        <v>450</v>
+        <v>456</v>
       </c>
       <c r="F312" s="7">
         <v>320</v>
@@ -11728,12 +11764,12 @@
         <v>116</v>
       </c>
       <c t="s" r="J312" s="7">
-        <v>403</v>
+        <v>409</v>
       </c>
       <c r="K312" s="7"/>
       <c r="L312" s="7"/>
       <c t="s" r="M312" s="7">
-        <v>433</v>
+        <v>439</v>
       </c>
     </row>
     <row r="313" ht="14.25" customHeight="1">
@@ -11748,7 +11784,7 @@
       </c>
       <c r="D313" s="7"/>
       <c t="s" r="E313" s="7">
-        <v>450</v>
+        <v>456</v>
       </c>
       <c r="F313" s="7">
         <v>320</v>
@@ -11768,7 +11804,7 @@
       <c r="K313" s="7"/>
       <c r="L313" s="7"/>
       <c t="s" r="M313" s="7">
-        <v>452</v>
+        <v>458</v>
       </c>
     </row>
     <row r="314" ht="14.25" customHeight="1">
@@ -11783,7 +11819,7 @@
       </c>
       <c r="D314" s="7"/>
       <c t="s" r="E314" s="7">
-        <v>450</v>
+        <v>456</v>
       </c>
       <c r="F314" s="7">
         <v>320</v>
@@ -11798,7 +11834,7 @@
         <v>121</v>
       </c>
       <c t="s" r="J314" s="7">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="K314" s="7"/>
       <c r="L314" s="7"/>
@@ -11816,7 +11852,7 @@
       </c>
       <c r="D315" s="7"/>
       <c t="s" r="E315" s="7">
-        <v>450</v>
+        <v>456</v>
       </c>
       <c r="F315" s="7">
         <v>320</v>
@@ -11828,7 +11864,7 @@
         <v>48</v>
       </c>
       <c t="s" r="I315" s="7">
-        <v>453</v>
+        <v>459</v>
       </c>
       <c t="s" r="J315" s="7">
         <v>105</v>
@@ -11864,7 +11900,7 @@
       </c>
       <c r="D317" s="7"/>
       <c t="s" r="E317" s="7">
-        <v>454</v>
+        <v>460</v>
       </c>
       <c r="F317" s="7">
         <v>321</v>
@@ -11899,7 +11935,7 @@
       </c>
       <c r="D318" s="7"/>
       <c t="s" r="E318" s="7">
-        <v>454</v>
+        <v>460</v>
       </c>
       <c r="F318" s="7">
         <v>321</v>
@@ -11911,7 +11947,7 @@
         <v>48</v>
       </c>
       <c t="s" r="I318" s="7">
-        <v>384</v>
+        <v>389</v>
       </c>
       <c t="s" r="J318" s="7">
         <v>160</v>
@@ -11919,7 +11955,7 @@
       <c r="K318" s="7"/>
       <c r="L318" s="7"/>
       <c t="s" r="M318" s="7">
-        <v>455</v>
+        <v>461</v>
       </c>
     </row>
     <row r="319" ht="14.25" customHeight="1">
@@ -11934,7 +11970,7 @@
       </c>
       <c r="D319" s="7"/>
       <c t="s" r="E319" s="7">
-        <v>454</v>
+        <v>460</v>
       </c>
       <c r="F319" s="7">
         <v>321</v>
@@ -11946,7 +11982,7 @@
         <v>141</v>
       </c>
       <c t="s" r="I319" s="7">
-        <v>456</v>
+        <v>462</v>
       </c>
       <c t="s" r="J319" s="7">
         <v>19</v>
@@ -11954,7 +11990,7 @@
       <c r="K319" s="7"/>
       <c r="L319" s="7"/>
       <c t="s" r="M319" s="7">
-        <v>342</v>
+        <v>343</v>
       </c>
     </row>
     <row r="320" ht="15" customHeight="1">
@@ -11969,7 +12005,7 @@
       </c>
       <c r="D320" s="7"/>
       <c t="s" r="E320" s="7">
-        <v>454</v>
+        <v>460</v>
       </c>
       <c r="F320" s="7">
         <v>321</v>
@@ -11981,7 +12017,7 @@
         <v>48</v>
       </c>
       <c t="s" r="I320" s="7">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c t="s" r="J320" s="7">
         <v>85</v>
@@ -11989,7 +12025,7 @@
       <c r="K320" s="7"/>
       <c r="L320" s="7"/>
       <c t="s" r="M320" s="7">
-        <v>457</v>
+        <v>463</v>
       </c>
     </row>
     <row r="321" ht="14.25" customHeight="1">
@@ -12004,7 +12040,7 @@
       </c>
       <c r="D321" s="7"/>
       <c t="s" r="E321" s="7">
-        <v>454</v>
+        <v>460</v>
       </c>
       <c r="F321" s="7">
         <v>321</v>
@@ -12037,7 +12073,7 @@
       </c>
       <c r="D322" s="7"/>
       <c t="s" r="E322" s="7">
-        <v>454</v>
+        <v>460</v>
       </c>
       <c r="F322" s="7">
         <v>321</v>
@@ -12046,13 +12082,13 @@
         <v>21</v>
       </c>
       <c t="s" r="H322" s="8">
-        <v>386</v>
+        <v>392</v>
       </c>
       <c t="s" r="I322" s="7">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c t="s" r="J322" s="7">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="K322" s="7"/>
       <c r="L322" s="7"/>
@@ -12085,7 +12121,7 @@
       </c>
       <c r="D324" s="7"/>
       <c t="s" r="E324" s="7">
-        <v>458</v>
+        <v>464</v>
       </c>
       <c r="F324" s="7">
         <v>320</v>
@@ -12097,7 +12133,7 @@
         <v>48</v>
       </c>
       <c t="s" r="I324" s="7">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c t="s" r="J324" s="7">
         <v>93</v>
@@ -12105,7 +12141,7 @@
       <c r="K324" s="7"/>
       <c r="L324" s="7"/>
       <c t="s" r="M324" s="7">
-        <v>459</v>
+        <v>465</v>
       </c>
     </row>
     <row r="325" ht="15" customHeight="1">
@@ -12120,7 +12156,7 @@
       </c>
       <c r="D325" s="7"/>
       <c t="s" r="E325" s="7">
-        <v>458</v>
+        <v>464</v>
       </c>
       <c r="F325" s="7">
         <v>320</v>
@@ -12132,7 +12168,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I325" s="7">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c t="s" r="J325" s="7">
         <v>160</v>
@@ -12140,7 +12176,7 @@
       <c r="K325" s="7"/>
       <c r="L325" s="7"/>
       <c t="s" r="M325" s="7">
-        <v>460</v>
+        <v>466</v>
       </c>
     </row>
     <row r="326" ht="14.25" customHeight="1">
@@ -12155,7 +12191,7 @@
       </c>
       <c r="D326" s="7"/>
       <c t="s" r="E326" s="7">
-        <v>458</v>
+        <v>464</v>
       </c>
       <c r="F326" s="7">
         <v>320</v>
@@ -12164,18 +12200,18 @@
         <v>17</v>
       </c>
       <c t="s" r="H326" s="8">
-        <v>446</v>
+        <v>452</v>
       </c>
       <c t="s" r="I326" s="7">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c t="s" r="J326" s="7">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="K326" s="7"/>
       <c r="L326" s="7"/>
       <c t="s" r="M326" s="7">
-        <v>461</v>
+        <v>467</v>
       </c>
     </row>
     <row r="327" ht="14.25" customHeight="1">
@@ -12190,13 +12226,13 @@
       </c>
       <c r="D327" s="7"/>
       <c t="s" r="E327" s="7">
-        <v>458</v>
+        <v>464</v>
       </c>
       <c r="F327" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G327" s="8">
-        <v>446</v>
+        <v>452</v>
       </c>
       <c t="s" r="H327" s="8">
         <v>17</v>
@@ -12225,7 +12261,7 @@
       </c>
       <c r="D328" s="7"/>
       <c t="s" r="E328" s="7">
-        <v>458</v>
+        <v>464</v>
       </c>
       <c r="F328" s="7">
         <v>320</v>
@@ -12247,7 +12283,7 @@
       </c>
       <c r="L328" s="7"/>
       <c t="s" r="M328" s="7">
-        <v>145</v>
+        <v>468</v>
       </c>
     </row>
     <row r="329" ht="14.25" customHeight="1">
@@ -12262,7 +12298,7 @@
       </c>
       <c r="D329" s="7"/>
       <c t="s" r="E329" s="7">
-        <v>458</v>
+        <v>464</v>
       </c>
       <c r="F329" s="7">
         <v>320</v>
@@ -12284,7 +12320,7 @@
       </c>
       <c r="L329" s="7"/>
       <c t="s" r="M329" s="7">
-        <v>333</v>
+        <v>334</v>
       </c>
     </row>
     <row r="330" ht="15" customHeight="1">
@@ -12314,7 +12350,7 @@
       </c>
       <c r="D331" s="7"/>
       <c t="s" r="E331" s="7">
-        <v>462</v>
+        <v>469</v>
       </c>
       <c r="F331" s="7">
         <v>320</v>
@@ -12334,7 +12370,7 @@
       <c r="K331" s="7"/>
       <c r="L331" s="7"/>
       <c t="s" r="M331" s="7">
-        <v>463</v>
+        <v>470</v>
       </c>
     </row>
     <row r="332" ht="14.25" customHeight="1">
@@ -12349,7 +12385,7 @@
       </c>
       <c r="D332" s="7"/>
       <c t="s" r="E332" s="7">
-        <v>462</v>
+        <v>469</v>
       </c>
       <c r="F332" s="7">
         <v>320</v>
@@ -12364,12 +12400,12 @@
         <v>168</v>
       </c>
       <c t="s" r="J332" s="7">
-        <v>464</v>
+        <v>471</v>
       </c>
       <c r="K332" s="7"/>
       <c r="L332" s="7"/>
       <c t="s" r="M332" s="7">
-        <v>465</v>
+        <v>472</v>
       </c>
     </row>
     <row r="333" ht="14.25" customHeight="1">
@@ -12384,7 +12420,7 @@
       </c>
       <c r="D333" s="7"/>
       <c t="s" r="E333" s="7">
-        <v>462</v>
+        <v>469</v>
       </c>
       <c r="F333" s="7">
         <v>320</v>
@@ -12396,7 +12432,7 @@
         <v>141</v>
       </c>
       <c t="s" r="I333" s="7">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c t="s" r="J333" s="7">
         <v>38</v>
@@ -12404,7 +12440,7 @@
       <c r="K333" s="7"/>
       <c r="L333" s="7"/>
       <c t="s" r="M333" s="7">
-        <v>466</v>
+        <v>473</v>
       </c>
     </row>
     <row r="334" ht="14.25" customHeight="1">
@@ -12419,7 +12455,7 @@
       </c>
       <c r="D334" s="7"/>
       <c t="s" r="E334" s="7">
-        <v>462</v>
+        <v>469</v>
       </c>
       <c r="F334" s="7">
         <v>320</v>
@@ -12439,7 +12475,7 @@
       <c r="K334" s="7"/>
       <c r="L334" s="7"/>
       <c t="s" r="M334" s="7">
-        <v>467</v>
+        <v>474</v>
       </c>
     </row>
     <row r="335" ht="15" customHeight="1">
@@ -12454,7 +12490,7 @@
       </c>
       <c r="D335" s="7"/>
       <c t="s" r="E335" s="7">
-        <v>462</v>
+        <v>469</v>
       </c>
       <c r="F335" s="7">
         <v>320</v>
@@ -12469,14 +12505,14 @@
         <v>100</v>
       </c>
       <c t="s" r="J335" s="7">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c t="s" r="K335" s="7">
         <v>201</v>
       </c>
       <c r="L335" s="7"/>
       <c t="s" r="M335" s="7">
-        <v>314</v>
+        <v>391</v>
       </c>
     </row>
     <row r="336" ht="14.25" customHeight="1">
@@ -12491,7 +12527,7 @@
       </c>
       <c r="D336" s="7"/>
       <c t="s" r="E336" s="7">
-        <v>462</v>
+        <v>469</v>
       </c>
       <c r="F336" s="7">
         <v>320</v>
@@ -12503,13 +12539,13 @@
         <v>48</v>
       </c>
       <c t="s" r="I336" s="7">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c t="s" r="J336" s="7">
         <v>87</v>
       </c>
       <c t="s" r="K336" s="7">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="L336" s="7"/>
       <c t="s" r="M336" s="7">
@@ -12528,7 +12564,7 @@
       </c>
       <c r="D337" s="7"/>
       <c t="s" r="E337" s="7">
-        <v>462</v>
+        <v>469</v>
       </c>
       <c r="F337" s="7">
         <v>320</v>
@@ -12537,17 +12573,21 @@
         <v>48</v>
       </c>
       <c t="s" r="H337" s="8">
-        <v>468</v>
+        <v>475</v>
       </c>
       <c t="s" r="I337" s="7">
-        <v>381</v>
+        <v>386</v>
       </c>
       <c t="s" r="J337" s="7">
-        <v>469</v>
-      </c>
-      <c r="K337" s="7"/>
+        <v>476</v>
+      </c>
+      <c t="s" r="K337" s="7">
+        <v>254</v>
+      </c>
       <c r="L337" s="7"/>
-      <c r="M337" s="7"/>
+      <c t="s" r="M337" s="7">
+        <v>477</v>
+      </c>
     </row>
     <row r="338" ht="14.25" customHeight="1">
       <c t="s" r="A338" s="6">
@@ -12561,26 +12601,30 @@
       </c>
       <c r="D338" s="7"/>
       <c t="s" r="E338" s="7">
-        <v>462</v>
+        <v>469</v>
       </c>
       <c r="F338" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G338" s="8">
-        <v>468</v>
+        <v>475</v>
       </c>
       <c t="s" r="H338" s="8">
         <v>48</v>
       </c>
       <c t="s" r="I338" s="7">
-        <v>470</v>
+        <v>478</v>
       </c>
       <c t="s" r="J338" s="7">
-        <v>471</v>
-      </c>
-      <c r="K338" s="7"/>
+        <v>479</v>
+      </c>
+      <c t="s" r="K338" s="7">
+        <v>480</v>
+      </c>
       <c r="L338" s="7"/>
-      <c r="M338" s="7"/>
+      <c t="s" r="M338" s="7">
+        <v>354</v>
+      </c>
     </row>
     <row r="339" ht="14.25" customHeight="1">
       <c r="A339" s="6"/>
@@ -12609,7 +12653,7 @@
       </c>
       <c r="D340" s="7"/>
       <c t="s" r="E340" s="7">
-        <v>472</v>
+        <v>481</v>
       </c>
       <c r="F340" s="7">
         <v>321</v>
@@ -12629,7 +12673,7 @@
       <c r="K340" s="7"/>
       <c r="L340" s="7"/>
       <c t="s" r="M340" s="7">
-        <v>391</v>
+        <v>397</v>
       </c>
     </row>
     <row r="341" ht="14.25" customHeight="1">
@@ -12644,7 +12688,7 @@
       </c>
       <c r="D341" s="7"/>
       <c t="s" r="E341" s="7">
-        <v>472</v>
+        <v>481</v>
       </c>
       <c r="F341" s="7">
         <v>321</v>
@@ -12656,7 +12700,7 @@
         <v>71</v>
       </c>
       <c t="s" r="I341" s="7">
-        <v>456</v>
+        <v>462</v>
       </c>
       <c t="s" r="J341" s="7">
         <v>23</v>
@@ -12679,7 +12723,7 @@
       </c>
       <c r="D342" s="7"/>
       <c t="s" r="E342" s="7">
-        <v>472</v>
+        <v>481</v>
       </c>
       <c r="F342" s="7">
         <v>321</v>
@@ -12691,15 +12735,15 @@
         <v>17</v>
       </c>
       <c t="s" r="I342" s="7">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c t="s" r="J342" s="7">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="K342" s="7"/>
       <c r="L342" s="7"/>
       <c t="s" r="M342" s="7">
-        <v>473</v>
+        <v>482</v>
       </c>
     </row>
     <row r="343" ht="14.25" customHeight="1">
@@ -12714,7 +12758,7 @@
       </c>
       <c r="D343" s="7"/>
       <c t="s" r="E343" s="7">
-        <v>472</v>
+        <v>481</v>
       </c>
       <c r="F343" s="7">
         <v>321</v>
@@ -12723,13 +12767,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H343" s="8">
-        <v>426</v>
+        <v>432</v>
       </c>
       <c t="s" r="I343" s="7">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c t="s" r="J343" s="7">
-        <v>474</v>
+        <v>483</v>
       </c>
       <c r="K343" s="7"/>
       <c r="L343" s="7"/>
@@ -12747,22 +12791,22 @@
       </c>
       <c r="D344" s="7"/>
       <c t="s" r="E344" s="7">
-        <v>472</v>
+        <v>481</v>
       </c>
       <c r="F344" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G344" s="8">
-        <v>426</v>
+        <v>432</v>
       </c>
       <c t="s" r="H344" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I344" s="7">
-        <v>475</v>
+        <v>480</v>
       </c>
       <c t="s" r="J344" s="7">
-        <v>476</v>
+        <v>484</v>
       </c>
       <c r="K344" s="7"/>
       <c r="L344" s="7"/>
@@ -12795,13 +12839,13 @@
       </c>
       <c r="D346" s="7"/>
       <c t="s" r="E346" s="7">
-        <v>477</v>
+        <v>485</v>
       </c>
       <c r="F346" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G346" s="8">
-        <v>398</v>
+        <v>404</v>
       </c>
       <c t="s" r="H346" s="8">
         <v>48</v>
@@ -12815,7 +12859,7 @@
       <c r="K346" s="7"/>
       <c r="L346" s="7"/>
       <c t="s" r="M346" s="7">
-        <v>384</v>
+        <v>389</v>
       </c>
     </row>
     <row r="347" ht="14.25" customHeight="1">
@@ -12830,7 +12874,7 @@
       </c>
       <c r="D347" s="7"/>
       <c t="s" r="E347" s="7">
-        <v>477</v>
+        <v>485</v>
       </c>
       <c r="F347" s="7">
         <v>321</v>
@@ -12850,7 +12894,7 @@
       <c r="K347" s="7"/>
       <c r="L347" s="7"/>
       <c t="s" r="M347" s="7">
-        <v>478</v>
+        <v>486</v>
       </c>
     </row>
     <row r="348" ht="14.25" customHeight="1">
@@ -12865,7 +12909,7 @@
       </c>
       <c r="D348" s="7"/>
       <c t="s" r="E348" s="7">
-        <v>477</v>
+        <v>485</v>
       </c>
       <c r="F348" s="7">
         <v>321</v>
@@ -12877,15 +12921,15 @@
         <v>48</v>
       </c>
       <c t="s" r="I348" s="7">
-        <v>445</v>
+        <v>451</v>
       </c>
       <c t="s" r="J348" s="7">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="K348" s="7"/>
       <c r="L348" s="7"/>
       <c t="s" r="M348" s="7">
-        <v>479</v>
+        <v>487</v>
       </c>
     </row>
     <row r="349" ht="14.25" customHeight="1">
@@ -12900,7 +12944,7 @@
       </c>
       <c r="D349" s="7"/>
       <c t="s" r="E349" s="7">
-        <v>477</v>
+        <v>485</v>
       </c>
       <c r="F349" s="7">
         <v>321</v>
@@ -12912,10 +12956,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I349" s="7">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c t="s" r="J349" s="7">
-        <v>381</v>
+        <v>386</v>
       </c>
       <c r="K349" s="7"/>
       <c r="L349" s="7"/>
@@ -12948,7 +12992,7 @@
       </c>
       <c r="D351" s="7"/>
       <c t="s" r="E351" s="7">
-        <v>481</v>
+        <v>488</v>
       </c>
       <c r="F351" s="7">
         <v>321</v>
@@ -12960,7 +13004,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I351" s="7">
-        <v>482</v>
+        <v>489</v>
       </c>
       <c t="s" r="J351" s="7">
         <v>155</v>
@@ -12968,7 +13012,7 @@
       <c r="K351" s="7"/>
       <c r="L351" s="7"/>
       <c t="s" r="M351" s="7">
-        <v>483</v>
+        <v>490</v>
       </c>
     </row>
     <row r="352" ht="14.25" customHeight="1">
@@ -12983,7 +13027,7 @@
       </c>
       <c r="D352" s="7"/>
       <c t="s" r="E352" s="7">
-        <v>481</v>
+        <v>488</v>
       </c>
       <c r="F352" s="7">
         <v>321</v>
@@ -12995,7 +13039,7 @@
         <v>110</v>
       </c>
       <c t="s" r="I352" s="7">
-        <v>484</v>
+        <v>491</v>
       </c>
       <c t="s" r="J352" s="7">
         <v>111</v>
@@ -13018,7 +13062,7 @@
       </c>
       <c r="D353" s="7"/>
       <c t="s" r="E353" s="7">
-        <v>481</v>
+        <v>488</v>
       </c>
       <c r="F353" s="7">
         <v>321</v>
@@ -13027,10 +13071,10 @@
         <v>110</v>
       </c>
       <c t="s" r="H353" s="8">
-        <v>408</v>
+        <v>414</v>
       </c>
       <c t="s" r="I353" s="7">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c t="s" r="J353" s="7">
         <v>163</v>
@@ -13053,19 +13097,19 @@
       </c>
       <c r="D354" s="7"/>
       <c t="s" r="E354" s="7">
-        <v>481</v>
+        <v>488</v>
       </c>
       <c r="F354" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G354" s="8">
-        <v>408</v>
+        <v>414</v>
       </c>
       <c t="s" r="H354" s="8">
         <v>110</v>
       </c>
       <c t="s" r="I354" s="7">
-        <v>403</v>
+        <v>409</v>
       </c>
       <c t="s" r="J354" s="7">
         <v>100</v>
@@ -13073,7 +13117,7 @@
       <c r="K354" s="7"/>
       <c r="L354" s="7"/>
       <c t="s" r="M354" s="7">
-        <v>485</v>
+        <v>492</v>
       </c>
     </row>
     <row r="355" ht="15" customHeight="1">
@@ -13088,7 +13132,7 @@
       </c>
       <c r="D355" s="7"/>
       <c t="s" r="E355" s="7">
-        <v>481</v>
+        <v>488</v>
       </c>
       <c r="F355" s="7">
         <v>321</v>
@@ -13097,13 +13141,13 @@
         <v>110</v>
       </c>
       <c t="s" r="H355" s="8">
-        <v>408</v>
+        <v>414</v>
       </c>
       <c t="s" r="I355" s="7">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c t="s" r="J355" s="7">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="K355" s="7"/>
       <c r="L355" s="7"/>
@@ -13121,19 +13165,19 @@
       </c>
       <c r="D356" s="7"/>
       <c t="s" r="E356" s="7">
-        <v>481</v>
+        <v>488</v>
       </c>
       <c r="F356" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G356" s="8">
-        <v>408</v>
+        <v>414</v>
       </c>
       <c t="s" r="H356" s="8">
         <v>110</v>
       </c>
       <c t="s" r="I356" s="7">
-        <v>486</v>
+        <v>493</v>
       </c>
       <c t="s" r="J356" s="7">
         <v>89</v>
@@ -13154,7 +13198,7 @@
       </c>
       <c r="D357" s="7"/>
       <c t="s" r="E357" s="7">
-        <v>481</v>
+        <v>488</v>
       </c>
       <c r="F357" s="7">
         <v>321</v>
@@ -13202,7 +13246,7 @@
       </c>
       <c r="D359" s="7"/>
       <c t="s" r="E359" s="7">
-        <v>487</v>
+        <v>494</v>
       </c>
       <c r="F359" s="7">
         <v>321</v>
@@ -13217,12 +13261,12 @@
         <v>56</v>
       </c>
       <c t="s" r="J359" s="7">
-        <v>488</v>
+        <v>495</v>
       </c>
       <c r="K359" s="7"/>
       <c r="L359" s="7"/>
       <c t="s" r="M359" s="7">
-        <v>489</v>
+        <v>496</v>
       </c>
     </row>
     <row r="360" ht="15" customHeight="1">
@@ -13237,7 +13281,7 @@
       </c>
       <c r="D360" s="7"/>
       <c t="s" r="E360" s="7">
-        <v>487</v>
+        <v>494</v>
       </c>
       <c r="F360" s="7">
         <v>321</v>
@@ -13249,15 +13293,15 @@
         <v>110</v>
       </c>
       <c t="s" r="I360" s="7">
-        <v>464</v>
+        <v>471</v>
       </c>
       <c t="s" r="J360" s="7">
-        <v>456</v>
+        <v>462</v>
       </c>
       <c r="K360" s="7"/>
       <c r="L360" s="7"/>
       <c t="s" r="M360" s="7">
-        <v>490</v>
+        <v>497</v>
       </c>
     </row>
     <row r="361" ht="14.25" customHeight="1">
@@ -13272,7 +13316,7 @@
       </c>
       <c r="D361" s="7"/>
       <c t="s" r="E361" s="7">
-        <v>487</v>
+        <v>494</v>
       </c>
       <c r="F361" s="7">
         <v>321</v>
@@ -13284,7 +13328,7 @@
         <v>21</v>
       </c>
       <c t="s" r="I361" s="7">
-        <v>491</v>
+        <v>498</v>
       </c>
       <c t="s" r="J361" s="7">
         <v>22</v>
@@ -13307,7 +13351,7 @@
       </c>
       <c r="D362" s="7"/>
       <c t="s" r="E362" s="7">
-        <v>487</v>
+        <v>494</v>
       </c>
       <c r="F362" s="7">
         <v>321</v>
@@ -13322,12 +13366,12 @@
         <v>150</v>
       </c>
       <c t="s" r="J362" s="7">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="K362" s="7"/>
       <c r="L362" s="7"/>
       <c t="s" r="M362" s="7">
-        <v>452</v>
+        <v>458</v>
       </c>
     </row>
     <row r="363" ht="14.25" customHeight="1">
@@ -13342,7 +13386,7 @@
       </c>
       <c r="D363" s="7"/>
       <c t="s" r="E363" s="7">
-        <v>487</v>
+        <v>494</v>
       </c>
       <c r="F363" s="7">
         <v>321</v>
@@ -13364,7 +13408,7 @@
       </c>
       <c r="L363" s="7"/>
       <c t="s" r="M363" s="7">
-        <v>298</v>
+        <v>299</v>
       </c>
     </row>
     <row r="364" ht="14.25" customHeight="1">
@@ -13379,7 +13423,7 @@
       </c>
       <c r="D364" s="7"/>
       <c t="s" r="E364" s="7">
-        <v>487</v>
+        <v>494</v>
       </c>
       <c r="F364" s="7">
         <v>321</v>
@@ -13388,10 +13432,10 @@
         <v>17</v>
       </c>
       <c t="s" r="H364" s="8">
-        <v>386</v>
+        <v>392</v>
       </c>
       <c t="s" r="I364" s="7">
-        <v>492</v>
+        <v>499</v>
       </c>
       <c t="s" r="J364" s="7">
         <v>34</v>
@@ -13427,7 +13471,7 @@
       </c>
       <c r="D366" s="7"/>
       <c t="s" r="E366" s="7">
-        <v>493</v>
+        <v>500</v>
       </c>
       <c r="F366" s="7">
         <v>320</v>
@@ -13436,10 +13480,10 @@
         <v>17</v>
       </c>
       <c t="s" r="H366" s="8">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c t="s" r="I366" s="7">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c t="s" r="J366" s="7">
         <v>108</v>
@@ -13447,7 +13491,7 @@
       <c r="K366" s="7"/>
       <c r="L366" s="7"/>
       <c t="s" r="M366" s="7">
-        <v>494</v>
+        <v>501</v>
       </c>
     </row>
     <row r="367" ht="14.25" customHeight="1">
@@ -13462,13 +13506,13 @@
       </c>
       <c r="D367" s="7"/>
       <c t="s" r="E367" s="7">
-        <v>493</v>
+        <v>500</v>
       </c>
       <c r="F367" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G367" s="8">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c t="s" r="H367" s="8">
         <v>17</v>
@@ -13514,7 +13558,7 @@
       </c>
       <c r="D369" s="7"/>
       <c t="s" r="E369" s="7">
-        <v>495</v>
+        <v>502</v>
       </c>
       <c r="F369" s="7">
         <v>321</v>
@@ -13529,14 +13573,14 @@
         <v>59</v>
       </c>
       <c t="s" r="J369" s="7">
-        <v>445</v>
+        <v>451</v>
       </c>
       <c t="s" r="K369" s="7">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="L369" s="7"/>
       <c t="s" r="M369" s="7">
-        <v>496</v>
+        <v>503</v>
       </c>
     </row>
     <row r="370" ht="15" customHeight="1">
@@ -13551,7 +13595,7 @@
       </c>
       <c r="D370" s="7"/>
       <c t="s" r="E370" s="7">
-        <v>495</v>
+        <v>502</v>
       </c>
       <c r="F370" s="7">
         <v>321</v>
@@ -13563,10 +13607,10 @@
         <v>48</v>
       </c>
       <c t="s" r="I370" s="7">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c t="s" r="J370" s="7">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c t="s" r="K370" s="7">
         <v>63</v>
@@ -13603,7 +13647,7 @@
       </c>
       <c r="D372" s="7"/>
       <c t="s" r="E372" s="7">
-        <v>497</v>
+        <v>504</v>
       </c>
       <c r="F372" s="7">
         <v>330</v>
@@ -13612,13 +13656,13 @@
         <v>141</v>
       </c>
       <c t="s" r="H372" s="8">
-        <v>498</v>
+        <v>505</v>
       </c>
       <c t="s" r="I372" s="7">
         <v>186</v>
       </c>
       <c t="s" r="J372" s="7">
-        <v>499</v>
+        <v>506</v>
       </c>
       <c r="K372" s="7"/>
       <c r="L372" s="7"/>
@@ -13636,22 +13680,22 @@
       </c>
       <c r="D373" s="7"/>
       <c t="s" r="E373" s="7">
-        <v>497</v>
+        <v>504</v>
       </c>
       <c r="F373" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G373" s="8">
-        <v>498</v>
+        <v>505</v>
       </c>
       <c t="s" r="H373" s="8">
         <v>141</v>
       </c>
       <c t="s" r="I373" s="7">
-        <v>436</v>
+        <v>442</v>
       </c>
       <c t="s" r="J373" s="7">
-        <v>500</v>
+        <v>507</v>
       </c>
       <c r="K373" s="7"/>
       <c r="L373" s="7"/>
@@ -13684,7 +13728,7 @@
       </c>
       <c r="D375" s="7"/>
       <c t="s" r="E375" s="7">
-        <v>501</v>
+        <v>508</v>
       </c>
       <c r="F375" s="7">
         <v>330</v>
@@ -13693,13 +13737,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H375" s="8">
-        <v>502</v>
+        <v>509</v>
       </c>
       <c t="s" r="I375" s="7">
-        <v>488</v>
+        <v>495</v>
       </c>
       <c t="s" r="J375" s="7">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="K375" s="7"/>
       <c r="L375" s="7"/>
@@ -13719,22 +13763,22 @@
       </c>
       <c r="D376" s="7"/>
       <c t="s" r="E376" s="7">
-        <v>501</v>
+        <v>508</v>
       </c>
       <c r="F376" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G376" s="8">
-        <v>502</v>
+        <v>509</v>
       </c>
       <c t="s" r="H376" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I376" s="7">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c t="s" r="J376" s="7">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="K376" s="7"/>
       <c r="L376" s="7"/>
@@ -13767,7 +13811,7 @@
       </c>
       <c r="D378" s="7"/>
       <c t="s" r="E378" s="7">
-        <v>503</v>
+        <v>510</v>
       </c>
       <c r="F378" s="7">
         <v>330</v>
@@ -13776,7 +13820,7 @@
         <v>17</v>
       </c>
       <c t="s" r="H378" s="8">
-        <v>504</v>
+        <v>511</v>
       </c>
       <c t="s" r="I378" s="7">
         <v>112</v>
@@ -13787,7 +13831,7 @@
       <c r="K378" s="7"/>
       <c r="L378" s="7"/>
       <c t="s" r="M378" s="7">
-        <v>505</v>
+        <v>512</v>
       </c>
     </row>
     <row r="379" ht="14.25" customHeight="1">
@@ -13802,22 +13846,22 @@
       </c>
       <c r="D379" s="7"/>
       <c t="s" r="E379" s="7">
-        <v>503</v>
+        <v>510</v>
       </c>
       <c r="F379" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G379" s="8">
-        <v>504</v>
+        <v>511</v>
       </c>
       <c t="s" r="H379" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I379" s="7">
-        <v>474</v>
+        <v>483</v>
       </c>
       <c t="s" r="J379" s="7">
-        <v>482</v>
+        <v>489</v>
       </c>
       <c r="K379" s="7"/>
       <c r="L379" s="7"/>
@@ -13846,11 +13890,11 @@
         <v>5805</v>
       </c>
       <c t="s" r="C381" s="7">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="D381" s="7"/>
       <c t="s" r="E381" s="7">
-        <v>506</v>
+        <v>513</v>
       </c>
       <c r="F381" s="7">
         <v>330</v>
@@ -13859,7 +13903,7 @@
         <v>141</v>
       </c>
       <c t="s" r="H381" s="8">
-        <v>507</v>
+        <v>514</v>
       </c>
       <c t="s" r="I381" s="7">
         <v>192</v>
@@ -13870,7 +13914,7 @@
       <c r="K381" s="7"/>
       <c r="L381" s="7"/>
       <c t="s" r="M381" s="7">
-        <v>272</v>
+        <v>515</v>
       </c>
     </row>
     <row r="382" ht="14.25" customHeight="1">
@@ -13881,23 +13925,23 @@
         <v>5806</v>
       </c>
       <c t="s" r="C382" s="7">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="D382" s="7"/>
       <c t="s" r="E382" s="7">
-        <v>506</v>
+        <v>513</v>
       </c>
       <c r="F382" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G382" s="8">
-        <v>507</v>
+        <v>514</v>
       </c>
       <c t="s" r="H382" s="8">
         <v>141</v>
       </c>
       <c t="s" r="I382" s="7">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c t="s" r="J382" s="7">
         <v>56</v>
@@ -13933,7 +13977,7 @@
       </c>
       <c r="D384" s="7"/>
       <c t="s" r="E384" s="7">
-        <v>508</v>
+        <v>516</v>
       </c>
       <c r="F384" s="7">
         <v>330</v>
@@ -13942,7 +13986,7 @@
         <v>141</v>
       </c>
       <c t="s" r="H384" s="8">
-        <v>509</v>
+        <v>517</v>
       </c>
       <c t="s" r="I384" s="7">
         <v>134</v>
@@ -13953,7 +13997,7 @@
       <c r="K384" s="7"/>
       <c r="L384" s="7"/>
       <c t="s" r="M384" s="7">
-        <v>466</v>
+        <v>473</v>
       </c>
     </row>
     <row r="385" ht="15" customHeight="1">
@@ -13968,13 +14012,13 @@
       </c>
       <c r="D385" s="7"/>
       <c t="s" r="E385" s="7">
-        <v>508</v>
+        <v>516</v>
       </c>
       <c r="F385" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G385" s="8">
-        <v>509</v>
+        <v>517</v>
       </c>
       <c t="s" r="H385" s="8">
         <v>141</v>
@@ -14016,19 +14060,19 @@
       </c>
       <c r="D387" s="7"/>
       <c t="s" r="E387" s="7">
-        <v>510</v>
+        <v>518</v>
       </c>
       <c r="F387" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G387" s="8">
-        <v>511</v>
+        <v>519</v>
       </c>
       <c t="s" r="H387" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I387" s="7">
-        <v>464</v>
+        <v>471</v>
       </c>
       <c t="s" r="J387" s="7">
         <v>98</v>
@@ -14036,7 +14080,7 @@
       <c r="K387" s="7"/>
       <c r="L387" s="7"/>
       <c t="s" r="M387" s="7">
-        <v>467</v>
+        <v>474</v>
       </c>
     </row>
     <row r="388" ht="14.25" customHeight="1">
@@ -14051,7 +14095,7 @@
       </c>
       <c r="D388" s="7"/>
       <c t="s" r="E388" s="7">
-        <v>510</v>
+        <v>518</v>
       </c>
       <c r="F388" s="7">
         <v>330</v>
@@ -14084,7 +14128,7 @@
       </c>
       <c r="D389" s="7"/>
       <c t="s" r="E389" s="7">
-        <v>510</v>
+        <v>518</v>
       </c>
       <c r="F389" s="7">
         <v>330</v>
@@ -14096,10 +14140,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I389" s="7">
-        <v>486</v>
+        <v>493</v>
       </c>
       <c t="s" r="J389" s="7">
-        <v>492</v>
+        <v>499</v>
       </c>
       <c r="K389" s="7"/>
       <c r="L389" s="7"/>
@@ -14107,7 +14151,7 @@
     </row>
     <row r="390" ht="16.5" customHeight="1">
       <c t="s" r="A390" s="9">
-        <v>512</v>
+        <v>520</v>
       </c>
       <c r="B390" s="9"/>
       <c r="C390" s="9"/>
@@ -14127,7 +14171,7 @@
     <row r="391" ht="65.25" customHeight="1"/>
     <row r="392" ht="16.5" customHeight="1">
       <c t="s" r="A392" s="10">
-        <v>513</v>
+        <v>521</v>
       </c>
       <c r="B392" s="10"/>
       <c r="C392" s="10"/>
@@ -14140,7 +14184,7 @@
       <c r="J392" s="10"/>
       <c r="K392" s="10"/>
       <c t="s" r="L392" s="11">
-        <v>514</v>
+        <v>522</v>
       </c>
       <c r="M392" s="11"/>
       <c r="N392" s="11"/>
